--- a/Result/analyze_1.xlsx
+++ b/Result/analyze_1.xlsx
@@ -441,57 +441,57 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-08-01</t>
         </is>
       </c>
     </row>
@@ -506,31 +506,31 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G2" t="n">
         <v>3</v>
       </c>
       <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
         <v>3</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1</v>
       </c>
       <c r="J2" t="n">
         <v>2</v>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M2" t="n">
         <v>2</v>
@@ -544,7 +544,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -556,25 +556,25 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
         <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -585,10 +585,10 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -606,13 +606,13 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M4" t="n">
         <v>1</v>
@@ -629,7 +629,7 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
@@ -638,22 +638,22 @@
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -670,10 +670,10 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -685,10 +685,10 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -697,7 +697,7 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -711,34 +711,34 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -749,34 +749,34 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
         <v>2</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" t="n">
-        <v>1</v>
       </c>
       <c r="H8" t="n">
         <v>2</v>
       </c>
       <c r="I8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
         <v>2</v>
-      </c>
-      <c r="J8" t="n">
-        <v>3</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
       </c>
       <c r="M8" t="n">
         <v>2</v>
@@ -788,20 +788,18 @@
           <t>其他電子業右下</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0</v>
-      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
         <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -810,16 +808,16 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" t="n">
         <v>1</v>
@@ -833,7 +831,7 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -863,7 +861,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -883,28 +881,28 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" t="n">
         <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
         <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -913,9 +911,7 @@
           <t>化學工業右下</t>
         </is>
       </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
         <v>0</v>
       </c>
@@ -926,10 +922,10 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -964,13 +960,13 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" t="n">
         <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -999,7 +995,7 @@
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -1011,13 +1007,13 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" t="n">
         <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1042,37 +1038,37 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>4</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>4</v>
+      </c>
+      <c r="L15" t="n">
+        <v>2</v>
+      </c>
+      <c r="M15" t="n">
         <v>3</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>4</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>4</v>
-      </c>
-      <c r="M15" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1083,37 +1079,37 @@
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" t="n">
         <v>2</v>
-      </c>
-      <c r="G16" t="n">
-        <v>1</v>
-      </c>
-      <c r="H16" t="n">
-        <v>1</v>
       </c>
       <c r="I16" t="n">
         <v>2</v>
       </c>
       <c r="J16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
         <v>1</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -1165,34 +1161,34 @@
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>3</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
         <v>2</v>
       </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
         <v>3</v>
       </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>2</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
       <c r="L18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -1256,10 +1252,10 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -1271,10 +1267,10 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -1329,7 +1325,7 @@
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
@@ -1379,10 +1375,10 @@
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -1409,7 +1405,9 @@
           <t>建材營造右下</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="n">
+        <v>0</v>
+      </c>
       <c r="C24" t="n">
         <v>0</v>
       </c>
@@ -1432,16 +1430,16 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1499,13 +1497,13 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1523,7 +1521,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1532,7 +1530,9 @@
           <t>數位雲端右下</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr"/>
+      <c r="B27" t="n">
+        <v>0</v>
+      </c>
       <c r="C27" t="n">
         <v>0</v>
       </c>
@@ -1599,10 +1599,10 @@
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -1672,10 +1672,10 @@
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1728,7 +1728,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -1798,10 +1798,10 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -1912,10 +1912,10 @@
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -1947,31 +1947,31 @@
         <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G37" t="n">
+        <v>1</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
         <v>2</v>
       </c>
-      <c r="H37" t="n">
-        <v>1</v>
-      </c>
-      <c r="I37" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
-      </c>
       <c r="L37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
@@ -1988,16 +1988,16 @@
         <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -2015,7 +2015,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2050,10 +2050,10 @@
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
@@ -2117,28 +2117,28 @@
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G41" t="n">
         <v>1</v>
       </c>
       <c r="H41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2199,10 +2199,10 @@
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -2237,13 +2237,13 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H44" t="n">
         <v>1</v>
@@ -2252,16 +2252,16 @@
         <v>1</v>
       </c>
       <c r="J44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L44" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2280,28 +2280,28 @@
         <v>1</v>
       </c>
       <c r="E45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G45" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I45" t="n">
         <v>1</v>
       </c>
       <c r="J45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
@@ -2330,13 +2330,13 @@
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
@@ -2371,7 +2371,7 @@
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I47" t="n">
         <v>0</v>
@@ -2456,7 +2456,7 @@
         <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -2488,28 +2488,28 @@
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G50" t="n">
         <v>1</v>
       </c>
       <c r="H50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K50" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -2523,10 +2523,10 @@
         <v>0</v>
       </c>
       <c r="D51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F51" t="n">
         <v>0</v>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D52" t="n">
         <v>0</v>
@@ -2617,10 +2617,10 @@
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -2658,10 +2658,10 @@
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -2725,10 +2725,10 @@
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E56" t="n">
         <v>0</v>
@@ -2746,7 +2746,7 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K56" t="n">
         <v>1</v>
@@ -2755,7 +2755,7 @@
         <v>1</v>
       </c>
       <c r="M56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -2778,10 +2778,10 @@
         <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I57" t="n">
         <v>0</v>
@@ -2796,7 +2796,7 @@
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -2869,10 +2869,10 @@
         <v>0</v>
       </c>
       <c r="J59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
@@ -2951,10 +2951,10 @@
         <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
@@ -3135,31 +3135,31 @@
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D66" t="n">
+        <v>4</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" t="n">
+        <v>4</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" t="n">
         <v>2</v>
       </c>
-      <c r="E66" t="n">
-        <v>3</v>
-      </c>
-      <c r="F66" t="n">
-        <v>0</v>
-      </c>
-      <c r="G66" t="n">
-        <v>0</v>
-      </c>
-      <c r="H66" t="n">
-        <v>3</v>
-      </c>
-      <c r="I66" t="n">
-        <v>0</v>
-      </c>
       <c r="J66" t="n">
+        <v>1</v>
+      </c>
+      <c r="K66" t="n">
         <v>2</v>
-      </c>
-      <c r="K66" t="n">
-        <v>1</v>
       </c>
       <c r="L66" t="n">
         <v>2</v>
@@ -3220,34 +3220,34 @@
         <v>0</v>
       </c>
       <c r="D68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E68" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" t="n">
+        <v>1</v>
+      </c>
+      <c r="G68" t="n">
         <v>2</v>
       </c>
-      <c r="F68" t="n">
-        <v>0</v>
-      </c>
-      <c r="G68" t="n">
-        <v>1</v>
-      </c>
       <c r="H68" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I68" t="n">
+        <v>1</v>
+      </c>
+      <c r="J68" t="n">
+        <v>1</v>
+      </c>
+      <c r="K68" t="n">
+        <v>1</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" t="n">
         <v>2</v>
-      </c>
-      <c r="J68" t="n">
-        <v>1</v>
-      </c>
-      <c r="K68" t="n">
-        <v>1</v>
-      </c>
-      <c r="L68" t="n">
-        <v>1</v>
-      </c>
-      <c r="M68" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -3258,10 +3258,10 @@
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E69" t="n">
         <v>0</v>
@@ -3273,10 +3273,10 @@
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -3390,10 +3390,10 @@
         <v>0</v>
       </c>
       <c r="F72" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G72" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
@@ -3422,7 +3422,7 @@
       </c>
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D73" t="n">
         <v>0</v>
@@ -3718,10 +3718,10 @@
         <v>0</v>
       </c>
       <c r="F80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
@@ -3748,7 +3748,9 @@
           <t>鋼鐵工業右下</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr"/>
+      <c r="B81" t="n">
+        <v>0</v>
+      </c>
       <c r="C81" t="n">
         <v>0</v>
       </c>
@@ -3759,10 +3761,10 @@
         <v>0</v>
       </c>
       <c r="F81" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G81" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
@@ -3821,7 +3823,7 @@
         <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -3832,10 +3834,10 @@
       </c>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E83" t="n">
         <v>0</v>
@@ -3897,10 +3899,10 @@
         <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
         <v>0</v>
@@ -3979,13 +3981,13 @@
         <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L86" t="n">
         <v>1</v>
       </c>
       <c r="M86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -3996,7 +3998,7 @@
       </c>
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D87" t="n">
         <v>0</v>
@@ -4008,7 +4010,7 @@
         <v>0</v>
       </c>
       <c r="G87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H87" t="n">
         <v>0</v>
@@ -4037,25 +4039,25 @@
       </c>
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E88" t="n">
         <v>0</v>
       </c>
       <c r="F88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
       </c>
       <c r="H88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -4078,37 +4080,37 @@
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="n">
+        <v>2</v>
+      </c>
+      <c r="D89" t="n">
         <v>3</v>
       </c>
-      <c r="D89" t="n">
-        <v>2</v>
-      </c>
       <c r="E89" t="n">
+        <v>1</v>
+      </c>
+      <c r="F89" t="n">
+        <v>4</v>
+      </c>
+      <c r="G89" t="n">
         <v>3</v>
       </c>
-      <c r="F89" t="n">
-        <v>1</v>
-      </c>
-      <c r="G89" t="n">
-        <v>4</v>
-      </c>
       <c r="H89" t="n">
+        <v>1</v>
+      </c>
+      <c r="I89" t="n">
+        <v>9</v>
+      </c>
+      <c r="J89" t="n">
         <v>3</v>
-      </c>
-      <c r="I89" t="n">
-        <v>1</v>
-      </c>
-      <c r="J89" t="n">
-        <v>8</v>
       </c>
       <c r="K89" t="n">
         <v>3</v>
       </c>
       <c r="L89" t="n">
+        <v>8</v>
+      </c>
+      <c r="M89" t="n">
         <v>3</v>
-      </c>
-      <c r="M89" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="90">
@@ -4119,37 +4121,37 @@
       </c>
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="n">
+        <v>3</v>
+      </c>
+      <c r="D90" t="n">
+        <v>1</v>
+      </c>
+      <c r="E90" t="n">
+        <v>0</v>
+      </c>
+      <c r="F90" t="n">
+        <v>0</v>
+      </c>
+      <c r="G90" t="n">
+        <v>0</v>
+      </c>
+      <c r="H90" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" t="n">
         <v>2</v>
       </c>
-      <c r="D90" t="n">
+      <c r="J90" t="n">
+        <v>1</v>
+      </c>
+      <c r="K90" t="n">
+        <v>1</v>
+      </c>
+      <c r="L90" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" t="n">
         <v>3</v>
-      </c>
-      <c r="E90" t="n">
-        <v>1</v>
-      </c>
-      <c r="F90" t="n">
-        <v>0</v>
-      </c>
-      <c r="G90" t="n">
-        <v>1</v>
-      </c>
-      <c r="H90" t="n">
-        <v>0</v>
-      </c>
-      <c r="I90" t="n">
-        <v>0</v>
-      </c>
-      <c r="J90" t="n">
-        <v>2</v>
-      </c>
-      <c r="K90" t="n">
-        <v>1</v>
-      </c>
-      <c r="L90" t="n">
-        <v>1</v>
-      </c>
-      <c r="M90" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="91">
@@ -4160,37 +4162,37 @@
       </c>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D91" t="n">
         <v>2</v>
       </c>
       <c r="E91" t="n">
+        <v>1</v>
+      </c>
+      <c r="F91" t="n">
+        <v>1</v>
+      </c>
+      <c r="G91" t="n">
+        <v>1</v>
+      </c>
+      <c r="H91" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" t="n">
         <v>2</v>
       </c>
-      <c r="F91" t="n">
-        <v>1</v>
-      </c>
-      <c r="G91" t="n">
-        <v>0</v>
-      </c>
-      <c r="H91" t="n">
-        <v>1</v>
-      </c>
-      <c r="I91" t="n">
-        <v>0</v>
-      </c>
       <c r="J91" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" t="n">
+        <v>4</v>
+      </c>
+      <c r="L91" t="n">
+        <v>5</v>
+      </c>
+      <c r="M91" t="n">
         <v>3</v>
-      </c>
-      <c r="K91" t="n">
-        <v>0</v>
-      </c>
-      <c r="L91" t="n">
-        <v>4</v>
-      </c>
-      <c r="M91" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="92">
@@ -4201,22 +4203,22 @@
       </c>
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E92" t="n">
         <v>0</v>
       </c>
       <c r="F92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I92" t="n">
         <v>1</v>
@@ -4225,13 +4227,13 @@
         <v>1</v>
       </c>
       <c r="K92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L92" t="n">
         <v>1</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93">
@@ -4242,13 +4244,13 @@
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D93" t="n">
         <v>1</v>
       </c>
       <c r="E93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F93" t="n">
         <v>0</v>
@@ -4269,10 +4271,10 @@
         <v>0</v>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -4283,16 +4285,16 @@
       </c>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -4301,19 +4303,19 @@
         <v>0</v>
       </c>
       <c r="I94" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J94" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K94" t="n">
         <v>1</v>
       </c>
       <c r="L94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -4324,37 +4326,37 @@
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D95" t="n">
         <v>2</v>
       </c>
       <c r="E95" t="n">
+        <v>0</v>
+      </c>
+      <c r="F95" t="n">
         <v>2</v>
-      </c>
-      <c r="F95" t="n">
-        <v>0</v>
       </c>
       <c r="G95" t="n">
         <v>2</v>
       </c>
       <c r="H95" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" t="n">
+        <v>0</v>
+      </c>
+      <c r="K95" t="n">
+        <v>1</v>
+      </c>
+      <c r="L95" t="n">
+        <v>1</v>
+      </c>
+      <c r="M95" t="n">
         <v>2</v>
-      </c>
-      <c r="I95" t="n">
-        <v>0</v>
-      </c>
-      <c r="J95" t="n">
-        <v>0</v>
-      </c>
-      <c r="K95" t="n">
-        <v>0</v>
-      </c>
-      <c r="L95" t="n">
-        <v>1</v>
-      </c>
-      <c r="M95" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="96">
@@ -4365,7 +4367,7 @@
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D96" t="n">
         <v>0</v>
@@ -4377,10 +4379,10 @@
         <v>0</v>
       </c>
       <c r="G96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I96" t="n">
         <v>0</v>
@@ -4395,7 +4397,7 @@
         <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -4409,28 +4411,28 @@
         <v>1</v>
       </c>
       <c r="D97" t="n">
+        <v>1</v>
+      </c>
+      <c r="E97" t="n">
+        <v>0</v>
+      </c>
+      <c r="F97" t="n">
+        <v>3</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" t="n">
+        <v>1</v>
+      </c>
+      <c r="J97" t="n">
+        <v>1</v>
+      </c>
+      <c r="K97" t="n">
         <v>2</v>
-      </c>
-      <c r="E97" t="n">
-        <v>1</v>
-      </c>
-      <c r="F97" t="n">
-        <v>0</v>
-      </c>
-      <c r="G97" t="n">
-        <v>3</v>
-      </c>
-      <c r="H97" t="n">
-        <v>0</v>
-      </c>
-      <c r="I97" t="n">
-        <v>0</v>
-      </c>
-      <c r="J97" t="n">
-        <v>1</v>
-      </c>
-      <c r="K97" t="n">
-        <v>1</v>
       </c>
       <c r="L97" t="n">
         <v>2</v>

--- a/Result/analyze_1.xlsx
+++ b/Result/analyze_1.xlsx
@@ -441,57 +441,57 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-04</t>
         </is>
       </c>
     </row>
@@ -503,37 +503,37 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F2" t="n">
         <v>3</v>
       </c>
       <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="n">
         <v>3</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1</v>
       </c>
       <c r="I2" t="n">
         <v>3</v>
       </c>
       <c r="J2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L2" t="n">
         <v>2</v>
       </c>
       <c r="M2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -553,28 +553,28 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -585,7 +585,7 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -609,7 +609,7 @@
         <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
         <v>1</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
@@ -635,28 +635,28 @@
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -667,10 +667,10 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -682,10 +682,10 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -694,7 +694,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
         <v>1</v>
@@ -708,34 +708,34 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
         <v>1</v>
@@ -749,10 +749,10 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
         <v>1</v>
@@ -764,22 +764,22 @@
         <v>2</v>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L8" t="n">
         <v>2</v>
       </c>
       <c r="M8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -790,13 +790,13 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
         <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -805,22 +805,22 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
         <v>1</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -834,13 +834,13 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -858,7 +858,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
         <v>1</v>
@@ -878,31 +878,31 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
         <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -919,10 +919,10 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -957,13 +957,13 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
         <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -995,7 +995,7 @@
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -1004,13 +1004,13 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -1025,7 +1025,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1038,37 +1038,37 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>4</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>4</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2</v>
+      </c>
+      <c r="L15" t="n">
         <v>3</v>
       </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>4</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>4</v>
-      </c>
-      <c r="L15" t="n">
-        <v>2</v>
-      </c>
       <c r="M15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1079,37 +1079,37 @@
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
         <v>3</v>
       </c>
-      <c r="E16" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" t="n">
-        <v>1</v>
-      </c>
-      <c r="G16" t="n">
-        <v>1</v>
-      </c>
-      <c r="H16" t="n">
-        <v>2</v>
-      </c>
-      <c r="I16" t="n">
-        <v>2</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1</v>
-      </c>
       <c r="M16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1161,31 +1161,31 @@
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
         <v>3</v>
       </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>2</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
       <c r="K18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -1232,7 +1232,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1249,10 +1249,10 @@
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -1372,10 +1372,10 @@
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1405,9 +1405,7 @@
           <t>建材營造右下</t>
         </is>
       </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
+      <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
         <v>0</v>
       </c>
@@ -1427,16 +1425,16 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" t="n">
         <v>1</v>
@@ -1494,13 +1492,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1518,10 +1516,10 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1530,9 +1528,7 @@
           <t>數位雲端右下</t>
         </is>
       </c>
-      <c r="B27" t="n">
-        <v>0</v>
-      </c>
+      <c r="B27" t="inlineStr"/>
       <c r="C27" t="n">
         <v>0</v>
       </c>
@@ -1596,10 +1592,10 @@
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -1669,10 +1665,10 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -1725,10 +1721,10 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -1795,10 +1791,10 @@
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1903,16 +1899,16 @@
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1930,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -1944,19 +1940,19 @@
       </c>
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -1965,10 +1961,10 @@
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
@@ -1985,16 +1981,16 @@
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -2006,7 +2002,7 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -2047,10 +2043,10 @@
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
@@ -2114,28 +2110,28 @@
         <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F41" t="n">
         <v>1</v>
       </c>
       <c r="G41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
@@ -2196,10 +2192,10 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -2234,13 +2230,13 @@
         <v>1</v>
       </c>
       <c r="D44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G44" t="n">
         <v>1</v>
@@ -2249,19 +2245,19 @@
         <v>1</v>
       </c>
       <c r="I44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K44" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -2270,35 +2266,33 @@
           <t>生技醫療業右下</t>
         </is>
       </c>
-      <c r="B45" t="n">
-        <v>0</v>
-      </c>
+      <c r="B45" t="inlineStr"/>
       <c r="C45" t="n">
         <v>1</v>
       </c>
       <c r="D45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F45" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H45" t="n">
         <v>1</v>
       </c>
       <c r="I45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
@@ -2327,25 +2321,25 @@
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -2368,10 +2362,10 @@
         <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I47" t="n">
         <v>0</v>
@@ -2468,7 +2462,7 @@
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -2485,31 +2479,31 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F50" t="n">
         <v>1</v>
       </c>
       <c r="G50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J50" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -2520,10 +2514,10 @@
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E51" t="n">
         <v>0</v>
@@ -2614,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I53" t="n">
         <v>0</v>
@@ -2632,7 +2626,7 @@
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -2655,10 +2649,10 @@
         <v>0</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I54" t="n">
         <v>0</v>
@@ -2725,7 +2719,7 @@
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D56" t="n">
         <v>0</v>
@@ -2743,7 +2737,7 @@
         <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J56" t="n">
         <v>1</v>
@@ -2752,7 +2746,7 @@
         <v>1</v>
       </c>
       <c r="L56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
         <v>0</v>
@@ -2775,10 +2769,10 @@
         <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -2793,10 +2787,10 @@
         <v>0</v>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -2866,10 +2860,10 @@
         <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K59" t="n">
         <v>0</v>
@@ -2951,7 +2945,7 @@
         <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K61" t="n">
         <v>0</v>
@@ -3030,7 +3024,7 @@
         <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -3042,7 +3036,7 @@
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -3135,25 +3129,25 @@
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D66" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" t="n">
         <v>4</v>
       </c>
-      <c r="E66" t="n">
-        <v>0</v>
-      </c>
-      <c r="F66" t="n">
-        <v>0</v>
-      </c>
       <c r="G66" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I66" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J66" t="n">
         <v>1</v>
@@ -3165,7 +3159,7 @@
         <v>2</v>
       </c>
       <c r="M66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -3206,7 +3200,7 @@
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68">
@@ -3217,16 +3211,16 @@
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G68" t="n">
         <v>2</v>
@@ -3235,19 +3229,19 @@
         <v>2</v>
       </c>
       <c r="I68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -3258,7 +3252,7 @@
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D69" t="n">
         <v>0</v>
@@ -3270,10 +3264,10 @@
         <v>0</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I69" t="n">
         <v>0</v>
@@ -3387,10 +3381,10 @@
         <v>0</v>
       </c>
       <c r="E72" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F72" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -3411,7 +3405,7 @@
         <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -3718,7 +3712,7 @@
         <v>0</v>
       </c>
       <c r="F80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -3748,9 +3742,7 @@
           <t>鋼鐵工業右下</t>
         </is>
       </c>
-      <c r="B81" t="n">
-        <v>0</v>
-      </c>
+      <c r="B81" t="inlineStr"/>
       <c r="C81" t="n">
         <v>0</v>
       </c>
@@ -3758,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="E81" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F81" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -3779,7 +3771,7 @@
         <v>0</v>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M81" t="n">
         <v>0</v>
@@ -3799,7 +3791,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -3823,7 +3815,7 @@
         <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -3834,7 +3826,7 @@
       </c>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D83" t="n">
         <v>0</v>
@@ -3864,7 +3856,7 @@
         <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
@@ -3896,10 +3888,10 @@
         <v>0</v>
       </c>
       <c r="J84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L84" t="n">
         <v>0</v>
@@ -3978,13 +3970,13 @@
         <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K86" t="n">
         <v>1</v>
       </c>
       <c r="L86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
         <v>0</v>
@@ -4028,7 +4020,7 @@
         <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88">
@@ -4039,22 +4031,22 @@
       </c>
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D88" t="n">
         <v>0</v>
       </c>
       <c r="E88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I88" t="n">
         <v>0</v>
@@ -4080,37 +4072,37 @@
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D89" t="n">
+        <v>1</v>
+      </c>
+      <c r="E89" t="n">
+        <v>4</v>
+      </c>
+      <c r="F89" t="n">
         <v>3</v>
       </c>
-      <c r="E89" t="n">
-        <v>1</v>
-      </c>
-      <c r="F89" t="n">
+      <c r="G89" t="n">
+        <v>1</v>
+      </c>
+      <c r="H89" t="n">
+        <v>8</v>
+      </c>
+      <c r="I89" t="n">
+        <v>3</v>
+      </c>
+      <c r="J89" t="n">
         <v>4</v>
       </c>
-      <c r="G89" t="n">
-        <v>3</v>
-      </c>
-      <c r="H89" t="n">
-        <v>1</v>
-      </c>
-      <c r="I89" t="n">
+      <c r="K89" t="n">
         <v>9</v>
       </c>
-      <c r="J89" t="n">
-        <v>3</v>
-      </c>
-      <c r="K89" t="n">
-        <v>3</v>
-      </c>
       <c r="L89" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M89" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="90">
@@ -4121,13 +4113,13 @@
       </c>
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F90" t="n">
         <v>0</v>
@@ -4136,10 +4128,10 @@
         <v>0</v>
       </c>
       <c r="H90" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I90" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J90" t="n">
         <v>1</v>
@@ -4148,10 +4140,10 @@
         <v>1</v>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M90" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="91">
@@ -4165,34 +4157,34 @@
         <v>2</v>
       </c>
       <c r="D91" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F91" t="n">
         <v>1</v>
       </c>
       <c r="G91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H91" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I91" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K91" t="n">
+        <v>3</v>
+      </c>
+      <c r="L91" t="n">
+        <v>3</v>
+      </c>
+      <c r="M91" t="n">
         <v>4</v>
-      </c>
-      <c r="L91" t="n">
-        <v>5</v>
-      </c>
-      <c r="M91" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="92">
@@ -4203,16 +4195,16 @@
       </c>
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D92" t="n">
         <v>0</v>
       </c>
       <c r="E92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -4224,13 +4216,13 @@
         <v>1</v>
       </c>
       <c r="J92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K92" t="n">
         <v>1</v>
       </c>
       <c r="L92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M92" t="n">
         <v>2</v>
@@ -4242,12 +4234,14 @@
           <t>電機機械右下</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr"/>
+      <c r="B93" t="n">
+        <v>0</v>
+      </c>
       <c r="C93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E93" t="n">
         <v>0</v>
@@ -4271,10 +4265,10 @@
         <v>0</v>
       </c>
       <c r="L93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="94">
@@ -4285,31 +4279,31 @@
       </c>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F94" t="n">
         <v>0</v>
       </c>
       <c r="G94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H94" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I94" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L94" t="n">
         <v>0</v>
@@ -4326,19 +4320,19 @@
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D95" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E95" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F95" t="n">
         <v>2</v>
       </c>
       <c r="G95" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H95" t="n">
         <v>0</v>
@@ -4347,16 +4341,16 @@
         <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K95" t="n">
         <v>1</v>
       </c>
       <c r="L95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M95" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
@@ -4376,10 +4370,10 @@
         <v>0</v>
       </c>
       <c r="F96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -4411,34 +4405,34 @@
         <v>1</v>
       </c>
       <c r="D97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E97" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F97" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
       </c>
       <c r="H97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I97" t="n">
         <v>1</v>
       </c>
       <c r="J97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K97" t="n">
         <v>2</v>
       </c>
       <c r="L97" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">

--- a/Result/analyze_1.xlsx
+++ b/Result/analyze_1.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M100"/>
+  <dimension ref="A1:M99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,57 +441,57 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-05</t>
         </is>
       </c>
     </row>
@@ -506,31 +506,31 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
         <v>3</v>
       </c>
       <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
         <v>3</v>
       </c>
-      <c r="G2" t="n">
-        <v>1</v>
-      </c>
       <c r="H2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L2" t="n">
         <v>3</v>
-      </c>
-      <c r="I2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J2" t="n">
-        <v>7</v>
-      </c>
-      <c r="K2" t="n">
-        <v>2</v>
-      </c>
-      <c r="L2" t="n">
-        <v>2</v>
       </c>
       <c r="M2" t="n">
         <v>3</v>
@@ -550,25 +550,25 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
         <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
         <v>1</v>
@@ -600,19 +600,19 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
         <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M4" t="n">
         <v>1</v>
@@ -632,28 +632,28 @@
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M5" t="n">
         <v>1</v>
@@ -667,7 +667,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -679,10 +679,10 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -694,10 +694,10 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -708,31 +708,31 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L7" t="n">
         <v>1</v>
@@ -749,34 +749,34 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
         <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K8" t="n">
         <v>2</v>
       </c>
       <c r="L8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
         <v>1</v>
@@ -793,7 +793,7 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -802,25 +802,25 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
         <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -831,16 +831,16 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -855,13 +855,13 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
         <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -875,34 +875,34 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -916,10 +916,10 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -940,10 +940,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -954,13 +954,13 @@
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
         <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -995,19 +995,19 @@
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" t="n">
         <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1022,10 +1022,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1034,38 +1034,36 @@
           <t>半導體業右下</t>
         </is>
       </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
+      <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>4</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>4</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2</v>
+      </c>
+      <c r="K15" t="n">
         <v>3</v>
       </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>4</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>4</v>
-      </c>
-      <c r="K15" t="n">
-        <v>2</v>
-      </c>
       <c r="L15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M15" t="n">
         <v>2</v>
@@ -1082,31 +1080,31 @@
         <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E16" t="n">
         <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G16" t="n">
         <v>2</v>
       </c>
       <c r="H16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
         <v>1</v>
@@ -1161,28 +1159,28 @@
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
         <v>3</v>
       </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>2</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
       <c r="J18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -1229,10 +1227,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1246,10 +1244,10 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -1261,10 +1259,10 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -1282,7 +1280,9 @@
           <t>居家生活右下</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr"/>
+      <c r="B21" t="n">
+        <v>0</v>
+      </c>
       <c r="C21" t="n">
         <v>0</v>
       </c>
@@ -1369,10 +1369,10 @@
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -1422,22 +1422,22 @@
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" t="n">
         <v>1</v>
       </c>
       <c r="M24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1489,13 +1489,13 @@
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -1513,13 +1513,13 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1560,7 +1560,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -1589,10 +1589,10 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -1662,10 +1662,10 @@
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -1718,13 +1718,13 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -1788,10 +1788,10 @@
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
@@ -1899,13 +1899,13 @@
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L36" t="n">
         <v>1</v>
@@ -1938,18 +1938,20 @@
           <t>汽車工業右下</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr"/>
+      <c r="B37" t="n">
+        <v>0</v>
+      </c>
       <c r="C37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1958,10 +1960,10 @@
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -1981,13 +1983,13 @@
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -2002,13 +2004,13 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M38" t="n">
         <v>1</v>
@@ -2040,10 +2042,10 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -2107,28 +2109,28 @@
         <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E41" t="n">
         <v>1</v>
       </c>
       <c r="F41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -2140,7 +2142,7 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>玻璃陶瓷右下</t>
+          <t>玻璃陶瓷平</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -2148,7 +2150,7 @@
         <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
@@ -2175,13 +2177,13 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>玻璃陶瓷平</t>
+          <t>生技醫療業右上</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -2195,42 +2197,44 @@
         <v>1</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>生技醫療業右上</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr"/>
+          <t>生技醫療業右下</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>0</v>
+      </c>
       <c r="C44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
@@ -2242,13 +2246,13 @@
         <v>1</v>
       </c>
       <c r="H44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
@@ -2257,54 +2261,54 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>生技醫療業右下</t>
+          <t>生技醫療業平</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D45" t="n">
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G45" t="n">
         <v>1</v>
       </c>
       <c r="H45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>生技醫療業平</t>
+          <t>紡織纖維右上</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -2318,37 +2322,39 @@
         <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>紡織纖維右上</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr"/>
+          <t>紡織纖維右下</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>0</v>
+      </c>
       <c r="C47" t="n">
         <v>0</v>
       </c>
@@ -2362,7 +2368,7 @@
         <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
@@ -2386,7 +2392,7 @@
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>紡織纖維右下</t>
+          <t>紡織纖維平</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -2418,7 +2424,7 @@
         <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M48" t="n">
         <v>0</v>
@@ -2427,7 +2433,7 @@
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>紡織纖維平</t>
+          <t>綠能環保右上</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -2435,19 +2441,19 @@
         <v>0</v>
       </c>
       <c r="D49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I49" t="n">
         <v>0</v>
@@ -2456,19 +2462,19 @@
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>綠能環保右上</t>
+          <t>綠能環保右下</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -2479,19 +2485,19 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -2500,7 +2506,7 @@
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
         <v>0</v>
@@ -2509,12 +2515,12 @@
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>綠能環保右下</t>
+          <t>綠能環保平</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>
@@ -2550,7 +2556,7 @@
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>綠能環保平</t>
+          <t>航運業右上</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -2564,7 +2570,7 @@
         <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -2582,16 +2588,16 @@
         <v>0</v>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>航運業右上</t>
+          <t>航運業右下</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
@@ -2605,10 +2611,10 @@
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
@@ -2626,13 +2632,13 @@
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>航運業右下</t>
+          <t>航運業平</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
@@ -2649,7 +2655,7 @@
         <v>0</v>
       </c>
       <c r="G54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
@@ -2673,7 +2679,7 @@
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>航運業平</t>
+          <t>觀光事業右上</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
@@ -2693,13 +2699,13 @@
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K55" t="n">
         <v>0</v>
@@ -2714,7 +2720,7 @@
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>觀光事業右上</t>
+          <t>觀光事業右下</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
@@ -2725,7 +2731,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -2737,10 +2743,10 @@
         <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K56" t="n">
         <v>1</v>
@@ -2755,7 +2761,7 @@
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>觀光事業右下</t>
+          <t>觀光事業平</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
@@ -2769,7 +2775,7 @@
         <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -2787,7 +2793,7 @@
         <v>0</v>
       </c>
       <c r="L57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
         <v>0</v>
@@ -2796,7 +2802,7 @@
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>觀光事業平</t>
+          <t>貿易百貨右下</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
@@ -2816,7 +2822,7 @@
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I58" t="n">
         <v>0</v>
@@ -2837,7 +2843,7 @@
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>貿易百貨右下</t>
+          <t>貿易百貨平</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -2860,7 +2866,7 @@
         <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -2878,7 +2884,7 @@
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>貿易百貨平</t>
+          <t>資訊服務業右上</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -2919,7 +2925,7 @@
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>資訊服務業右上</t>
+          <t>資訊服務業右下</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
@@ -2960,7 +2966,7 @@
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>資訊服務業右下</t>
+          <t>資訊服務業平</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
@@ -2992,16 +2998,16 @@
         <v>0</v>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>資訊服務業平</t>
+          <t>農業科技業右上</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
@@ -3024,7 +3030,7 @@
         <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -3036,13 +3042,13 @@
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>農業科技業右上</t>
+          <t>農業科技業右下</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
@@ -3083,7 +3089,7 @@
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>農業科技業右下</t>
+          <t>通信網路業右上</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
@@ -3094,42 +3100,42 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>通信網路業右上</t>
+          <t>通信網路業右下</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D66" t="n">
         <v>0</v>
@@ -3138,25 +3144,25 @@
         <v>0</v>
       </c>
       <c r="F66" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I66" t="n">
         <v>0</v>
       </c>
       <c r="J66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M66" t="n">
         <v>1</v>
@@ -3165,7 +3171,7 @@
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>通信網路業右下</t>
+          <t>通信網路業平</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
@@ -3173,31 +3179,31 @@
         <v>0</v>
       </c>
       <c r="D67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M67" t="n">
         <v>2</v>
@@ -3206,48 +3212,48 @@
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>通信網路業平</t>
+          <t>造紙工業右下</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D68" t="n">
         <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G68" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K68" t="n">
         <v>0</v>
       </c>
       <c r="L68" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>造紙工業右下</t>
+          <t>造紙工業平</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
@@ -3264,7 +3270,7 @@
         <v>0</v>
       </c>
       <c r="G69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -3288,7 +3294,7 @@
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>造紙工業平</t>
+          <t>運動休閒右上</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
@@ -3329,7 +3335,7 @@
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>運動休閒右上</t>
+          <t>運動休閒右下</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
@@ -3337,7 +3343,7 @@
         <v>0</v>
       </c>
       <c r="D71" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E71" t="n">
         <v>0</v>
@@ -3361,7 +3367,7 @@
         <v>0</v>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M71" t="n">
         <v>0</v>
@@ -3370,7 +3376,7 @@
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>運動休閒右下</t>
+          <t>運動休閒平</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
@@ -3381,7 +3387,7 @@
         <v>0</v>
       </c>
       <c r="E72" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F72" t="n">
         <v>0</v>
@@ -3405,13 +3411,13 @@
         <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>運動休閒平</t>
+          <t>金融保險右上</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
@@ -3452,7 +3458,7 @@
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>金融保險右上</t>
+          <t>金融保險右下</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
@@ -3493,7 +3499,7 @@
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>金融保險右下</t>
+          <t>金融保險平</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
@@ -3534,7 +3540,7 @@
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>金融保險平</t>
+          <t>金融業右上</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
@@ -3575,10 +3581,12 @@
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>金融業右上</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr"/>
+          <t>金融業右下</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>0</v>
+      </c>
       <c r="C77" t="n">
         <v>0</v>
       </c>
@@ -3616,7 +3624,7 @@
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>金融業右下</t>
+          <t>金融業平</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
@@ -3657,7 +3665,7 @@
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>金融業平</t>
+          <t>鋼鐵工業右上</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
@@ -3698,7 +3706,7 @@
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業右上</t>
+          <t>鋼鐵工業右下</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
@@ -3706,7 +3714,7 @@
         <v>0</v>
       </c>
       <c r="D80" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E80" t="n">
         <v>0</v>
@@ -3739,7 +3747,7 @@
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業右下</t>
+          <t>鋼鐵工業平</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
@@ -3747,10 +3755,10 @@
         <v>0</v>
       </c>
       <c r="D81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E81" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F81" t="n">
         <v>0</v>
@@ -3768,10 +3776,10 @@
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
         <v>0</v>
@@ -3780,7 +3788,7 @@
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業平</t>
+          <t>電器電纜右上</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
@@ -3791,7 +3799,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -3812,7 +3820,7 @@
         <v>0</v>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M82" t="n">
         <v>0</v>
@@ -3821,7 +3829,7 @@
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>電器電纜右上</t>
+          <t>電器電纜右下</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
@@ -3844,7 +3852,7 @@
         <v>0</v>
       </c>
       <c r="I83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -3856,13 +3864,13 @@
         <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>電器電纜右下</t>
+          <t>電器電纜平</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
@@ -3888,7 +3896,7 @@
         <v>0</v>
       </c>
       <c r="J84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K84" t="n">
         <v>0</v>
@@ -3903,7 +3911,7 @@
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>電器電纜平</t>
+          <t>電子通路業右上</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
@@ -3926,10 +3934,10 @@
         <v>0</v>
       </c>
       <c r="I85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K85" t="n">
         <v>0</v>
@@ -3944,15 +3952,17 @@
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>電子通路業右上</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr"/>
+          <t>電子通路業右下</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>0</v>
+      </c>
       <c r="C86" t="n">
         <v>0</v>
       </c>
       <c r="D86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E86" t="n">
         <v>0</v>
@@ -3970,22 +3980,22 @@
         <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>電子通路業右下</t>
+          <t>電子通路業平</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
@@ -3999,7 +4009,7 @@
         <v>0</v>
       </c>
       <c r="F87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -4020,95 +4030,95 @@
         <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>電子通路業平</t>
+          <t>電子零組件業右上</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D88" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E88" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G88" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H88" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I88" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J88" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K88" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業右上</t>
+          <t>電子零組件業右下</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="n">
+        <v>0</v>
+      </c>
+      <c r="D89" t="n">
+        <v>1</v>
+      </c>
+      <c r="E89" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" t="n">
+        <v>2</v>
+      </c>
+      <c r="H89" t="n">
+        <v>1</v>
+      </c>
+      <c r="I89" t="n">
+        <v>1</v>
+      </c>
+      <c r="J89" t="n">
+        <v>2</v>
+      </c>
+      <c r="K89" t="n">
+        <v>2</v>
+      </c>
+      <c r="L89" t="n">
         <v>3</v>
       </c>
-      <c r="D89" t="n">
-        <v>1</v>
-      </c>
-      <c r="E89" t="n">
-        <v>4</v>
-      </c>
-      <c r="F89" t="n">
+      <c r="M89" t="n">
         <v>3</v>
-      </c>
-      <c r="G89" t="n">
-        <v>1</v>
-      </c>
-      <c r="H89" t="n">
-        <v>8</v>
-      </c>
-      <c r="I89" t="n">
-        <v>3</v>
-      </c>
-      <c r="J89" t="n">
-        <v>4</v>
-      </c>
-      <c r="K89" t="n">
-        <v>9</v>
-      </c>
-      <c r="L89" t="n">
-        <v>4</v>
-      </c>
-      <c r="M89" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業右下</t>
+          <t>電子零組件業平</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
@@ -4125,36 +4135,36 @@
         <v>0</v>
       </c>
       <c r="G90" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H90" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I90" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K90" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L90" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M90" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業平</t>
+          <t>電機機械右上</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D91" t="n">
         <v>1</v>
@@ -4166,31 +4176,31 @@
         <v>1</v>
       </c>
       <c r="G91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H91" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J91" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K91" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L91" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M91" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>電機機械右上</t>
+          <t>電機機械右下</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
@@ -4201,7 +4211,7 @@
         <v>0</v>
       </c>
       <c r="E92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F92" t="n">
         <v>0</v>
@@ -4210,35 +4220,33 @@
         <v>0</v>
       </c>
       <c r="H92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L92" t="n">
         <v>2</v>
       </c>
       <c r="M92" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>電機機械右下</t>
-        </is>
-      </c>
-      <c r="B93" t="n">
-        <v>0</v>
-      </c>
+          <t>電機機械平</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr"/>
       <c r="C93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D93" t="n">
         <v>0</v>
@@ -4250,13 +4258,13 @@
         <v>0</v>
       </c>
       <c r="G93" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H93" t="n">
         <v>0</v>
       </c>
       <c r="I93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -4268,13 +4276,13 @@
         <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>電機機械平</t>
+          <t>電腦及週邊設備業右上</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
@@ -4282,10 +4290,10 @@
         <v>0</v>
       </c>
       <c r="D94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E94" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F94" t="n">
         <v>0</v>
@@ -4294,42 +4302,44 @@
         <v>1</v>
       </c>
       <c r="H94" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K94" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右上</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr"/>
+          <t>電腦及週邊設備業右下</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>0</v>
+      </c>
       <c r="C95" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D95" t="n">
         <v>0</v>
       </c>
       <c r="E95" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F95" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -4341,22 +4351,22 @@
         <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L95" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右下</t>
+          <t>電腦及週邊設備業平</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
@@ -4364,51 +4374,51 @@
         <v>0</v>
       </c>
       <c r="D96" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E96" t="n">
         <v>0</v>
       </c>
       <c r="F96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
       </c>
       <c r="H96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I96" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J96" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L96" t="n">
         <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業平</t>
+          <t>食品工業右上</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D97" t="n">
         <v>0</v>
       </c>
       <c r="E97" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F97" t="n">
         <v>0</v>
@@ -4417,19 +4427,19 @@
         <v>0</v>
       </c>
       <c r="H97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J97" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K97" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
         <v>0</v>
@@ -4438,7 +4448,7 @@
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>食品工業右上</t>
+          <t>食品工業右下</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
@@ -4479,7 +4489,7 @@
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>食品工業右下</t>
+          <t>食品工業平</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
@@ -4514,47 +4524,6 @@
         <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="1" t="inlineStr">
-        <is>
-          <t>食品工業平</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr"/>
-      <c r="C100" t="n">
-        <v>0</v>
-      </c>
-      <c r="D100" t="n">
-        <v>0</v>
-      </c>
-      <c r="E100" t="n">
-        <v>0</v>
-      </c>
-      <c r="F100" t="n">
-        <v>0</v>
-      </c>
-      <c r="G100" t="n">
-        <v>0</v>
-      </c>
-      <c r="H100" t="n">
-        <v>0</v>
-      </c>
-      <c r="I100" t="n">
-        <v>0</v>
-      </c>
-      <c r="J100" t="n">
-        <v>0</v>
-      </c>
-      <c r="K100" t="n">
-        <v>0</v>
-      </c>
-      <c r="L100" t="n">
-        <v>0</v>
-      </c>
-      <c r="M100" t="n">
         <v>0</v>
       </c>
     </row>

--- a/Result/analyze_1.xlsx
+++ b/Result/analyze_1.xlsx
@@ -441,57 +441,57 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-06</t>
         </is>
       </c>
     </row>
@@ -503,37 +503,37 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
         <v>3</v>
       </c>
       <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
         <v>3</v>
       </c>
-      <c r="F2" t="n">
-        <v>1</v>
-      </c>
       <c r="G2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2" t="n">
+        <v>7</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K2" t="n">
         <v>3</v>
-      </c>
-      <c r="H2" t="n">
-        <v>2</v>
-      </c>
-      <c r="I2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J2" t="n">
-        <v>2</v>
-      </c>
-      <c r="K2" t="n">
-        <v>2</v>
       </c>
       <c r="L2" t="n">
         <v>3</v>
       </c>
       <c r="M2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -542,27 +542,29 @@
           <t>光電業右下</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
         <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -571,10 +573,10 @@
         <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -597,25 +599,25 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -629,34 +631,34 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -665,7 +667,9 @@
           <t>其他右下</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
@@ -676,10 +680,10 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -708,10 +712,10 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -720,25 +724,25 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K7" t="n">
         <v>2</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -749,37 +753,37 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
         <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
         <v>3</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>2</v>
-      </c>
-      <c r="K8" t="n">
-        <v>2</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -790,7 +794,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -799,25 +803,25 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
         <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M9" t="n">
         <v>1</v>
@@ -831,13 +835,13 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -852,16 +856,16 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
         <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -872,34 +876,34 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
         <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
         <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -911,12 +915,14 @@
           <t>化學工業右下</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
+      <c r="B12" t="n">
+        <v>0</v>
+      </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -937,10 +943,10 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -954,10 +960,10 @@
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -998,13 +1004,13 @@
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -1019,13 +1025,13 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -1036,37 +1042,37 @@
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
         <v>4</v>
       </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
       <c r="I15" t="n">
+        <v>2</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2</v>
+      </c>
+      <c r="L15" t="n">
+        <v>3</v>
+      </c>
+      <c r="M15" t="n">
         <v>4</v>
-      </c>
-      <c r="J15" t="n">
-        <v>2</v>
-      </c>
-      <c r="K15" t="n">
-        <v>3</v>
-      </c>
-      <c r="L15" t="n">
-        <v>2</v>
-      </c>
-      <c r="M15" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1077,37 +1083,37 @@
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F16" t="n">
         <v>2</v>
       </c>
       <c r="G16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1159,25 +1165,25 @@
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
         <v>3</v>
       </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>2</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
       <c r="I18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1224,10 +1230,10 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -1241,10 +1247,10 @@
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -1256,10 +1262,10 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1280,9 +1286,7 @@
           <t>居家生活右下</t>
         </is>
       </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
+      <c r="B21" t="inlineStr"/>
       <c r="C21" t="n">
         <v>0</v>
       </c>
@@ -1366,10 +1370,10 @@
       </c>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -1419,22 +1423,22 @@
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
         <v>1</v>
       </c>
       <c r="L24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -1489,10 +1493,10 @@
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -1510,16 +1514,16 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1557,10 +1561,10 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -1586,10 +1590,10 @@
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1659,10 +1663,10 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1715,16 +1719,16 @@
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -1785,10 +1789,10 @@
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -1920,7 +1924,7 @@
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K36" t="n">
         <v>1</v>
@@ -1929,7 +1933,7 @@
         <v>1</v>
       </c>
       <c r="M36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -1938,17 +1942,15 @@
           <t>汽車工業右下</t>
         </is>
       </c>
-      <c r="B37" t="n">
-        <v>0</v>
-      </c>
+      <c r="B37" t="inlineStr"/>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
@@ -1957,10 +1959,10 @@
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -1983,10 +1985,10 @@
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
@@ -2007,13 +2009,13 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L38" t="n">
         <v>1</v>
       </c>
       <c r="M38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2039,10 +2041,10 @@
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2106,28 +2108,28 @@
       </c>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D41" t="n">
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -2147,10 +2149,10 @@
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
@@ -2174,10 +2176,10 @@
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2191,7 +2193,7 @@
         <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E43" t="n">
         <v>1</v>
@@ -2200,22 +2202,22 @@
         <v>1</v>
       </c>
       <c r="G43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I43" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M43" t="n">
         <v>1</v>
@@ -2231,25 +2233,25 @@
         <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D44" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F44" t="n">
         <v>1</v>
       </c>
       <c r="G44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -2258,10 +2260,10 @@
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M44" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2278,13 +2280,13 @@
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -2296,13 +2298,13 @@
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45" t="n">
         <v>1</v>
       </c>
       <c r="M45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -2319,10 +2321,10 @@
         <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -2352,9 +2354,7 @@
           <t>紡織纖維右下</t>
         </is>
       </c>
-      <c r="B47" t="n">
-        <v>0</v>
-      </c>
+      <c r="B47" t="inlineStr"/>
       <c r="C47" t="n">
         <v>0</v>
       </c>
@@ -2421,10 +2421,10 @@
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
         <v>0</v>
@@ -2438,31 +2438,31 @@
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D49" t="n">
         <v>1</v>
       </c>
       <c r="E49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I49" t="n">
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
@@ -2567,10 +2567,10 @@
         <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -2585,13 +2585,13 @@
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -2696,7 +2696,7 @@
         <v>0</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H55" t="n">
         <v>1</v>
@@ -2705,7 +2705,7 @@
         <v>1</v>
       </c>
       <c r="J55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K55" t="n">
         <v>0</v>
@@ -2728,10 +2728,10 @@
         <v>0</v>
       </c>
       <c r="D56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -2746,10 +2746,10 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
@@ -2819,10 +2819,10 @@
         <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I58" t="n">
         <v>0</v>
@@ -2983,7 +2983,7 @@
         <v>0</v>
       </c>
       <c r="G62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H62" t="n">
         <v>0</v>
@@ -2995,13 +2995,13 @@
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L62" t="n">
         <v>1</v>
       </c>
       <c r="M62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -3097,19 +3097,19 @@
         <v>0</v>
       </c>
       <c r="D65" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E65" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F65" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G65" t="n">
         <v>2</v>
       </c>
       <c r="H65" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I65" t="n">
         <v>2</v>
@@ -3118,13 +3118,13 @@
         <v>2</v>
       </c>
       <c r="K65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L65" t="n">
         <v>1</v>
       </c>
       <c r="M65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
@@ -3133,7 +3133,9 @@
           <t>通信網路業右下</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr"/>
+      <c r="B66" t="n">
+        <v>0</v>
+      </c>
       <c r="C66" t="n">
         <v>0</v>
       </c>
@@ -3159,13 +3161,13 @@
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L66" t="n">
         <v>1</v>
       </c>
       <c r="M66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -3176,28 +3178,28 @@
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D67" t="n">
         <v>1</v>
       </c>
       <c r="E67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K67" t="n">
         <v>2</v>
@@ -3206,7 +3208,7 @@
         <v>2</v>
       </c>
       <c r="M67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -3223,10 +3225,10 @@
         <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -3340,10 +3342,10 @@
       </c>
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D71" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E71" t="n">
         <v>0</v>
@@ -3364,13 +3366,13 @@
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -3584,9 +3586,7 @@
           <t>金融業右下</t>
         </is>
       </c>
-      <c r="B77" t="n">
-        <v>0</v>
-      </c>
+      <c r="B77" t="inlineStr"/>
       <c r="C77" t="n">
         <v>0</v>
       </c>
@@ -3711,10 +3711,10 @@
       </c>
       <c r="B80" t="inlineStr"/>
       <c r="C80" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D80" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E80" t="n">
         <v>0</v>
@@ -3732,7 +3732,7 @@
         <v>0</v>
       </c>
       <c r="J80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K80" t="n">
         <v>0</v>
@@ -3741,7 +3741,7 @@
         <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
@@ -3752,10 +3752,10 @@
       </c>
       <c r="B81" t="inlineStr"/>
       <c r="C81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E81" t="n">
         <v>0</v>
@@ -3776,7 +3776,7 @@
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L81" t="n">
         <v>0</v>
@@ -3817,13 +3817,13 @@
         <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -3849,10 +3849,10 @@
         <v>0</v>
       </c>
       <c r="H83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
         <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
@@ -3931,13 +3931,13 @@
         <v>0</v>
       </c>
       <c r="H85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I85" t="n">
         <v>1</v>
       </c>
       <c r="J85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K85" t="n">
         <v>0</v>
@@ -3946,7 +3946,7 @@
         <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
@@ -3955,14 +3955,12 @@
           <t>電子通路業右下</t>
         </is>
       </c>
-      <c r="B86" t="n">
-        <v>0</v>
-      </c>
+      <c r="B86" t="inlineStr"/>
       <c r="C86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E86" t="n">
         <v>0</v>
@@ -3983,13 +3981,13 @@
         <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L86" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M86" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -4006,10 +4004,10 @@
         <v>0</v>
       </c>
       <c r="E87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -4027,7 +4025,7 @@
         <v>0</v>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M87" t="n">
         <v>1</v>
@@ -4041,37 +4039,37 @@
       </c>
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D88" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E88" t="n">
+        <v>1</v>
+      </c>
+      <c r="F88" t="n">
+        <v>8</v>
+      </c>
+      <c r="G88" t="n">
         <v>3</v>
-      </c>
-      <c r="F88" t="n">
-        <v>1</v>
-      </c>
-      <c r="G88" t="n">
-        <v>8</v>
       </c>
       <c r="H88" t="n">
         <v>3</v>
       </c>
       <c r="I88" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J88" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="K88" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L88" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M88" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="89">
@@ -4082,37 +4080,37 @@
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E89" t="n">
         <v>0</v>
       </c>
       <c r="F89" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G89" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H89" t="n">
         <v>1</v>
       </c>
       <c r="I89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J89" t="n">
         <v>2</v>
       </c>
       <c r="K89" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L89" t="n">
         <v>3</v>
       </c>
       <c r="M89" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
@@ -4123,37 +4121,37 @@
       </c>
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F90" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G90" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H90" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I90" t="n">
         <v>3</v>
       </c>
       <c r="J90" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K90" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L90" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
@@ -4164,13 +4162,13 @@
       </c>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F91" t="n">
         <v>1</v>
@@ -4185,13 +4183,13 @@
         <v>1</v>
       </c>
       <c r="J91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K91" t="n">
         <v>2</v>
       </c>
       <c r="L91" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
         <v>0</v>
@@ -4203,7 +4201,9 @@
           <t>電機機械右下</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr"/>
+      <c r="B92" t="n">
+        <v>0</v>
+      </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
@@ -4223,19 +4223,19 @@
         <v>0</v>
       </c>
       <c r="I92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L92" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
@@ -4246,7 +4246,7 @@
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D93" t="n">
         <v>0</v>
@@ -4255,16 +4255,16 @@
         <v>0</v>
       </c>
       <c r="F93" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G93" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -4273,10 +4273,10 @@
         <v>0</v>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -4287,34 +4287,34 @@
       </c>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D94" t="n">
         <v>2</v>
       </c>
       <c r="E94" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I94" t="n">
         <v>1</v>
       </c>
       <c r="J94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M94" t="n">
         <v>2</v>
@@ -4326,9 +4326,7 @@
           <t>電腦及週邊設備業右下</t>
         </is>
       </c>
-      <c r="B95" t="n">
-        <v>0</v>
-      </c>
+      <c r="B95" t="inlineStr"/>
       <c r="C95" t="n">
         <v>0</v>
       </c>
@@ -4336,7 +4334,7 @@
         <v>0</v>
       </c>
       <c r="E95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F95" t="n">
         <v>0</v>
@@ -4371,10 +4369,10 @@
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D96" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E96" t="n">
         <v>0</v>
@@ -4383,25 +4381,25 @@
         <v>0</v>
       </c>
       <c r="G96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I96" t="n">
         <v>2</v>
       </c>
       <c r="J96" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M96" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">

--- a/Result/analyze_1.xlsx
+++ b/Result/analyze_1.xlsx
@@ -441,57 +441,57 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-07</t>
         </is>
       </c>
     </row>
@@ -506,31 +506,31 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="n">
         <v>3</v>
       </c>
-      <c r="E2" t="n">
-        <v>1</v>
-      </c>
       <c r="F2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G2" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J2" t="n">
         <v>3</v>
       </c>
-      <c r="G2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H2" t="n">
-        <v>7</v>
-      </c>
-      <c r="I2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J2" t="n">
-        <v>2</v>
-      </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -546,37 +546,37 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -596,25 +596,25 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M4" t="n">
         <v>2</v>
@@ -628,37 +628,37 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K5" t="n">
         <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -667,9 +667,7 @@
           <t>其他右下</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>0</v>
-      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
         <v>0</v>
       </c>
@@ -677,10 +675,10 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -712,34 +710,34 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -756,19 +754,19 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I8" t="n">
         <v>2</v>
@@ -780,10 +778,10 @@
         <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M8" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -792,7 +790,9 @@
           <t>其他電子業右下</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
@@ -800,25 +800,25 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
         <v>1</v>
@@ -835,10 +835,10 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -853,10 +853,10 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
         <v>1</v>
@@ -865,7 +865,7 @@
         <v>2</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -876,31 +876,31 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
         <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -919,7 +919,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -940,16 +940,16 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -981,7 +981,7 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1001,13 +1001,13 @@
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -1022,16 +1022,16 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -1042,25 +1042,25 @@
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
         <v>4</v>
       </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
       <c r="H15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J15" t="n">
         <v>3</v>
@@ -1069,7 +1069,7 @@
         <v>2</v>
       </c>
       <c r="L15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M15" t="n">
         <v>4</v>
@@ -1086,34 +1086,34 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" t="n">
         <v>2</v>
       </c>
       <c r="F16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
         <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
         <v>3</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1165,22 +1165,22 @@
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
         <v>3</v>
       </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>2</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
       <c r="H18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -1227,10 +1227,10 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -1259,10 +1259,10 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -1277,7 +1277,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1318,7 +1318,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
@@ -1420,22 +1420,22 @@
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
       </c>
       <c r="K24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
@@ -1511,19 +1511,19 @@
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1558,10 +1558,10 @@
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -1587,10 +1587,10 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -1660,10 +1660,10 @@
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -1687,7 +1687,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -1716,16 +1716,16 @@
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -1786,10 +1786,10 @@
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1860,7 +1860,9 @@
           <t>水泥工業右下</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr"/>
+      <c r="B35" t="n">
+        <v>0</v>
+      </c>
       <c r="C35" t="n">
         <v>0</v>
       </c>
@@ -1921,7 +1923,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
         <v>1</v>
@@ -1930,10 +1932,10 @@
         <v>1</v>
       </c>
       <c r="L36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -1942,12 +1944,14 @@
           <t>汽車工業右下</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr"/>
+      <c r="B37" t="n">
+        <v>0</v>
+      </c>
       <c r="C37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
@@ -1956,10 +1960,10 @@
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
@@ -1985,7 +1989,7 @@
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
@@ -2006,16 +2010,16 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K38" t="n">
         <v>1</v>
       </c>
       <c r="L38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2038,10 +2042,10 @@
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
@@ -2111,22 +2115,22 @@
         <v>1</v>
       </c>
       <c r="D41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2149,7 +2153,7 @@
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D42" t="n">
         <v>0</v>
@@ -2173,10 +2177,10 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
@@ -2190,7 +2194,7 @@
       </c>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D43" t="n">
         <v>1</v>
@@ -2199,28 +2203,28 @@
         <v>1</v>
       </c>
       <c r="F43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H43" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L43" t="n">
         <v>1</v>
       </c>
       <c r="M43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -2229,23 +2233,21 @@
           <t>生技醫療業右下</t>
         </is>
       </c>
-      <c r="B44" t="n">
-        <v>0</v>
-      </c>
+      <c r="B44" t="inlineStr"/>
       <c r="C44" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E44" t="n">
         <v>1</v>
       </c>
       <c r="F44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -2257,13 +2259,13 @@
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L44" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -2277,13 +2279,13 @@
         <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -2295,13 +2297,13 @@
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
@@ -2321,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
@@ -2345,7 +2347,7 @@
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -2400,7 +2402,7 @@
         <v>0</v>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E48" t="n">
         <v>0</v>
@@ -2418,10 +2420,10 @@
         <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
@@ -2441,25 +2443,25 @@
         <v>1</v>
       </c>
       <c r="D49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
@@ -2468,7 +2470,7 @@
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -2564,10 +2566,10 @@
         <v>0</v>
       </c>
       <c r="D52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F52" t="n">
         <v>0</v>
@@ -2582,16 +2584,16 @@
         <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -2605,10 +2607,10 @@
         <v>0</v>
       </c>
       <c r="D53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F53" t="n">
         <v>0</v>
@@ -2693,7 +2695,7 @@
         <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G55" t="n">
         <v>1</v>
@@ -2702,7 +2704,7 @@
         <v>1</v>
       </c>
       <c r="I55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -2725,10 +2727,10 @@
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E56" t="n">
         <v>0</v>
@@ -2743,10 +2745,10 @@
         <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -2816,10 +2818,10 @@
         <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
@@ -2980,10 +2982,10 @@
         <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H62" t="n">
         <v>0</v>
@@ -2992,13 +2994,13 @@
         <v>0</v>
       </c>
       <c r="J62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K62" t="n">
         <v>1</v>
       </c>
       <c r="L62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
         <v>0</v>
@@ -3094,37 +3096,37 @@
       </c>
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D65" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F65" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G65" t="n">
         <v>2</v>
       </c>
       <c r="H65" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I65" t="n">
         <v>2</v>
       </c>
       <c r="J65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M65" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="66">
@@ -3133,9 +3135,7 @@
           <t>通信網路業右下</t>
         </is>
       </c>
-      <c r="B66" t="n">
-        <v>0</v>
-      </c>
+      <c r="B66" t="inlineStr"/>
       <c r="C66" t="n">
         <v>0</v>
       </c>
@@ -3158,13 +3158,13 @@
         <v>0</v>
       </c>
       <c r="J66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
         <v>0</v>
@@ -3187,28 +3187,28 @@
         <v>1</v>
       </c>
       <c r="F67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K67" t="n">
         <v>2</v>
       </c>
       <c r="L67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -3222,10 +3222,10 @@
         <v>0</v>
       </c>
       <c r="D68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F68" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D71" t="n">
         <v>0</v>
@@ -3363,16 +3363,16 @@
         <v>0</v>
       </c>
       <c r="J71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -3700,7 +3700,7 @@
         <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="B80" t="inlineStr"/>
       <c r="C80" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D80" t="n">
         <v>0</v>
@@ -3729,19 +3729,19 @@
         <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K80" t="n">
         <v>0</v>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="B81" t="inlineStr"/>
       <c r="C81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D81" t="n">
         <v>0</v>
@@ -3814,16 +3814,16 @@
         <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -3846,10 +3846,10 @@
         <v>0</v>
       </c>
       <c r="G83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I83" t="n">
         <v>0</v>
@@ -3902,7 +3902,7 @@
         <v>0</v>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M84" t="n">
         <v>1</v>
@@ -3928,13 +3928,13 @@
         <v>0</v>
       </c>
       <c r="G85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H85" t="n">
         <v>1</v>
       </c>
       <c r="I85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -3943,10 +3943,10 @@
         <v>0</v>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -3957,7 +3957,7 @@
       </c>
       <c r="B86" t="inlineStr"/>
       <c r="C86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D86" t="n">
         <v>0</v>
@@ -3978,13 +3978,13 @@
         <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K86" t="n">
         <v>2</v>
       </c>
       <c r="L86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
         <v>0</v>
@@ -4001,10 +4001,10 @@
         <v>0</v>
       </c>
       <c r="D87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F87" t="n">
         <v>0</v>
@@ -4022,13 +4022,13 @@
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L87" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -4039,37 +4039,37 @@
       </c>
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D88" t="n">
+        <v>0</v>
+      </c>
+      <c r="E88" t="n">
+        <v>7</v>
+      </c>
+      <c r="F88" t="n">
         <v>3</v>
-      </c>
-      <c r="E88" t="n">
-        <v>1</v>
-      </c>
-      <c r="F88" t="n">
-        <v>8</v>
       </c>
       <c r="G88" t="n">
         <v>3</v>
       </c>
       <c r="H88" t="n">
+        <v>8</v>
+      </c>
+      <c r="I88" t="n">
         <v>3</v>
       </c>
-      <c r="I88" t="n">
-        <v>8</v>
-      </c>
       <c r="J88" t="n">
+        <v>6</v>
+      </c>
+      <c r="K88" t="n">
         <v>3</v>
       </c>
-      <c r="K88" t="n">
-        <v>7</v>
-      </c>
       <c r="L88" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M88" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="89">
@@ -4080,34 +4080,34 @@
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D89" t="n">
         <v>0</v>
       </c>
       <c r="E89" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F89" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G89" t="n">
         <v>1</v>
       </c>
       <c r="H89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I89" t="n">
         <v>2</v>
       </c>
       <c r="J89" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K89" t="n">
         <v>3</v>
       </c>
       <c r="L89" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M89" t="n">
         <v>1</v>
@@ -4121,34 +4121,34 @@
       </c>
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D90" t="n">
         <v>1</v>
       </c>
       <c r="E90" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F90" t="n">
+        <v>0</v>
+      </c>
+      <c r="G90" t="n">
+        <v>4</v>
+      </c>
+      <c r="H90" t="n">
         <v>3</v>
       </c>
-      <c r="G90" t="n">
-        <v>0</v>
-      </c>
-      <c r="H90" t="n">
+      <c r="I90" t="n">
         <v>4</v>
       </c>
-      <c r="I90" t="n">
-        <v>3</v>
-      </c>
       <c r="J90" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K90" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
         <v>0</v>
@@ -4162,10 +4162,10 @@
       </c>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E91" t="n">
         <v>1</v>
@@ -4180,13 +4180,13 @@
         <v>1</v>
       </c>
       <c r="I91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J91" t="n">
         <v>2</v>
       </c>
       <c r="K91" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L91" t="n">
         <v>0</v>
@@ -4201,9 +4201,7 @@
           <t>電機機械右下</t>
         </is>
       </c>
-      <c r="B92" t="n">
-        <v>0</v>
-      </c>
+      <c r="B92" t="inlineStr"/>
       <c r="C92" t="n">
         <v>0</v>
       </c>
@@ -4220,22 +4218,22 @@
         <v>0</v>
       </c>
       <c r="H92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K92" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L92" t="n">
         <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -4252,16 +4250,16 @@
         <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F93" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I93" t="n">
         <v>0</v>
@@ -4270,7 +4268,7 @@
         <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L93" t="n">
         <v>1</v>
@@ -4290,28 +4288,28 @@
         <v>2</v>
       </c>
       <c r="D94" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H94" t="n">
         <v>1</v>
       </c>
       <c r="I94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L94" t="n">
         <v>2</v>
@@ -4328,7 +4326,7 @@
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D95" t="n">
         <v>0</v>
@@ -4369,37 +4367,37 @@
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E96" t="n">
         <v>0</v>
       </c>
       <c r="F96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H96" t="n">
         <v>2</v>
       </c>
       <c r="I96" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L96" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97">
@@ -4449,7 +4447,9 @@
           <t>食品工業右下</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr"/>
+      <c r="B98" t="n">
+        <v>0</v>
+      </c>
       <c r="C98" t="n">
         <v>0</v>
       </c>

--- a/Result/analyze_1.xlsx
+++ b/Result/analyze_1.xlsx
@@ -441,57 +441,57 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-08</t>
         </is>
       </c>
     </row>
@@ -503,37 +503,37 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
         <v>3</v>
       </c>
-      <c r="D2" t="n">
-        <v>1</v>
-      </c>
       <c r="E2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" t="n">
+        <v>7</v>
+      </c>
+      <c r="G2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I2" t="n">
         <v>3</v>
       </c>
-      <c r="F2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G2" t="n">
-        <v>7</v>
-      </c>
-      <c r="H2" t="n">
-        <v>2</v>
-      </c>
-      <c r="I2" t="n">
-        <v>2</v>
-      </c>
       <c r="J2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -542,41 +542,39 @@
           <t>光電業右下</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>0</v>
-      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -593,16 +591,16 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I4" t="n">
         <v>2</v>
@@ -611,13 +609,13 @@
         <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L4" t="n">
         <v>2</v>
       </c>
       <c r="M4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -628,34 +626,34 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -672,10 +670,10 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -713,28 +711,28 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
         <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -751,37 +749,37 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2</v>
+      </c>
+      <c r="L8" t="n">
+        <v>8</v>
+      </c>
+      <c r="M8" t="n">
         <v>3</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>2</v>
-      </c>
-      <c r="I8" t="n">
-        <v>2</v>
-      </c>
-      <c r="J8" t="n">
-        <v>2</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" t="n">
-        <v>2</v>
-      </c>
-      <c r="M8" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -790,23 +788,21 @@
           <t>其他電子業右下</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0</v>
-      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
         <v>1</v>
@@ -815,7 +811,7 @@
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
         <v>1</v>
@@ -835,7 +831,7 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -850,22 +846,22 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
         <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -876,25 +872,25 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" t="n">
         <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -915,9 +911,7 @@
           <t>化學工業右下</t>
         </is>
       </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
         <v>0</v>
       </c>
@@ -940,16 +934,16 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -963,7 +957,7 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -978,16 +972,16 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1004,7 +998,7 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -1019,19 +1013,19 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1040,7 +1034,9 @@
           <t>半導體業右下</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
+      <c r="B15" t="n">
+        <v>0</v>
+      </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
@@ -1051,28 +1047,28 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I15" t="n">
         <v>3</v>
       </c>
       <c r="J15" t="n">
+        <v>2</v>
+      </c>
+      <c r="K15" t="n">
+        <v>4</v>
+      </c>
+      <c r="L15" t="n">
         <v>3</v>
       </c>
-      <c r="K15" t="n">
-        <v>2</v>
-      </c>
-      <c r="L15" t="n">
-        <v>4</v>
-      </c>
       <c r="M15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1083,37 +1079,37 @@
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
         <v>2</v>
       </c>
       <c r="E16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
         <v>3</v>
       </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
       <c r="M16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1168,16 +1164,16 @@
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -1224,10 +1220,10 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1256,10 +1252,10 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -1274,10 +1270,10 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1315,10 +1311,10 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1417,22 +1413,22 @@
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24" t="n">
         <v>1</v>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -1508,19 +1504,19 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -1555,10 +1551,10 @@
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -1584,10 +1580,10 @@
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -1657,10 +1653,10 @@
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -1684,10 +1680,10 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -1713,16 +1709,16 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -1783,10 +1779,10 @@
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -1860,9 +1856,7 @@
           <t>水泥工業右下</t>
         </is>
       </c>
-      <c r="B35" t="n">
-        <v>0</v>
-      </c>
+      <c r="B35" t="inlineStr"/>
       <c r="C35" t="n">
         <v>0</v>
       </c>
@@ -1920,19 +1914,19 @@
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I36" t="n">
         <v>1</v>
       </c>
       <c r="J36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M36" t="n">
         <v>1</v>
@@ -1944,11 +1938,9 @@
           <t>汽車工業右下</t>
         </is>
       </c>
-      <c r="B37" t="n">
-        <v>0</v>
-      </c>
+      <c r="B37" t="inlineStr"/>
       <c r="C37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
@@ -1957,10 +1949,10 @@
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -2007,19 +1999,19 @@
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2039,10 +2031,10 @@
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -2112,22 +2104,22 @@
       </c>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -2174,10 +2166,10 @@
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
@@ -2200,31 +2192,31 @@
         <v>1</v>
       </c>
       <c r="E43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G43" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K43" t="n">
         <v>1</v>
       </c>
       <c r="L43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2233,21 +2225,23 @@
           <t>生技醫療業右下</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr"/>
+      <c r="B44" t="n">
+        <v>0</v>
+      </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D44" t="n">
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -2256,16 +2250,16 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K44" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2276,37 +2270,37 @@
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -2344,7 +2338,7 @@
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M46" t="n">
         <v>1</v>
@@ -2399,10 +2393,10 @@
       </c>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E48" t="n">
         <v>0</v>
@@ -2417,10 +2411,10 @@
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
@@ -2429,7 +2423,7 @@
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -2440,25 +2434,25 @@
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -2467,10 +2461,10 @@
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -2563,10 +2557,10 @@
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E52" t="n">
         <v>0</v>
@@ -2581,16 +2575,16 @@
         <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
         <v>0</v>
@@ -2604,10 +2598,10 @@
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E53" t="n">
         <v>0</v>
@@ -2675,7 +2669,7 @@
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -2692,7 +2686,7 @@
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F55" t="n">
         <v>1</v>
@@ -2701,7 +2695,7 @@
         <v>1</v>
       </c>
       <c r="H55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I55" t="n">
         <v>0</v>
@@ -2727,7 +2721,7 @@
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D56" t="n">
         <v>0</v>
@@ -2742,10 +2736,10 @@
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -2815,10 +2809,10 @@
         <v>0</v>
       </c>
       <c r="E58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -2979,10 +2973,10 @@
         <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2991,13 +2985,13 @@
         <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J62" t="n">
         <v>1</v>
       </c>
       <c r="K62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
@@ -3096,13 +3090,13 @@
       </c>
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D65" t="n">
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F65" t="n">
         <v>1</v>
@@ -3114,19 +3108,19 @@
         <v>2</v>
       </c>
       <c r="I65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L65" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M65" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -3155,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="I66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J66" t="n">
         <v>2</v>
       </c>
       <c r="K66" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
@@ -3178,37 +3172,37 @@
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -3219,10 +3213,10 @@
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E68" t="n">
         <v>0</v>
@@ -3360,16 +3354,16 @@
         <v>0</v>
       </c>
       <c r="I71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
         <v>0</v>
@@ -3463,7 +3457,9 @@
           <t>金融保險右下</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr"/>
+      <c r="B74" t="n">
+        <v>0</v>
+      </c>
       <c r="C74" t="n">
         <v>0</v>
       </c>
@@ -3697,7 +3693,7 @@
         <v>0</v>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M79" t="n">
         <v>1</v>
@@ -3726,19 +3722,19 @@
         <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
         <v>0</v>
@@ -3811,16 +3807,16 @@
         <v>0</v>
       </c>
       <c r="I82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
         <v>0</v>
@@ -3843,10 +3839,10 @@
         <v>0</v>
       </c>
       <c r="F83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
@@ -3899,13 +3895,13 @@
         <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L84" t="n">
         <v>1</v>
       </c>
       <c r="M84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -3925,13 +3921,13 @@
         <v>0</v>
       </c>
       <c r="F85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G85" t="n">
         <v>1</v>
       </c>
       <c r="H85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I85" t="n">
         <v>0</v>
@@ -3940,13 +3936,13 @@
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
@@ -3975,13 +3971,13 @@
         <v>0</v>
       </c>
       <c r="I86" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J86" t="n">
         <v>2</v>
       </c>
       <c r="K86" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L86" t="n">
         <v>0</v>
@@ -3998,10 +3994,10 @@
       </c>
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E87" t="n">
         <v>0</v>
@@ -4019,13 +4015,13 @@
         <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K87" t="n">
         <v>1</v>
       </c>
       <c r="L87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
         <v>0</v>
@@ -4039,37 +4035,37 @@
       </c>
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="n">
+        <v>0</v>
+      </c>
+      <c r="D88" t="n">
+        <v>7</v>
+      </c>
+      <c r="E88" t="n">
         <v>3</v>
       </c>
-      <c r="D88" t="n">
-        <v>0</v>
-      </c>
-      <c r="E88" t="n">
-        <v>7</v>
-      </c>
       <c r="F88" t="n">
+        <v>4</v>
+      </c>
+      <c r="G88" t="n">
+        <v>8</v>
+      </c>
+      <c r="H88" t="n">
         <v>3</v>
       </c>
-      <c r="G88" t="n">
-        <v>3</v>
-      </c>
-      <c r="H88" t="n">
+      <c r="I88" t="n">
+        <v>6</v>
+      </c>
+      <c r="J88" t="n">
+        <v>4</v>
+      </c>
+      <c r="K88" t="n">
+        <v>5</v>
+      </c>
+      <c r="L88" t="n">
+        <v>4</v>
+      </c>
+      <c r="M88" t="n">
         <v>8</v>
-      </c>
-      <c r="I88" t="n">
-        <v>3</v>
-      </c>
-      <c r="J88" t="n">
-        <v>6</v>
-      </c>
-      <c r="K88" t="n">
-        <v>3</v>
-      </c>
-      <c r="L88" t="n">
-        <v>5</v>
-      </c>
-      <c r="M88" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="89">
@@ -4083,34 +4079,34 @@
         <v>0</v>
       </c>
       <c r="D89" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E89" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F89" t="n">
         <v>1</v>
       </c>
       <c r="G89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H89" t="n">
         <v>2</v>
       </c>
       <c r="I89" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J89" t="n">
         <v>3</v>
       </c>
       <c r="K89" t="n">
+        <v>1</v>
+      </c>
+      <c r="L89" t="n">
+        <v>1</v>
+      </c>
+      <c r="M89" t="n">
         <v>3</v>
-      </c>
-      <c r="L89" t="n">
-        <v>1</v>
-      </c>
-      <c r="M89" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="90">
@@ -4124,28 +4120,28 @@
         <v>1</v>
       </c>
       <c r="D90" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E90" t="n">
+        <v>0</v>
+      </c>
+      <c r="F90" t="n">
+        <v>3</v>
+      </c>
+      <c r="G90" t="n">
+        <v>3</v>
+      </c>
+      <c r="H90" t="n">
         <v>4</v>
       </c>
-      <c r="F90" t="n">
-        <v>0</v>
-      </c>
-      <c r="G90" t="n">
-        <v>4</v>
-      </c>
-      <c r="H90" t="n">
-        <v>3</v>
-      </c>
       <c r="I90" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J90" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L90" t="n">
         <v>0</v>
@@ -4162,7 +4158,7 @@
       </c>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D91" t="n">
         <v>1</v>
@@ -4177,13 +4173,13 @@
         <v>1</v>
       </c>
       <c r="H91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I91" t="n">
         <v>2</v>
       </c>
       <c r="J91" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K91" t="n">
         <v>0</v>
@@ -4192,7 +4188,7 @@
         <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="92">
@@ -4215,19 +4211,19 @@
         <v>0</v>
       </c>
       <c r="G92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I92" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J92" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L92" t="n">
         <v>0</v>
@@ -4247,16 +4243,16 @@
         <v>0</v>
       </c>
       <c r="D93" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E93" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H93" t="n">
         <v>0</v>
@@ -4265,16 +4261,16 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">
@@ -4285,28 +4281,28 @@
       </c>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G94" t="n">
         <v>1</v>
       </c>
       <c r="H94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K94" t="n">
         <v>2</v>
@@ -4315,7 +4311,7 @@
         <v>2</v>
       </c>
       <c r="M94" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="95">
@@ -4326,7 +4322,7 @@
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D95" t="n">
         <v>0</v>
@@ -4356,7 +4352,7 @@
         <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
@@ -4373,31 +4369,31 @@
         <v>0</v>
       </c>
       <c r="E96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G96" t="n">
         <v>2</v>
       </c>
       <c r="H96" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J96" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K96" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -4447,9 +4443,7 @@
           <t>食品工業右下</t>
         </is>
       </c>
-      <c r="B98" t="n">
-        <v>0</v>
-      </c>
+      <c r="B98" t="inlineStr"/>
       <c r="C98" t="n">
         <v>0</v>
       </c>

--- a/Result/analyze_1.xlsx
+++ b/Result/analyze_1.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M99"/>
+  <dimension ref="A1:M101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,57 +441,57 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-11</t>
         </is>
       </c>
     </row>
@@ -503,37 +503,37 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" t="n">
+        <v>7</v>
+      </c>
+      <c r="F2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G2" t="n">
         <v>3</v>
       </c>
-      <c r="E2" t="n">
-        <v>2</v>
-      </c>
-      <c r="F2" t="n">
-        <v>7</v>
-      </c>
-      <c r="G2" t="n">
-        <v>2</v>
-      </c>
       <c r="H2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L2" t="n">
         <v>3</v>
       </c>
-      <c r="J2" t="n">
-        <v>2</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
       <c r="M2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -544,37 +544,37 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -585,16 +585,16 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
@@ -603,19 +603,19 @@
         <v>2</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -626,37 +626,37 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -667,10 +667,10 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -711,25 +711,25 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -749,37 +749,37 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
         <v>3</v>
       </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>2</v>
-      </c>
-      <c r="H8" t="n">
-        <v>2</v>
-      </c>
-      <c r="I8" t="n">
-        <v>2</v>
-      </c>
-      <c r="J8" t="n">
-        <v>2</v>
-      </c>
       <c r="K8" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="L8" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="M8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -788,18 +788,20 @@
           <t>其他電子業右下</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
         <v>1</v>
@@ -820,7 +822,7 @@
         <v>1</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -843,7 +845,7 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
         <v>1</v>
@@ -855,13 +857,13 @@
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -872,25 +874,25 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
         <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -937,10 +939,10 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -957,7 +959,7 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -969,19 +971,19 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -995,7 +997,7 @@
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -1010,22 +1012,22 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K14" t="n">
+        <v>5</v>
+      </c>
+      <c r="L14" t="n">
         <v>3</v>
       </c>
-      <c r="L14" t="n">
-        <v>5</v>
-      </c>
       <c r="M14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -1044,31 +1046,31 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" t="n">
+        <v>3</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2</v>
+      </c>
+      <c r="J15" t="n">
         <v>4</v>
       </c>
-      <c r="G15" t="n">
-        <v>2</v>
-      </c>
-      <c r="H15" t="n">
+      <c r="K15" t="n">
         <v>3</v>
       </c>
-      <c r="I15" t="n">
-        <v>3</v>
-      </c>
-      <c r="J15" t="n">
-        <v>2</v>
-      </c>
-      <c r="K15" t="n">
-        <v>4</v>
-      </c>
       <c r="L15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1082,31 +1084,31 @@
         <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" t="n">
         <v>1</v>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H16" t="n">
+        <v>2</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
         <v>3</v>
       </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
       <c r="L16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
         <v>1</v>
@@ -1161,16 +1163,16 @@
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -1191,7 +1193,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1217,10 +1219,10 @@
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1249,10 +1251,10 @@
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -1267,10 +1269,10 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -1308,10 +1310,10 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -1410,22 +1412,22 @@
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24" t="n">
         <v>1</v>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1501,19 +1503,19 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H26" t="n">
         <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
       </c>
       <c r="K26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -1548,10 +1550,10 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -1577,22 +1579,22 @@
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -1601,7 +1603,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -1653,7 +1655,7 @@
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -1677,13 +1679,13 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -1706,16 +1708,16 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -1730,12 +1732,12 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>橡膠工業右上</t>
+          <t>橡膠工業右下</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
@@ -1771,7 +1773,7 @@
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>橡膠工業右下</t>
+          <t>橡膠工業平</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -1779,7 +1781,7 @@
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -1812,7 +1814,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>橡膠工業平</t>
+          <t>水泥工業右下</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -1853,7 +1855,7 @@
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>水泥工業右下</t>
+          <t>水泥工業平</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -1911,25 +1913,25 @@
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H36" t="n">
         <v>1</v>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L36" t="n">
         <v>1</v>
       </c>
       <c r="M36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -1946,10 +1948,10 @@
         <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1996,28 +1998,28 @@
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>油電燃氣業右下</t>
+          <t>油電燃氣業右上</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -2031,7 +2033,7 @@
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -2058,7 +2060,7 @@
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>油電燃氣業平</t>
+          <t>油電燃氣業右下</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -2069,7 +2071,7 @@
         <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
@@ -2099,7 +2101,7 @@
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>玻璃陶瓷右上</t>
+          <t>油電燃氣業平</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -2107,7 +2109,7 @@
         <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
@@ -2116,7 +2118,7 @@
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -2140,12 +2142,12 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>玻璃陶瓷平</t>
+          <t>玻璃陶瓷右上</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D42" t="n">
         <v>0</v>
@@ -2154,7 +2156,7 @@
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -2166,7 +2168,7 @@
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -2181,21 +2183,21 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>生技醫療業右上</t>
+          <t>玻璃陶瓷右下</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E43" t="n">
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -2204,41 +2206,39 @@
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>生技醫療業右下</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
-        <v>0</v>
-      </c>
+          <t>玻璃陶瓷平</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr"/>
       <c r="C44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -2247,16 +2247,16 @@
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J44" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
@@ -2265,59 +2265,59 @@
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>生技醫療業平</t>
+          <t>生技醫療業右上</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I45" t="n">
         <v>1</v>
       </c>
       <c r="J45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>紡織纖維右上</t>
+          <t>生技醫療業右下</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D46" t="n">
         <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
@@ -2326,42 +2326,42 @@
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>紡織纖維右下</t>
+          <t>生技醫療業平</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D47" t="n">
         <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -2370,7 +2370,7 @@
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -2379,7 +2379,7 @@
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
@@ -2388,12 +2388,12 @@
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>紡織纖維平</t>
+          <t>紡織纖維右上</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
@@ -2411,25 +2411,25 @@
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>綠能環保右上</t>
+          <t>紡織纖維右下</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -2437,10 +2437,10 @@
         <v>0</v>
       </c>
       <c r="D49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -2449,7 +2449,7 @@
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I49" t="n">
         <v>0</v>
@@ -2461,7 +2461,7 @@
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
         <v>0</v>
@@ -2470,7 +2470,7 @@
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>綠能環保右下</t>
+          <t>紡織纖維平</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -2490,7 +2490,7 @@
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I50" t="n">
         <v>0</v>
@@ -2502,7 +2502,7 @@
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M50" t="n">
         <v>0</v>
@@ -2511,15 +2511,15 @@
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>綠能環保平</t>
+          <t>綠能環保右上</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E51" t="n">
         <v>0</v>
@@ -2540,7 +2540,7 @@
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
@@ -2552,12 +2552,12 @@
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>航運業右上</t>
+          <t>綠能環保右下</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D52" t="n">
         <v>0</v>
@@ -2575,13 +2575,13 @@
         <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
@@ -2593,12 +2593,12 @@
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>航運業右下</t>
+          <t>綠能環保平</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D53" t="n">
         <v>0</v>
@@ -2610,7 +2610,7 @@
         <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
@@ -2634,7 +2634,7 @@
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>航運業平</t>
+          <t>航運業右上</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
@@ -2654,13 +2654,13 @@
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K54" t="n">
         <v>0</v>
@@ -2669,13 +2669,13 @@
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>觀光事業右上</t>
+          <t>航運業右下</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
@@ -2686,13 +2686,13 @@
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
@@ -2716,7 +2716,7 @@
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>觀光事業右下</t>
+          <t>航運業平</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
@@ -2736,7 +2736,7 @@
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I56" t="n">
         <v>0</v>
@@ -2748,16 +2748,16 @@
         <v>0</v>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>觀光事業平</t>
+          <t>觀光事業右上</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
@@ -2765,13 +2765,13 @@
         <v>0</v>
       </c>
       <c r="D57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -2798,7 +2798,7 @@
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>貿易百貨右下</t>
+          <t>觀光事業右下</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
@@ -2809,13 +2809,13 @@
         <v>0</v>
       </c>
       <c r="E58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F58" t="n">
         <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
@@ -2833,13 +2833,13 @@
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>貿易百貨平</t>
+          <t>觀光事業平</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -2880,7 +2880,7 @@
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>資訊服務業右上</t>
+          <t>貿易百貨右下</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -2888,7 +2888,7 @@
         <v>0</v>
       </c>
       <c r="D60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E60" t="n">
         <v>0</v>
@@ -2921,7 +2921,7 @@
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>資訊服務業右下</t>
+          <t>貿易百貨平</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
@@ -2962,7 +2962,7 @@
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>資訊服務業平</t>
+          <t>資訊服務業右上</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
@@ -2973,7 +2973,7 @@
         <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F62" t="n">
         <v>0</v>
@@ -2985,10 +2985,10 @@
         <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K62" t="n">
         <v>0</v>
@@ -2997,13 +2997,13 @@
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>農業科技業右上</t>
+          <t>資訊服務業右下</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
@@ -3044,7 +3044,7 @@
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>農業科技業右下</t>
+          <t>資訊服務業平</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
@@ -3052,7 +3052,7 @@
         <v>0</v>
       </c>
       <c r="D64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E64" t="n">
         <v>0</v>
@@ -3064,10 +3064,10 @@
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -3085,7 +3085,7 @@
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>通信網路業右上</t>
+          <t>農業科技業右上</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
@@ -3093,40 +3093,40 @@
         <v>0</v>
       </c>
       <c r="D65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E65" t="n">
         <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G65" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L65" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>通信網路業右下</t>
+          <t>農業科技業右下</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="I66" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J66" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K66" t="n">
         <v>0</v>
@@ -3167,53 +3167,55 @@
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>通信網路業平</t>
+          <t>通信網路業右上</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F67" t="n">
         <v>2</v>
       </c>
       <c r="G67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K67" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>造紙工業右下</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr"/>
+          <t>通信網路業右下</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>0</v>
+      </c>
       <c r="C68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D68" t="n">
         <v>0</v>
@@ -3228,10 +3230,10 @@
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -3249,48 +3251,48 @@
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>造紙工業平</t>
+          <t>通信網路業平</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F69" t="n">
         <v>0</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L69" t="n">
         <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>運動休閒右上</t>
+          <t>造紙工業右下</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
@@ -3331,7 +3333,7 @@
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>運動休閒右下</t>
+          <t>造紙工業平</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
@@ -3354,13 +3356,13 @@
         <v>0</v>
       </c>
       <c r="I71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
@@ -3372,7 +3374,7 @@
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>運動休閒平</t>
+          <t>運動休閒右上</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
@@ -3413,7 +3415,7 @@
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>金融保險右上</t>
+          <t>運動休閒右下</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
@@ -3433,13 +3435,13 @@
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I73" t="n">
         <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>
@@ -3454,12 +3456,10 @@
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>金融保險右下</t>
-        </is>
-      </c>
-      <c r="B74" t="n">
-        <v>0</v>
-      </c>
+          <t>運動休閒平</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr"/>
       <c r="C74" t="n">
         <v>0</v>
       </c>
@@ -3497,7 +3497,7 @@
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>金融保險平</t>
+          <t>金融保險右上</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
@@ -3538,7 +3538,7 @@
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>金融業右上</t>
+          <t>金融保險右下</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
@@ -3579,7 +3579,7 @@
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>金融業右下</t>
+          <t>金融保險平</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
@@ -3620,7 +3620,7 @@
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>金融業平</t>
+          <t>金融業右上</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
@@ -3661,7 +3661,7 @@
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業右上</t>
+          <t>金融業右下</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
@@ -3693,16 +3693,16 @@
         <v>0</v>
       </c>
       <c r="L79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業右下</t>
+          <t>金融業平</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
@@ -3722,7 +3722,7 @@
         <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I80" t="n">
         <v>0</v>
@@ -3731,7 +3731,7 @@
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L80" t="n">
         <v>0</v>
@@ -3743,7 +3743,7 @@
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業平</t>
+          <t>鋼鐵工業右上</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
@@ -3772,10 +3772,10 @@
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M81" t="n">
         <v>0</v>
@@ -3784,10 +3784,12 @@
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>電器電纜右上</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr"/>
+          <t>鋼鐵工業右下</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>0</v>
+      </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
@@ -3801,19 +3803,19 @@
         <v>0</v>
       </c>
       <c r="G82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H82" t="n">
         <v>0</v>
       </c>
       <c r="I82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L82" t="n">
         <v>0</v>
@@ -3825,7 +3827,7 @@
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>電器電纜右下</t>
+          <t>鋼鐵工業平</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
@@ -3839,7 +3841,7 @@
         <v>0</v>
       </c>
       <c r="F83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -3860,13 +3862,13 @@
         <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>電器電纜平</t>
+          <t>電器電纜右上</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
@@ -3886,19 +3888,19 @@
         <v>0</v>
       </c>
       <c r="H84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I84" t="n">
         <v>0</v>
       </c>
       <c r="J84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
         <v>0</v>
@@ -3907,7 +3909,7 @@
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>電子通路業右上</t>
+          <t>電器電纜右下</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
@@ -3918,13 +3920,13 @@
         <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H85" t="n">
         <v>0</v>
@@ -3936,19 +3938,19 @@
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L85" t="n">
         <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>電子通路業右下</t>
+          <t>電器電纜平</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
@@ -3971,13 +3973,13 @@
         <v>0</v>
       </c>
       <c r="I86" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L86" t="n">
         <v>0</v>
@@ -3989,21 +3991,21 @@
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>電子通路業平</t>
+          <t>電子通路業右上</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D87" t="n">
         <v>0</v>
       </c>
       <c r="E87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -4018,10 +4020,10 @@
         <v>1</v>
       </c>
       <c r="K87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M87" t="n">
         <v>0</v>
@@ -4030,7 +4032,7 @@
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業右上</t>
+          <t>電子通路業右下</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
@@ -4038,40 +4040,40 @@
         <v>0</v>
       </c>
       <c r="D88" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E88" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F88" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G88" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H88" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I88" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J88" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L88" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業右下</t>
+          <t>電子通路業平</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
@@ -4079,204 +4081,206 @@
         <v>0</v>
       </c>
       <c r="D89" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G89" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I89" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J89" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業平</t>
+          <t>電子零組件業右上</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D90" t="n">
+        <v>3</v>
+      </c>
+      <c r="E90" t="n">
         <v>4</v>
       </c>
-      <c r="E90" t="n">
-        <v>0</v>
-      </c>
       <c r="F90" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G90" t="n">
         <v>3</v>
       </c>
       <c r="H90" t="n">
+        <v>6</v>
+      </c>
+      <c r="I90" t="n">
         <v>4</v>
       </c>
-      <c r="I90" t="n">
+      <c r="J90" t="n">
         <v>5</v>
       </c>
-      <c r="J90" t="n">
-        <v>0</v>
-      </c>
       <c r="K90" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>電機機械右上</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr"/>
+          <t>電子零組件業右下</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>0</v>
+      </c>
       <c r="C91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D91" t="n">
         <v>1</v>
       </c>
       <c r="E91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G91" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H91" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I91" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M91" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>電機機械右下</t>
+          <t>電子零組件業平</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D92" t="n">
         <v>0</v>
       </c>
       <c r="E92" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F92" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G92" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H92" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I92" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L92" t="n">
         <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>電機機械平</t>
+          <t>電機機械右上</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D93" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E93" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F93" t="n">
         <v>1</v>
       </c>
       <c r="G93" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H93" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I93" t="n">
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K93" t="n">
         <v>0</v>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M93" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右上</t>
+          <t>電機機械右下</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
@@ -4284,7 +4288,7 @@
         <v>0</v>
       </c>
       <c r="D94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E94" t="n">
         <v>0</v>
@@ -4293,31 +4297,31 @@
         <v>1</v>
       </c>
       <c r="G94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H94" t="n">
         <v>2</v>
       </c>
       <c r="I94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K94" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L94" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右下</t>
+          <t>電機機械平</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
@@ -4340,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="I95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -4352,18 +4356,18 @@
         <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業平</t>
+          <t>電腦及週邊設備業右上</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D96" t="n">
         <v>0</v>
@@ -4372,7 +4376,7 @@
         <v>1</v>
       </c>
       <c r="F96" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G96" t="n">
         <v>2</v>
@@ -4381,25 +4385,25 @@
         <v>1</v>
       </c>
       <c r="I96" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J96" t="n">
         <v>2</v>
       </c>
       <c r="K96" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L96" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>食品工業右上</t>
+          <t>電腦及週邊設備業右下</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
@@ -4431,7 +4435,7 @@
         <v>0</v>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M97" t="n">
         <v>0</v>
@@ -4440,7 +4444,7 @@
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>食品工業右下</t>
+          <t>電腦及週邊設備業平</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
@@ -4448,28 +4452,28 @@
         <v>0</v>
       </c>
       <c r="D98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E98" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F98" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H98" t="n">
         <v>0</v>
       </c>
       <c r="I98" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
       </c>
       <c r="K98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L98" t="n">
         <v>0</v>
@@ -4481,7 +4485,7 @@
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>食品工業平</t>
+          <t>食品工業右上</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
@@ -4517,6 +4521,88 @@
       </c>
       <c r="M99" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="inlineStr">
+        <is>
+          <t>食品工業右下</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr"/>
+      <c r="C100" t="n">
+        <v>0</v>
+      </c>
+      <c r="D100" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" t="n">
+        <v>0</v>
+      </c>
+      <c r="G100" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" t="n">
+        <v>0</v>
+      </c>
+      <c r="K100" t="n">
+        <v>0</v>
+      </c>
+      <c r="L100" t="n">
+        <v>0</v>
+      </c>
+      <c r="M100" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="inlineStr">
+        <is>
+          <t>食品工業平</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr"/>
+      <c r="C101" t="n">
+        <v>0</v>
+      </c>
+      <c r="D101" t="n">
+        <v>0</v>
+      </c>
+      <c r="E101" t="n">
+        <v>0</v>
+      </c>
+      <c r="F101" t="n">
+        <v>0</v>
+      </c>
+      <c r="G101" t="n">
+        <v>0</v>
+      </c>
+      <c r="H101" t="n">
+        <v>0</v>
+      </c>
+      <c r="I101" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" t="n">
+        <v>0</v>
+      </c>
+      <c r="K101" t="n">
+        <v>0</v>
+      </c>
+      <c r="L101" t="n">
+        <v>0</v>
+      </c>
+      <c r="M101" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Result/analyze_1.xlsx
+++ b/Result/analyze_1.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M101"/>
+  <dimension ref="A1:M100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,57 +441,57 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-13</t>
         </is>
       </c>
     </row>
@@ -503,28 +503,28 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
         <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G2" t="n">
         <v>3</v>
       </c>
       <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J2" t="n">
         <v>3</v>
-      </c>
-      <c r="I2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1</v>
       </c>
       <c r="K2" t="n">
         <v>2</v>
@@ -533,7 +533,7 @@
         <v>3</v>
       </c>
       <c r="M2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -544,37 +544,37 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
         <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -591,31 +591,31 @@
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -626,37 +626,37 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
         <v>2</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -667,7 +667,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -697,7 +697,7 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -708,25 +708,25 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -749,37 +749,37 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" t="n">
         <v>3</v>
       </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>2</v>
-      </c>
-      <c r="G8" t="n">
-        <v>2</v>
-      </c>
-      <c r="H8" t="n">
-        <v>2</v>
-      </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J8" t="n">
         <v>3</v>
       </c>
       <c r="K8" t="n">
+        <v>4</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
         <v>8</v>
-      </c>
-      <c r="L8" t="n">
-        <v>3</v>
-      </c>
-      <c r="M8" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -788,17 +788,15 @@
           <t>其他電子業右下</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0</v>
-      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
         <v>1</v>
@@ -816,13 +814,13 @@
         <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L9" t="n">
         <v>1</v>
       </c>
       <c r="M9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -839,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
         <v>1</v>
@@ -851,19 +849,19 @@
         <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -877,10 +875,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>1</v>
@@ -901,10 +899,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -924,7 +922,7 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -933,13 +931,13 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -971,22 +969,22 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1006,22 +1004,22 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J14" t="n">
         <v>3</v>
       </c>
       <c r="K14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L14" t="n">
         <v>3</v>
@@ -1040,37 +1038,37 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" t="n">
         <v>3</v>
       </c>
-      <c r="H15" t="n">
-        <v>1</v>
-      </c>
       <c r="I15" t="n">
         <v>2</v>
       </c>
       <c r="J15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1084,31 +1082,31 @@
         <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M16" t="n">
         <v>1</v>
@@ -1163,13 +1161,13 @@
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -1187,13 +1185,13 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1213,13 +1211,13 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -1231,7 +1229,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -1245,13 +1243,13 @@
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -1263,16 +1261,16 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -1304,13 +1302,13 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -1395,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -1412,19 +1410,19 @@
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -1436,10 +1434,10 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1480,7 +1478,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1497,31 +1495,31 @@
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G26" t="n">
         <v>1</v>
       </c>
       <c r="H26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1530,7 +1528,9 @@
           <t>數位雲端右下</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr"/>
+      <c r="B27" t="n">
+        <v>0</v>
+      </c>
       <c r="C27" t="n">
         <v>0</v>
       </c>
@@ -1544,13 +1544,13 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1573,13 +1573,13 @@
       </c>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
@@ -1588,13 +1588,13 @@
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -1603,7 +1603,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -1673,7 +1673,7 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1682,7 +1682,7 @@
         <v>1</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30" t="n">
         <v>1</v>
@@ -1702,19 +1702,19 @@
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G31" t="n">
         <v>1</v>
       </c>
       <c r="H31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1737,7 +1737,7 @@
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
@@ -1907,31 +1907,31 @@
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -1940,15 +1940,17 @@
           <t>汽車工業右下</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr"/>
+      <c r="B37" t="n">
+        <v>0</v>
+      </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
@@ -1969,7 +1971,7 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
@@ -1992,16 +1994,16 @@
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2013,7 +2015,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2063,15 +2065,17 @@
           <t>油電燃氣業右下</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr"/>
+      <c r="B40" t="n">
+        <v>0</v>
+      </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D40" t="n">
         <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
@@ -2147,19 +2151,19 @@
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -2174,16 +2178,16 @@
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>玻璃陶瓷右下</t>
+          <t>玻璃陶瓷平</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -2215,48 +2219,48 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>玻璃陶瓷平</t>
+          <t>生技醫療業右上</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
@@ -2265,10 +2269,12 @@
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>生技醫療業右上</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr"/>
+          <t>生技醫療業右下</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>0</v>
+      </c>
       <c r="C45" t="n">
         <v>1</v>
       </c>
@@ -2276,69 +2282,69 @@
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L45" t="n">
         <v>1</v>
       </c>
       <c r="M45" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>生技醫療業右下</t>
+          <t>生技醫療業平</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D46" t="n">
         <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -2347,21 +2353,21 @@
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>生技醫療業平</t>
+          <t>紡織纖維右上</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D47" t="n">
         <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -2370,16 +2376,16 @@
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
@@ -2388,7 +2394,7 @@
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>紡織纖維右上</t>
+          <t>紡織纖維右下</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -2417,19 +2423,19 @@
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>紡織纖維右下</t>
+          <t>紡織纖維平</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -2443,7 +2449,7 @@
         <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -2455,7 +2461,7 @@
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
@@ -2470,7 +2476,7 @@
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>紡織纖維平</t>
+          <t>綠能環保右上</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -2490,10 +2496,10 @@
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -2502,7 +2508,7 @@
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
         <v>0</v>
@@ -2511,15 +2517,17 @@
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>綠能環保右上</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr"/>
+          <t>綠能環保右下</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>0</v>
+      </c>
       <c r="C51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D51" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E51" t="n">
         <v>0</v>
@@ -2540,7 +2548,7 @@
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
@@ -2552,7 +2560,7 @@
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>綠能環保右下</t>
+          <t>綠能環保平</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -2563,7 +2571,7 @@
         <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F52" t="n">
         <v>0</v>
@@ -2593,7 +2601,7 @@
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>綠能環保平</t>
+          <t>航運業右上</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
@@ -2607,13 +2615,13 @@
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I53" t="n">
         <v>0</v>
@@ -2622,10 +2630,10 @@
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M53" t="n">
         <v>0</v>
@@ -2634,7 +2642,7 @@
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>航運業右上</t>
+          <t>航運業右下</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
@@ -2654,13 +2662,13 @@
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K54" t="n">
         <v>0</v>
@@ -2669,13 +2677,13 @@
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>航運業右下</t>
+          <t>航運業平</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
@@ -2701,10 +2709,10 @@
         <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
@@ -2716,15 +2724,15 @@
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>航運業平</t>
+          <t>觀光事業右上</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E56" t="n">
         <v>0</v>
@@ -2751,13 +2759,13 @@
         <v>1</v>
       </c>
       <c r="M56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>觀光事業右上</t>
+          <t>觀光事業右下</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
@@ -2765,13 +2773,13 @@
         <v>0</v>
       </c>
       <c r="D57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E57" t="n">
         <v>1</v>
       </c>
       <c r="F57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -2786,7 +2794,7 @@
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
@@ -2798,7 +2806,7 @@
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>觀光事業右下</t>
+          <t>觀光事業平</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
@@ -2815,7 +2823,7 @@
         <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
@@ -2833,13 +2841,13 @@
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>觀光事業平</t>
+          <t>貿易百貨右下</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -2880,7 +2888,7 @@
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>貿易百貨右下</t>
+          <t>貿易百貨平</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -2888,7 +2896,7 @@
         <v>0</v>
       </c>
       <c r="D60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E60" t="n">
         <v>0</v>
@@ -2921,7 +2929,7 @@
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>貿易百貨平</t>
+          <t>資訊服務業右上</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
@@ -2950,19 +2958,19 @@
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>資訊服務業右上</t>
+          <t>資訊服務業右下</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
@@ -2997,13 +3005,13 @@
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>資訊服務業右下</t>
+          <t>資訊服務業平</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
@@ -3017,10 +3025,10 @@
         <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
@@ -3035,7 +3043,7 @@
         <v>0</v>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M63" t="n">
         <v>0</v>
@@ -3044,7 +3052,7 @@
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>資訊服務業平</t>
+          <t>農業科技業右上</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
@@ -3052,7 +3060,7 @@
         <v>0</v>
       </c>
       <c r="D64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E64" t="n">
         <v>0</v>
@@ -3064,10 +3072,10 @@
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -3085,7 +3093,7 @@
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>農業科技業右上</t>
+          <t>農業科技業右下</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
@@ -3126,59 +3134,59 @@
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>農業科技業右下</t>
+          <t>通信網路業右上</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I66" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K66" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>通信網路業右上</t>
+          <t>通信網路業右下</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D67" t="n">
         <v>0</v>
       </c>
       <c r="E67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F67" t="n">
         <v>2</v>
@@ -3187,50 +3195,48 @@
         <v>2</v>
       </c>
       <c r="H67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I67" t="n">
         <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L67" t="n">
         <v>1</v>
       </c>
       <c r="M67" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>通信網路業右下</t>
-        </is>
-      </c>
-      <c r="B68" t="n">
-        <v>0</v>
-      </c>
+          <t>通信網路業平</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr"/>
       <c r="C68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D68" t="n">
         <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I68" t="n">
         <v>2</v>
@@ -3239,10 +3245,10 @@
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M68" t="n">
         <v>0</v>
@@ -3251,48 +3257,48 @@
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>通信網路業平</t>
+          <t>造紙工業右下</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F69" t="n">
         <v>0</v>
       </c>
       <c r="G69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L69" t="n">
         <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>造紙工業右下</t>
+          <t>造紙工業平</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
@@ -3333,7 +3339,7 @@
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>造紙工業平</t>
+          <t>運動休閒右上</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
@@ -3374,7 +3380,7 @@
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>運動休閒右上</t>
+          <t>運動休閒右下</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
@@ -3388,13 +3394,13 @@
         <v>0</v>
       </c>
       <c r="F72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I72" t="n">
         <v>0</v>
@@ -3415,7 +3421,7 @@
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>運動休閒右下</t>
+          <t>運動休閒平</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
@@ -3435,13 +3441,13 @@
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I73" t="n">
         <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>
@@ -3456,7 +3462,7 @@
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>運動休閒平</t>
+          <t>金融保險右上</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
@@ -3497,7 +3503,7 @@
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>金融保險右上</t>
+          <t>金融保險右下</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
@@ -3538,7 +3544,7 @@
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>金融保險右下</t>
+          <t>金融保險平</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
@@ -3579,7 +3585,7 @@
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>金融保險平</t>
+          <t>金融業右上</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
@@ -3620,7 +3626,7 @@
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>金融業右上</t>
+          <t>金融業右下</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
@@ -3661,7 +3667,7 @@
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>金融業右下</t>
+          <t>金融業平</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
@@ -3702,7 +3708,7 @@
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>金融業平</t>
+          <t>鋼鐵工業右上</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
@@ -3725,7 +3731,7 @@
         <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -3743,7 +3749,7 @@
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業右上</t>
+          <t>鋼鐵工業右下</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
@@ -3754,7 +3760,7 @@
         <v>0</v>
       </c>
       <c r="E81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F81" t="n">
         <v>0</v>
@@ -3763,7 +3769,7 @@
         <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I81" t="n">
         <v>0</v>
@@ -3772,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
         <v>0</v>
@@ -3784,12 +3790,10 @@
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業右下</t>
-        </is>
-      </c>
-      <c r="B82" t="n">
-        <v>0</v>
-      </c>
+          <t>鋼鐵工業平</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr"/>
       <c r="C82" t="n">
         <v>0</v>
       </c>
@@ -3803,7 +3807,7 @@
         <v>0</v>
       </c>
       <c r="G82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H82" t="n">
         <v>0</v>
@@ -3815,7 +3819,7 @@
         <v>1</v>
       </c>
       <c r="K82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L82" t="n">
         <v>0</v>
@@ -3827,7 +3831,7 @@
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業平</t>
+          <t>電器電纜右上</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
@@ -3841,13 +3845,13 @@
         <v>0</v>
       </c>
       <c r="F83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
       </c>
       <c r="H83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I83" t="n">
         <v>0</v>
@@ -3862,18 +3866,18 @@
         <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>電器電纜右上</t>
+          <t>電器電纜右下</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
       <c r="C84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D84" t="n">
         <v>0</v>
@@ -3888,13 +3892,13 @@
         <v>0</v>
       </c>
       <c r="H84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I84" t="n">
         <v>0</v>
       </c>
       <c r="J84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K84" t="n">
         <v>0</v>
@@ -3909,7 +3913,7 @@
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>電器電纜右下</t>
+          <t>電器電纜平</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
@@ -3920,7 +3924,7 @@
         <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F85" t="n">
         <v>0</v>
@@ -3929,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="H85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -3950,15 +3954,15 @@
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>電器電纜平</t>
+          <t>電子通路業右上</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
       <c r="C86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E86" t="n">
         <v>0</v>
@@ -3970,7 +3974,7 @@
         <v>0</v>
       </c>
       <c r="H86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I86" t="n">
         <v>0</v>
@@ -3979,10 +3983,10 @@
         <v>1</v>
       </c>
       <c r="K86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M86" t="n">
         <v>0</v>
@@ -3991,7 +3995,7 @@
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>電子通路業右上</t>
+          <t>電子通路業右下</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
@@ -4002,13 +4006,13 @@
         <v>0</v>
       </c>
       <c r="E87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G87" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H87" t="n">
         <v>0</v>
@@ -4017,13 +4021,13 @@
         <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K87" t="n">
         <v>0</v>
       </c>
       <c r="L87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
         <v>0</v>
@@ -4032,7 +4036,7 @@
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>電子通路業右下</t>
+          <t>電子通路業平</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
@@ -4049,13 +4053,13 @@
         <v>0</v>
       </c>
       <c r="G88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H88" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I88" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -4064,108 +4068,106 @@
         <v>0</v>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>電子通路業平</t>
+          <t>電子零組件業右上</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D89" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E89" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F89" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G89" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H89" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I89" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J89" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K89" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業右上</t>
+          <t>電子零組件業右下</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D90" t="n">
+        <v>2</v>
+      </c>
+      <c r="E90" t="n">
         <v>3</v>
       </c>
-      <c r="E90" t="n">
-        <v>4</v>
-      </c>
       <c r="F90" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G90" t="n">
         <v>3</v>
       </c>
       <c r="H90" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I90" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J90" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K90" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L90" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="M90" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業右下</t>
-        </is>
-      </c>
-      <c r="B91" t="n">
-        <v>0</v>
-      </c>
+          <t>電子零組件業平</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr"/>
       <c r="C91" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E91" t="n">
         <v>2</v>
@@ -4174,31 +4176,31 @@
         <v>2</v>
       </c>
       <c r="G91" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" t="n">
         <v>3</v>
       </c>
-      <c r="H91" t="n">
-        <v>4</v>
-      </c>
-      <c r="I91" t="n">
-        <v>3</v>
-      </c>
-      <c r="J91" t="n">
-        <v>1</v>
-      </c>
-      <c r="K91" t="n">
-        <v>1</v>
-      </c>
       <c r="L91" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M91" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業平</t>
+          <t>電機機械右上</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
@@ -4206,7 +4208,7 @@
         <v>1</v>
       </c>
       <c r="D92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E92" t="n">
         <v>2</v>
@@ -4215,51 +4217,51 @@
         <v>2</v>
       </c>
       <c r="G92" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H92" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I92" t="n">
         <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K92" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M92" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>電機機械右上</t>
+          <t>電機機械右下</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D93" t="n">
         <v>1</v>
       </c>
       <c r="E93" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G93" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H93" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I93" t="n">
         <v>0</v>
@@ -4271,21 +4273,21 @@
         <v>0</v>
       </c>
       <c r="L93" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>電機機械右下</t>
+          <t>電機機械平</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D94" t="n">
         <v>0</v>
@@ -4294,133 +4296,135 @@
         <v>0</v>
       </c>
       <c r="F94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H94" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I94" t="n">
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L94" t="n">
         <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>電機機械平</t>
+          <t>電腦及週邊設備業右上</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E95" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G95" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H95" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J95" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右上</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr"/>
+          <t>電腦及週邊設備業右下</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>0</v>
+      </c>
       <c r="C96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D96" t="n">
         <v>0</v>
       </c>
       <c r="E96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G96" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I96" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J96" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K96" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L96" t="n">
+        <v>2</v>
+      </c>
+      <c r="M96" t="n">
         <v>3</v>
-      </c>
-      <c r="M96" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右下</t>
+          <t>電腦及週邊設備業平</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D97" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F97" t="n">
         <v>0</v>
       </c>
       <c r="G97" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H97" t="n">
         <v>0</v>
@@ -4435,16 +4439,16 @@
         <v>0</v>
       </c>
       <c r="L97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業平</t>
+          <t>食品工業右上</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
@@ -4452,28 +4456,28 @@
         <v>0</v>
       </c>
       <c r="D98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E98" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F98" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H98" t="n">
         <v>0</v>
       </c>
       <c r="I98" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
       </c>
       <c r="K98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L98" t="n">
         <v>0</v>
@@ -4485,7 +4489,7 @@
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>食品工業右上</t>
+          <t>食品工業右下</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
@@ -4526,7 +4530,7 @@
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>食品工業右下</t>
+          <t>食品工業平</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
@@ -4555,54 +4559,13 @@
         <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L100" t="n">
         <v>0</v>
       </c>
       <c r="M100" t="n">
         <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="1" t="inlineStr">
-        <is>
-          <t>食品工業平</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr"/>
-      <c r="C101" t="n">
-        <v>0</v>
-      </c>
-      <c r="D101" t="n">
-        <v>0</v>
-      </c>
-      <c r="E101" t="n">
-        <v>0</v>
-      </c>
-      <c r="F101" t="n">
-        <v>0</v>
-      </c>
-      <c r="G101" t="n">
-        <v>0</v>
-      </c>
-      <c r="H101" t="n">
-        <v>0</v>
-      </c>
-      <c r="I101" t="n">
-        <v>0</v>
-      </c>
-      <c r="J101" t="n">
-        <v>0</v>
-      </c>
-      <c r="K101" t="n">
-        <v>0</v>
-      </c>
-      <c r="L101" t="n">
-        <v>0</v>
-      </c>
-      <c r="M101" t="n">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Result/analyze_1.xlsx
+++ b/Result/analyze_1.xlsx
@@ -441,57 +441,57 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-14</t>
         </is>
       </c>
     </row>
@@ -503,34 +503,34 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
         <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I2" t="n">
         <v>3</v>
       </c>
-      <c r="H2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" t="n">
-        <v>2</v>
-      </c>
       <c r="J2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K2" t="n">
         <v>3</v>
       </c>
-      <c r="K2" t="n">
-        <v>2</v>
-      </c>
       <c r="L2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M2" t="n">
         <v>2</v>
@@ -542,39 +542,41 @@
           <t>光電業右下</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="n">
         <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -591,31 +593,31 @@
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>3</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -626,31 +628,31 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
         <v>1</v>
@@ -665,7 +667,9 @@
           <t>其他右下</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
@@ -694,10 +698,10 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -708,19 +712,19 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -738,7 +742,7 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -749,7 +753,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
         <v>2</v>
@@ -761,25 +765,25 @@
         <v>2</v>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H8" t="n">
+        <v>8</v>
+      </c>
+      <c r="I8" t="n">
         <v>3</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
+        <v>4</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2</v>
+      </c>
+      <c r="L8" t="n">
         <v>8</v>
       </c>
-      <c r="J8" t="n">
+      <c r="M8" t="n">
         <v>3</v>
-      </c>
-      <c r="K8" t="n">
-        <v>4</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -790,7 +794,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
         <v>1</v>
@@ -811,16 +815,16 @@
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
         <v>1</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -834,7 +838,7 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
         <v>1</v>
@@ -846,22 +850,22 @@
         <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
         <v>2</v>
       </c>
       <c r="M10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -875,13 +879,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -896,7 +900,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
         <v>1</v>
@@ -919,19 +923,19 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -943,7 +947,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -960,7 +964,7 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -969,10 +973,10 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -981,10 +985,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1001,25 +1005,25 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H14" t="n">
+        <v>5</v>
+      </c>
+      <c r="I14" t="n">
+        <v>4</v>
+      </c>
+      <c r="J14" t="n">
+        <v>5</v>
+      </c>
+      <c r="K14" t="n">
         <v>3</v>
-      </c>
-      <c r="I14" t="n">
-        <v>5</v>
-      </c>
-      <c r="J14" t="n">
-        <v>3</v>
-      </c>
-      <c r="K14" t="n">
-        <v>4</v>
       </c>
       <c r="L14" t="n">
         <v>3</v>
@@ -1038,19 +1042,19 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" t="n">
+        <v>4</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="n">
         <v>3</v>
-      </c>
-      <c r="D15" t="n">
-        <v>1</v>
-      </c>
-      <c r="E15" t="n">
-        <v>3</v>
-      </c>
-      <c r="F15" t="n">
-        <v>3</v>
-      </c>
-      <c r="G15" t="n">
-        <v>1</v>
       </c>
       <c r="H15" t="n">
         <v>3</v>
@@ -1059,16 +1063,16 @@
         <v>2</v>
       </c>
       <c r="J15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -1079,34 +1083,34 @@
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
         <v>2</v>
       </c>
       <c r="E16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" t="n">
         <v>3</v>
       </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>2</v>
-      </c>
-      <c r="H16" t="n">
-        <v>1</v>
-      </c>
       <c r="I16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L16" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
         <v>1</v>
@@ -1161,7 +1165,7 @@
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -1182,13 +1186,13 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>1</v>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -1208,10 +1212,10 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -1226,10 +1230,10 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -1243,7 +1247,7 @@
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -1258,22 +1262,22 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1299,10 +1303,10 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1390,13 +1394,13 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1416,7 +1420,7 @@
         <v>1</v>
       </c>
       <c r="F24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1431,13 +1435,13 @@
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" t="n">
         <v>1</v>
       </c>
       <c r="M24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1451,7 +1455,7 @@
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -1475,7 +1479,7 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M25" t="n">
         <v>1</v>
@@ -1492,25 +1496,25 @@
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E26" t="n">
         <v>1</v>
       </c>
       <c r="F26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G26" t="n">
         <v>1</v>
       </c>
       <c r="H26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" t="n">
         <v>1</v>
@@ -1519,7 +1523,7 @@
         <v>1</v>
       </c>
       <c r="M26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1528,9 +1532,7 @@
           <t>數位雲端右下</t>
         </is>
       </c>
-      <c r="B27" t="n">
-        <v>0</v>
-      </c>
+      <c r="B27" t="inlineStr"/>
       <c r="C27" t="n">
         <v>0</v>
       </c>
@@ -1541,10 +1543,10 @@
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1573,19 +1575,19 @@
       </c>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -1670,13 +1672,13 @@
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30" t="n">
         <v>1</v>
@@ -1685,7 +1687,7 @@
         <v>1</v>
       </c>
       <c r="M30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -1699,16 +1701,16 @@
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -1904,34 +1906,34 @@
         <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E36" t="n">
         <v>1</v>
       </c>
       <c r="F36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I36" t="n">
         <v>1</v>
       </c>
       <c r="J36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -1940,11 +1942,9 @@
           <t>汽車工業右下</t>
         </is>
       </c>
-      <c r="B37" t="n">
-        <v>0</v>
-      </c>
+      <c r="B37" t="inlineStr"/>
       <c r="C37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
@@ -1968,10 +1968,10 @@
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
@@ -1991,25 +1991,25 @@
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
@@ -2065,11 +2065,9 @@
           <t>油電燃氣業右下</t>
         </is>
       </c>
-      <c r="B40" t="n">
-        <v>0</v>
-      </c>
+      <c r="B40" t="inlineStr"/>
       <c r="C40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D40" t="n">
         <v>0</v>
@@ -2151,19 +2149,19 @@
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -2175,13 +2173,13 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2216,13 +2214,13 @@
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L43" t="n">
         <v>1</v>
       </c>
       <c r="M43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2233,34 +2231,34 @@
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>2</v>
+      </c>
+      <c r="F44" t="n">
+        <v>1</v>
+      </c>
+      <c r="G44" t="n">
+        <v>1</v>
+      </c>
+      <c r="H44" t="n">
+        <v>2</v>
+      </c>
+      <c r="I44" t="n">
+        <v>1</v>
+      </c>
+      <c r="J44" t="n">
         <v>3</v>
       </c>
-      <c r="D44" t="n">
-        <v>1</v>
-      </c>
-      <c r="E44" t="n">
-        <v>0</v>
-      </c>
-      <c r="F44" t="n">
-        <v>2</v>
-      </c>
-      <c r="G44" t="n">
-        <v>1</v>
-      </c>
-      <c r="H44" t="n">
-        <v>1</v>
-      </c>
-      <c r="I44" t="n">
-        <v>2</v>
-      </c>
-      <c r="J44" t="n">
-        <v>1</v>
-      </c>
       <c r="K44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
@@ -2276,31 +2274,31 @@
         <v>0</v>
       </c>
       <c r="C45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D45" t="n">
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F45" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G45" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45" t="n">
         <v>1</v>
@@ -2326,28 +2324,28 @@
         <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -2373,13 +2371,13 @@
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I47" t="n">
         <v>1</v>
       </c>
       <c r="J47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
@@ -2426,10 +2424,10 @@
         <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M48" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -2446,10 +2444,10 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -2458,10 +2456,10 @@
         <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
@@ -2496,10 +2494,10 @@
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -2568,10 +2566,10 @@
         <v>0</v>
       </c>
       <c r="D52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F52" t="n">
         <v>0</v>
@@ -2612,28 +2610,28 @@
         <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I53" t="n">
         <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
         <v>0</v>
@@ -2706,13 +2704,13 @@
         <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J55" t="n">
         <v>1</v>
       </c>
       <c r="K55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
@@ -2732,7 +2730,7 @@
         <v>1</v>
       </c>
       <c r="D56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E56" t="n">
         <v>0</v>
@@ -2753,10 +2751,10 @@
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
         <v>0</v>
@@ -2773,10 +2771,10 @@
         <v>0</v>
       </c>
       <c r="D57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -2791,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
@@ -2955,13 +2953,13 @@
         <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K61" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L61" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M61" t="n">
         <v>1</v>
@@ -3022,13 +3020,13 @@
         <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F63" t="n">
         <v>1</v>
       </c>
       <c r="G63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
@@ -3040,13 +3038,13 @@
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -3139,37 +3137,37 @@
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D66" t="n">
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H66" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I66" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J66" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K66" t="n">
         <v>4</v>
       </c>
       <c r="L66" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M66" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="67">
@@ -3186,13 +3184,13 @@
         <v>0</v>
       </c>
       <c r="E67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F67" t="n">
         <v>2</v>
       </c>
       <c r="G67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -3204,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L67" t="n">
         <v>1</v>
       </c>
       <c r="M67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -3221,37 +3219,37 @@
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E68" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H68" t="n">
         <v>1</v>
       </c>
       <c r="I68" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K68" t="n">
         <v>1</v>
       </c>
       <c r="L68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -3391,16 +3389,16 @@
         <v>0</v>
       </c>
       <c r="E72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I72" t="n">
         <v>0</v>
@@ -3506,7 +3504,9 @@
           <t>金融保險右下</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr"/>
+      <c r="B75" t="n">
+        <v>0</v>
+      </c>
       <c r="C75" t="n">
         <v>0</v>
       </c>
@@ -3728,10 +3728,10 @@
         <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -3757,19 +3757,19 @@
         <v>0</v>
       </c>
       <c r="D81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F81" t="n">
         <v>0</v>
       </c>
       <c r="G81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I81" t="n">
         <v>0</v>
@@ -3813,13 +3813,13 @@
         <v>0</v>
       </c>
       <c r="I82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J82" t="n">
         <v>1</v>
       </c>
       <c r="K82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L82" t="n">
         <v>0</v>
@@ -3842,16 +3842,16 @@
         <v>0</v>
       </c>
       <c r="E83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I83" t="n">
         <v>0</v>
@@ -3866,7 +3866,7 @@
         <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
@@ -3877,7 +3877,7 @@
       </c>
       <c r="B84" t="inlineStr"/>
       <c r="C84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D84" t="n">
         <v>0</v>
@@ -3930,13 +3930,13 @@
         <v>0</v>
       </c>
       <c r="G85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H85" t="n">
         <v>1</v>
       </c>
       <c r="I85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -3962,7 +3962,7 @@
         <v>1</v>
       </c>
       <c r="D86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E86" t="n">
         <v>0</v>
@@ -3971,22 +3971,22 @@
         <v>0</v>
       </c>
       <c r="G86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
         <v>0</v>
@@ -3998,7 +3998,9 @@
           <t>電子通路業右下</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr"/>
+      <c r="B87" t="n">
+        <v>0</v>
+      </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
@@ -4006,13 +4008,13 @@
         <v>0</v>
       </c>
       <c r="E87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F87" t="n">
         <v>2</v>
       </c>
       <c r="G87" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H87" t="n">
         <v>0</v>
@@ -4050,13 +4052,13 @@
         <v>0</v>
       </c>
       <c r="F88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G88" t="n">
         <v>1</v>
       </c>
       <c r="H88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I88" t="n">
         <v>0</v>
@@ -4065,13 +4067,13 @@
         <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L88" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="89">
@@ -4082,37 +4084,37 @@
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="n">
+        <v>9</v>
+      </c>
+      <c r="D89" t="n">
         <v>4</v>
       </c>
-      <c r="D89" t="n">
-        <v>9</v>
-      </c>
       <c r="E89" t="n">
+        <v>8</v>
+      </c>
+      <c r="F89" t="n">
         <v>4</v>
       </c>
-      <c r="F89" t="n">
-        <v>8</v>
-      </c>
       <c r="G89" t="n">
+        <v>5</v>
+      </c>
+      <c r="H89" t="n">
         <v>4</v>
       </c>
-      <c r="H89" t="n">
-        <v>5</v>
-      </c>
       <c r="I89" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J89" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K89" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="L89" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="M89" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="90">
@@ -4121,39 +4123,41 @@
           <t>電子零組件業右下</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr"/>
+      <c r="B90" t="n">
+        <v>0</v>
+      </c>
       <c r="C90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D90" t="n">
         <v>2</v>
       </c>
       <c r="E90" t="n">
+        <v>4</v>
+      </c>
+      <c r="F90" t="n">
         <v>3</v>
       </c>
-      <c r="F90" t="n">
-        <v>5</v>
-      </c>
       <c r="G90" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H90" t="n">
         <v>1</v>
       </c>
       <c r="I90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J90" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K90" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L90" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M90" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="91">
@@ -4164,16 +4168,16 @@
       </c>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="n">
+        <v>2</v>
+      </c>
+      <c r="D91" t="n">
         <v>3</v>
       </c>
-      <c r="D91" t="n">
-        <v>2</v>
-      </c>
       <c r="E91" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F91" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -4185,16 +4189,16 @@
         <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K91" t="n">
+        <v>1</v>
+      </c>
+      <c r="L91" t="n">
+        <v>2</v>
+      </c>
+      <c r="M91" t="n">
         <v>3</v>
-      </c>
-      <c r="L91" t="n">
-        <v>2</v>
-      </c>
-      <c r="M91" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="92">
@@ -4208,13 +4212,13 @@
         <v>1</v>
       </c>
       <c r="D92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E92" t="n">
         <v>2</v>
       </c>
       <c r="F92" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -4223,16 +4227,16 @@
         <v>0</v>
       </c>
       <c r="I92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K92" t="n">
         <v>2</v>
       </c>
       <c r="L92" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M92" t="n">
         <v>1</v>
@@ -4244,24 +4248,26 @@
           <t>電機機械右下</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr"/>
+      <c r="B93" t="n">
+        <v>0</v>
+      </c>
       <c r="C93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F93" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I93" t="n">
         <v>0</v>
@@ -4287,34 +4293,34 @@
       </c>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D94" t="n">
         <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H94" t="n">
         <v>0</v>
       </c>
       <c r="I94" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M94" t="n">
         <v>1</v>
@@ -4331,34 +4337,34 @@
         <v>1</v>
       </c>
       <c r="D95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E95" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G95" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H95" t="n">
         <v>2</v>
       </c>
       <c r="I95" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J95" t="n">
+        <v>1</v>
+      </c>
+      <c r="K95" t="n">
+        <v>2</v>
+      </c>
+      <c r="L95" t="n">
         <v>3</v>
       </c>
-      <c r="K95" t="n">
-        <v>1</v>
-      </c>
-      <c r="L95" t="n">
-        <v>2</v>
-      </c>
       <c r="M95" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -4386,22 +4392,22 @@
         <v>0</v>
       </c>
       <c r="H96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I96" t="n">
         <v>1</v>
       </c>
       <c r="J96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L96" t="n">
         <v>2</v>
       </c>
       <c r="M96" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="97">
@@ -4415,16 +4421,16 @@
         <v>2</v>
       </c>
       <c r="D97" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F97" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G97" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H97" t="n">
         <v>0</v>
@@ -4439,7 +4445,7 @@
         <v>0</v>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M97" t="n">
         <v>1</v>
@@ -4515,7 +4521,7 @@
         <v>0</v>
       </c>
       <c r="J99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K99" t="n">
         <v>0</v>
@@ -4559,7 +4565,7 @@
         <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L100" t="n">
         <v>0</v>

--- a/Result/analyze_1.xlsx
+++ b/Result/analyze_1.xlsx
@@ -441,57 +441,57 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-15</t>
         </is>
       </c>
     </row>
@@ -503,37 +503,37 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
         <v>3</v>
       </c>
       <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2" t="n">
         <v>3</v>
       </c>
-      <c r="G2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H2" t="n">
-        <v>2</v>
-      </c>
       <c r="I2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J2" t="n">
         <v>3</v>
       </c>
-      <c r="J2" t="n">
-        <v>2</v>
-      </c>
       <c r="K2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M2" t="n">
         <v>3</v>
-      </c>
-      <c r="L2" t="n">
-        <v>2</v>
-      </c>
-      <c r="M2" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -542,41 +542,39 @@
           <t>光電業右下</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>0</v>
-      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" t="n">
         <v>3</v>
-      </c>
-      <c r="G3" t="n">
-        <v>4</v>
-      </c>
-      <c r="H3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -590,34 +588,34 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
         <v>3</v>
       </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
       <c r="M4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -631,25 +629,25 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
         <v>1</v>
@@ -667,9 +665,7 @@
           <t>其他右下</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>0</v>
-      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
         <v>0</v>
       </c>
@@ -695,10 +691,10 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -712,16 +708,16 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -739,10 +735,10 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -762,28 +758,28 @@
         <v>2</v>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G8" t="n">
+        <v>8</v>
+      </c>
+      <c r="H8" t="n">
         <v>3</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
+        <v>4</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" t="n">
         <v>8</v>
       </c>
-      <c r="I8" t="n">
+      <c r="L8" t="n">
         <v>3</v>
       </c>
-      <c r="J8" t="n">
-        <v>4</v>
-      </c>
-      <c r="K8" t="n">
-        <v>2</v>
-      </c>
-      <c r="L8" t="n">
-        <v>8</v>
-      </c>
       <c r="M8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -815,16 +811,16 @@
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
         <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -835,7 +831,7 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
         <v>1</v>
@@ -844,25 +840,25 @@
         <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
         <v>1</v>
@@ -876,7 +872,7 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -897,16 +893,16 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -915,24 +911,26 @@
           <t>化學工業右下</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
+      <c r="B12" t="n">
+        <v>0</v>
+      </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -944,7 +942,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
         <v>1</v>
@@ -961,19 +959,19 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -982,10 +980,10 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1002,34 +1000,34 @@
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G14" t="n">
+        <v>5</v>
+      </c>
+      <c r="H14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I14" t="n">
+        <v>5</v>
+      </c>
+      <c r="J14" t="n">
         <v>3</v>
       </c>
-      <c r="H14" t="n">
-        <v>5</v>
-      </c>
-      <c r="I14" t="n">
+      <c r="K14" t="n">
+        <v>2</v>
+      </c>
+      <c r="L14" t="n">
         <v>4</v>
       </c>
-      <c r="J14" t="n">
-        <v>5</v>
-      </c>
-      <c r="K14" t="n">
-        <v>3</v>
-      </c>
-      <c r="L14" t="n">
-        <v>3</v>
-      </c>
       <c r="M14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1038,32 +1036,30 @@
           <t>半導體業右下</t>
         </is>
       </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
+      <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G15" t="n">
         <v>3</v>
       </c>
       <c r="H15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K15" t="n">
         <v>2</v>
@@ -1072,7 +1068,7 @@
         <v>2</v>
       </c>
       <c r="M15" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -1083,34 +1079,34 @@
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
         <v>3</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
       </c>
       <c r="K16" t="n">
         <v>3</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M16" t="n">
         <v>1</v>
@@ -1183,13 +1179,13 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -1209,10 +1205,10 @@
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -1227,10 +1223,10 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -1259,25 +1255,25 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1286,7 +1282,9 @@
           <t>居家生活右下</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr"/>
+      <c r="B21" t="n">
+        <v>0</v>
+      </c>
       <c r="C21" t="n">
         <v>0</v>
       </c>
@@ -1300,10 +1298,10 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -1391,16 +1389,16 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1409,15 +1407,17 @@
           <t>建材營造右下</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="n">
+        <v>0</v>
+      </c>
       <c r="C24" t="n">
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -1432,13 +1432,13 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
         <v>1</v>
       </c>
       <c r="L24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -1452,10 +1452,10 @@
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -1476,13 +1476,13 @@
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25" t="n">
         <v>1</v>
       </c>
       <c r="M25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D26" t="n">
         <v>1</v>
@@ -1505,7 +1505,7 @@
         <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1520,10 +1520,10 @@
         <v>1</v>
       </c>
       <c r="L26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1540,10 +1540,10 @@
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1578,22 +1578,22 @@
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1669,13 +1669,13 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30" t="n">
         <v>1</v>
@@ -1684,7 +1684,7 @@
         <v>1</v>
       </c>
       <c r="L30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -1698,16 +1698,16 @@
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1903,37 +1903,37 @@
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D36" t="n">
         <v>1</v>
       </c>
       <c r="E36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H36" t="n">
         <v>1</v>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -1965,16 +1965,16 @@
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -1988,25 +1988,25 @@
         <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -2149,16 +2149,16 @@
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D42" t="n">
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -2170,16 +2170,16 @@
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2214,10 +2214,10 @@
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
@@ -2231,37 +2231,37 @@
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F44" t="n">
         <v>1</v>
       </c>
       <c r="G44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I44" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2270,32 +2270,30 @@
           <t>生技醫療業右下</t>
         </is>
       </c>
-      <c r="B45" t="n">
-        <v>0</v>
-      </c>
+      <c r="B45" t="inlineStr"/>
       <c r="C45" t="n">
         <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E45" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F45" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K45" t="n">
         <v>1</v>
@@ -2304,7 +2302,7 @@
         <v>1</v>
       </c>
       <c r="M45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46">
@@ -2321,28 +2319,28 @@
         <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M46" t="n">
         <v>2</v>
@@ -2368,13 +2366,13 @@
         <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H47" t="n">
         <v>1</v>
       </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -2421,13 +2419,13 @@
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L48" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -2441,10 +2439,10 @@
         <v>0</v>
       </c>
       <c r="D49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -2453,16 +2451,16 @@
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
@@ -2479,7 +2477,7 @@
       </c>
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D50" t="n">
         <v>0</v>
@@ -2491,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I50" t="n">
         <v>0</v>
@@ -2518,9 +2516,7 @@
           <t>綠能環保右下</t>
         </is>
       </c>
-      <c r="B51" t="n">
-        <v>0</v>
-      </c>
+      <c r="B51" t="inlineStr"/>
       <c r="C51" t="n">
         <v>0</v>
       </c>
@@ -2566,7 +2562,7 @@
         <v>0</v>
       </c>
       <c r="D52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E52" t="n">
         <v>0</v>
@@ -2607,34 +2603,34 @@
         <v>0</v>
       </c>
       <c r="D53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -2701,13 +2697,13 @@
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I55" t="n">
         <v>1</v>
       </c>
       <c r="J55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K55" t="n">
         <v>0</v>
@@ -2727,7 +2723,7 @@
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D56" t="n">
         <v>0</v>
@@ -2748,16 +2744,16 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -2766,12 +2762,14 @@
           <t>觀光事業右下</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr"/>
+      <c r="B57" t="n">
+        <v>0</v>
+      </c>
       <c r="C57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E57" t="n">
         <v>0</v>
@@ -2786,10 +2784,10 @@
         <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K57" t="n">
         <v>0</v>
@@ -2950,13 +2948,13 @@
         <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J61" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K61" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L61" t="n">
         <v>1</v>
@@ -2971,7 +2969,9 @@
           <t>資訊服務業右下</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr"/>
+      <c r="B62" t="n">
+        <v>0</v>
+      </c>
       <c r="C62" t="n">
         <v>0</v>
       </c>
@@ -3000,7 +3000,7 @@
         <v>0</v>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M62" t="n">
         <v>0</v>
@@ -3017,13 +3017,13 @@
         <v>0</v>
       </c>
       <c r="D63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E63" t="n">
         <v>1</v>
       </c>
       <c r="F63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -3035,16 +3035,16 @@
         <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -3140,31 +3140,31 @@
         <v>2</v>
       </c>
       <c r="D66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G66" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H66" t="n">
+        <v>1</v>
+      </c>
+      <c r="I66" t="n">
         <v>4</v>
-      </c>
-      <c r="I66" t="n">
-        <v>1</v>
       </c>
       <c r="J66" t="n">
         <v>4</v>
       </c>
       <c r="K66" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L66" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M66" t="n">
         <v>7</v>
@@ -3176,18 +3176,20 @@
           <t>通信網路業右下</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr"/>
+      <c r="B67" t="n">
+        <v>0</v>
+      </c>
       <c r="C67" t="n">
         <v>0</v>
       </c>
       <c r="D67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E67" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -3205,10 +3207,10 @@
         <v>1</v>
       </c>
       <c r="L67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -3219,37 +3221,37 @@
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F68" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G68" t="n">
         <v>1</v>
       </c>
       <c r="H68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69">
@@ -3386,16 +3388,16 @@
         <v>0</v>
       </c>
       <c r="D72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
@@ -3504,9 +3506,7 @@
           <t>金融保險右下</t>
         </is>
       </c>
-      <c r="B75" t="n">
-        <v>0</v>
-      </c>
+      <c r="B75" t="inlineStr"/>
       <c r="C75" t="n">
         <v>0</v>
       </c>
@@ -3725,10 +3725,10 @@
         <v>0</v>
       </c>
       <c r="G80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I80" t="n">
         <v>0</v>
@@ -3754,19 +3754,19 @@
       </c>
       <c r="B81" t="inlineStr"/>
       <c r="C81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E81" t="n">
         <v>0</v>
       </c>
       <c r="F81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
@@ -3810,13 +3810,13 @@
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I82" t="n">
         <v>1</v>
       </c>
       <c r="J82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K82" t="n">
         <v>0</v>
@@ -3839,16 +3839,16 @@
         <v>0</v>
       </c>
       <c r="D83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
@@ -3866,7 +3866,7 @@
         <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -3927,13 +3927,13 @@
         <v>0</v>
       </c>
       <c r="F85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G85" t="n">
         <v>1</v>
       </c>
       <c r="H85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I85" t="n">
         <v>0</v>
@@ -3945,7 +3945,7 @@
         <v>0</v>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M85" t="n">
         <v>0</v>
@@ -3959,7 +3959,7 @@
       </c>
       <c r="B86" t="inlineStr"/>
       <c r="C86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D86" t="n">
         <v>0</v>
@@ -3968,22 +3968,22 @@
         <v>0</v>
       </c>
       <c r="F86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L86" t="n">
         <v>0</v>
@@ -3998,20 +3998,18 @@
           <t>電子通路業右下</t>
         </is>
       </c>
-      <c r="B87" t="n">
-        <v>0</v>
-      </c>
+      <c r="B87" t="inlineStr"/>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F87" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -4032,7 +4030,7 @@
         <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88">
@@ -4049,13 +4047,13 @@
         <v>0</v>
       </c>
       <c r="E88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F88" t="n">
         <v>1</v>
       </c>
       <c r="G88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H88" t="n">
         <v>0</v>
@@ -4064,16 +4062,16 @@
         <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K88" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M88" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -4084,37 +4082,37 @@
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D89" t="n">
+        <v>7</v>
+      </c>
+      <c r="E89" t="n">
         <v>4</v>
       </c>
-      <c r="E89" t="n">
+      <c r="F89" t="n">
+        <v>5</v>
+      </c>
+      <c r="G89" t="n">
+        <v>4</v>
+      </c>
+      <c r="H89" t="n">
         <v>8</v>
       </c>
-      <c r="F89" t="n">
-        <v>4</v>
-      </c>
-      <c r="G89" t="n">
-        <v>5</v>
-      </c>
-      <c r="H89" t="n">
-        <v>4</v>
-      </c>
       <c r="I89" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="J89" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K89" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="L89" t="n">
         <v>11</v>
       </c>
       <c r="M89" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="90">
@@ -4130,34 +4128,34 @@
         <v>2</v>
       </c>
       <c r="D90" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E90" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F90" t="n">
+        <v>1</v>
+      </c>
+      <c r="G90" t="n">
+        <v>1</v>
+      </c>
+      <c r="H90" t="n">
         <v>3</v>
       </c>
-      <c r="G90" t="n">
-        <v>1</v>
-      </c>
-      <c r="H90" t="n">
-        <v>1</v>
-      </c>
       <c r="I90" t="n">
         <v>2</v>
       </c>
       <c r="J90" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K90" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L90" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M90" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
@@ -4168,37 +4166,37 @@
       </c>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D91" t="n">
+        <v>4</v>
+      </c>
+      <c r="E91" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" t="n">
         <v>3</v>
       </c>
-      <c r="E91" t="n">
+      <c r="J91" t="n">
+        <v>2</v>
+      </c>
+      <c r="K91" t="n">
+        <v>2</v>
+      </c>
+      <c r="L91" t="n">
         <v>3</v>
       </c>
-      <c r="F91" t="n">
-        <v>0</v>
-      </c>
-      <c r="G91" t="n">
-        <v>0</v>
-      </c>
-      <c r="H91" t="n">
-        <v>0</v>
-      </c>
-      <c r="I91" t="n">
-        <v>0</v>
-      </c>
-      <c r="J91" t="n">
-        <v>3</v>
-      </c>
-      <c r="K91" t="n">
-        <v>1</v>
-      </c>
-      <c r="L91" t="n">
-        <v>2</v>
-      </c>
       <c r="M91" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
@@ -4209,13 +4207,13 @@
       </c>
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D92" t="n">
         <v>2</v>
       </c>
       <c r="E92" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F92" t="n">
         <v>0</v>
@@ -4224,10 +4222,10 @@
         <v>0</v>
       </c>
       <c r="H92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J92" t="n">
         <v>2</v>
@@ -4239,7 +4237,7 @@
         <v>1</v>
       </c>
       <c r="M92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93">
@@ -4252,19 +4250,19 @@
         <v>0</v>
       </c>
       <c r="C93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H93" t="n">
         <v>0</v>
@@ -4296,31 +4294,31 @@
         <v>0</v>
       </c>
       <c r="D94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E94" t="n">
         <v>1</v>
       </c>
       <c r="F94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
       </c>
       <c r="H94" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K94" t="n">
         <v>0</v>
       </c>
       <c r="L94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
         <v>1</v>
@@ -4334,37 +4332,37 @@
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D95" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F95" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H95" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I95" t="n">
+        <v>1</v>
+      </c>
+      <c r="J95" t="n">
+        <v>2</v>
+      </c>
+      <c r="K95" t="n">
         <v>3</v>
       </c>
-      <c r="J95" t="n">
-        <v>1</v>
-      </c>
-      <c r="K95" t="n">
-        <v>2</v>
-      </c>
       <c r="L95" t="n">
+        <v>0</v>
+      </c>
+      <c r="M95" t="n">
         <v>3</v>
-      </c>
-      <c r="M95" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -4373,9 +4371,7 @@
           <t>電腦及週邊設備業右下</t>
         </is>
       </c>
-      <c r="B96" t="n">
-        <v>0</v>
-      </c>
+      <c r="B96" t="inlineStr"/>
       <c r="C96" t="n">
         <v>0</v>
       </c>
@@ -4389,25 +4385,25 @@
         <v>0</v>
       </c>
       <c r="G96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H96" t="n">
         <v>1</v>
       </c>
       <c r="I96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J96" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K96" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L96" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M96" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="97">
@@ -4418,19 +4414,19 @@
       </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E97" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F97" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H97" t="n">
         <v>0</v>
@@ -4442,10 +4438,10 @@
         <v>0</v>
       </c>
       <c r="K97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L97" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
         <v>1</v>
@@ -4518,10 +4514,10 @@
         <v>0</v>
       </c>
       <c r="I99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K99" t="n">
         <v>0</v>

--- a/Result/analyze_1.xlsx
+++ b/Result/analyze_1.xlsx
@@ -441,57 +441,57 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2025-08-18</t>
         </is>
       </c>
     </row>
@@ -503,37 +503,37 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D2" t="n">
         <v>3</v>
       </c>
-      <c r="D2" t="n">
-        <v>2</v>
-      </c>
       <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G2" t="n">
         <v>3</v>
       </c>
-      <c r="F2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" t="n">
-        <v>2</v>
-      </c>
       <c r="H2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I2" t="n">
         <v>3</v>
       </c>
-      <c r="I2" t="n">
-        <v>2</v>
-      </c>
       <c r="J2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K2" t="n">
         <v>3</v>
       </c>
-      <c r="K2" t="n">
-        <v>2</v>
-      </c>
       <c r="L2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -544,37 +544,37 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
         <v>3</v>
       </c>
       <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" t="n">
         <v>4</v>
-      </c>
-      <c r="G3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1</v>
-      </c>
-      <c r="M3" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -585,37 +585,37 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
         <v>3</v>
       </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -626,37 +626,37 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>1</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -688,10 +688,10 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -708,13 +708,13 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
         <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -732,10 +732,10 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -755,31 +755,31 @@
         <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F8" t="n">
+        <v>8</v>
+      </c>
+      <c r="G8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H8" t="n">
         <v>4</v>
       </c>
-      <c r="G8" t="n">
+      <c r="I8" t="n">
+        <v>2</v>
+      </c>
+      <c r="J8" t="n">
         <v>8</v>
       </c>
-      <c r="H8" t="n">
+      <c r="K8" t="n">
         <v>3</v>
       </c>
-      <c r="I8" t="n">
-        <v>4</v>
-      </c>
-      <c r="J8" t="n">
-        <v>2</v>
-      </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
+        <v>5</v>
+      </c>
+      <c r="M8" t="n">
         <v>8</v>
-      </c>
-      <c r="L8" t="n">
-        <v>3</v>
-      </c>
-      <c r="M8" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -788,9 +788,11 @@
           <t>其他電子業右下</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
         <v>1</v>
@@ -814,7 +816,7 @@
         <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -831,37 +833,37 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
         <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -890,19 +892,19 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -911,23 +913,21 @@
           <t>化學工業右下</t>
         </is>
       </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -939,13 +939,13 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
         <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -956,19 +956,19 @@
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -977,16 +977,16 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -997,37 +997,37 @@
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F14" t="n">
+        <v>5</v>
+      </c>
+      <c r="G14" t="n">
+        <v>4</v>
+      </c>
+      <c r="H14" t="n">
+        <v>5</v>
+      </c>
+      <c r="I14" t="n">
         <v>3</v>
       </c>
-      <c r="G14" t="n">
-        <v>5</v>
-      </c>
-      <c r="H14" t="n">
+      <c r="J14" t="n">
+        <v>2</v>
+      </c>
+      <c r="K14" t="n">
         <v>4</v>
       </c>
-      <c r="I14" t="n">
-        <v>5</v>
-      </c>
-      <c r="J14" t="n">
-        <v>3</v>
-      </c>
-      <c r="K14" t="n">
-        <v>2</v>
-      </c>
       <c r="L14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1036,27 +1036,29 @@
           <t>半導體業右下</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
+      <c r="B15" t="n">
+        <v>0</v>
+      </c>
       <c r="C15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" t="n">
         <v>3</v>
-      </c>
-      <c r="E15" t="n">
-        <v>1</v>
       </c>
       <c r="F15" t="n">
         <v>3</v>
       </c>
       <c r="G15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J15" t="n">
         <v>2</v>
@@ -1065,7 +1067,7 @@
         <v>2</v>
       </c>
       <c r="L15" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M15" t="n">
         <v>6</v>
@@ -1079,37 +1081,37 @@
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
         <v>3</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
       </c>
       <c r="J16" t="n">
         <v>3</v>
       </c>
       <c r="K16" t="n">
+        <v>2</v>
+      </c>
+      <c r="L16" t="n">
+        <v>2</v>
+      </c>
+      <c r="M16" t="n">
         <v>3</v>
-      </c>
-      <c r="L16" t="n">
-        <v>2</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1182,7 +1184,7 @@
         <v>1</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -1191,7 +1193,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1202,10 +1204,10 @@
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -1217,13 +1219,13 @@
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1232,7 +1234,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1252,28 +1254,28 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1282,9 +1284,7 @@
           <t>居家生活右下</t>
         </is>
       </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
+      <c r="B21" t="inlineStr"/>
       <c r="C21" t="n">
         <v>0</v>
       </c>
@@ -1295,10 +1295,10 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -1316,7 +1316,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1386,16 +1386,16 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -1407,14 +1407,12 @@
           <t>建材營造右下</t>
         </is>
       </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
+      <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -1429,13 +1427,13 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
       </c>
       <c r="K24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -1452,7 +1450,7 @@
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
@@ -1473,13 +1471,13 @@
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
         <v>1</v>
       </c>
       <c r="L25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -1502,7 +1500,7 @@
         <v>1</v>
       </c>
       <c r="F26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1511,19 +1509,19 @@
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
       </c>
       <c r="K26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1537,10 +1535,10 @@
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -1575,25 +1573,25 @@
       </c>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1666,13 +1664,13 @@
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30" t="n">
         <v>1</v>
@@ -1681,13 +1679,13 @@
         <v>1</v>
       </c>
       <c r="K30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -1698,13 +1696,13 @@
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -1906,31 +1904,31 @@
         <v>1</v>
       </c>
       <c r="D36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G36" t="n">
         <v>1</v>
       </c>
       <c r="H36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M36" t="n">
         <v>1</v>
@@ -1962,16 +1960,16 @@
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M37" t="n">
         <v>1</v>
@@ -1985,25 +1983,25 @@
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2152,10 +2150,10 @@
         <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -2167,16 +2165,16 @@
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M42" t="n">
         <v>1</v>
@@ -2231,37 +2229,37 @@
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E44" t="n">
         <v>1</v>
       </c>
       <c r="F44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H44" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M44" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="45">
@@ -2270,27 +2268,29 @@
           <t>生技醫療業右下</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr"/>
+      <c r="B45" t="n">
+        <v>0</v>
+      </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J45" t="n">
         <v>1</v>
@@ -2299,7 +2299,7 @@
         <v>1</v>
       </c>
       <c r="L45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M45" t="n">
         <v>3</v>
@@ -2316,34 +2316,34 @@
         <v>0</v>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -2363,19 +2363,19 @@
         <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G47" t="n">
         <v>1</v>
       </c>
       <c r="H47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I47" t="n">
         <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
@@ -2384,7 +2384,7 @@
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -2416,13 +2416,13 @@
         <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
         <v>0</v>
@@ -2436,10 +2436,10 @@
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E49" t="n">
         <v>0</v>
@@ -2448,10 +2448,10 @@
         <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I49" t="n">
         <v>0</v>
@@ -2460,7 +2460,7 @@
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
@@ -2477,7 +2477,7 @@
       </c>
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D50" t="n">
         <v>0</v>
@@ -2486,10 +2486,10 @@
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
@@ -2516,7 +2516,9 @@
           <t>綠能環保右下</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr"/>
+      <c r="B51" t="n">
+        <v>0</v>
+      </c>
       <c r="C51" t="n">
         <v>0</v>
       </c>
@@ -2600,34 +2602,34 @@
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K53" t="n">
         <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M53" t="n">
         <v>1</v>
@@ -2694,13 +2696,13 @@
         <v>0</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H55" t="n">
         <v>1</v>
       </c>
       <c r="I55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -2712,7 +2714,7 @@
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -2741,19 +2743,19 @@
         <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -2762,11 +2764,9 @@
           <t>觀光事業右下</t>
         </is>
       </c>
-      <c r="B57" t="n">
-        <v>0</v>
-      </c>
+      <c r="B57" t="inlineStr"/>
       <c r="C57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D57" t="n">
         <v>0</v>
@@ -2781,10 +2781,10 @@
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -2796,7 +2796,7 @@
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -2945,13 +2945,13 @@
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I61" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J61" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K61" t="n">
         <v>1</v>
@@ -2969,9 +2969,7 @@
           <t>資訊服務業右下</t>
         </is>
       </c>
-      <c r="B62" t="n">
-        <v>0</v>
-      </c>
+      <c r="B62" t="inlineStr"/>
       <c r="C62" t="n">
         <v>0</v>
       </c>
@@ -2997,10 +2995,10 @@
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
         <v>0</v>
@@ -3014,13 +3012,13 @@
       </c>
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D63" t="n">
         <v>1</v>
       </c>
       <c r="E63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
@@ -3032,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K63" t="n">
         <v>0</v>
@@ -3137,37 +3135,37 @@
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F66" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G66" t="n">
+        <v>1</v>
+      </c>
+      <c r="H66" t="n">
         <v>4</v>
-      </c>
-      <c r="H66" t="n">
-        <v>1</v>
       </c>
       <c r="I66" t="n">
         <v>4</v>
       </c>
       <c r="J66" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K66" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L66" t="n">
         <v>7</v>
       </c>
       <c r="M66" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="67">
@@ -3176,17 +3174,15 @@
           <t>通信網路業右下</t>
         </is>
       </c>
-      <c r="B67" t="n">
-        <v>0</v>
-      </c>
+      <c r="B67" t="inlineStr"/>
       <c r="C67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D67" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F67" t="n">
         <v>0</v>
@@ -3201,16 +3197,16 @@
         <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68">
@@ -3221,37 +3217,37 @@
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D68" t="n">
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J68" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -3385,16 +3381,16 @@
       </c>
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -3722,10 +3718,10 @@
         <v>0</v>
       </c>
       <c r="F80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
@@ -3754,16 +3750,16 @@
       </c>
       <c r="B81" t="inlineStr"/>
       <c r="C81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D81" t="n">
         <v>0</v>
       </c>
       <c r="E81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -3784,7 +3780,7 @@
         <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82">
@@ -3807,13 +3803,13 @@
         <v>0</v>
       </c>
       <c r="G82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H82" t="n">
         <v>1</v>
       </c>
       <c r="I82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -3836,16 +3832,16 @@
       </c>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -3860,7 +3856,7 @@
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L83" t="n">
         <v>0</v>
@@ -3924,13 +3920,13 @@
         <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F85" t="n">
         <v>1</v>
       </c>
       <c r="G85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H85" t="n">
         <v>0</v>
@@ -3945,7 +3941,7 @@
         <v>0</v>
       </c>
       <c r="L85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
         <v>0</v>
@@ -3965,22 +3961,22 @@
         <v>0</v>
       </c>
       <c r="E86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K86" t="n">
         <v>0</v>
@@ -3998,15 +3994,17 @@
           <t>電子通路業右下</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr"/>
+      <c r="B87" t="n">
+        <v>0</v>
+      </c>
       <c r="C87" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D87" t="n">
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F87" t="n">
         <v>0</v>
@@ -4027,10 +4025,10 @@
         <v>0</v>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M87" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
@@ -4044,13 +4042,13 @@
         <v>0</v>
       </c>
       <c r="D88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E88" t="n">
         <v>1</v>
       </c>
       <c r="F88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -4059,16 +4057,16 @@
         <v>0</v>
       </c>
       <c r="I88" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J88" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L88" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
         <v>0</v>
@@ -4082,37 +4080,37 @@
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="n">
+        <v>8</v>
+      </c>
+      <c r="D89" t="n">
+        <v>3</v>
+      </c>
+      <c r="E89" t="n">
+        <v>5</v>
+      </c>
+      <c r="F89" t="n">
         <v>4</v>
       </c>
-      <c r="D89" t="n">
+      <c r="G89" t="n">
         <v>7</v>
       </c>
-      <c r="E89" t="n">
-        <v>4</v>
-      </c>
-      <c r="F89" t="n">
-        <v>5</v>
-      </c>
-      <c r="G89" t="n">
-        <v>4</v>
-      </c>
       <c r="H89" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I89" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="J89" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="K89" t="n">
         <v>11</v>
       </c>
       <c r="L89" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M89" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
     </row>
     <row r="90">
@@ -4121,41 +4119,39 @@
           <t>電子零組件業右下</t>
         </is>
       </c>
-      <c r="B90" t="n">
-        <v>0</v>
-      </c>
+      <c r="B90" t="inlineStr"/>
       <c r="C90" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D90" t="n">
         <v>3</v>
       </c>
       <c r="E90" t="n">
+        <v>1</v>
+      </c>
+      <c r="F90" t="n">
+        <v>1</v>
+      </c>
+      <c r="G90" t="n">
         <v>3</v>
       </c>
-      <c r="F90" t="n">
-        <v>1</v>
-      </c>
-      <c r="G90" t="n">
-        <v>1</v>
-      </c>
       <c r="H90" t="n">
+        <v>2</v>
+      </c>
+      <c r="I90" t="n">
         <v>3</v>
       </c>
-      <c r="I90" t="n">
-        <v>2</v>
-      </c>
       <c r="J90" t="n">
+        <v>0</v>
+      </c>
+      <c r="K90" t="n">
         <v>3</v>
       </c>
-      <c r="K90" t="n">
-        <v>1</v>
-      </c>
       <c r="L90" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M90" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="91">
@@ -4166,37 +4162,37 @@
       </c>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="n">
+        <v>4</v>
+      </c>
+      <c r="D91" t="n">
+        <v>1</v>
+      </c>
+      <c r="E91" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" t="n">
+        <v>1</v>
+      </c>
+      <c r="H91" t="n">
+        <v>4</v>
+      </c>
+      <c r="I91" t="n">
+        <v>1</v>
+      </c>
+      <c r="J91" t="n">
         <v>3</v>
       </c>
-      <c r="D91" t="n">
-        <v>4</v>
-      </c>
-      <c r="E91" t="n">
-        <v>0</v>
-      </c>
-      <c r="F91" t="n">
-        <v>0</v>
-      </c>
-      <c r="G91" t="n">
-        <v>0</v>
-      </c>
-      <c r="H91" t="n">
-        <v>0</v>
-      </c>
-      <c r="I91" t="n">
+      <c r="K91" t="n">
         <v>3</v>
       </c>
-      <c r="J91" t="n">
-        <v>2</v>
-      </c>
-      <c r="K91" t="n">
-        <v>2</v>
-      </c>
       <c r="L91" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="92">
@@ -4210,7 +4206,7 @@
         <v>2</v>
       </c>
       <c r="D92" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E92" t="n">
         <v>0</v>
@@ -4219,10 +4215,10 @@
         <v>0</v>
       </c>
       <c r="G92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I92" t="n">
         <v>2</v>
@@ -4231,13 +4227,13 @@
         <v>2</v>
       </c>
       <c r="K92" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M92" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="93">
@@ -4250,16 +4246,16 @@
         <v>0</v>
       </c>
       <c r="C93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D93" t="n">
         <v>1</v>
       </c>
       <c r="E93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -4291,37 +4287,37 @@
       </c>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F94" t="n">
         <v>0</v>
       </c>
       <c r="G94" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -4332,37 +4328,37 @@
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D95" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E95" t="n">
         <v>2</v>
       </c>
       <c r="F95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G95" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H95" t="n">
+        <v>1</v>
+      </c>
+      <c r="I95" t="n">
+        <v>2</v>
+      </c>
+      <c r="J95" t="n">
         <v>3</v>
       </c>
-      <c r="I95" t="n">
-        <v>1</v>
-      </c>
-      <c r="J95" t="n">
-        <v>2</v>
-      </c>
       <c r="K95" t="n">
+        <v>0</v>
+      </c>
+      <c r="L95" t="n">
         <v>3</v>
       </c>
-      <c r="L95" t="n">
-        <v>0</v>
-      </c>
       <c r="M95" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="96">
@@ -4371,7 +4367,9 @@
           <t>電腦及週邊設備業右下</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr"/>
+      <c r="B96" t="n">
+        <v>0</v>
+      </c>
       <c r="C96" t="n">
         <v>0</v>
       </c>
@@ -4382,22 +4380,22 @@
         <v>0</v>
       </c>
       <c r="F96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G96" t="n">
         <v>1</v>
       </c>
       <c r="H96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I96" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J96" t="n">
         <v>2</v>
       </c>
       <c r="K96" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L96" t="n">
         <v>3</v>
@@ -4414,16 +4412,16 @@
       </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E97" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -4435,16 +4433,16 @@
         <v>0</v>
       </c>
       <c r="J97" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K97" t="n">
         <v>1</v>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -4511,10 +4509,10 @@
         <v>0</v>
       </c>
       <c r="H99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>

--- a/Result/analyze_1.xlsx
+++ b/Result/analyze_1.xlsx
@@ -441,57 +441,57 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-19</t>
         </is>
       </c>
     </row>
@@ -503,25 +503,25 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" t="n">
         <v>3</v>
       </c>
-      <c r="E2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" t="n">
-        <v>2</v>
-      </c>
       <c r="G2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2" t="n">
         <v>3</v>
       </c>
-      <c r="H2" t="n">
-        <v>2</v>
-      </c>
       <c r="I2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
         <v>2</v>
@@ -530,10 +530,10 @@
         <v>3</v>
       </c>
       <c r="L2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -542,39 +542,41 @@
           <t>光電業右下</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
         <v>3</v>
       </c>
       <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" t="n">
         <v>3</v>
       </c>
-      <c r="F3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1</v>
-      </c>
       <c r="M3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -588,34 +590,34 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
         <v>3</v>
       </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
       <c r="K4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L4" t="n">
         <v>4</v>
       </c>
       <c r="M4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -626,37 +628,37 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -665,7 +667,9 @@
           <t>其他右下</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
@@ -685,10 +689,10 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -697,7 +701,7 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -711,7 +715,7 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -729,10 +733,10 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -752,34 +756,34 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G8" t="n">
         <v>4</v>
       </c>
-      <c r="F8" t="n">
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
         <v>8</v>
       </c>
-      <c r="G8" t="n">
-        <v>3</v>
-      </c>
-      <c r="H8" t="n">
+      <c r="J8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" t="n">
+        <v>5</v>
+      </c>
+      <c r="L8" t="n">
+        <v>8</v>
+      </c>
+      <c r="M8" t="n">
         <v>4</v>
-      </c>
-      <c r="I8" t="n">
-        <v>2</v>
-      </c>
-      <c r="J8" t="n">
-        <v>8</v>
-      </c>
-      <c r="K8" t="n">
-        <v>3</v>
-      </c>
-      <c r="L8" t="n">
-        <v>5</v>
-      </c>
-      <c r="M8" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -788,11 +792,9 @@
           <t>其他電子業右下</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0</v>
-      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
         <v>1</v>
@@ -804,7 +806,7 @@
         <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
         <v>1</v>
@@ -813,16 +815,16 @@
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -833,31 +835,31 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H10" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J10" t="n">
         <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L10" t="n">
         <v>2</v>
@@ -889,7 +891,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
         <v>1</v>
@@ -901,10 +903,10 @@
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -915,16 +917,16 @@
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -936,16 +938,16 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -956,16 +958,16 @@
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -974,10 +976,10 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -986,7 +988,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -997,37 +999,37 @@
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E14" t="n">
+        <v>5</v>
+      </c>
+      <c r="F14" t="n">
         <v>3</v>
-      </c>
-      <c r="F14" t="n">
-        <v>5</v>
       </c>
       <c r="G14" t="n">
         <v>4</v>
       </c>
       <c r="H14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1040,22 +1042,22 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="n">
         <v>3</v>
-      </c>
-      <c r="D15" t="n">
-        <v>1</v>
       </c>
       <c r="E15" t="n">
         <v>3</v>
       </c>
       <c r="F15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I15" t="n">
         <v>2</v>
@@ -1064,13 +1066,13 @@
         <v>2</v>
       </c>
       <c r="K15" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M15" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -1081,37 +1083,37 @@
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" t="n">
         <v>3</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
       </c>
       <c r="I16" t="n">
         <v>3</v>
       </c>
       <c r="J16" t="n">
+        <v>2</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2</v>
+      </c>
+      <c r="L16" t="n">
         <v>3</v>
       </c>
-      <c r="K16" t="n">
-        <v>2</v>
-      </c>
-      <c r="L16" t="n">
-        <v>2</v>
-      </c>
       <c r="M16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1175,13 +1177,13 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1190,10 +1192,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1204,7 +1206,7 @@
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -1222,7 +1224,7 @@
         <v>1</v>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1234,7 +1236,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1251,31 +1253,31 @@
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1284,7 +1286,9 @@
           <t>居家生活右下</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr"/>
+      <c r="B21" t="n">
+        <v>0</v>
+      </c>
       <c r="C21" t="n">
         <v>0</v>
       </c>
@@ -1292,10 +1296,10 @@
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -1316,7 +1320,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1383,16 +1387,16 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -1409,7 +1413,7 @@
       </c>
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
@@ -1424,13 +1428,13 @@
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24" t="n">
         <v>1</v>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -1468,13 +1472,13 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
       </c>
       <c r="K25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -1497,7 +1501,7 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -1506,19 +1510,19 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26" t="n">
         <v>1</v>
       </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -1532,10 +1536,10 @@
       </c>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -1573,22 +1577,22 @@
       </c>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -1603,7 +1607,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -1653,7 +1657,9 @@
           <t>文化創意業右下</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr"/>
+      <c r="B30" t="n">
+        <v>0</v>
+      </c>
       <c r="C30" t="n">
         <v>0</v>
       </c>
@@ -1661,13 +1667,13 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H30" t="n">
         <v>1</v>
@@ -1676,16 +1682,16 @@
         <v>1</v>
       </c>
       <c r="J30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -1696,10 +1702,10 @@
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -1901,37 +1907,37 @@
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F36" t="n">
         <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L36" t="n">
         <v>1</v>
       </c>
       <c r="M36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -1957,16 +1963,16 @@
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37" t="n">
         <v>1</v>
@@ -1983,22 +1989,22 @@
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -2147,10 +2153,10 @@
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
@@ -2162,22 +2168,22 @@
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I42" t="n">
         <v>2</v>
       </c>
       <c r="J42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L42" t="n">
         <v>1</v>
       </c>
       <c r="M42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2203,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -2229,37 +2235,37 @@
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D44" t="n">
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G44" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L44" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M44" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2272,22 +2278,22 @@
         <v>0</v>
       </c>
       <c r="C45" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I45" t="n">
         <v>1</v>
@@ -2296,13 +2302,13 @@
         <v>1</v>
       </c>
       <c r="K45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -2313,37 +2319,37 @@
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D46" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E46" t="n">
         <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K46" t="n">
         <v>1</v>
       </c>
       <c r="L46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -2360,31 +2366,31 @@
         <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F47" t="n">
         <v>1</v>
       </c>
       <c r="G47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -2413,13 +2419,13 @@
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
@@ -2436,7 +2442,7 @@
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D49" t="n">
         <v>0</v>
@@ -2445,10 +2451,10 @@
         <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
@@ -2483,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -2507,7 +2513,7 @@
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -2516,9 +2522,7 @@
           <t>綠能環保右下</t>
         </is>
       </c>
-      <c r="B51" t="n">
-        <v>0</v>
-      </c>
+      <c r="B51" t="inlineStr"/>
       <c r="C51" t="n">
         <v>0</v>
       </c>
@@ -2602,37 +2606,37 @@
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F53" t="n">
         <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L53" t="n">
         <v>1</v>
       </c>
       <c r="M53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -2693,13 +2697,13 @@
         <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G55" t="n">
         <v>1</v>
       </c>
       <c r="H55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I55" t="n">
         <v>0</v>
@@ -2711,7 +2715,7 @@
         <v>0</v>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M55" t="n">
         <v>1</v>
@@ -2740,19 +2744,19 @@
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
         <v>0</v>
@@ -2778,10 +2782,10 @@
         <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I57" t="n">
         <v>0</v>
@@ -2793,10 +2797,10 @@
         <v>0</v>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -2843,7 +2847,7 @@
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>貿易百貨右下</t>
+          <t>貿易百貨右上</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -2884,7 +2888,7 @@
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>貿易百貨平</t>
+          <t>貿易百貨右下</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -2942,13 +2946,13 @@
         <v>0</v>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H61" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I61" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J61" t="n">
         <v>1</v>
@@ -2960,7 +2964,7 @@
         <v>1</v>
       </c>
       <c r="M61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -2992,10 +2996,10 @@
         <v>0</v>
       </c>
       <c r="J62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
@@ -3015,7 +3019,7 @@
         <v>1</v>
       </c>
       <c r="D63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E63" t="n">
         <v>0</v>
@@ -3027,7 +3031,7 @@
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I63" t="n">
         <v>1</v>
@@ -3135,37 +3139,37 @@
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F66" t="n">
+        <v>1</v>
+      </c>
+      <c r="G66" t="n">
         <v>4</v>
-      </c>
-      <c r="G66" t="n">
-        <v>1</v>
       </c>
       <c r="H66" t="n">
         <v>4</v>
       </c>
       <c r="I66" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J66" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K66" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L66" t="n">
         <v>7</v>
       </c>
       <c r="M66" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67">
@@ -3174,12 +3178,14 @@
           <t>通信網路業右下</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr"/>
+      <c r="B67" t="n">
+        <v>0</v>
+      </c>
       <c r="C67" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D67" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E67" t="n">
         <v>0</v>
@@ -3194,19 +3200,19 @@
         <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -3220,34 +3226,34 @@
         <v>1</v>
       </c>
       <c r="D68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I68" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K68" t="n">
         <v>1</v>
       </c>
       <c r="L68" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -3381,13 +3387,13 @@
       </c>
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F72" t="n">
         <v>0</v>
@@ -3715,10 +3721,10 @@
         <v>0</v>
       </c>
       <c r="E80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -3748,15 +3754,17 @@
           <t>鋼鐵工業右下</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr"/>
+      <c r="B81" t="n">
+        <v>0</v>
+      </c>
       <c r="C81" t="n">
         <v>0</v>
       </c>
       <c r="D81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F81" t="n">
         <v>0</v>
@@ -3777,10 +3785,10 @@
         <v>0</v>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M81" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82">
@@ -3800,13 +3808,13 @@
         <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G82" t="n">
         <v>1</v>
       </c>
       <c r="H82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I82" t="n">
         <v>0</v>
@@ -3818,10 +3826,10 @@
         <v>0</v>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -3832,13 +3840,13 @@
       </c>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F83" t="n">
         <v>0</v>
@@ -3853,10 +3861,10 @@
         <v>0</v>
       </c>
       <c r="J83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L83" t="n">
         <v>0</v>
@@ -3917,13 +3925,13 @@
         <v>0</v>
       </c>
       <c r="D85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E85" t="n">
         <v>1</v>
       </c>
       <c r="F85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -3958,22 +3966,22 @@
         <v>0</v>
       </c>
       <c r="D86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -3994,14 +4002,12 @@
           <t>電子通路業右下</t>
         </is>
       </c>
-      <c r="B87" t="n">
-        <v>0</v>
-      </c>
+      <c r="B87" t="inlineStr"/>
       <c r="C87" t="n">
         <v>2</v>
       </c>
       <c r="D87" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E87" t="n">
         <v>0</v>
@@ -4022,13 +4028,13 @@
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L87" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -4039,13 +4045,13 @@
       </c>
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D88" t="n">
         <v>1</v>
       </c>
       <c r="E88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F88" t="n">
         <v>0</v>
@@ -4054,22 +4060,22 @@
         <v>0</v>
       </c>
       <c r="H88" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I88" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K88" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
@@ -4080,37 +4086,37 @@
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D89" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E89" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F89" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G89" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="H89" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="I89" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="J89" t="n">
         <v>11</v>
       </c>
       <c r="K89" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L89" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="M89" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90">
@@ -4124,34 +4130,34 @@
         <v>3</v>
       </c>
       <c r="D90" t="n">
+        <v>1</v>
+      </c>
+      <c r="E90" t="n">
+        <v>1</v>
+      </c>
+      <c r="F90" t="n">
         <v>3</v>
       </c>
-      <c r="E90" t="n">
-        <v>1</v>
-      </c>
-      <c r="F90" t="n">
-        <v>1</v>
-      </c>
       <c r="G90" t="n">
+        <v>2</v>
+      </c>
+      <c r="H90" t="n">
         <v>3</v>
       </c>
-      <c r="H90" t="n">
-        <v>2</v>
-      </c>
       <c r="I90" t="n">
+        <v>1</v>
+      </c>
+      <c r="J90" t="n">
+        <v>4</v>
+      </c>
+      <c r="K90" t="n">
+        <v>1</v>
+      </c>
+      <c r="L90" t="n">
+        <v>4</v>
+      </c>
+      <c r="M90" t="n">
         <v>3</v>
-      </c>
-      <c r="J90" t="n">
-        <v>0</v>
-      </c>
-      <c r="K90" t="n">
-        <v>3</v>
-      </c>
-      <c r="L90" t="n">
-        <v>1</v>
-      </c>
-      <c r="M90" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="91">
@@ -4162,34 +4168,34 @@
       </c>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="n">
+        <v>1</v>
+      </c>
+      <c r="D91" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" t="n">
+        <v>1</v>
+      </c>
+      <c r="G91" t="n">
         <v>4</v>
       </c>
-      <c r="D91" t="n">
-        <v>1</v>
-      </c>
-      <c r="E91" t="n">
-        <v>0</v>
-      </c>
-      <c r="F91" t="n">
-        <v>0</v>
-      </c>
-      <c r="G91" t="n">
-        <v>1</v>
-      </c>
       <c r="H91" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J91" t="n">
+        <v>2</v>
+      </c>
+      <c r="K91" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" t="n">
         <v>3</v>
-      </c>
-      <c r="K91" t="n">
-        <v>3</v>
-      </c>
-      <c r="L91" t="n">
-        <v>0</v>
       </c>
       <c r="M91" t="n">
         <v>2</v>
@@ -4203,7 +4209,7 @@
       </c>
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D92" t="n">
         <v>0</v>
@@ -4212,28 +4218,28 @@
         <v>0</v>
       </c>
       <c r="F92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H92" t="n">
         <v>2</v>
       </c>
       <c r="I92" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J92" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K92" t="n">
         <v>1</v>
       </c>
       <c r="L92" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M92" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
@@ -4242,9 +4248,7 @@
           <t>電機機械右下</t>
         </is>
       </c>
-      <c r="B93" t="n">
-        <v>0</v>
-      </c>
+      <c r="B93" t="inlineStr"/>
       <c r="C93" t="n">
         <v>1</v>
       </c>
@@ -4252,7 +4256,7 @@
         <v>1</v>
       </c>
       <c r="E93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F93" t="n">
         <v>0</v>
@@ -4287,7 +4291,7 @@
       </c>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D94" t="n">
         <v>0</v>
@@ -4296,28 +4300,28 @@
         <v>0</v>
       </c>
       <c r="F94" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K94" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L94" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
@@ -4328,37 +4332,37 @@
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D95" t="n">
+        <v>2</v>
+      </c>
+      <c r="E95" t="n">
+        <v>2</v>
+      </c>
+      <c r="F95" t="n">
         <v>3</v>
       </c>
-      <c r="E95" t="n">
-        <v>2</v>
-      </c>
-      <c r="F95" t="n">
-        <v>2</v>
-      </c>
       <c r="G95" t="n">
+        <v>1</v>
+      </c>
+      <c r="H95" t="n">
+        <v>2</v>
+      </c>
+      <c r="I95" t="n">
         <v>3</v>
       </c>
-      <c r="H95" t="n">
-        <v>1</v>
-      </c>
-      <c r="I95" t="n">
-        <v>2</v>
-      </c>
       <c r="J95" t="n">
+        <v>0</v>
+      </c>
+      <c r="K95" t="n">
         <v>3</v>
       </c>
-      <c r="K95" t="n">
-        <v>0</v>
-      </c>
       <c r="L95" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M95" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
@@ -4367,9 +4371,7 @@
           <t>電腦及週邊設備業右下</t>
         </is>
       </c>
-      <c r="B96" t="n">
-        <v>0</v>
-      </c>
+      <c r="B96" t="inlineStr"/>
       <c r="C96" t="n">
         <v>0</v>
       </c>
@@ -4377,19 +4379,19 @@
         <v>0</v>
       </c>
       <c r="E96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F96" t="n">
         <v>1</v>
       </c>
       <c r="G96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H96" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I96" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J96" t="n">
         <v>2</v>
@@ -4398,10 +4400,10 @@
         <v>2</v>
       </c>
       <c r="L96" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M96" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -4412,10 +4414,10 @@
       </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E97" t="n">
         <v>0</v>
@@ -4430,19 +4432,19 @@
         <v>0</v>
       </c>
       <c r="I97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J97" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98">
@@ -4509,7 +4511,7 @@
         <v>0</v>
       </c>
       <c r="H99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I99" t="n">
         <v>0</v>
@@ -4547,7 +4549,7 @@
         <v>0</v>
       </c>
       <c r="G100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H100" t="n">
         <v>0</v>

--- a/Result/analyze_1.xlsx
+++ b/Result/analyze_1.xlsx
@@ -441,57 +441,57 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-20</t>
         </is>
       </c>
     </row>
@@ -503,37 +503,37 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G2" t="n">
         <v>3</v>
       </c>
-      <c r="G2" t="n">
-        <v>2</v>
-      </c>
       <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
         <v>3</v>
       </c>
-      <c r="I2" t="n">
-        <v>1</v>
-      </c>
       <c r="J2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L2" t="n">
         <v>5</v>
       </c>
       <c r="M2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -542,38 +542,36 @@
           <t>光電業右下</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>0</v>
-      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M3" t="n">
         <v>1</v>
@@ -587,37 +585,37 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
         <v>3</v>
       </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
       <c r="J4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K4" t="n">
+        <v>4</v>
+      </c>
+      <c r="L4" t="n">
         <v>3</v>
       </c>
-      <c r="K4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L4" t="n">
-        <v>4</v>
-      </c>
       <c r="M4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -628,34 +626,34 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
         <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -689,7 +687,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -698,7 +696,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
         <v>1</v>
@@ -712,7 +710,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -730,10 +728,10 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -753,37 +751,37 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
+        <v>8</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" t="n">
         <v>4</v>
       </c>
-      <c r="E8" t="n">
+      <c r="G8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" t="n">
         <v>8</v>
       </c>
-      <c r="F8" t="n">
+      <c r="I8" t="n">
         <v>3</v>
       </c>
-      <c r="G8" t="n">
+      <c r="J8" t="n">
+        <v>5</v>
+      </c>
+      <c r="K8" t="n">
+        <v>8</v>
+      </c>
+      <c r="L8" t="n">
         <v>4</v>
       </c>
-      <c r="H8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" t="n">
-        <v>8</v>
-      </c>
-      <c r="J8" t="n">
-        <v>2</v>
-      </c>
-      <c r="K8" t="n">
-        <v>5</v>
-      </c>
-      <c r="L8" t="n">
-        <v>8</v>
-      </c>
       <c r="M8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -792,7 +790,9 @@
           <t>其他電子業右下</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
       <c r="C9" t="n">
         <v>1</v>
       </c>
@@ -803,25 +803,25 @@
         <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G9" t="n">
         <v>2</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M9" t="n">
         <v>2</v>
@@ -835,28 +835,28 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
         <v>2</v>
@@ -865,7 +865,7 @@
         <v>2</v>
       </c>
       <c r="M10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -888,7 +888,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
         <v>1</v>
@@ -900,13 +900,13 @@
         <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -915,15 +915,17 @@
           <t>化學工業右下</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
+      <c r="B12" t="n">
+        <v>0</v>
+      </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -935,16 +937,16 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -961,10 +963,10 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -973,10 +975,10 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -999,34 +1001,34 @@
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D14" t="n">
+        <v>4</v>
+      </c>
+      <c r="E14" t="n">
         <v>3</v>
       </c>
-      <c r="E14" t="n">
-        <v>5</v>
-      </c>
       <c r="F14" t="n">
+        <v>4</v>
+      </c>
+      <c r="G14" t="n">
         <v>3</v>
       </c>
-      <c r="G14" t="n">
-        <v>4</v>
-      </c>
       <c r="H14" t="n">
+        <v>2</v>
+      </c>
+      <c r="I14" t="n">
         <v>3</v>
       </c>
-      <c r="I14" t="n">
-        <v>2</v>
-      </c>
       <c r="J14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
         <v>1</v>
@@ -1042,37 +1044,37 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D15" t="n">
         <v>3</v>
       </c>
       <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2</v>
+      </c>
+      <c r="J15" t="n">
+        <v>4</v>
+      </c>
+      <c r="K15" t="n">
+        <v>6</v>
+      </c>
+      <c r="L15" t="n">
+        <v>4</v>
+      </c>
+      <c r="M15" t="n">
         <v>3</v>
-      </c>
-      <c r="F15" t="n">
-        <v>2</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>2</v>
-      </c>
-      <c r="I15" t="n">
-        <v>2</v>
-      </c>
-      <c r="J15" t="n">
-        <v>2</v>
-      </c>
-      <c r="K15" t="n">
-        <v>5</v>
-      </c>
-      <c r="L15" t="n">
-        <v>6</v>
-      </c>
-      <c r="M15" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -1083,37 +1085,37 @@
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="n">
         <v>3</v>
-      </c>
-      <c r="F16" t="n">
-        <v>1</v>
-      </c>
-      <c r="G16" t="n">
-        <v>1</v>
       </c>
       <c r="H16" t="n">
         <v>3</v>
       </c>
       <c r="I16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J16" t="n">
         <v>2</v>
       </c>
       <c r="K16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1174,13 +1176,13 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18" t="n">
         <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -1189,10 +1191,10 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -1218,10 +1220,10 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -1250,31 +1252,31 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -1286,17 +1288,15 @@
           <t>居家生活右下</t>
         </is>
       </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
+      <c r="B21" t="inlineStr"/>
       <c r="C21" t="n">
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -1314,13 +1314,13 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1384,16 +1384,16 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -1411,7 +1411,9 @@
           <t>建材營造右下</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="n">
+        <v>0</v>
+      </c>
       <c r="C24" t="n">
         <v>0</v>
       </c>
@@ -1425,13 +1427,13 @@
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24" t="n">
         <v>1</v>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1469,13 +1471,13 @@
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25" t="n">
         <v>1</v>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -1498,7 +1500,7 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -1507,19 +1509,19 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H26" t="n">
         <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -1580,16 +1582,16 @@
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -1604,10 +1606,10 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -1657,20 +1659,18 @@
           <t>文化創意業右下</t>
         </is>
       </c>
-      <c r="B30" t="n">
-        <v>0</v>
-      </c>
+      <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G30" t="n">
         <v>1</v>
@@ -1679,16 +1679,16 @@
         <v>1</v>
       </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -1702,7 +1702,7 @@
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
@@ -1907,34 +1907,34 @@
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
         <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K36" t="n">
         <v>1</v>
       </c>
       <c r="L36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
@@ -1957,19 +1957,19 @@
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K37" t="n">
         <v>1</v>
@@ -1978,7 +1978,7 @@
         <v>1</v>
       </c>
       <c r="M37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -1992,16 +1992,16 @@
         <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -2153,7 +2153,7 @@
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D42" t="n">
         <v>0</v>
@@ -2165,22 +2165,22 @@
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H42" t="n">
         <v>1</v>
       </c>
       <c r="I42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K42" t="n">
         <v>1</v>
       </c>
       <c r="L42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
@@ -2206,13 +2206,13 @@
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -2238,31 +2238,31 @@
         <v>1</v>
       </c>
       <c r="D44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F44" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K44" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L44" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
@@ -2278,19 +2278,19 @@
         <v>0</v>
       </c>
       <c r="C45" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H45" t="n">
         <v>1</v>
@@ -2299,7 +2299,7 @@
         <v>1</v>
       </c>
       <c r="J45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K45" t="n">
         <v>3</v>
@@ -2308,7 +2308,7 @@
         <v>2</v>
       </c>
       <c r="M45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -2319,37 +2319,37 @@
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D46" t="n">
         <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J46" t="n">
         <v>1</v>
       </c>
       <c r="K46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -2363,13 +2363,13 @@
         <v>0</v>
       </c>
       <c r="D47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E47" t="n">
         <v>1</v>
       </c>
       <c r="F47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -2378,7 +2378,7 @@
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -2387,7 +2387,7 @@
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
@@ -2399,7 +2399,9 @@
           <t>紡織纖維右下</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr"/>
+      <c r="B48" t="n">
+        <v>0</v>
+      </c>
       <c r="C48" t="n">
         <v>0</v>
       </c>
@@ -2416,13 +2418,13 @@
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
@@ -2448,16 +2450,16 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I49" t="n">
         <v>0</v>
@@ -2466,7 +2468,7 @@
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
@@ -2486,10 +2488,10 @@
         <v>0</v>
       </c>
       <c r="D50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -2510,10 +2512,10 @@
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -2606,34 +2608,34 @@
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E53" t="n">
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I53" t="n">
         <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K53" t="n">
         <v>1</v>
       </c>
       <c r="L53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
         <v>0</v>
@@ -2694,13 +2696,13 @@
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F55" t="n">
         <v>1</v>
       </c>
       <c r="G55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
@@ -2712,13 +2714,13 @@
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L55" t="n">
         <v>1</v>
       </c>
       <c r="M55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -2741,19 +2743,19 @@
         <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I56" t="n">
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
@@ -2779,10 +2781,10 @@
         <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -2794,10 +2796,10 @@
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
         <v>0</v>
@@ -2943,16 +2945,16 @@
         <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G61" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H61" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J61" t="n">
         <v>1</v>
@@ -2961,10 +2963,10 @@
         <v>1</v>
       </c>
       <c r="L61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -2993,10 +2995,10 @@
         <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K62" t="n">
         <v>0</v>
@@ -3005,7 +3007,7 @@
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -3016,7 +3018,7 @@
       </c>
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D63" t="n">
         <v>0</v>
@@ -3028,13 +3030,13 @@
         <v>0</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -3139,37 +3141,37 @@
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D66" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E66" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F66" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G66" t="n">
         <v>4</v>
       </c>
       <c r="H66" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I66" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J66" t="n">
+        <v>8</v>
+      </c>
+      <c r="K66" t="n">
         <v>7</v>
       </c>
-      <c r="K66" t="n">
-        <v>8</v>
-      </c>
       <c r="L66" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M66" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -3178,11 +3180,9 @@
           <t>通信網路業右下</t>
         </is>
       </c>
-      <c r="B67" t="n">
-        <v>0</v>
-      </c>
+      <c r="B67" t="inlineStr"/>
       <c r="C67" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D67" t="n">
         <v>0</v>
@@ -3194,25 +3194,25 @@
         <v>0</v>
       </c>
       <c r="G67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -3223,31 +3223,31 @@
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E68" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G68" t="n">
         <v>1</v>
       </c>
       <c r="H68" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J68" t="n">
         <v>1</v>
       </c>
       <c r="K68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
@@ -3385,12 +3385,14 @@
           <t>運動休閒右下</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr"/>
+      <c r="B72" t="n">
+        <v>0</v>
+      </c>
       <c r="C72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E72" t="n">
         <v>0</v>
@@ -3508,7 +3510,9 @@
           <t>金融保險右下</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr"/>
+      <c r="B75" t="n">
+        <v>0</v>
+      </c>
       <c r="C75" t="n">
         <v>0</v>
       </c>
@@ -3718,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="D80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F80" t="n">
         <v>0</v>
@@ -3754,14 +3758,12 @@
           <t>鋼鐵工業右下</t>
         </is>
       </c>
-      <c r="B81" t="n">
-        <v>0</v>
-      </c>
+      <c r="B81" t="inlineStr"/>
       <c r="C81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E81" t="n">
         <v>0</v>
@@ -3782,13 +3784,13 @@
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -3805,13 +3807,13 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
         <v>1</v>
       </c>
       <c r="G82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H82" t="n">
         <v>0</v>
@@ -3826,10 +3828,10 @@
         <v>0</v>
       </c>
       <c r="L82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -3840,10 +3842,10 @@
       </c>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E83" t="n">
         <v>0</v>
@@ -3861,7 +3863,7 @@
         <v>0</v>
       </c>
       <c r="J83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K83" t="n">
         <v>0</v>
@@ -3922,13 +3924,13 @@
       </c>
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D85" t="n">
         <v>1</v>
       </c>
       <c r="E85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F85" t="n">
         <v>0</v>
@@ -3940,7 +3942,7 @@
         <v>0</v>
       </c>
       <c r="I85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -3963,22 +3965,22 @@
       </c>
       <c r="B86" t="inlineStr"/>
       <c r="C86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I86" t="n">
         <v>0</v>
@@ -4004,7 +4006,7 @@
       </c>
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D87" t="n">
         <v>0</v>
@@ -4025,13 +4027,13 @@
         <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K87" t="n">
         <v>1</v>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M87" t="n">
         <v>0</v>
@@ -4045,10 +4047,10 @@
       </c>
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E88" t="n">
         <v>0</v>
@@ -4057,25 +4059,25 @@
         <v>0</v>
       </c>
       <c r="G88" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H88" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J88" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -4086,37 +4088,37 @@
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D89" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E89" t="n">
+        <v>7</v>
+      </c>
+      <c r="F89" t="n">
+        <v>11</v>
+      </c>
+      <c r="G89" t="n">
+        <v>16</v>
+      </c>
+      <c r="H89" t="n">
+        <v>10</v>
+      </c>
+      <c r="I89" t="n">
+        <v>9</v>
+      </c>
+      <c r="J89" t="n">
+        <v>9</v>
+      </c>
+      <c r="K89" t="n">
+        <v>17</v>
+      </c>
+      <c r="L89" t="n">
+        <v>2</v>
+      </c>
+      <c r="M89" t="n">
         <v>4</v>
-      </c>
-      <c r="F89" t="n">
-        <v>7</v>
-      </c>
-      <c r="G89" t="n">
-        <v>12</v>
-      </c>
-      <c r="H89" t="n">
-        <v>17</v>
-      </c>
-      <c r="I89" t="n">
-        <v>11</v>
-      </c>
-      <c r="J89" t="n">
-        <v>11</v>
-      </c>
-      <c r="K89" t="n">
-        <v>12</v>
-      </c>
-      <c r="L89" t="n">
-        <v>18</v>
-      </c>
-      <c r="M89" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="90">
@@ -4125,39 +4127,41 @@
           <t>電子零組件業右下</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr"/>
+      <c r="B90" t="n">
+        <v>0</v>
+      </c>
       <c r="C90" t="n">
+        <v>1</v>
+      </c>
+      <c r="D90" t="n">
+        <v>1</v>
+      </c>
+      <c r="E90" t="n">
         <v>3</v>
       </c>
-      <c r="D90" t="n">
-        <v>1</v>
-      </c>
-      <c r="E90" t="n">
-        <v>1</v>
-      </c>
       <c r="F90" t="n">
+        <v>2</v>
+      </c>
+      <c r="G90" t="n">
         <v>3</v>
       </c>
-      <c r="G90" t="n">
-        <v>2</v>
-      </c>
       <c r="H90" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I90" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J90" t="n">
+        <v>1</v>
+      </c>
+      <c r="K90" t="n">
         <v>4</v>
-      </c>
-      <c r="K90" t="n">
-        <v>1</v>
       </c>
       <c r="L90" t="n">
         <v>4</v>
       </c>
       <c r="M90" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
@@ -4168,37 +4172,37 @@
       </c>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D91" t="n">
         <v>0</v>
       </c>
       <c r="E91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F91" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G91" t="n">
+        <v>3</v>
+      </c>
+      <c r="H91" t="n">
+        <v>1</v>
+      </c>
+      <c r="I91" t="n">
         <v>4</v>
       </c>
-      <c r="H91" t="n">
-        <v>2</v>
-      </c>
-      <c r="I91" t="n">
-        <v>2</v>
-      </c>
       <c r="J91" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K91" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L91" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M91" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
@@ -4215,16 +4219,16 @@
         <v>0</v>
       </c>
       <c r="E92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G92" t="n">
         <v>2</v>
       </c>
       <c r="H92" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I92" t="n">
         <v>1</v>
@@ -4233,13 +4237,13 @@
         <v>1</v>
       </c>
       <c r="K92" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L92" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -4253,7 +4257,7 @@
         <v>1</v>
       </c>
       <c r="D93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E93" t="n">
         <v>0</v>
@@ -4280,7 +4284,7 @@
         <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="94">
@@ -4297,31 +4301,31 @@
         <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I94" t="n">
         <v>1</v>
       </c>
       <c r="J94" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K94" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -4332,37 +4336,37 @@
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D95" t="n">
         <v>2</v>
       </c>
       <c r="E95" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F95" t="n">
+        <v>1</v>
+      </c>
+      <c r="G95" t="n">
+        <v>2</v>
+      </c>
+      <c r="H95" t="n">
         <v>3</v>
       </c>
-      <c r="G95" t="n">
-        <v>1</v>
-      </c>
-      <c r="H95" t="n">
-        <v>2</v>
-      </c>
       <c r="I95" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" t="n">
         <v>3</v>
       </c>
-      <c r="J95" t="n">
-        <v>0</v>
-      </c>
       <c r="K95" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L95" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -4376,31 +4380,31 @@
         <v>0</v>
       </c>
       <c r="D96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E96" t="n">
         <v>1</v>
       </c>
       <c r="F96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G96" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H96" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I96" t="n">
+        <v>2</v>
+      </c>
+      <c r="J96" t="n">
         <v>3</v>
       </c>
-      <c r="J96" t="n">
-        <v>2</v>
-      </c>
       <c r="K96" t="n">
         <v>2</v>
       </c>
       <c r="L96" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
         <v>0</v>
@@ -4414,7 +4418,7 @@
       </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D97" t="n">
         <v>0</v>
@@ -4429,7 +4433,7 @@
         <v>0</v>
       </c>
       <c r="H97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I97" t="n">
         <v>1</v>
@@ -4441,7 +4445,7 @@
         <v>2</v>
       </c>
       <c r="L97" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M97" t="n">
         <v>1</v>
@@ -4505,7 +4509,7 @@
         <v>0</v>
       </c>
       <c r="F99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -4549,7 +4553,7 @@
         <v>0</v>
       </c>
       <c r="G100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H100" t="n">
         <v>0</v>

--- a/Result/analyze_1.xlsx
+++ b/Result/analyze_1.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M100"/>
+  <dimension ref="A1:M101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,57 +441,57 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
     </row>
@@ -503,37 +503,37 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
         <v>2</v>
       </c>
       <c r="G2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J2" t="n">
+        <v>7</v>
+      </c>
+      <c r="K2" t="n">
+        <v>6</v>
+      </c>
+      <c r="L2" t="n">
         <v>4</v>
       </c>
-      <c r="K2" t="n">
+      <c r="M2" t="n">
         <v>5</v>
-      </c>
-      <c r="L2" t="n">
-        <v>5</v>
-      </c>
-      <c r="M2" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -542,39 +542,41 @@
           <t>光電業右下</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
       <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J3" t="n">
         <v>4</v>
       </c>
-      <c r="D3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>2</v>
-      </c>
       <c r="K3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
         <v>1</v>
       </c>
       <c r="M3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -585,34 +587,34 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J4" t="n">
         <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>1</v>
@@ -626,37 +628,37 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
         <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
         <v>3</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -665,9 +667,7 @@
           <t>其他右下</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>0</v>
-      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
         <v>0</v>
       </c>
@@ -681,7 +681,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -693,13 +693,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
         <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -725,10 +725,10 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -740,7 +740,7 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -751,37 +751,37 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
+        <v>8</v>
+      </c>
+      <c r="D8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" t="n">
         <v>4</v>
       </c>
-      <c r="D8" t="n">
+      <c r="F8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" t="n">
         <v>8</v>
       </c>
-      <c r="E8" t="n">
+      <c r="H8" t="n">
         <v>3</v>
       </c>
-      <c r="F8" t="n">
+      <c r="I8" t="n">
+        <v>5</v>
+      </c>
+      <c r="J8" t="n">
+        <v>8</v>
+      </c>
+      <c r="K8" t="n">
         <v>4</v>
       </c>
-      <c r="G8" t="n">
-        <v>2</v>
-      </c>
-      <c r="H8" t="n">
-        <v>8</v>
-      </c>
-      <c r="I8" t="n">
-        <v>3</v>
-      </c>
-      <c r="J8" t="n">
-        <v>5</v>
-      </c>
-      <c r="K8" t="n">
-        <v>8</v>
-      </c>
       <c r="L8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -800,31 +800,31 @@
         <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
         <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -838,34 +838,34 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" t="n">
         <v>3</v>
       </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>1</v>
-      </c>
-      <c r="I10" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>2</v>
-      </c>
       <c r="L10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -885,7 +885,7 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" t="n">
         <v>1</v>
@@ -897,16 +897,16 @@
         <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -915,14 +915,12 @@
           <t>化學工業右下</t>
         </is>
       </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -934,16 +932,16 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -960,10 +958,10 @@
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -972,10 +970,10 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -1001,28 +999,28 @@
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E14" t="n">
         <v>4</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>3</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
+        <v>2</v>
+      </c>
+      <c r="H14" t="n">
         <v>4</v>
       </c>
-      <c r="G14" t="n">
-        <v>3</v>
-      </c>
-      <c r="H14" t="n">
-        <v>2</v>
-      </c>
       <c r="I14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
@@ -1031,7 +1029,7 @@
         <v>1</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1040,41 +1038,39 @@
           <t>半導體業右下</t>
         </is>
       </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
+      <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
         <v>3</v>
       </c>
       <c r="D15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" t="n">
         <v>3</v>
       </c>
-      <c r="E15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>2</v>
-      </c>
       <c r="H15" t="n">
         <v>2</v>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J15" t="n">
+        <v>6</v>
+      </c>
+      <c r="K15" t="n">
         <v>4</v>
       </c>
-      <c r="K15" t="n">
-        <v>6</v>
-      </c>
       <c r="L15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M15" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
@@ -1085,37 +1081,37 @@
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" t="n">
         <v>3</v>
       </c>
-      <c r="E16" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" t="n">
-        <v>1</v>
-      </c>
       <c r="G16" t="n">
+        <v>2</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2</v>
+      </c>
+      <c r="J16" t="n">
+        <v>4</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
         <v>3</v>
-      </c>
-      <c r="H16" t="n">
-        <v>3</v>
-      </c>
-      <c r="I16" t="n">
-        <v>2</v>
-      </c>
-      <c r="J16" t="n">
-        <v>2</v>
-      </c>
-      <c r="K16" t="n">
-        <v>4</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1173,13 +1169,13 @@
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18" t="n">
         <v>1</v>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -1188,16 +1184,16 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -1217,10 +1213,10 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -1249,31 +1245,31 @@
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -1288,12 +1284,14 @@
           <t>居家生活右下</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr"/>
+      <c r="B21" t="n">
+        <v>0</v>
+      </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -1311,16 +1309,16 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1381,16 +1379,16 @@
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1411,9 +1409,7 @@
           <t>建材營造右下</t>
         </is>
       </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
+      <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
         <v>0</v>
       </c>
@@ -1424,13 +1420,13 @@
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -1445,7 +1441,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1468,13 +1464,13 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25" t="n">
         <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1497,7 +1493,7 @@
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
@@ -1506,19 +1502,19 @@
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26" t="n">
         <v>1</v>
       </c>
       <c r="H26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -1527,7 +1523,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1536,9 +1532,11 @@
           <t>數位雲端右下</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr"/>
+      <c r="B27" t="n">
+        <v>0</v>
+      </c>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
@@ -1585,10 +1583,10 @@
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1603,10 +1601,10 @@
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -1650,7 +1648,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -1661,13 +1659,13 @@
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F30" t="n">
         <v>1</v>
@@ -1676,16 +1674,16 @@
         <v>1</v>
       </c>
       <c r="H30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -1907,31 +1905,31 @@
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D36" t="n">
         <v>1</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
         <v>1</v>
       </c>
       <c r="K36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -1946,7 +1944,9 @@
           <t>汽車工業右下</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr"/>
+      <c r="B37" t="n">
+        <v>0</v>
+      </c>
       <c r="C37" t="n">
         <v>0</v>
       </c>
@@ -1954,19 +1954,19 @@
         <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F37" t="n">
         <v>1</v>
       </c>
       <c r="G37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J37" t="n">
         <v>1</v>
@@ -1975,7 +1975,7 @@
         <v>1</v>
       </c>
       <c r="L37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
@@ -1989,10 +1989,10 @@
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
@@ -2101,7 +2101,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2162,22 +2162,22 @@
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G42" t="n">
         <v>1</v>
       </c>
       <c r="H42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J42" t="n">
         <v>1</v>
       </c>
       <c r="K42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
@@ -2235,37 +2235,37 @@
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F44" t="n">
         <v>3</v>
       </c>
       <c r="G44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J44" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K44" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2274,20 +2274,18 @@
           <t>生技醫療業右下</t>
         </is>
       </c>
-      <c r="B45" t="n">
-        <v>0</v>
-      </c>
+      <c r="B45" t="inlineStr"/>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E45" t="n">
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G45" t="n">
         <v>1</v>
@@ -2296,19 +2294,19 @@
         <v>1</v>
       </c>
       <c r="I45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J45" t="n">
         <v>3</v>
       </c>
       <c r="K45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M45" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="46">
@@ -2322,34 +2320,34 @@
         <v>0</v>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I46" t="n">
         <v>1</v>
       </c>
       <c r="J46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -2360,19 +2358,19 @@
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D47" t="n">
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F47" t="n">
         <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
@@ -2381,7 +2379,7 @@
         <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
@@ -2415,10 +2413,10 @@
         <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I48" t="n">
         <v>0</v>
@@ -2447,10 +2445,10 @@
         <v>0</v>
       </c>
       <c r="D49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -2459,7 +2457,7 @@
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I49" t="n">
         <v>0</v>
@@ -2468,7 +2466,7 @@
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
@@ -2485,10 +2483,10 @@
       </c>
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E50" t="n">
         <v>0</v>
@@ -2509,13 +2507,13 @@
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -2608,31 +2606,31 @@
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D53" t="n">
         <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J53" t="n">
         <v>1</v>
       </c>
       <c r="K53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
@@ -2693,13 +2691,13 @@
         <v>0</v>
       </c>
       <c r="D55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E55" t="n">
         <v>1</v>
       </c>
       <c r="F55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -2711,13 +2709,13 @@
         <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K55" t="n">
         <v>1</v>
       </c>
       <c r="L55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
         <v>0</v>
@@ -2740,19 +2738,19 @@
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -2778,10 +2776,10 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -2793,10 +2791,10 @@
         <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
@@ -2931,7 +2929,7 @@
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>資訊服務業右上</t>
+          <t>貿易百貨平</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
@@ -2945,34 +2943,34 @@
         <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G61" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>資訊服務業右下</t>
+          <t>資訊服務業右上</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
@@ -2983,28 +2981,28 @@
         <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F62" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I62" t="n">
         <v>1</v>
       </c>
       <c r="J62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K62" t="n">
         <v>0</v>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M62" t="n">
         <v>1</v>
@@ -3013,7 +3011,7 @@
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>資訊服務業平</t>
+          <t>資訊服務業右下</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
@@ -3030,7 +3028,7 @@
         <v>0</v>
       </c>
       <c r="G63" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H63" t="n">
         <v>1</v>
@@ -3045,7 +3043,7 @@
         <v>0</v>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M63" t="n">
         <v>0</v>
@@ -3054,7 +3052,7 @@
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>農業科技業右上</t>
+          <t>資訊服務業平</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
@@ -3068,7 +3066,7 @@
         <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -3095,7 +3093,7 @@
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>農業科技業右下</t>
+          <t>農業科技業右上</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
@@ -3136,39 +3134,39 @@
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>通信網路業右上</t>
+          <t>農業科技業右下</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D66" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F66" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I66" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J66" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L66" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
         <v>0</v>
@@ -3177,33 +3175,33 @@
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>通信網路業右下</t>
+          <t>通信網路業右上</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E67" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F67" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H67" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I67" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J67" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K67" t="n">
         <v>2</v>
@@ -3212,13 +3210,13 @@
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>通信網路業平</t>
+          <t>通信網路業右下</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
@@ -3226,7 +3224,7 @@
         <v>0</v>
       </c>
       <c r="D68" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E68" t="n">
         <v>0</v>
@@ -3244,45 +3242,45 @@
         <v>1</v>
       </c>
       <c r="J68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K68" t="n">
         <v>0</v>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>造紙工業右下</t>
+          <t>通信網路業平</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D69" t="n">
         <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -3300,7 +3298,7 @@
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>造紙工業平</t>
+          <t>造紙工業右下</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
@@ -3341,7 +3339,7 @@
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>運動休閒右上</t>
+          <t>造紙工業平</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
@@ -3382,14 +3380,12 @@
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>運動休閒右下</t>
-        </is>
-      </c>
-      <c r="B72" t="n">
-        <v>0</v>
-      </c>
+          <t>運動休閒右上</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr"/>
       <c r="C72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D72" t="n">
         <v>0</v>
@@ -3425,7 +3421,7 @@
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>運動休閒平</t>
+          <t>運動休閒右下</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
@@ -3466,7 +3462,7 @@
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>金融保險右上</t>
+          <t>運動休閒平</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
@@ -3501,18 +3497,16 @@
         <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>金融保險右下</t>
-        </is>
-      </c>
-      <c r="B75" t="n">
-        <v>0</v>
-      </c>
+          <t>金融保險右上</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr"/>
       <c r="C75" t="n">
         <v>0</v>
       </c>
@@ -3550,7 +3544,7 @@
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>金融保險平</t>
+          <t>金融保險右下</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
@@ -3591,7 +3585,7 @@
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>金融業右上</t>
+          <t>金融保險平</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
@@ -3632,7 +3626,7 @@
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>金融業右下</t>
+          <t>金融業右上</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
@@ -3673,7 +3667,7 @@
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>金融業平</t>
+          <t>金融業右下</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
@@ -3714,7 +3708,7 @@
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業右上</t>
+          <t>金融業平</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
@@ -3722,7 +3716,7 @@
         <v>0</v>
       </c>
       <c r="D80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E80" t="n">
         <v>0</v>
@@ -3755,7 +3749,7 @@
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業右下</t>
+          <t>鋼鐵工業右上</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
@@ -3784,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L81" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
         <v>0</v>
@@ -3796,7 +3790,7 @@
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業平</t>
+          <t>鋼鐵工業右下</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
@@ -3807,10 +3801,10 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -3822,10 +3816,10 @@
         <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K82" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L82" t="n">
         <v>0</v>
@@ -3837,18 +3831,18 @@
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>電器電纜右上</t>
+          <t>鋼鐵工業平</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F83" t="n">
         <v>0</v>
@@ -3878,7 +3872,7 @@
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>電器電纜右下</t>
+          <t>電器電纜右上</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
@@ -3919,15 +3913,15 @@
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>電器電纜平</t>
+          <t>電器電纜右下</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E85" t="n">
         <v>0</v>
@@ -3942,7 +3936,7 @@
         <v>0</v>
       </c>
       <c r="I85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -3960,7 +3954,7 @@
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>電子通路業右上</t>
+          <t>電器電纜平</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
@@ -3971,16 +3965,16 @@
         <v>0</v>
       </c>
       <c r="E86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F86" t="n">
         <v>0</v>
       </c>
       <c r="G86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I86" t="n">
         <v>0</v>
@@ -4001,21 +3995,21 @@
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>電子通路業右下</t>
+          <t>電子通路業右上</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E87" t="n">
         <v>0</v>
       </c>
       <c r="F87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -4027,22 +4021,22 @@
         <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>電子通路業平</t>
+          <t>電子通路業右下</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
@@ -4059,13 +4053,13 @@
         <v>0</v>
       </c>
       <c r="G88" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I88" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -4083,123 +4077,121 @@
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業右上</t>
+          <t>電子通路業平</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D89" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E89" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F89" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="G89" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="H89" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="I89" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J89" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="K89" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="L89" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業右下</t>
-        </is>
-      </c>
-      <c r="B90" t="n">
-        <v>0</v>
-      </c>
+          <t>電子零組件業右上</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr"/>
       <c r="C90" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D90" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E90" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="F90" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G90" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="H90" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I90" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J90" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="K90" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L90" t="n">
         <v>4</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業平</t>
+          <t>電子零組件業右下</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D91" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F91" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G91" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H91" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I91" t="n">
+        <v>1</v>
+      </c>
+      <c r="J91" t="n">
         <v>4</v>
-      </c>
-      <c r="J91" t="n">
-        <v>3</v>
       </c>
       <c r="K91" t="n">
         <v>4</v>
       </c>
       <c r="L91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
         <v>1</v>
@@ -4208,7 +4200,7 @@
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>電機機械右上</t>
+          <t>電子零組件業平</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
@@ -4216,81 +4208,81 @@
         <v>0</v>
       </c>
       <c r="D92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E92" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F92" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G92" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H92" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J92" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K92" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L92" t="n">
         <v>1</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>電機機械右下</t>
+          <t>電機機械右上</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E93" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F93" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G93" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I93" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J93" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L93" t="n">
         <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>電機機械平</t>
+          <t>電機機械右下</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
@@ -4301,119 +4293,119 @@
         <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
       </c>
       <c r="H94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右上</t>
+          <t>電機機械平</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D95" t="n">
         <v>2</v>
       </c>
       <c r="E95" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G95" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H95" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I95" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J95" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K95" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右下</t>
+          <t>電腦及週邊設備業右上</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D96" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E96" t="n">
         <v>1</v>
       </c>
       <c r="F96" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G96" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" t="n">
         <v>3</v>
       </c>
-      <c r="I96" t="n">
-        <v>2</v>
-      </c>
       <c r="J96" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K96" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L96" t="n">
         <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業平</t>
+          <t>電腦及週邊設備業右下</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
@@ -4421,31 +4413,31 @@
         <v>1</v>
       </c>
       <c r="D97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E97" t="n">
         <v>0</v>
       </c>
       <c r="F97" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G97" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K97" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
         <v>1</v>
@@ -4454,7 +4446,7 @@
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>食品工業右上</t>
+          <t>電腦及週邊設備業平</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
@@ -4471,31 +4463,31 @@
         <v>0</v>
       </c>
       <c r="G98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I98" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>食品工業右下</t>
+          <t>食品工業右上</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
@@ -4509,7 +4501,7 @@
         <v>0</v>
       </c>
       <c r="F99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -4536,7 +4528,7 @@
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>食品工業平</t>
+          <t>食品工業右下</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
@@ -4571,6 +4563,47 @@
         <v>0</v>
       </c>
       <c r="M100" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="inlineStr">
+        <is>
+          <t>食品工業平</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr"/>
+      <c r="C101" t="n">
+        <v>0</v>
+      </c>
+      <c r="D101" t="n">
+        <v>0</v>
+      </c>
+      <c r="E101" t="n">
+        <v>0</v>
+      </c>
+      <c r="F101" t="n">
+        <v>0</v>
+      </c>
+      <c r="G101" t="n">
+        <v>0</v>
+      </c>
+      <c r="H101" t="n">
+        <v>0</v>
+      </c>
+      <c r="I101" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" t="n">
+        <v>0</v>
+      </c>
+      <c r="K101" t="n">
+        <v>0</v>
+      </c>
+      <c r="L101" t="n">
+        <v>0</v>
+      </c>
+      <c r="M101" t="n">
         <v>0</v>
       </c>
     </row>

--- a/Result/analyze_1.xlsx
+++ b/Result/analyze_1.xlsx
@@ -441,57 +441,57 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-22</t>
         </is>
       </c>
     </row>
@@ -503,37 +503,37 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" t="n">
         <v>3</v>
       </c>
-      <c r="E2" t="n">
-        <v>2</v>
-      </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J2" t="n">
+        <v>6</v>
+      </c>
+      <c r="K2" t="n">
         <v>5</v>
       </c>
-      <c r="I2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J2" t="n">
-        <v>7</v>
-      </c>
-      <c r="K2" t="n">
-        <v>6</v>
-      </c>
       <c r="L2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -542,14 +542,12 @@
           <t>光電業右下</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>0</v>
-      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -561,22 +559,22 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K3" t="n">
         <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -590,10 +588,10 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -605,19 +603,19 @@
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -631,34 +629,34 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
         <v>3</v>
       </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
       <c r="M5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -678,10 +676,10 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -690,13 +688,13 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
         <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -722,10 +720,10 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -737,10 +735,10 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -751,34 +749,34 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
         <v>3</v>
       </c>
       <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>8</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" t="n">
+        <v>5</v>
+      </c>
+      <c r="I8" t="n">
+        <v>8</v>
+      </c>
+      <c r="J8" t="n">
         <v>4</v>
       </c>
-      <c r="F8" t="n">
-        <v>2</v>
-      </c>
-      <c r="G8" t="n">
-        <v>8</v>
-      </c>
-      <c r="H8" t="n">
-        <v>3</v>
-      </c>
-      <c r="I8" t="n">
-        <v>5</v>
-      </c>
-      <c r="J8" t="n">
-        <v>8</v>
-      </c>
       <c r="K8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M8" t="n">
         <v>2</v>
@@ -797,22 +795,22 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E9" t="n">
         <v>2</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
         <v>1</v>
@@ -821,7 +819,7 @@
         <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -835,13 +833,13 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
         <v>1</v>
@@ -850,22 +848,22 @@
         <v>2</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I10" t="n">
         <v>2</v>
       </c>
       <c r="J10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -882,7 +880,7 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
         <v>1</v>
@@ -894,16 +892,16 @@
         <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -917,7 +915,7 @@
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -929,16 +927,16 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
         <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -958,7 +956,7 @@
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -967,10 +965,10 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -999,25 +997,25 @@
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D14" t="n">
+        <v>4</v>
+      </c>
+      <c r="E14" t="n">
         <v>3</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G14" t="n">
         <v>4</v>
       </c>
-      <c r="F14" t="n">
-        <v>3</v>
-      </c>
-      <c r="G14" t="n">
-        <v>2</v>
-      </c>
       <c r="H14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -1026,10 +1024,10 @@
         <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1040,37 +1038,37 @@
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" t="n">
         <v>3</v>
       </c>
-      <c r="D15" t="n">
-        <v>2</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>2</v>
-      </c>
       <c r="G15" t="n">
+        <v>2</v>
+      </c>
+      <c r="H15" t="n">
+        <v>5</v>
+      </c>
+      <c r="I15" t="n">
+        <v>6</v>
+      </c>
+      <c r="J15" t="n">
+        <v>4</v>
+      </c>
+      <c r="K15" t="n">
         <v>3</v>
       </c>
-      <c r="H15" t="n">
-        <v>2</v>
-      </c>
-      <c r="I15" t="n">
-        <v>5</v>
-      </c>
-      <c r="J15" t="n">
-        <v>6</v>
-      </c>
-      <c r="K15" t="n">
-        <v>4</v>
-      </c>
       <c r="L15" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="M15" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1081,37 +1079,37 @@
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="n">
         <v>3</v>
       </c>
-      <c r="D16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" t="n">
-        <v>1</v>
-      </c>
       <c r="F16" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2</v>
+      </c>
+      <c r="I16" t="n">
+        <v>4</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
         <v>3</v>
       </c>
-      <c r="G16" t="n">
-        <v>2</v>
-      </c>
-      <c r="H16" t="n">
-        <v>2</v>
-      </c>
-      <c r="I16" t="n">
-        <v>2</v>
-      </c>
-      <c r="J16" t="n">
-        <v>4</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
       <c r="M16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -1166,13 +1164,13 @@
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E18" t="n">
         <v>1</v>
       </c>
       <c r="F18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -1181,19 +1179,19 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1210,10 +1208,10 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -1245,28 +1243,28 @@
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -1284,11 +1282,9 @@
           <t>居家生活右下</t>
         </is>
       </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
+      <c r="B21" t="inlineStr"/>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -1306,19 +1302,19 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1376,16 +1372,16 @@
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -1409,7 +1405,9 @@
           <t>建材營造右下</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="n">
+        <v>0</v>
+      </c>
       <c r="C24" t="n">
         <v>0</v>
       </c>
@@ -1417,13 +1415,13 @@
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24" t="n">
         <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1438,10 +1436,10 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1461,13 +1459,13 @@
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
@@ -1496,22 +1494,22 @@
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F26" t="n">
         <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1520,7 +1518,7 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M26" t="n">
         <v>1</v>
@@ -1532,9 +1530,7 @@
           <t>數位雲端右下</t>
         </is>
       </c>
-      <c r="B27" t="n">
-        <v>0</v>
-      </c>
+      <c r="B27" t="inlineStr"/>
       <c r="C27" t="n">
         <v>0</v>
       </c>
@@ -1583,7 +1579,7 @@
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
@@ -1598,10 +1594,10 @@
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -1645,7 +1641,7 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M29" t="n">
         <v>1</v>
@@ -1659,10 +1655,10 @@
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E30" t="n">
         <v>1</v>
@@ -1671,16 +1667,16 @@
         <v>1</v>
       </c>
       <c r="G30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -1908,25 +1904,25 @@
         <v>1</v>
       </c>
       <c r="D36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I36" t="n">
         <v>1</v>
       </c>
       <c r="J36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -1951,19 +1947,19 @@
         <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E37" t="n">
         <v>1</v>
       </c>
       <c r="F37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I37" t="n">
         <v>1</v>
@@ -1972,7 +1968,7 @@
         <v>1</v>
       </c>
       <c r="K37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
@@ -1989,7 +1985,7 @@
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
@@ -2098,10 +2094,10 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2159,22 +2155,22 @@
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F42" t="n">
         <v>1</v>
       </c>
       <c r="G42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I42" t="n">
         <v>1</v>
       </c>
       <c r="J42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -2200,13 +2196,13 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -2235,37 +2231,37 @@
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D44" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E44" t="n">
         <v>3</v>
       </c>
       <c r="F44" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I44" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J44" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -2274,15 +2270,17 @@
           <t>生技醫療業右下</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr"/>
+      <c r="B45" t="n">
+        <v>0</v>
+      </c>
       <c r="C45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D45" t="n">
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F45" t="n">
         <v>1</v>
@@ -2291,22 +2289,22 @@
         <v>1</v>
       </c>
       <c r="H45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I45" t="n">
         <v>3</v>
       </c>
       <c r="J45" t="n">
+        <v>2</v>
+      </c>
+      <c r="K45" t="n">
+        <v>1</v>
+      </c>
+      <c r="L45" t="n">
         <v>3</v>
       </c>
-      <c r="K45" t="n">
-        <v>2</v>
-      </c>
-      <c r="L45" t="n">
-        <v>1</v>
-      </c>
       <c r="M45" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -2317,10 +2315,10 @@
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E46" t="n">
         <v>0</v>
@@ -2329,25 +2327,25 @@
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H46" t="n">
         <v>1</v>
       </c>
       <c r="I46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -2361,7 +2359,7 @@
         <v>1</v>
       </c>
       <c r="D47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E47" t="n">
         <v>0</v>
@@ -2370,7 +2368,7 @@
         <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
@@ -2379,7 +2377,7 @@
         <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
@@ -2397,9 +2395,7 @@
           <t>紡織纖維右下</t>
         </is>
       </c>
-      <c r="B48" t="n">
-        <v>0</v>
-      </c>
+      <c r="B48" t="inlineStr"/>
       <c r="C48" t="n">
         <v>0</v>
       </c>
@@ -2410,13 +2406,13 @@
         <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I48" t="n">
         <v>0</v>
@@ -2442,16 +2438,16 @@
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E49" t="n">
         <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -2460,7 +2456,7 @@
         <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -2472,7 +2468,7 @@
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -2483,7 +2479,7 @@
       </c>
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D50" t="n">
         <v>0</v>
@@ -2504,16 +2500,16 @@
         <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -2595,7 +2591,7 @@
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -2609,25 +2605,25 @@
         <v>0</v>
       </c>
       <c r="D53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I53" t="n">
         <v>1</v>
       </c>
       <c r="J53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K53" t="n">
         <v>0</v>
@@ -2694,7 +2690,7 @@
         <v>1</v>
       </c>
       <c r="E55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -2712,7 +2708,7 @@
         <v>1</v>
       </c>
       <c r="K55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
@@ -2735,19 +2731,19 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -2773,10 +2769,10 @@
         <v>0</v>
       </c>
       <c r="D57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -2788,10 +2784,10 @@
         <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K57" t="n">
         <v>0</v>
@@ -2978,13 +2974,13 @@
         <v>0</v>
       </c>
       <c r="D62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F62" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G62" t="n">
         <v>1</v>
@@ -2996,16 +2992,16 @@
         <v>1</v>
       </c>
       <c r="J62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -3014,7 +3010,9 @@
           <t>資訊服務業右下</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr"/>
+      <c r="B63" t="n">
+        <v>0</v>
+      </c>
       <c r="C63" t="n">
         <v>0</v>
       </c>
@@ -3028,10 +3026,10 @@
         <v>0</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I63" t="n">
         <v>0</v>
@@ -3043,7 +3041,7 @@
         <v>0</v>
       </c>
       <c r="L63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
         <v>0</v>
@@ -3063,10 +3061,10 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -3180,37 +3178,37 @@
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="n">
+        <v>1</v>
+      </c>
+      <c r="D67" t="n">
+        <v>4</v>
+      </c>
+      <c r="E67" t="n">
         <v>3</v>
       </c>
-      <c r="D67" t="n">
-        <v>1</v>
-      </c>
-      <c r="E67" t="n">
-        <v>4</v>
-      </c>
       <c r="F67" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G67" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H67" t="n">
+        <v>8</v>
+      </c>
+      <c r="I67" t="n">
         <v>7</v>
       </c>
-      <c r="I67" t="n">
-        <v>8</v>
-      </c>
       <c r="J67" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M67" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -3219,7 +3217,9 @@
           <t>通信網路業右下</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr"/>
+      <c r="B68" t="n">
+        <v>0</v>
+      </c>
       <c r="C68" t="n">
         <v>0</v>
       </c>
@@ -3227,25 +3227,25 @@
         <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F68" t="n">
         <v>1</v>
       </c>
       <c r="G68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J68" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L68" t="n">
         <v>1</v>
@@ -3262,25 +3262,25 @@
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D69" t="n">
         <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F69" t="n">
         <v>1</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H69" t="n">
         <v>1</v>
       </c>
       <c r="I69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -3494,10 +3494,10 @@
         <v>0</v>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -3754,7 +3754,7 @@
       </c>
       <c r="B81" t="inlineStr"/>
       <c r="C81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D81" t="n">
         <v>0</v>
@@ -3813,13 +3813,13 @@
         <v>0</v>
       </c>
       <c r="I82" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J82" t="n">
         <v>2</v>
       </c>
       <c r="K82" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L82" t="n">
         <v>0</v>
@@ -3836,13 +3836,13 @@
       </c>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D83" t="n">
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F83" t="n">
         <v>0</v>
@@ -3959,7 +3959,7 @@
       </c>
       <c r="B86" t="inlineStr"/>
       <c r="C86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D86" t="n">
         <v>0</v>
@@ -3971,10 +3971,10 @@
         <v>0</v>
       </c>
       <c r="G86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I86" t="n">
         <v>0</v>
@@ -4000,19 +4000,19 @@
       </c>
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H87" t="n">
         <v>0</v>
@@ -4027,10 +4027,10 @@
         <v>0</v>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -4056,10 +4056,10 @@
         <v>0</v>
       </c>
       <c r="H88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -4088,16 +4088,16 @@
         <v>0</v>
       </c>
       <c r="E89" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F89" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G89" t="n">
         <v>1</v>
       </c>
       <c r="H89" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I89" t="n">
         <v>1</v>
@@ -4106,13 +4106,13 @@
         <v>1</v>
       </c>
       <c r="K89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -4123,37 +4123,37 @@
       </c>
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D90" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E90" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F90" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G90" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H90" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I90" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="J90" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="K90" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L90" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="M90" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
@@ -4164,34 +4164,34 @@
       </c>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D91" t="n">
         <v>3</v>
       </c>
       <c r="E91" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F91" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G91" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H91" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I91" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J91" t="n">
         <v>4</v>
       </c>
       <c r="K91" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M91" t="n">
         <v>1</v>
@@ -4205,37 +4205,37 @@
       </c>
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D92" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E92" t="n">
         <v>5</v>
       </c>
       <c r="F92" t="n">
+        <v>2</v>
+      </c>
+      <c r="G92" t="n">
+        <v>2</v>
+      </c>
+      <c r="H92" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" t="n">
         <v>3</v>
       </c>
-      <c r="G92" t="n">
-        <v>1</v>
-      </c>
-      <c r="H92" t="n">
-        <v>4</v>
-      </c>
-      <c r="I92" t="n">
-        <v>2</v>
-      </c>
       <c r="J92" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M92" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -4246,37 +4246,37 @@
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E93" t="n">
         <v>2</v>
       </c>
       <c r="F93" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G93" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H93" t="n">
         <v>1</v>
       </c>
       <c r="I93" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J93" t="n">
+        <v>1</v>
+      </c>
+      <c r="K93" t="n">
+        <v>0</v>
+      </c>
+      <c r="L93" t="n">
         <v>4</v>
       </c>
-      <c r="K93" t="n">
-        <v>1</v>
-      </c>
-      <c r="L93" t="n">
-        <v>0</v>
-      </c>
       <c r="M93" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">
@@ -4285,7 +4285,9 @@
           <t>電機機械右下</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr"/>
+      <c r="B94" t="n">
+        <v>0</v>
+      </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
@@ -4311,7 +4313,7 @@
         <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L94" t="n">
         <v>2</v>
@@ -4328,34 +4330,34 @@
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D95" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H95" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I95" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J95" t="n">
         <v>1</v>
       </c>
       <c r="K95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M95" t="n">
         <v>1</v>
@@ -4369,37 +4371,37 @@
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D96" t="n">
+        <v>1</v>
+      </c>
+      <c r="E96" t="n">
+        <v>2</v>
+      </c>
+      <c r="F96" t="n">
         <v>3</v>
       </c>
-      <c r="E96" t="n">
-        <v>1</v>
-      </c>
-      <c r="F96" t="n">
-        <v>2</v>
-      </c>
       <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
         <v>3</v>
       </c>
-      <c r="H96" t="n">
-        <v>0</v>
-      </c>
       <c r="I96" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J96" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M96" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97">
@@ -4413,31 +4415,31 @@
         <v>1</v>
       </c>
       <c r="D97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E97" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F97" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G97" t="n">
+        <v>2</v>
+      </c>
+      <c r="H97" t="n">
         <v>3</v>
       </c>
-      <c r="H97" t="n">
-        <v>2</v>
-      </c>
       <c r="I97" t="n">
         <v>2</v>
       </c>
       <c r="J97" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K97" t="n">
         <v>0</v>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M97" t="n">
         <v>1</v>
@@ -4460,7 +4462,7 @@
         <v>0</v>
       </c>
       <c r="F98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G98" t="n">
         <v>1</v>
@@ -4478,10 +4480,10 @@
         <v>1</v>
       </c>
       <c r="L98" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -4536,7 +4538,7 @@
         <v>0</v>
       </c>
       <c r="D100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E100" t="n">
         <v>0</v>

--- a/Result/analyze_1.xlsx
+++ b/Result/analyze_1.xlsx
@@ -441,57 +441,57 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2025-08-25</t>
         </is>
       </c>
     </row>
@@ -506,34 +506,34 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G2" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2" t="n">
+        <v>7</v>
+      </c>
+      <c r="I2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J2" t="n">
         <v>5</v>
       </c>
-      <c r="H2" t="n">
+      <c r="K2" t="n">
         <v>4</v>
       </c>
-      <c r="I2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J2" t="n">
-        <v>6</v>
-      </c>
-      <c r="K2" t="n">
-        <v>5</v>
-      </c>
       <c r="L2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -544,7 +544,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
         <v>1</v>
@@ -553,28 +553,28 @@
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H3" t="n">
+        <v>5</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
         <v>3</v>
       </c>
-      <c r="I3" t="n">
-        <v>5</v>
-      </c>
-      <c r="J3" t="n">
-        <v>2</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1</v>
-      </c>
       <c r="L3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -585,16 +585,16 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
@@ -606,16 +606,16 @@
         <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -626,37 +626,37 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
         <v>3</v>
       </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
       <c r="L5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -665,7 +665,9 @@
           <t>其他右下</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
@@ -673,10 +675,10 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -685,13 +687,13 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -717,10 +719,10 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -732,10 +734,10 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -749,37 +751,37 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F8" t="n">
         <v>3</v>
       </c>
-      <c r="D8" t="n">
+      <c r="G8" t="n">
+        <v>5</v>
+      </c>
+      <c r="H8" t="n">
+        <v>8</v>
+      </c>
+      <c r="I8" t="n">
+        <v>5</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
         <v>3</v>
       </c>
-      <c r="E8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F8" t="n">
-        <v>8</v>
-      </c>
-      <c r="G8" t="n">
-        <v>2</v>
-      </c>
-      <c r="H8" t="n">
+      <c r="L8" t="n">
+        <v>3</v>
+      </c>
+      <c r="M8" t="n">
         <v>5</v>
-      </c>
-      <c r="I8" t="n">
-        <v>8</v>
-      </c>
-      <c r="J8" t="n">
-        <v>4</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>2</v>
-      </c>
-      <c r="M8" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -788,26 +790,24 @@
           <t>其他電子業右下</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0</v>
-      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
@@ -816,7 +816,7 @@
         <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -833,13 +833,13 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F10" t="n">
         <v>1</v>
@@ -854,13 +854,13 @@
         <v>2</v>
       </c>
       <c r="J10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
         <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>1</v>
@@ -877,7 +877,7 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -889,22 +889,22 @@
         <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -924,16 +924,16 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -962,10 +962,10 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -997,37 +997,37 @@
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
+        <v>4</v>
+      </c>
+      <c r="D14" t="n">
         <v>3</v>
       </c>
-      <c r="D14" t="n">
+      <c r="E14" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" t="n">
         <v>4</v>
       </c>
-      <c r="E14" t="n">
-        <v>3</v>
-      </c>
-      <c r="F14" t="n">
-        <v>2</v>
-      </c>
       <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
         <v>4</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>1</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" t="n">
-        <v>2</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1036,39 +1036,41 @@
           <t>半導體業右下</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
+      <c r="B15" t="n">
+        <v>0</v>
+      </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>6</v>
+      </c>
+      <c r="H15" t="n">
+        <v>7</v>
+      </c>
+      <c r="I15" t="n">
+        <v>4</v>
+      </c>
+      <c r="J15" t="n">
         <v>3</v>
       </c>
-      <c r="G15" t="n">
-        <v>2</v>
-      </c>
-      <c r="H15" t="n">
-        <v>5</v>
-      </c>
-      <c r="I15" t="n">
-        <v>6</v>
-      </c>
-      <c r="J15" t="n">
-        <v>4</v>
-      </c>
       <c r="K15" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="L15" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1082,7 +1084,7 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E16" t="n">
         <v>3</v>
@@ -1091,25 +1093,25 @@
         <v>2</v>
       </c>
       <c r="G16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
         <v>2</v>
       </c>
       <c r="I16" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2</v>
+      </c>
+      <c r="L16" t="n">
+        <v>2</v>
+      </c>
+      <c r="M16" t="n">
         <v>4</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>3</v>
-      </c>
-      <c r="M16" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -1161,13 +1163,13 @@
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
         <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -1176,19 +1178,19 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -1205,10 +1207,10 @@
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -1246,22 +1248,22 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1299,19 +1301,19 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -1369,16 +1371,16 @@
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -1405,20 +1407,18 @@
           <t>建材營造右下</t>
         </is>
       </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
+      <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24" t="n">
         <v>1</v>
       </c>
       <c r="F24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1433,10 +1433,10 @@
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -1456,13 +1456,13 @@
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25" t="n">
         <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1491,7 +1491,7 @@
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D26" t="n">
         <v>1</v>
@@ -1500,13 +1500,13 @@
         <v>1</v>
       </c>
       <c r="F26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -1515,13 +1515,13 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" t="n">
         <v>1</v>
       </c>
       <c r="M26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1591,10 +1591,10 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -1638,7 +1638,7 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29" t="n">
         <v>1</v>
@@ -1655,7 +1655,7 @@
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D30" t="n">
         <v>1</v>
@@ -1664,16 +1664,16 @@
         <v>1</v>
       </c>
       <c r="F30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1901,25 +1901,25 @@
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H36" t="n">
         <v>1</v>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -1931,7 +1931,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -1940,23 +1940,21 @@
           <t>汽車工業右下</t>
         </is>
       </c>
-      <c r="B37" t="n">
-        <v>0</v>
-      </c>
+      <c r="B37" t="inlineStr"/>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D37" t="n">
         <v>1</v>
       </c>
       <c r="E37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H37" t="n">
         <v>1</v>
@@ -1965,7 +1963,7 @@
         <v>1</v>
       </c>
       <c r="J37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -2091,10 +2089,10 @@
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
@@ -2152,22 +2150,22 @@
         <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H42" t="n">
         <v>1</v>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -2193,13 +2191,13 @@
         <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E43" t="n">
         <v>1</v>
       </c>
       <c r="F43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -2231,37 +2229,37 @@
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D44" t="n">
+        <v>2</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>1</v>
+      </c>
+      <c r="G44" t="n">
+        <v>2</v>
+      </c>
+      <c r="H44" t="n">
         <v>3</v>
       </c>
-      <c r="E44" t="n">
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
         <v>3</v>
       </c>
-      <c r="F44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" t="n">
-        <v>1</v>
-      </c>
-      <c r="H44" t="n">
-        <v>2</v>
-      </c>
-      <c r="I44" t="n">
-        <v>4</v>
-      </c>
-      <c r="J44" t="n">
-        <v>0</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" t="n">
-        <v>1</v>
-      </c>
       <c r="M44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2277,7 +2275,7 @@
         <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E45" t="n">
         <v>1</v>
@@ -2286,25 +2284,25 @@
         <v>1</v>
       </c>
       <c r="G45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H45" t="n">
+        <v>2</v>
+      </c>
+      <c r="I45" t="n">
+        <v>2</v>
+      </c>
+      <c r="J45" t="n">
+        <v>1</v>
+      </c>
+      <c r="K45" t="n">
         <v>3</v>
       </c>
-      <c r="I45" t="n">
-        <v>3</v>
-      </c>
-      <c r="J45" t="n">
-        <v>2</v>
-      </c>
-      <c r="K45" t="n">
-        <v>1</v>
-      </c>
       <c r="L45" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -2315,16 +2313,16 @@
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E46" t="n">
         <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G46" t="n">
         <v>1</v>
@@ -2333,19 +2331,19 @@
         <v>1</v>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L46" t="n">
         <v>2</v>
       </c>
       <c r="M46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -2356,7 +2354,7 @@
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D47" t="n">
         <v>0</v>
@@ -2403,13 +2401,13 @@
         <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
@@ -2438,25 +2436,25 @@
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D49" t="n">
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -2465,10 +2463,10 @@
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -2497,16 +2495,16 @@
         <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M50" t="n">
         <v>1</v>
@@ -2588,10 +2586,10 @@
         <v>0</v>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -2602,25 +2600,25 @@
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F53" t="n">
         <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H53" t="n">
         <v>1</v>
       </c>
       <c r="I53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -2632,7 +2630,7 @@
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -2641,7 +2639,9 @@
           <t>航運業右下</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr"/>
+      <c r="B54" t="n">
+        <v>0</v>
+      </c>
       <c r="C54" t="n">
         <v>0</v>
       </c>
@@ -2684,10 +2684,10 @@
       </c>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E55" t="n">
         <v>0</v>
@@ -2699,13 +2699,13 @@
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K55" t="n">
         <v>0</v>
@@ -2728,19 +2728,19 @@
         <v>0</v>
       </c>
       <c r="D56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I56" t="n">
         <v>0</v>
@@ -2764,12 +2764,14 @@
           <t>觀光事業右下</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr"/>
+      <c r="B57" t="n">
+        <v>0</v>
+      </c>
       <c r="C57" t="n">
         <v>0</v>
       </c>
       <c r="D57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E57" t="n">
         <v>0</v>
@@ -2781,10 +2783,10 @@
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -2971,34 +2973,34 @@
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D62" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E62" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G62" t="n">
         <v>1</v>
       </c>
       <c r="H62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J62" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
         <v>0</v>
@@ -3023,10 +3025,10 @@
         <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
@@ -3035,7 +3037,7 @@
         <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K63" t="n">
         <v>0</v>
@@ -3058,10 +3060,10 @@
         <v>0</v>
       </c>
       <c r="D64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -3178,37 +3180,37 @@
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D67" t="n">
         <v>4</v>
       </c>
       <c r="E67" t="n">
+        <v>2</v>
+      </c>
+      <c r="F67" t="n">
+        <v>7</v>
+      </c>
+      <c r="G67" t="n">
+        <v>8</v>
+      </c>
+      <c r="H67" t="n">
+        <v>7</v>
+      </c>
+      <c r="I67" t="n">
+        <v>2</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" t="n">
         <v>3</v>
       </c>
-      <c r="F67" t="n">
-        <v>1</v>
-      </c>
-      <c r="G67" t="n">
-        <v>7</v>
-      </c>
-      <c r="H67" t="n">
-        <v>8</v>
-      </c>
-      <c r="I67" t="n">
-        <v>7</v>
-      </c>
-      <c r="J67" t="n">
-        <v>2</v>
-      </c>
-      <c r="K67" t="n">
-        <v>0</v>
-      </c>
       <c r="L67" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M67" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="68">
@@ -3217,41 +3219,39 @@
           <t>通信網路業右下</t>
         </is>
       </c>
-      <c r="B68" t="n">
-        <v>0</v>
-      </c>
+      <c r="B68" t="inlineStr"/>
       <c r="C68" t="n">
         <v>0</v>
       </c>
       <c r="D68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E68" t="n">
         <v>1</v>
       </c>
       <c r="F68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I68" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -3262,22 +3262,22 @@
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D69" t="n">
         <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F69" t="n">
         <v>1</v>
       </c>
       <c r="G69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I69" t="n">
         <v>0</v>
@@ -3286,13 +3286,13 @@
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -3491,10 +3491,10 @@
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
         <v>0</v>
@@ -3810,13 +3810,13 @@
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I82" t="n">
         <v>2</v>
       </c>
       <c r="J82" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K82" t="n">
         <v>0</v>
@@ -3839,7 +3839,7 @@
         <v>1</v>
       </c>
       <c r="D83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E83" t="n">
         <v>0</v>
@@ -3886,7 +3886,7 @@
         <v>0</v>
       </c>
       <c r="F84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -3971,7 +3971,7 @@
         <v>0</v>
       </c>
       <c r="G86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H86" t="n">
         <v>0</v>
@@ -4000,19 +4000,19 @@
       </c>
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H87" t="n">
         <v>0</v>
@@ -4024,10 +4024,10 @@
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
         <v>0</v>
@@ -4053,10 +4053,10 @@
         <v>0</v>
       </c>
       <c r="G88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I88" t="n">
         <v>0</v>
@@ -4085,10 +4085,10 @@
         <v>0</v>
       </c>
       <c r="D89" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E89" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F89" t="n">
         <v>1</v>
@@ -4103,13 +4103,13 @@
         <v>1</v>
       </c>
       <c r="J89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
         <v>0</v>
@@ -4123,37 +4123,37 @@
       </c>
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D90" t="n">
+        <v>16</v>
+      </c>
+      <c r="E90" t="n">
+        <v>10</v>
+      </c>
+      <c r="F90" t="n">
+        <v>11</v>
+      </c>
+      <c r="G90" t="n">
+        <v>11</v>
+      </c>
+      <c r="H90" t="n">
+        <v>16</v>
+      </c>
+      <c r="I90" t="n">
+        <v>2</v>
+      </c>
+      <c r="J90" t="n">
+        <v>3</v>
+      </c>
+      <c r="K90" t="n">
         <v>12</v>
       </c>
-      <c r="E90" t="n">
-        <v>14</v>
-      </c>
-      <c r="F90" t="n">
-        <v>10</v>
-      </c>
-      <c r="G90" t="n">
-        <v>10</v>
-      </c>
-      <c r="H90" t="n">
-        <v>12</v>
-      </c>
-      <c r="I90" t="n">
-        <v>17</v>
-      </c>
-      <c r="J90" t="n">
-        <v>2</v>
-      </c>
-      <c r="K90" t="n">
-        <v>3</v>
-      </c>
       <c r="L90" t="n">
+        <v>1</v>
+      </c>
+      <c r="M90" t="n">
         <v>13</v>
-      </c>
-      <c r="M90" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="91">
@@ -4162,39 +4162,41 @@
           <t>電子零組件業右下</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr"/>
+      <c r="B91" t="n">
+        <v>0</v>
+      </c>
       <c r="C91" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D91" t="n">
         <v>3</v>
       </c>
       <c r="E91" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F91" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G91" t="n">
+        <v>1</v>
+      </c>
+      <c r="H91" t="n">
         <v>5</v>
       </c>
-      <c r="H91" t="n">
-        <v>1</v>
-      </c>
       <c r="I91" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J91" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L91" t="n">
         <v>1</v>
       </c>
       <c r="M91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -4205,37 +4207,37 @@
       </c>
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D92" t="n">
         <v>3</v>
       </c>
       <c r="E92" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F92" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G92" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H92" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I92" t="n">
+        <v>1</v>
+      </c>
+      <c r="J92" t="n">
+        <v>2</v>
+      </c>
+      <c r="K92" t="n">
         <v>3</v>
       </c>
-      <c r="J92" t="n">
-        <v>1</v>
-      </c>
-      <c r="K92" t="n">
-        <v>2</v>
-      </c>
       <c r="L92" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93">
@@ -4246,7 +4248,7 @@
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D93" t="n">
         <v>2</v>
@@ -4255,28 +4257,28 @@
         <v>2</v>
       </c>
       <c r="F93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H93" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I93" t="n">
+        <v>1</v>
+      </c>
+      <c r="J93" t="n">
+        <v>0</v>
+      </c>
+      <c r="K93" t="n">
         <v>4</v>
       </c>
-      <c r="J93" t="n">
-        <v>1</v>
-      </c>
-      <c r="K93" t="n">
-        <v>0</v>
-      </c>
       <c r="L93" t="n">
+        <v>1</v>
+      </c>
+      <c r="M93" t="n">
         <v>4</v>
-      </c>
-      <c r="M93" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="94">
@@ -4285,9 +4287,7 @@
           <t>電機機械右下</t>
         </is>
       </c>
-      <c r="B94" t="n">
-        <v>0</v>
-      </c>
+      <c r="B94" t="inlineStr"/>
       <c r="C94" t="n">
         <v>0</v>
       </c>
@@ -4310,13 +4310,13 @@
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M94" t="n">
         <v>2</v>
@@ -4330,10 +4330,10 @@
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E95" t="n">
         <v>0</v>
@@ -4342,25 +4342,25 @@
         <v>1</v>
       </c>
       <c r="G95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H95" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J95" t="n">
         <v>1</v>
       </c>
       <c r="K95" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -4371,37 +4371,37 @@
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="n">
+        <v>1</v>
+      </c>
+      <c r="D96" t="n">
+        <v>2</v>
+      </c>
+      <c r="E96" t="n">
         <v>3</v>
       </c>
-      <c r="D96" t="n">
-        <v>1</v>
-      </c>
-      <c r="E96" t="n">
-        <v>2</v>
-      </c>
       <c r="F96" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" t="n">
         <v>3</v>
       </c>
-      <c r="G96" t="n">
-        <v>0</v>
-      </c>
       <c r="H96" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I96" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L96" t="n">
+        <v>1</v>
+      </c>
+      <c r="M96" t="n">
         <v>4</v>
-      </c>
-      <c r="M96" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="97">
@@ -4412,37 +4412,37 @@
       </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D97" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E97" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F97" t="n">
+        <v>2</v>
+      </c>
+      <c r="G97" t="n">
+        <v>2</v>
+      </c>
+      <c r="H97" t="n">
+        <v>1</v>
+      </c>
+      <c r="I97" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" t="n">
+        <v>0</v>
+      </c>
+      <c r="K97" t="n">
+        <v>1</v>
+      </c>
+      <c r="L97" t="n">
+        <v>1</v>
+      </c>
+      <c r="M97" t="n">
         <v>3</v>
-      </c>
-      <c r="G97" t="n">
-        <v>2</v>
-      </c>
-      <c r="H97" t="n">
-        <v>3</v>
-      </c>
-      <c r="I97" t="n">
-        <v>2</v>
-      </c>
-      <c r="J97" t="n">
-        <v>0</v>
-      </c>
-      <c r="K97" t="n">
-        <v>0</v>
-      </c>
-      <c r="L97" t="n">
-        <v>1</v>
-      </c>
-      <c r="M97" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="98">
@@ -4459,31 +4459,31 @@
         <v>0</v>
       </c>
       <c r="E98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F98" t="n">
         <v>1</v>
       </c>
       <c r="G98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I98" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J98" t="n">
         <v>1</v>
       </c>
       <c r="K98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L98" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="99">
@@ -4535,10 +4535,10 @@
       </c>
       <c r="B100" t="inlineStr"/>
       <c r="C100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E100" t="n">
         <v>0</v>

--- a/Result/analyze_1.xlsx
+++ b/Result/analyze_1.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M101"/>
+  <dimension ref="A1:M100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,57 +441,57 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-26</t>
         </is>
       </c>
     </row>
@@ -506,34 +506,34 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G2" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2" t="n">
+        <v>6</v>
+      </c>
+      <c r="I2" t="n">
         <v>5</v>
       </c>
-      <c r="G2" t="n">
+      <c r="J2" t="n">
         <v>4</v>
       </c>
-      <c r="H2" t="n">
+      <c r="K2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L2" t="n">
+        <v>9</v>
+      </c>
+      <c r="M2" t="n">
         <v>7</v>
-      </c>
-      <c r="I2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J2" t="n">
-        <v>5</v>
-      </c>
-      <c r="K2" t="n">
-        <v>4</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M2" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -550,31 +550,31 @@
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -585,13 +585,13 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
@@ -603,19 +603,19 @@
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -626,37 +626,37 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
         <v>3</v>
       </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
       <c r="K5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -665,14 +665,12 @@
           <t>其他右下</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>0</v>
-      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -684,7 +682,7 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
@@ -716,10 +714,10 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -734,13 +732,13 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -751,37 +749,37 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" t="n">
+        <v>5</v>
+      </c>
+      <c r="G8" t="n">
         <v>8</v>
       </c>
-      <c r="F8" t="n">
+      <c r="H8" t="n">
+        <v>5</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
         <v>3</v>
-      </c>
-      <c r="G8" t="n">
-        <v>5</v>
-      </c>
-      <c r="H8" t="n">
-        <v>8</v>
-      </c>
-      <c r="I8" t="n">
-        <v>5</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1</v>
       </c>
       <c r="K8" t="n">
         <v>3</v>
       </c>
       <c r="L8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -792,19 +790,19 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
         <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
         <v>1</v>
@@ -813,7 +811,7 @@
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -833,16 +831,16 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G10" t="n">
         <v>2</v>
@@ -851,16 +849,16 @@
         <v>2</v>
       </c>
       <c r="I10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
         <v>1</v>
@@ -874,7 +872,7 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
         <v>1</v>
@@ -886,22 +884,22 @@
         <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" t="n">
         <v>1</v>
@@ -921,16 +919,16 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" t="n">
         <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -959,10 +957,10 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -997,37 +995,37 @@
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" t="n">
+        <v>5</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
         <v>3</v>
       </c>
-      <c r="E14" t="n">
-        <v>2</v>
-      </c>
-      <c r="F14" t="n">
-        <v>4</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
       <c r="H14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1040,37 +1038,37 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H15" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J15" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="K15" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1081,34 +1079,34 @@
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" t="n">
         <v>3</v>
       </c>
-      <c r="E16" t="n">
-        <v>3</v>
-      </c>
-      <c r="F16" t="n">
-        <v>2</v>
-      </c>
-      <c r="G16" t="n">
-        <v>1</v>
-      </c>
       <c r="H16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K16" t="n">
         <v>2</v>
       </c>
       <c r="L16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M16" t="n">
         <v>4</v>
@@ -1163,10 +1161,10 @@
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -1175,19 +1173,19 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -1207,7 +1205,7 @@
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -1245,22 +1243,22 @@
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -1298,19 +1296,19 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -1368,16 +1366,16 @@
       </c>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1409,13 +1407,13 @@
       </c>
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D24" t="n">
         <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -1430,10 +1428,10 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -1453,13 +1451,13 @@
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E25" t="n">
         <v>1</v>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1497,13 +1495,13 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1512,13 +1510,13 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" t="n">
         <v>1</v>
       </c>
       <c r="L26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -1588,10 +1586,10 @@
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1635,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" t="n">
         <v>1</v>
@@ -1644,7 +1642,7 @@
         <v>1</v>
       </c>
       <c r="M29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -1661,16 +1659,16 @@
         <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -1901,22 +1899,22 @@
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G36" t="n">
         <v>1</v>
       </c>
       <c r="H36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
@@ -1928,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -1945,13 +1943,13 @@
         <v>1</v>
       </c>
       <c r="D37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G37" t="n">
         <v>1</v>
@@ -1960,7 +1958,7 @@
         <v>1</v>
       </c>
       <c r="I37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2086,16 +2084,16 @@
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2147,22 +2145,22 @@
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G42" t="n">
         <v>1</v>
       </c>
       <c r="H42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -2177,7 +2175,7 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -2191,10 +2189,10 @@
         <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -2229,22 +2227,22 @@
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G44" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H44" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -2253,13 +2251,13 @@
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L44" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2268,11 +2266,9 @@
           <t>生技醫療業右下</t>
         </is>
       </c>
-      <c r="B45" t="n">
-        <v>0</v>
-      </c>
+      <c r="B45" t="inlineStr"/>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D45" t="n">
         <v>1</v>
@@ -2281,28 +2277,28 @@
         <v>1</v>
       </c>
       <c r="F45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G45" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H45" t="n">
         <v>2</v>
       </c>
       <c r="I45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J45" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -2313,37 +2309,37 @@
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F46" t="n">
         <v>1</v>
       </c>
       <c r="G46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H46" t="n">
         <v>1</v>
       </c>
       <c r="I46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L46" t="n">
         <v>2</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -2398,13 +2394,13 @@
         <v>0</v>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -2439,19 +2435,19 @@
         <v>0</v>
       </c>
       <c r="D49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I49" t="n">
         <v>0</v>
@@ -2463,7 +2459,7 @@
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
         <v>0</v>
@@ -2492,22 +2488,22 @@
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L50" t="n">
         <v>1</v>
       </c>
       <c r="M50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -2583,13 +2579,13 @@
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -2600,22 +2596,22 @@
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E53" t="n">
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G53" t="n">
         <v>1</v>
       </c>
       <c r="H53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I53" t="n">
         <v>0</v>
@@ -2627,10 +2623,10 @@
         <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -2639,9 +2635,7 @@
           <t>航運業右下</t>
         </is>
       </c>
-      <c r="B54" t="n">
-        <v>0</v>
-      </c>
+      <c r="B54" t="inlineStr"/>
       <c r="C54" t="n">
         <v>0</v>
       </c>
@@ -2658,7 +2652,7 @@
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I54" t="n">
         <v>0</v>
@@ -2684,7 +2678,7 @@
       </c>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D55" t="n">
         <v>0</v>
@@ -2696,13 +2690,13 @@
         <v>0</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -2725,19 +2719,19 @@
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E56" t="n">
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
@@ -2764,9 +2758,7 @@
           <t>觀光事業右下</t>
         </is>
       </c>
-      <c r="B57" t="n">
-        <v>0</v>
-      </c>
+      <c r="B57" t="inlineStr"/>
       <c r="C57" t="n">
         <v>0</v>
       </c>
@@ -2780,10 +2772,10 @@
         <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I57" t="n">
         <v>0</v>
@@ -2798,7 +2790,7 @@
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -2927,56 +2919,56 @@
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>貿易百貨平</t>
+          <t>資訊服務業右上</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K61" t="n">
         <v>0</v>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>資訊服務業右上</t>
+          <t>資訊服務業右下</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D62" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E62" t="n">
         <v>1</v>
@@ -2985,19 +2977,19 @@
         <v>0</v>
       </c>
       <c r="G62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H62" t="n">
         <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J62" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
@@ -3009,14 +3001,12 @@
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>資訊服務業右下</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>0</v>
-      </c>
+          <t>資訊服務業平</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr"/>
       <c r="C63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D63" t="n">
         <v>0</v>
@@ -3025,7 +3015,7 @@
         <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -3037,7 +3027,7 @@
         <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K63" t="n">
         <v>0</v>
@@ -3052,7 +3042,7 @@
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>資訊服務業平</t>
+          <t>農業科技業右上</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
@@ -3060,7 +3050,7 @@
         <v>0</v>
       </c>
       <c r="D64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E64" t="n">
         <v>0</v>
@@ -3093,7 +3083,7 @@
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>農業科技業右上</t>
+          <t>農業科技業右下</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
@@ -3134,89 +3124,91 @@
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>農業科技業右下</t>
+          <t>通信網路業右上</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F66" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I66" t="n">
         <v>0</v>
       </c>
       <c r="J66" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>通信網路業右上</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr"/>
+          <t>通信網路業右下</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>0</v>
+      </c>
       <c r="C67" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D67" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G67" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H67" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>通信網路業右下</t>
+          <t>通信網路業平</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
@@ -3224,7 +3216,7 @@
         <v>0</v>
       </c>
       <c r="D68" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E68" t="n">
         <v>1</v>
@@ -3233,10 +3225,10 @@
         <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I68" t="n">
         <v>0</v>
@@ -3245,10 +3237,10 @@
         <v>1</v>
       </c>
       <c r="K68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M68" t="n">
         <v>0</v>
@@ -3257,12 +3249,12 @@
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>通信網路業平</t>
+          <t>造紙工業右下</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D69" t="n">
         <v>0</v>
@@ -3271,7 +3263,7 @@
         <v>0</v>
       </c>
       <c r="F69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -3286,19 +3278,19 @@
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>造紙工業右下</t>
+          <t>造紙工業平</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
@@ -3339,7 +3331,7 @@
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>造紙工業平</t>
+          <t>運動休閒右上</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
@@ -3380,7 +3372,7 @@
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>運動休閒右上</t>
+          <t>運動休閒右下</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
@@ -3421,7 +3413,7 @@
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>運動休閒右下</t>
+          <t>運動休閒平</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
@@ -3447,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>
@@ -3462,7 +3454,7 @@
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>運動休閒平</t>
+          <t>金融保險右上</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
@@ -3491,7 +3483,7 @@
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L74" t="n">
         <v>0</v>
@@ -3503,7 +3495,7 @@
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>金融保險右上</t>
+          <t>金融保險右下</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
@@ -3544,7 +3536,7 @@
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>金融保險右下</t>
+          <t>金融保險平</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
@@ -3585,7 +3577,7 @@
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>金融保險平</t>
+          <t>金融業右上</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
@@ -3626,7 +3618,7 @@
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>金融業右上</t>
+          <t>金融業右下</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
@@ -3667,7 +3659,7 @@
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>金融業右下</t>
+          <t>金融業平</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
@@ -3708,7 +3700,7 @@
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>金融業平</t>
+          <t>鋼鐵工業右上</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
@@ -3749,7 +3741,7 @@
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業右上</t>
+          <t>鋼鐵工業右下</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
@@ -3766,10 +3758,10 @@
         <v>0</v>
       </c>
       <c r="G81" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H81" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I81" t="n">
         <v>0</v>
@@ -3790,7 +3782,7 @@
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業右下</t>
+          <t>鋼鐵工業平</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
@@ -3810,10 +3802,10 @@
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I82" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -3831,12 +3823,12 @@
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業平</t>
+          <t>電器電纜右上</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D83" t="n">
         <v>0</v>
@@ -3872,7 +3864,7 @@
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>電器電纜右上</t>
+          <t>電器電纜右下</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
@@ -3886,7 +3878,7 @@
         <v>0</v>
       </c>
       <c r="F84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -3913,7 +3905,7 @@
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>電器電纜右下</t>
+          <t>電器電纜平</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
@@ -3924,7 +3916,7 @@
         <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F85" t="n">
         <v>0</v>
@@ -3954,12 +3946,12 @@
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>電器電纜平</t>
+          <t>電子通路業右上</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
       <c r="C86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D86" t="n">
         <v>0</v>
@@ -3980,7 +3972,7 @@
         <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K86" t="n">
         <v>0</v>
@@ -3995,7 +3987,7 @@
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>電子通路業右上</t>
+          <t>電子通路業右下</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
@@ -4003,10 +3995,10 @@
         <v>0</v>
       </c>
       <c r="D87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F87" t="n">
         <v>1</v>
@@ -4024,7 +4016,7 @@
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L87" t="n">
         <v>0</v>
@@ -4036,33 +4028,33 @@
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>電子通路業右下</t>
+          <t>電子通路業平</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G88" t="n">
         <v>1</v>
       </c>
       <c r="H88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I88" t="n">
         <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
@@ -4071,170 +4063,170 @@
         <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>電子通路業平</t>
+          <t>電子零組件業右上</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="D89" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E89" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="F89" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="G89" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="H89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I89" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J89" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K89" t="n">
         <v>1</v>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業右上</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr"/>
+          <t>電子零組件業右下</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>0</v>
+      </c>
       <c r="C90" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D90" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="E90" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F90" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="G90" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="H90" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="I90" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J90" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K90" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="L90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業右下</t>
-        </is>
-      </c>
-      <c r="B91" t="n">
-        <v>0</v>
-      </c>
+          <t>電子零組件業平</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr"/>
       <c r="C91" t="n">
         <v>2</v>
       </c>
       <c r="D91" t="n">
+        <v>2</v>
+      </c>
+      <c r="E91" t="n">
+        <v>1</v>
+      </c>
+      <c r="F91" t="n">
+        <v>1</v>
+      </c>
+      <c r="G91" t="n">
+        <v>4</v>
+      </c>
+      <c r="H91" t="n">
+        <v>1</v>
+      </c>
+      <c r="I91" t="n">
+        <v>2</v>
+      </c>
+      <c r="J91" t="n">
         <v>3</v>
       </c>
-      <c r="E91" t="n">
-        <v>2</v>
-      </c>
-      <c r="F91" t="n">
-        <v>5</v>
-      </c>
-      <c r="G91" t="n">
-        <v>1</v>
-      </c>
-      <c r="H91" t="n">
-        <v>5</v>
-      </c>
-      <c r="I91" t="n">
-        <v>4</v>
-      </c>
-      <c r="J91" t="n">
-        <v>0</v>
-      </c>
       <c r="K91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業平</t>
+          <t>電機機械右上</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="n">
+        <v>2</v>
+      </c>
+      <c r="D92" t="n">
+        <v>2</v>
+      </c>
+      <c r="E92" t="n">
+        <v>1</v>
+      </c>
+      <c r="F92" t="n">
+        <v>2</v>
+      </c>
+      <c r="G92" t="n">
+        <v>5</v>
+      </c>
+      <c r="H92" t="n">
+        <v>1</v>
+      </c>
+      <c r="I92" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" t="n">
         <v>4</v>
       </c>
-      <c r="D92" t="n">
-        <v>3</v>
-      </c>
-      <c r="E92" t="n">
-        <v>2</v>
-      </c>
-      <c r="F92" t="n">
-        <v>1</v>
-      </c>
-      <c r="G92" t="n">
-        <v>1</v>
-      </c>
-      <c r="H92" t="n">
+      <c r="K92" t="n">
+        <v>1</v>
+      </c>
+      <c r="L92" t="n">
         <v>4</v>
-      </c>
-      <c r="I92" t="n">
-        <v>1</v>
-      </c>
-      <c r="J92" t="n">
-        <v>2</v>
-      </c>
-      <c r="K92" t="n">
-        <v>3</v>
-      </c>
-      <c r="L92" t="n">
-        <v>0</v>
       </c>
       <c r="M92" t="n">
         <v>2</v>
@@ -4243,48 +4235,48 @@
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>電機機械右上</t>
+          <t>電機機械右下</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D93" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G93" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H93" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I93" t="n">
         <v>1</v>
       </c>
       <c r="J93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K93" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M93" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>電機機械右下</t>
+          <t>電機機械平</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
@@ -4295,119 +4287,121 @@
         <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F94" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
       </c>
       <c r="H94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>電機機械平</t>
+          <t>電腦及週邊設備業右上</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D95" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E95" t="n">
         <v>0</v>
       </c>
       <c r="F95" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G95" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K95" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L95" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右上</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr"/>
+          <t>電腦及週邊設備業右下</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>0</v>
+      </c>
       <c r="C96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D96" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E96" t="n">
+        <v>2</v>
+      </c>
+      <c r="F96" t="n">
+        <v>2</v>
+      </c>
+      <c r="G96" t="n">
+        <v>1</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" t="n">
+        <v>1</v>
+      </c>
+      <c r="K96" t="n">
+        <v>1</v>
+      </c>
+      <c r="L96" t="n">
         <v>3</v>
       </c>
-      <c r="F96" t="n">
-        <v>0</v>
-      </c>
-      <c r="G96" t="n">
-        <v>3</v>
-      </c>
-      <c r="H96" t="n">
-        <v>7</v>
-      </c>
-      <c r="I96" t="n">
-        <v>1</v>
-      </c>
-      <c r="J96" t="n">
-        <v>0</v>
-      </c>
-      <c r="K96" t="n">
-        <v>5</v>
-      </c>
-      <c r="L96" t="n">
-        <v>1</v>
-      </c>
       <c r="M96" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右下</t>
+          <t>電腦及週邊設備業平</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
@@ -4415,10 +4409,10 @@
         <v>0</v>
       </c>
       <c r="D97" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E97" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F97" t="n">
         <v>2</v>
@@ -4430,25 +4424,25 @@
         <v>1</v>
       </c>
       <c r="I97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J97" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L97" t="n">
         <v>1</v>
       </c>
       <c r="M97" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業平</t>
+          <t>食品工業右上</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
@@ -4459,37 +4453,37 @@
         <v>0</v>
       </c>
       <c r="E98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G98" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H98" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K98" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L98" t="n">
         <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>食品工業右上</t>
+          <t>食品工業右下</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
@@ -4530,12 +4524,12 @@
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>食品工業右下</t>
+          <t>食品工業平</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
       <c r="C100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D100" t="n">
         <v>0</v>
@@ -4565,47 +4559,6 @@
         <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="1" t="inlineStr">
-        <is>
-          <t>食品工業平</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr"/>
-      <c r="C101" t="n">
-        <v>0</v>
-      </c>
-      <c r="D101" t="n">
-        <v>0</v>
-      </c>
-      <c r="E101" t="n">
-        <v>0</v>
-      </c>
-      <c r="F101" t="n">
-        <v>0</v>
-      </c>
-      <c r="G101" t="n">
-        <v>0</v>
-      </c>
-      <c r="H101" t="n">
-        <v>0</v>
-      </c>
-      <c r="I101" t="n">
-        <v>0</v>
-      </c>
-      <c r="J101" t="n">
-        <v>0</v>
-      </c>
-      <c r="K101" t="n">
-        <v>0</v>
-      </c>
-      <c r="L101" t="n">
-        <v>0</v>
-      </c>
-      <c r="M101" t="n">
         <v>0</v>
       </c>
     </row>

--- a/Result/analyze_1.xlsx
+++ b/Result/analyze_1.xlsx
@@ -441,57 +441,57 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-27</t>
         </is>
       </c>
     </row>
@@ -503,37 +503,37 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F2" t="n">
+        <v>7</v>
+      </c>
+      <c r="G2" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2" t="n">
         <v>5</v>
-      </c>
-      <c r="F2" t="n">
-        <v>4</v>
-      </c>
-      <c r="G2" t="n">
-        <v>7</v>
-      </c>
-      <c r="H2" t="n">
-        <v>6</v>
       </c>
       <c r="I2" t="n">
         <v>5</v>
       </c>
       <c r="J2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -542,36 +542,38 @@
           <t>光電業右下</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -588,7 +590,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
@@ -600,22 +602,22 @@
         <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
         <v>2</v>
       </c>
       <c r="M4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -629,34 +631,34 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
         <v>3</v>
       </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
       <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2</v>
+      </c>
+      <c r="M5" t="n">
         <v>3</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" t="n">
-        <v>2</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -667,19 +669,19 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
         <v>1</v>
@@ -688,7 +690,7 @@
         <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -711,10 +713,10 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -738,7 +740,7 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -749,37 +751,37 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" t="n">
         <v>8</v>
       </c>
-      <c r="E8" t="n">
+      <c r="G8" t="n">
+        <v>5</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
         <v>3</v>
-      </c>
-      <c r="F8" t="n">
-        <v>5</v>
-      </c>
-      <c r="G8" t="n">
-        <v>8</v>
-      </c>
-      <c r="H8" t="n">
-        <v>5</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1</v>
       </c>
       <c r="J8" t="n">
         <v>3</v>
       </c>
       <c r="K8" t="n">
+        <v>5</v>
+      </c>
+      <c r="L8" t="n">
         <v>3</v>
       </c>
-      <c r="L8" t="n">
-        <v>5</v>
-      </c>
       <c r="M8" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -793,22 +795,22 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
         <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -820,7 +822,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -834,31 +836,31 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F10" t="n">
         <v>2</v>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>1</v>
@@ -881,28 +883,28 @@
         <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
         <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -916,16 +918,16 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -954,10 +956,10 @@
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -995,34 +997,34 @@
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="n">
+        <v>4</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
         <v>3</v>
       </c>
-      <c r="D14" t="n">
-        <v>2</v>
-      </c>
-      <c r="E14" t="n">
-        <v>5</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
       <c r="G14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L14" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M14" t="n">
         <v>2</v>
@@ -1038,37 +1040,37 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F15" t="n">
         <v>5</v>
       </c>
       <c r="G15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H15" t="n">
+        <v>3</v>
+      </c>
+      <c r="I15" t="n">
+        <v>8</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
         <v>4</v>
-      </c>
-      <c r="I15" t="n">
-        <v>3</v>
-      </c>
-      <c r="J15" t="n">
-        <v>9</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1</v>
-      </c>
-      <c r="M15" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1079,37 +1081,37 @@
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
         <v>3</v>
       </c>
-      <c r="H16" t="n">
-        <v>1</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
       <c r="J16" t="n">
         <v>2</v>
       </c>
       <c r="K16" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M16" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17">
@@ -1161,7 +1163,7 @@
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -1170,19 +1172,19 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -1211,7 +1213,7 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -1243,19 +1245,19 @@
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -1293,19 +1295,19 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -1366,13 +1368,13 @@
       </c>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -1410,7 +1412,7 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -1425,10 +1427,10 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -1448,13 +1450,13 @@
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D25" t="n">
         <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -1492,13 +1494,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1507,13 +1509,13 @@
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
       </c>
       <c r="K26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -1583,10 +1585,10 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -1630,7 +1632,7 @@
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J29" t="n">
         <v>1</v>
@@ -1639,7 +1641,7 @@
         <v>1</v>
       </c>
       <c r="L29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
@@ -1656,16 +1658,16 @@
         <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -1899,19 +1901,19 @@
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F36" t="n">
         <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -1923,13 +1925,13 @@
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -1940,13 +1942,13 @@
       </c>
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F37" t="n">
         <v>1</v>
@@ -1955,7 +1957,7 @@
         <v>1</v>
       </c>
       <c r="H37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
@@ -1970,7 +1972,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -2081,19 +2083,19 @@
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2148,16 +2150,16 @@
         <v>2</v>
       </c>
       <c r="D42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F42" t="n">
         <v>1</v>
       </c>
       <c r="G42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -2172,10 +2174,10 @@
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2186,7 +2188,7 @@
       </c>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D43" t="n">
         <v>0</v>
@@ -2213,7 +2215,7 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
@@ -2227,19 +2229,19 @@
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F44" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G44" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -2248,16 +2250,16 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -2274,28 +2276,28 @@
         <v>1</v>
       </c>
       <c r="E45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F45" t="n">
+        <v>2</v>
+      </c>
+      <c r="G45" t="n">
+        <v>2</v>
+      </c>
+      <c r="H45" t="n">
+        <v>1</v>
+      </c>
+      <c r="I45" t="n">
         <v>3</v>
       </c>
-      <c r="G45" t="n">
-        <v>1</v>
-      </c>
-      <c r="H45" t="n">
-        <v>2</v>
-      </c>
-      <c r="I45" t="n">
-        <v>1</v>
-      </c>
       <c r="J45" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M45" t="n">
         <v>2</v>
@@ -2309,10 +2311,10 @@
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E46" t="n">
         <v>1</v>
@@ -2321,25 +2323,25 @@
         <v>1</v>
       </c>
       <c r="G46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J46" t="n">
         <v>2</v>
       </c>
       <c r="K46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -2380,7 +2382,7 @@
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -2391,13 +2393,13 @@
       </c>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F48" t="n">
         <v>0</v>
@@ -2432,19 +2434,19 @@
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E49" t="n">
         <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
@@ -2453,7 +2455,7 @@
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
@@ -2485,22 +2487,22 @@
         <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K50" t="n">
         <v>1</v>
       </c>
       <c r="L50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
         <v>0</v>
@@ -2576,13 +2578,13 @@
         <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
         <v>0</v>
@@ -2596,19 +2598,19 @@
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D53" t="n">
         <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
@@ -2620,10 +2622,10 @@
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M53" t="n">
         <v>1</v>
@@ -2652,7 +2654,7 @@
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I54" t="n">
         <v>0</v>
@@ -2719,16 +2721,16 @@
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D56" t="n">
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -2769,10 +2771,10 @@
         <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -2787,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M57" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -2924,37 +2926,37 @@
       </c>
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E61" t="n">
         <v>1</v>
       </c>
       <c r="F61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K61" t="n">
         <v>0</v>
       </c>
       <c r="L61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -2963,15 +2965,17 @@
           <t>資訊服務業右下</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr"/>
+      <c r="B62" t="n">
+        <v>0</v>
+      </c>
       <c r="C62" t="n">
         <v>0</v>
       </c>
       <c r="D62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F62" t="n">
         <v>0</v>
@@ -2980,10 +2984,10 @@
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -3006,7 +3010,7 @@
       </c>
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D63" t="n">
         <v>0</v>
@@ -3129,37 +3133,37 @@
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="n">
+        <v>2</v>
+      </c>
+      <c r="D66" t="n">
+        <v>7</v>
+      </c>
+      <c r="E66" t="n">
+        <v>8</v>
+      </c>
+      <c r="F66" t="n">
+        <v>7</v>
+      </c>
+      <c r="G66" t="n">
+        <v>2</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" t="n">
+        <v>3</v>
+      </c>
+      <c r="J66" t="n">
+        <v>1</v>
+      </c>
+      <c r="K66" t="n">
+        <v>5</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" t="n">
         <v>4</v>
-      </c>
-      <c r="D66" t="n">
-        <v>2</v>
-      </c>
-      <c r="E66" t="n">
-        <v>7</v>
-      </c>
-      <c r="F66" t="n">
-        <v>8</v>
-      </c>
-      <c r="G66" t="n">
-        <v>7</v>
-      </c>
-      <c r="H66" t="n">
-        <v>2</v>
-      </c>
-      <c r="I66" t="n">
-        <v>0</v>
-      </c>
-      <c r="J66" t="n">
-        <v>3</v>
-      </c>
-      <c r="K66" t="n">
-        <v>1</v>
-      </c>
-      <c r="L66" t="n">
-        <v>5</v>
-      </c>
-      <c r="M66" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -3168,41 +3172,39 @@
           <t>通信網路業右下</t>
         </is>
       </c>
-      <c r="B67" t="n">
-        <v>0</v>
-      </c>
+      <c r="B67" t="inlineStr"/>
       <c r="C67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F67" t="n">
         <v>2</v>
       </c>
       <c r="G67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I67" t="n">
         <v>1</v>
       </c>
       <c r="J67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -3216,7 +3218,7 @@
         <v>0</v>
       </c>
       <c r="D68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E68" t="n">
         <v>1</v>
@@ -3234,16 +3236,16 @@
         <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L68" t="n">
         <v>1</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69">
@@ -3436,10 +3438,10 @@
         <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>
@@ -3755,13 +3757,13 @@
         <v>0</v>
       </c>
       <c r="F81" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G81" t="n">
         <v>2</v>
       </c>
       <c r="H81" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I81" t="n">
         <v>0</v>
@@ -3831,7 +3833,7 @@
         <v>0</v>
       </c>
       <c r="D83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E83" t="n">
         <v>0</v>
@@ -3858,7 +3860,7 @@
         <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
@@ -3916,7 +3918,7 @@
         <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F85" t="n">
         <v>0</v>
@@ -3951,7 +3953,7 @@
       </c>
       <c r="B86" t="inlineStr"/>
       <c r="C86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D86" t="n">
         <v>0</v>
@@ -3969,10 +3971,10 @@
         <v>0</v>
       </c>
       <c r="I86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K86" t="n">
         <v>0</v>
@@ -3995,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="D87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E87" t="n">
         <v>1</v>
       </c>
       <c r="F87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -4033,7 +4035,7 @@
       </c>
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D88" t="n">
         <v>1</v>
@@ -4048,19 +4050,19 @@
         <v>1</v>
       </c>
       <c r="H88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M88" t="n">
         <v>2</v>
@@ -4074,37 +4076,37 @@
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D89" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E89" t="n">
         <v>11</v>
       </c>
       <c r="F89" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G89" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="H89" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I89" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="J89" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="K89" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="L89" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="M89" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="90">
@@ -4113,41 +4115,39 @@
           <t>電子零組件業右下</t>
         </is>
       </c>
-      <c r="B90" t="n">
-        <v>0</v>
-      </c>
+      <c r="B90" t="inlineStr"/>
       <c r="C90" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D90" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E90" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F90" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G90" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H90" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J90" t="n">
         <v>1</v>
       </c>
       <c r="K90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M90" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
@@ -4158,7 +4158,7 @@
       </c>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D91" t="n">
         <v>2</v>
@@ -4167,28 +4167,28 @@
         <v>1</v>
       </c>
       <c r="F91" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G91" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I91" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J91" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L91" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="92">
@@ -4202,34 +4202,34 @@
         <v>2</v>
       </c>
       <c r="D92" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F92" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G92" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I92" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J92" t="n">
+        <v>1</v>
+      </c>
+      <c r="K92" t="n">
         <v>4</v>
       </c>
-      <c r="K92" t="n">
-        <v>1</v>
-      </c>
       <c r="L92" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M92" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
@@ -4255,7 +4255,7 @@
         <v>0</v>
       </c>
       <c r="H93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I93" t="n">
         <v>1</v>
@@ -4264,13 +4264,13 @@
         <v>1</v>
       </c>
       <c r="K93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L93" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -4284,34 +4284,34 @@
         <v>0</v>
       </c>
       <c r="D94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F94" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H94" t="n">
         <v>1</v>
       </c>
       <c r="I94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J94" t="n">
         <v>2</v>
       </c>
       <c r="K94" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -4322,37 +4322,37 @@
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D95" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" t="n">
         <v>3</v>
       </c>
-      <c r="E95" t="n">
-        <v>0</v>
-      </c>
       <c r="F95" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G95" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I95" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J95" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K95" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L95" t="n">
+        <v>2</v>
+      </c>
+      <c r="M95" t="n">
         <v>4</v>
-      </c>
-      <c r="M95" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="96">
@@ -4361,41 +4361,39 @@
           <t>電腦及週邊設備業右下</t>
         </is>
       </c>
-      <c r="B96" t="n">
-        <v>0</v>
-      </c>
+      <c r="B96" t="inlineStr"/>
       <c r="C96" t="n">
         <v>2</v>
       </c>
       <c r="D96" t="n">
+        <v>1</v>
+      </c>
+      <c r="E96" t="n">
+        <v>2</v>
+      </c>
+      <c r="F96" t="n">
+        <v>1</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" t="n">
+        <v>1</v>
+      </c>
+      <c r="K96" t="n">
         <v>3</v>
       </c>
-      <c r="E96" t="n">
-        <v>2</v>
-      </c>
-      <c r="F96" t="n">
-        <v>2</v>
-      </c>
-      <c r="G96" t="n">
-        <v>1</v>
-      </c>
-      <c r="H96" t="n">
-        <v>0</v>
-      </c>
-      <c r="I96" t="n">
-        <v>0</v>
-      </c>
-      <c r="J96" t="n">
-        <v>1</v>
-      </c>
-      <c r="K96" t="n">
-        <v>1</v>
-      </c>
       <c r="L96" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="97">
@@ -4406,34 +4404,34 @@
       </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F97" t="n">
         <v>2</v>
       </c>
       <c r="G97" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H97" t="n">
         <v>1</v>
       </c>
       <c r="I97" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J97" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K97" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
         <v>1</v>
@@ -4518,7 +4516,7 @@
         <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100">

--- a/Result/analyze_1.xlsx
+++ b/Result/analyze_1.xlsx
@@ -441,57 +441,57 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-28</t>
         </is>
       </c>
     </row>
@@ -503,37 +503,37 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F2" t="n">
         <v>5</v>
       </c>
-      <c r="E2" t="n">
+      <c r="G2" t="n">
         <v>4</v>
       </c>
-      <c r="F2" t="n">
-        <v>7</v>
-      </c>
-      <c r="G2" t="n">
-        <v>6</v>
-      </c>
       <c r="H2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="K2" t="n">
         <v>10</v>
       </c>
       <c r="L2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -546,31 +546,31 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
         <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -587,34 +587,34 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M4" t="n">
         <v>1</v>
@@ -628,37 +628,37 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
         <v>3</v>
       </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
       <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L5" t="n">
         <v>3</v>
       </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>2</v>
-      </c>
-      <c r="L5" t="n">
-        <v>2</v>
-      </c>
       <c r="M5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -669,25 +669,25 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
         <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -699,7 +699,7 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -710,10 +710,10 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -725,7 +725,7 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -740,7 +740,7 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -751,37 +751,37 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F8" t="n">
+        <v>5</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
         <v>3</v>
-      </c>
-      <c r="E8" t="n">
-        <v>5</v>
-      </c>
-      <c r="F8" t="n">
-        <v>8</v>
-      </c>
-      <c r="G8" t="n">
-        <v>5</v>
-      </c>
-      <c r="H8" t="n">
-        <v>1</v>
       </c>
       <c r="I8" t="n">
         <v>3</v>
       </c>
       <c r="J8" t="n">
+        <v>5</v>
+      </c>
+      <c r="K8" t="n">
         <v>3</v>
       </c>
-      <c r="K8" t="n">
-        <v>5</v>
-      </c>
       <c r="L8" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="M8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -792,22 +792,22 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -819,10 +819,10 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -842,25 +842,25 @@
         <v>2</v>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
         <v>1</v>
@@ -880,28 +880,28 @@
         <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11" t="n">
         <v>2</v>
       </c>
       <c r="G11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -913,18 +913,20 @@
           <t>化學工業右下</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
+      <c r="B12" t="n">
+        <v>0</v>
+      </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
         <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -956,7 +958,7 @@
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -997,37 +999,37 @@
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K14" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L14" t="n">
         <v>2</v>
       </c>
       <c r="M14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1040,34 +1042,34 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" t="n">
+        <v>4</v>
+      </c>
+      <c r="E15" t="n">
+        <v>5</v>
+      </c>
+      <c r="F15" t="n">
+        <v>4</v>
+      </c>
+      <c r="G15" t="n">
         <v>3</v>
       </c>
-      <c r="D15" t="n">
-        <v>2</v>
-      </c>
-      <c r="E15" t="n">
+      <c r="H15" t="n">
+        <v>7</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
         <v>4</v>
-      </c>
-      <c r="F15" t="n">
-        <v>5</v>
-      </c>
-      <c r="G15" t="n">
-        <v>4</v>
-      </c>
-      <c r="H15" t="n">
-        <v>3</v>
-      </c>
-      <c r="I15" t="n">
-        <v>8</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1</v>
       </c>
       <c r="M15" t="n">
         <v>4</v>
@@ -1081,37 +1083,37 @@
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E16" t="n">
         <v>3</v>
       </c>
       <c r="F16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J16" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K16" t="n">
         <v>5</v>
       </c>
       <c r="L16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M16" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -1169,19 +1171,19 @@
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1213,7 +1215,7 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -1245,16 +1247,16 @@
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -1292,19 +1294,19 @@
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1368,10 +1370,10 @@
       </c>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -1407,9 +1409,11 @@
           <t>建材營造右下</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="n">
+        <v>0</v>
+      </c>
       <c r="C24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
@@ -1424,10 +1428,10 @@
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1453,7 +1457,7 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -1491,13 +1495,13 @@
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -1506,13 +1510,13 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26" t="n">
         <v>1</v>
       </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -1582,10 +1586,10 @@
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -1629,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29" t="n">
         <v>1</v>
@@ -1638,7 +1642,7 @@
         <v>1</v>
       </c>
       <c r="K29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -1655,16 +1659,16 @@
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1901,16 +1905,16 @@
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E36" t="n">
         <v>1</v>
       </c>
       <c r="F36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1922,13 +1926,13 @@
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M36" t="n">
         <v>1</v>
@@ -1945,7 +1949,7 @@
         <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E37" t="n">
         <v>1</v>
@@ -1954,7 +1958,7 @@
         <v>1</v>
       </c>
       <c r="G37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -1969,10 +1973,10 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2080,19 +2084,19 @@
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
@@ -2147,16 +2151,16 @@
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E42" t="n">
         <v>1</v>
       </c>
       <c r="F42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -2171,10 +2175,10 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
@@ -2188,7 +2192,7 @@
       </c>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D43" t="n">
         <v>0</v>
@@ -2212,10 +2216,10 @@
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
@@ -2229,16 +2233,16 @@
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E44" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F44" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -2247,19 +2251,19 @@
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2268,36 +2272,38 @@
           <t>生技醫療業右下</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr"/>
+      <c r="B45" t="n">
+        <v>0</v>
+      </c>
       <c r="C45" t="n">
         <v>1</v>
       </c>
       <c r="D45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E45" t="n">
+        <v>2</v>
+      </c>
+      <c r="F45" t="n">
+        <v>2</v>
+      </c>
+      <c r="G45" t="n">
+        <v>1</v>
+      </c>
+      <c r="H45" t="n">
+        <v>4</v>
+      </c>
+      <c r="I45" t="n">
+        <v>2</v>
+      </c>
+      <c r="J45" t="n">
+        <v>1</v>
+      </c>
+      <c r="K45" t="n">
         <v>3</v>
       </c>
-      <c r="F45" t="n">
-        <v>2</v>
-      </c>
-      <c r="G45" t="n">
-        <v>2</v>
-      </c>
-      <c r="H45" t="n">
-        <v>1</v>
-      </c>
-      <c r="I45" t="n">
-        <v>3</v>
-      </c>
-      <c r="J45" t="n">
-        <v>2</v>
-      </c>
-      <c r="K45" t="n">
-        <v>1</v>
-      </c>
       <c r="L45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M45" t="n">
         <v>2</v>
@@ -2311,7 +2317,7 @@
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D46" t="n">
         <v>1</v>
@@ -2323,25 +2329,25 @@
         <v>1</v>
       </c>
       <c r="G46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K46" t="n">
         <v>1</v>
       </c>
       <c r="L46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -2379,7 +2385,7 @@
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M47" t="n">
         <v>1</v>
@@ -2393,10 +2399,10 @@
       </c>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E48" t="n">
         <v>0</v>
@@ -2434,16 +2440,16 @@
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D49" t="n">
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -2452,10 +2458,10 @@
         <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
@@ -2484,28 +2490,28 @@
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J50" t="n">
         <v>1</v>
       </c>
       <c r="K50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -2546,7 +2552,7 @@
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -2575,13 +2581,13 @@
         <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
@@ -2601,13 +2607,13 @@
         <v>0</v>
       </c>
       <c r="D53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -2619,10 +2625,10 @@
         <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L53" t="n">
         <v>1</v>
@@ -2648,7 +2654,7 @@
         <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -2692,7 +2698,7 @@
         <v>0</v>
       </c>
       <c r="G55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
@@ -2710,7 +2716,7 @@
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -2724,10 +2730,10 @@
         <v>0</v>
       </c>
       <c r="D56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -2760,7 +2766,9 @@
           <t>觀光事業右下</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr"/>
+      <c r="B57" t="n">
+        <v>0</v>
+      </c>
       <c r="C57" t="n">
         <v>0</v>
       </c>
@@ -2768,10 +2776,10 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -2786,10 +2794,10 @@
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L57" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
         <v>0</v>
@@ -2839,7 +2847,7 @@
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>貿易百貨右上</t>
+          <t>貿易百貨右下</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -2880,7 +2888,7 @@
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>貿易百貨右下</t>
+          <t>貿易百貨平</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -2929,7 +2937,7 @@
         <v>1</v>
       </c>
       <c r="D61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E61" t="n">
         <v>1</v>
@@ -2938,19 +2946,19 @@
         <v>0</v>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
@@ -2965,14 +2973,12 @@
           <t>資訊服務業右下</t>
         </is>
       </c>
-      <c r="B62" t="n">
-        <v>0</v>
-      </c>
+      <c r="B62" t="inlineStr"/>
       <c r="C62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E62" t="n">
         <v>0</v>
@@ -2981,10 +2987,10 @@
         <v>0</v>
       </c>
       <c r="G62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I62" t="n">
         <v>0</v>
@@ -3090,7 +3096,9 @@
           <t>農業科技業右下</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr"/>
+      <c r="B65" t="n">
+        <v>0</v>
+      </c>
       <c r="C65" t="n">
         <v>0</v>
       </c>
@@ -3133,37 +3141,37 @@
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D66" t="n">
+        <v>8</v>
+      </c>
+      <c r="E66" t="n">
         <v>7</v>
       </c>
-      <c r="E66" t="n">
-        <v>8</v>
-      </c>
       <c r="F66" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G66" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I66" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J66" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K66" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M66" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -3172,21 +3180,23 @@
           <t>通信網路業右下</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr"/>
+      <c r="B67" t="n">
+        <v>0</v>
+      </c>
       <c r="C67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H67" t="n">
         <v>1</v>
@@ -3198,13 +3208,13 @@
         <v>1</v>
       </c>
       <c r="K67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -3215,13 +3225,13 @@
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D68" t="n">
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F68" t="n">
         <v>0</v>
@@ -3233,19 +3243,19 @@
         <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K68" t="n">
         <v>0</v>
       </c>
       <c r="L68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -3435,10 +3445,10 @@
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -3737,7 +3747,7 @@
         <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
@@ -3754,13 +3764,13 @@
         <v>0</v>
       </c>
       <c r="E81" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F81" t="n">
         <v>2</v>
       </c>
       <c r="G81" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
@@ -3830,10 +3840,10 @@
       </c>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E83" t="n">
         <v>0</v>
@@ -3857,10 +3867,10 @@
         <v>0</v>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -3968,22 +3978,22 @@
         <v>0</v>
       </c>
       <c r="H86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
@@ -3994,13 +4004,13 @@
       </c>
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D87" t="n">
         <v>1</v>
       </c>
       <c r="E87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F87" t="n">
         <v>0</v>
@@ -4024,7 +4034,7 @@
         <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
@@ -4047,25 +4057,25 @@
         <v>1</v>
       </c>
       <c r="G88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L88" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M88" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -4082,31 +4092,31 @@
         <v>11</v>
       </c>
       <c r="E89" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F89" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="G89" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H89" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="I89" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="J89" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="K89" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="L89" t="n">
+        <v>14</v>
+      </c>
+      <c r="M89" t="n">
         <v>5</v>
-      </c>
-      <c r="M89" t="n">
-        <v>14</v>
       </c>
     </row>
     <row r="90">
@@ -4117,37 +4127,37 @@
       </c>
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D90" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E90" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F90" t="n">
         <v>4</v>
       </c>
       <c r="G90" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I90" t="n">
         <v>1</v>
       </c>
       <c r="J90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L90" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M90" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="91">
@@ -4161,31 +4171,31 @@
         <v>1</v>
       </c>
       <c r="D91" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E91" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F91" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H91" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I91" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K91" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M91" t="n">
         <v>2</v>
@@ -4199,37 +4209,37 @@
       </c>
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D92" t="n">
         <v>1</v>
       </c>
       <c r="E92" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F92" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H92" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I92" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J92" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K92" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L92" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93">
@@ -4252,7 +4262,7 @@
         <v>0</v>
       </c>
       <c r="G93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H93" t="n">
         <v>1</v>
@@ -4261,13 +4271,13 @@
         <v>1</v>
       </c>
       <c r="J93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K93" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
         <v>0</v>
@@ -4281,37 +4291,37 @@
       </c>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D94" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E94" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G94" t="n">
         <v>1</v>
       </c>
       <c r="H94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I94" t="n">
         <v>2</v>
       </c>
       <c r="J94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
@@ -4322,37 +4332,37 @@
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" t="n">
         <v>3</v>
       </c>
-      <c r="D95" t="n">
-        <v>0</v>
-      </c>
       <c r="E95" t="n">
+        <v>7</v>
+      </c>
+      <c r="F95" t="n">
+        <v>1</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" t="n">
+        <v>5</v>
+      </c>
+      <c r="I95" t="n">
+        <v>1</v>
+      </c>
+      <c r="J95" t="n">
+        <v>4</v>
+      </c>
+      <c r="K95" t="n">
+        <v>1</v>
+      </c>
+      <c r="L95" t="n">
         <v>3</v>
       </c>
-      <c r="F95" t="n">
-        <v>7</v>
-      </c>
-      <c r="G95" t="n">
-        <v>1</v>
-      </c>
-      <c r="H95" t="n">
-        <v>0</v>
-      </c>
-      <c r="I95" t="n">
-        <v>5</v>
-      </c>
-      <c r="J95" t="n">
-        <v>1</v>
-      </c>
-      <c r="K95" t="n">
-        <v>4</v>
-      </c>
-      <c r="L95" t="n">
-        <v>2</v>
-      </c>
       <c r="M95" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="96">
@@ -4361,39 +4371,41 @@
           <t>電腦及週邊設備業右下</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr"/>
+      <c r="B96" t="n">
+        <v>0</v>
+      </c>
       <c r="C96" t="n">
         <v>2</v>
       </c>
       <c r="D96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E96" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
       </c>
       <c r="H96" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J96" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K96" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L96" t="n">
         <v>1</v>
       </c>
       <c r="M96" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -4404,7 +4416,7 @@
       </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D97" t="n">
         <v>2</v>
@@ -4413,7 +4425,7 @@
         <v>2</v>
       </c>
       <c r="F97" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G97" t="n">
         <v>1</v>
@@ -4422,16 +4434,16 @@
         <v>1</v>
       </c>
       <c r="I97" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" t="n">
+        <v>2</v>
+      </c>
+      <c r="K97" t="n">
+        <v>1</v>
+      </c>
+      <c r="L97" t="n">
         <v>3</v>
-      </c>
-      <c r="J97" t="n">
-        <v>0</v>
-      </c>
-      <c r="K97" t="n">
-        <v>2</v>
-      </c>
-      <c r="L97" t="n">
-        <v>0</v>
       </c>
       <c r="M97" t="n">
         <v>1</v>
@@ -4516,7 +4528,7 @@
         <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -4554,10 +4566,10 @@
         <v>0</v>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Result/analyze_1.xlsx
+++ b/Result/analyze_1.xlsx
@@ -441,57 +441,57 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
     </row>
@@ -503,10 +503,10 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E2" t="n">
         <v>6</v>
@@ -515,25 +515,25 @@
         <v>5</v>
       </c>
       <c r="G2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>11</v>
+      </c>
+      <c r="J2" t="n">
+        <v>9</v>
+      </c>
+      <c r="K2" t="n">
+        <v>5</v>
+      </c>
+      <c r="L2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M2" t="n">
         <v>4</v>
-      </c>
-      <c r="H2" t="n">
-        <v>4</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J2" t="n">
-        <v>11</v>
-      </c>
-      <c r="K2" t="n">
-        <v>10</v>
-      </c>
-      <c r="L2" t="n">
-        <v>5</v>
-      </c>
-      <c r="M2" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -542,17 +542,15 @@
           <t>光電業右下</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>0</v>
-      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
@@ -561,13 +559,13 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -576,7 +574,7 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -587,31 +585,31 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
         <v>3</v>
       </c>
-      <c r="F4" t="n">
-        <v>3</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1</v>
-      </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
         <v>1</v>
@@ -628,37 +626,37 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
         <v>3</v>
       </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
       <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" t="n">
         <v>3</v>
       </c>
-      <c r="I5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" t="n">
-        <v>2</v>
-      </c>
-      <c r="K5" t="n">
-        <v>2</v>
-      </c>
       <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
         <v>3</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -667,7 +665,9 @@
           <t>其他右下</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
@@ -675,13 +675,13 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -696,10 +696,10 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -710,7 +710,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -722,10 +722,10 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -737,10 +737,10 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -751,37 +751,37 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
+        <v>5</v>
+      </c>
+      <c r="D8" t="n">
+        <v>8</v>
+      </c>
+      <c r="E8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
         <v>3</v>
-      </c>
-      <c r="D8" t="n">
-        <v>5</v>
-      </c>
-      <c r="E8" t="n">
-        <v>8</v>
-      </c>
-      <c r="F8" t="n">
-        <v>5</v>
-      </c>
-      <c r="G8" t="n">
-        <v>1</v>
       </c>
       <c r="H8" t="n">
         <v>3</v>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -790,21 +790,23 @@
           <t>其他電子業右下</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -816,13 +818,13 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -833,37 +835,37 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L10" t="n">
         <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -877,34 +879,34 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -920,10 +922,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -947,7 +949,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -999,37 +1001,37 @@
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E14" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>6</v>
+      </c>
+      <c r="J14" t="n">
         <v>3</v>
       </c>
-      <c r="F14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" t="n">
-        <v>2</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
+      <c r="K14" t="n">
+        <v>2</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
         <v>6</v>
-      </c>
-      <c r="K14" t="n">
-        <v>2</v>
-      </c>
-      <c r="L14" t="n">
-        <v>2</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1042,37 +1044,37 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D15" t="n">
+        <v>5</v>
+      </c>
+      <c r="E15" t="n">
         <v>4</v>
       </c>
-      <c r="E15" t="n">
-        <v>5</v>
-      </c>
       <c r="F15" t="n">
+        <v>3</v>
+      </c>
+      <c r="G15" t="n">
+        <v>7</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
         <v>4</v>
-      </c>
-      <c r="G15" t="n">
-        <v>3</v>
-      </c>
-      <c r="H15" t="n">
-        <v>7</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1</v>
       </c>
       <c r="L15" t="n">
         <v>4</v>
       </c>
       <c r="M15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -1083,37 +1085,37 @@
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
         <v>3</v>
       </c>
       <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>4</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2</v>
+      </c>
+      <c r="I16" t="n">
+        <v>4</v>
+      </c>
+      <c r="J16" t="n">
         <v>3</v>
       </c>
-      <c r="F16" t="n">
-        <v>1</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>4</v>
-      </c>
-      <c r="I16" t="n">
-        <v>2</v>
-      </c>
-      <c r="J16" t="n">
-        <v>5</v>
-      </c>
       <c r="K16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L16" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -1168,19 +1170,19 @@
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -1247,13 +1249,13 @@
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -1291,19 +1293,19 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -1359,7 +1361,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1370,7 +1372,7 @@
       </c>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
@@ -1409,9 +1411,7 @@
           <t>建材營造右下</t>
         </is>
       </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
+      <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
         <v>0</v>
       </c>
@@ -1425,10 +1425,10 @@
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
@@ -1495,10 +1495,10 @@
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -1507,13 +1507,13 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H26" t="n">
         <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1566,7 +1566,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -1583,10 +1583,10 @@
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1630,7 +1630,7 @@
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H29" t="n">
         <v>1</v>
@@ -1639,7 +1639,7 @@
         <v>1</v>
       </c>
       <c r="J29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -1662,10 +1662,10 @@
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -1905,13 +1905,13 @@
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D36" t="n">
         <v>1</v>
       </c>
       <c r="E36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
@@ -1923,13 +1923,13 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L36" t="n">
         <v>1</v>
@@ -1949,13 +1949,13 @@
         <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E37" t="n">
         <v>1</v>
       </c>
       <c r="F37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1970,13 +1970,13 @@
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -1987,10 +1987,10 @@
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
@@ -2011,13 +2011,13 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2081,19 +2081,19 @@
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -2151,13 +2151,13 @@
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D42" t="n">
         <v>1</v>
       </c>
       <c r="E42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -2172,10 +2172,10 @@
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
@@ -2213,10 +2213,10 @@
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -2233,13 +2233,13 @@
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D44" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E44" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
@@ -2248,22 +2248,22 @@
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2272,41 +2272,39 @@
           <t>生技醫療業右下</t>
         </is>
       </c>
-      <c r="B45" t="n">
-        <v>0</v>
-      </c>
+      <c r="B45" t="inlineStr"/>
       <c r="C45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D45" t="n">
+        <v>2</v>
+      </c>
+      <c r="E45" t="n">
+        <v>2</v>
+      </c>
+      <c r="F45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" t="n">
+        <v>4</v>
+      </c>
+      <c r="H45" t="n">
+        <v>2</v>
+      </c>
+      <c r="I45" t="n">
+        <v>1</v>
+      </c>
+      <c r="J45" t="n">
         <v>3</v>
       </c>
-      <c r="E45" t="n">
-        <v>2</v>
-      </c>
-      <c r="F45" t="n">
-        <v>2</v>
-      </c>
-      <c r="G45" t="n">
-        <v>1</v>
-      </c>
-      <c r="H45" t="n">
-        <v>4</v>
-      </c>
-      <c r="I45" t="n">
-        <v>2</v>
-      </c>
-      <c r="J45" t="n">
-        <v>1</v>
-      </c>
       <c r="K45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -2326,25 +2324,25 @@
         <v>1</v>
       </c>
       <c r="F46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H46" t="n">
         <v>2</v>
       </c>
       <c r="I46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J46" t="n">
         <v>1</v>
       </c>
       <c r="K46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M46" t="n">
         <v>1</v>
@@ -2382,13 +2380,13 @@
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L47" t="n">
         <v>1</v>
       </c>
       <c r="M47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -2399,7 +2397,7 @@
       </c>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
@@ -2443,10 +2441,10 @@
         <v>0</v>
       </c>
       <c r="D49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -2455,10 +2453,10 @@
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -2487,31 +2485,31 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H50" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I50" t="n">
         <v>1</v>
       </c>
       <c r="J50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -2520,7 +2518,9 @@
           <t>綠能環保右下</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr"/>
+      <c r="B51" t="n">
+        <v>0</v>
+      </c>
       <c r="C51" t="n">
         <v>0</v>
       </c>
@@ -2537,7 +2537,7 @@
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I51" t="n">
         <v>0</v>
@@ -2549,10 +2549,10 @@
         <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -2578,13 +2578,13 @@
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K52" t="n">
         <v>0</v>
@@ -2593,7 +2593,7 @@
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -2604,13 +2604,13 @@
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F53" t="n">
         <v>0</v>
@@ -2622,10 +2622,10 @@
         <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K53" t="n">
         <v>1</v>
@@ -2651,10 +2651,10 @@
         <v>0</v>
       </c>
       <c r="E54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -2713,10 +2713,10 @@
         <v>0</v>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -2727,10 +2727,10 @@
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E56" t="n">
         <v>0</v>
@@ -2773,10 +2773,10 @@
         <v>0</v>
       </c>
       <c r="D57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -2791,10 +2791,10 @@
         <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
@@ -2940,25 +2940,25 @@
         <v>1</v>
       </c>
       <c r="E61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J61" t="n">
         <v>1</v>
       </c>
       <c r="K61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
@@ -2973,9 +2973,11 @@
           <t>資訊服務業右下</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr"/>
+      <c r="B62" t="n">
+        <v>0</v>
+      </c>
       <c r="C62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D62" t="n">
         <v>0</v>
@@ -2984,10 +2986,10 @@
         <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H62" t="n">
         <v>0</v>
@@ -3096,9 +3098,7 @@
           <t>農業科技業右下</t>
         </is>
       </c>
-      <c r="B65" t="n">
-        <v>0</v>
-      </c>
+      <c r="B65" t="inlineStr"/>
       <c r="C65" t="n">
         <v>0</v>
       </c>
@@ -3141,37 +3141,37 @@
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="n">
+        <v>8</v>
+      </c>
+      <c r="D66" t="n">
         <v>7</v>
       </c>
-      <c r="D66" t="n">
-        <v>8</v>
-      </c>
       <c r="E66" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F66" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H66" t="n">
+        <v>1</v>
+      </c>
+      <c r="I66" t="n">
+        <v>5</v>
+      </c>
+      <c r="J66" t="n">
+        <v>1</v>
+      </c>
+      <c r="K66" t="n">
+        <v>4</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" t="n">
         <v>3</v>
-      </c>
-      <c r="I66" t="n">
-        <v>0</v>
-      </c>
-      <c r="J66" t="n">
-        <v>4</v>
-      </c>
-      <c r="K66" t="n">
-        <v>1</v>
-      </c>
-      <c r="L66" t="n">
-        <v>4</v>
-      </c>
-      <c r="M66" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -3180,20 +3180,18 @@
           <t>通信網路業右下</t>
         </is>
       </c>
-      <c r="B67" t="n">
-        <v>0</v>
-      </c>
+      <c r="B67" t="inlineStr"/>
       <c r="C67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G67" t="n">
         <v>1</v>
@@ -3205,16 +3203,16 @@
         <v>1</v>
       </c>
       <c r="J67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68">
@@ -3225,10 +3223,10 @@
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E68" t="n">
         <v>0</v>
@@ -3243,19 +3241,19 @@
         <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69">
@@ -3442,10 +3440,10 @@
         <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I73" t="n">
         <v>0</v>
@@ -3744,10 +3742,10 @@
         <v>0</v>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -3756,18 +3754,20 @@
           <t>鋼鐵工業右下</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr"/>
+      <c r="B81" t="n">
+        <v>0</v>
+      </c>
       <c r="C81" t="n">
         <v>0</v>
       </c>
       <c r="D81" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E81" t="n">
         <v>2</v>
       </c>
       <c r="F81" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -3840,7 +3840,7 @@
       </c>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D83" t="n">
         <v>0</v>
@@ -3864,10 +3864,10 @@
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
         <v>0</v>
@@ -3975,16 +3975,16 @@
         <v>0</v>
       </c>
       <c r="G86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I86" t="n">
         <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K86" t="n">
         <v>1</v>
@@ -4002,12 +4002,14 @@
           <t>電子通路業右下</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr"/>
+      <c r="B87" t="n">
+        <v>0</v>
+      </c>
       <c r="C87" t="n">
         <v>1</v>
       </c>
       <c r="D87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E87" t="n">
         <v>0</v>
@@ -4054,19 +4056,19 @@
         <v>1</v>
       </c>
       <c r="F88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I88" t="n">
         <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K88" t="n">
         <v>1</v>
@@ -4075,7 +4077,7 @@
         <v>1</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
@@ -4089,34 +4091,34 @@
         <v>11</v>
       </c>
       <c r="D89" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E89" t="n">
+        <v>2</v>
+      </c>
+      <c r="F89" t="n">
+        <v>3</v>
+      </c>
+      <c r="G89" t="n">
+        <v>13</v>
+      </c>
+      <c r="H89" t="n">
+        <v>1</v>
+      </c>
+      <c r="I89" t="n">
+        <v>14</v>
+      </c>
+      <c r="J89" t="n">
+        <v>6</v>
+      </c>
+      <c r="K89" t="n">
+        <v>14</v>
+      </c>
+      <c r="L89" t="n">
+        <v>4</v>
+      </c>
+      <c r="M89" t="n">
         <v>17</v>
-      </c>
-      <c r="F89" t="n">
-        <v>2</v>
-      </c>
-      <c r="G89" t="n">
-        <v>3</v>
-      </c>
-      <c r="H89" t="n">
-        <v>12</v>
-      </c>
-      <c r="I89" t="n">
-        <v>1</v>
-      </c>
-      <c r="J89" t="n">
-        <v>14</v>
-      </c>
-      <c r="K89" t="n">
-        <v>5</v>
-      </c>
-      <c r="L89" t="n">
-        <v>14</v>
-      </c>
-      <c r="M89" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="90">
@@ -4127,37 +4129,37 @@
       </c>
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D90" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E90" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F90" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H90" t="n">
         <v>1</v>
       </c>
       <c r="I90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J90" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K90" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L90" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M90" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
@@ -4171,34 +4173,34 @@
         <v>1</v>
       </c>
       <c r="D91" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E91" t="n">
+        <v>1</v>
+      </c>
+      <c r="F91" t="n">
+        <v>2</v>
+      </c>
+      <c r="G91" t="n">
+        <v>2</v>
+      </c>
+      <c r="H91" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" t="n">
+        <v>1</v>
+      </c>
+      <c r="J91" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" t="n">
+        <v>2</v>
+      </c>
+      <c r="L91" t="n">
         <v>3</v>
       </c>
-      <c r="F91" t="n">
-        <v>1</v>
-      </c>
-      <c r="G91" t="n">
-        <v>2</v>
-      </c>
-      <c r="H91" t="n">
+      <c r="M91" t="n">
         <v>3</v>
-      </c>
-      <c r="I91" t="n">
-        <v>0</v>
-      </c>
-      <c r="J91" t="n">
-        <v>1</v>
-      </c>
-      <c r="K91" t="n">
-        <v>1</v>
-      </c>
-      <c r="L91" t="n">
-        <v>2</v>
-      </c>
-      <c r="M91" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="92">
@@ -4209,37 +4211,37 @@
       </c>
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D92" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E92" t="n">
+        <v>1</v>
+      </c>
+      <c r="F92" t="n">
+        <v>1</v>
+      </c>
+      <c r="G92" t="n">
         <v>5</v>
       </c>
-      <c r="F92" t="n">
-        <v>1</v>
-      </c>
-      <c r="G92" t="n">
-        <v>0</v>
-      </c>
       <c r="H92" t="n">
+        <v>2</v>
+      </c>
+      <c r="I92" t="n">
         <v>4</v>
       </c>
-      <c r="I92" t="n">
-        <v>1</v>
-      </c>
       <c r="J92" t="n">
+        <v>2</v>
+      </c>
+      <c r="K92" t="n">
+        <v>1</v>
+      </c>
+      <c r="L92" t="n">
         <v>3</v>
       </c>
-      <c r="K92" t="n">
-        <v>2</v>
-      </c>
-      <c r="L92" t="n">
-        <v>1</v>
-      </c>
       <c r="M92" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -4259,22 +4261,22 @@
         <v>0</v>
       </c>
       <c r="F93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G93" t="n">
         <v>1</v>
       </c>
       <c r="H93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J93" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L93" t="n">
         <v>0</v>
@@ -4291,31 +4293,31 @@
       </c>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D94" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G94" t="n">
         <v>1</v>
       </c>
       <c r="H94" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I94" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J94" t="n">
         <v>1</v>
       </c>
       <c r="K94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L94" t="n">
         <v>0</v>
@@ -4332,37 +4334,37 @@
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D95" t="n">
+        <v>7</v>
+      </c>
+      <c r="E95" t="n">
+        <v>1</v>
+      </c>
+      <c r="F95" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" t="n">
+        <v>5</v>
+      </c>
+      <c r="H95" t="n">
+        <v>1</v>
+      </c>
+      <c r="I95" t="n">
+        <v>4</v>
+      </c>
+      <c r="J95" t="n">
+        <v>1</v>
+      </c>
+      <c r="K95" t="n">
         <v>3</v>
       </c>
-      <c r="E95" t="n">
-        <v>7</v>
-      </c>
-      <c r="F95" t="n">
-        <v>1</v>
-      </c>
-      <c r="G95" t="n">
-        <v>0</v>
-      </c>
-      <c r="H95" t="n">
-        <v>5</v>
-      </c>
-      <c r="I95" t="n">
-        <v>1</v>
-      </c>
-      <c r="J95" t="n">
-        <v>4</v>
-      </c>
-      <c r="K95" t="n">
-        <v>1</v>
-      </c>
       <c r="L95" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M95" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
@@ -4371,35 +4373,33 @@
           <t>電腦及週邊設備業右下</t>
         </is>
       </c>
-      <c r="B96" t="n">
-        <v>0</v>
-      </c>
+      <c r="B96" t="inlineStr"/>
       <c r="C96" t="n">
         <v>2</v>
       </c>
       <c r="D96" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F96" t="n">
         <v>0</v>
       </c>
       <c r="G96" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H96" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J96" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L96" t="n">
         <v>1</v>
@@ -4416,13 +4416,13 @@
       </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D97" t="n">
         <v>2</v>
       </c>
       <c r="E97" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F97" t="n">
         <v>1</v>
@@ -4431,22 +4431,22 @@
         <v>1</v>
       </c>
       <c r="H97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I97" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J97" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L97" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -4563,13 +4563,13 @@
         <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L100" t="n">
         <v>1</v>
       </c>
       <c r="M100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Result/analyze_1.xlsx
+++ b/Result/analyze_1.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M100"/>
+  <dimension ref="A1:M101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,57 +441,57 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-01</t>
         </is>
       </c>
     </row>
@@ -503,37 +503,37 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E2" t="n">
         <v>3</v>
-      </c>
-      <c r="D2" t="n">
-        <v>7</v>
-      </c>
-      <c r="E2" t="n">
-        <v>6</v>
       </c>
       <c r="F2" t="n">
         <v>5</v>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I2" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J2" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="K2" t="n">
         <v>5</v>
       </c>
       <c r="L2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -544,25 +544,25 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -571,7 +571,7 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" t="n">
         <v>1</v>
@@ -585,31 +585,31 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L4" t="n">
         <v>1</v>
@@ -626,37 +626,37 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
         <v>3</v>
       </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
       <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J5" t="n">
         <v>3</v>
       </c>
-      <c r="H5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" t="n">
-        <v>2</v>
-      </c>
-      <c r="J5" t="n">
-        <v>2</v>
-      </c>
       <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
         <v>3</v>
       </c>
-      <c r="L5" t="n">
-        <v>1</v>
-      </c>
       <c r="M5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -665,20 +665,18 @@
           <t>其他右下</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>0</v>
-      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -693,13 +691,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -719,10 +717,10 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -734,10 +732,10 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -751,37 +749,37 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
+        <v>8</v>
+      </c>
+      <c r="D8" t="n">
         <v>5</v>
       </c>
-      <c r="D8" t="n">
-        <v>8</v>
-      </c>
       <c r="E8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G8" t="n">
         <v>3</v>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K8" t="n">
         <v>6</v>
       </c>
       <c r="L8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M8" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -790,20 +788,18 @@
           <t>其他電子業右下</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0</v>
-      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -815,16 +811,16 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
         <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -838,34 +834,34 @@
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
         <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -876,31 +872,31 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
         <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
         <v>1</v>
@@ -915,14 +911,12 @@
           <t>化學工業右下</t>
         </is>
       </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -946,10 +940,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1001,37 +995,37 @@
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>5</v>
+      </c>
+      <c r="I14" t="n">
         <v>3</v>
       </c>
-      <c r="E14" t="n">
-        <v>2</v>
-      </c>
-      <c r="F14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" t="n">
-        <v>2</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
+        <v>2</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
         <v>6</v>
       </c>
-      <c r="J14" t="n">
-        <v>3</v>
-      </c>
-      <c r="K14" t="n">
-        <v>2</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
       <c r="M14" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1044,37 +1038,37 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
+        <v>6</v>
+      </c>
+      <c r="D15" t="n">
         <v>4</v>
       </c>
-      <c r="D15" t="n">
+      <c r="E15" t="n">
+        <v>3</v>
+      </c>
+      <c r="F15" t="n">
+        <v>9</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" t="n">
         <v>5</v>
-      </c>
-      <c r="E15" t="n">
-        <v>4</v>
-      </c>
-      <c r="F15" t="n">
-        <v>3</v>
-      </c>
-      <c r="G15" t="n">
-        <v>7</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1</v>
       </c>
       <c r="K15" t="n">
         <v>4</v>
       </c>
       <c r="L15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1088,34 +1082,34 @@
         <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H16" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I16" t="n">
         <v>4</v>
       </c>
       <c r="J16" t="n">
+        <v>5</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2</v>
+      </c>
+      <c r="L16" t="n">
         <v>3</v>
       </c>
-      <c r="K16" t="n">
-        <v>6</v>
-      </c>
-      <c r="L16" t="n">
-        <v>2</v>
-      </c>
       <c r="M16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -1167,19 +1161,19 @@
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -1249,10 +1243,10 @@
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -1290,19 +1284,19 @@
       </c>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -1320,7 +1314,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1358,10 +1352,10 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1422,10 +1416,10 @@
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1495,7 +1489,7 @@
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
@@ -1504,13 +1498,13 @@
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26" t="n">
         <v>1</v>
       </c>
       <c r="H26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -1563,7 +1557,7 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M27" t="n">
         <v>1</v>
@@ -1580,10 +1574,10 @@
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
@@ -1607,7 +1601,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -1627,7 +1621,7 @@
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G29" t="n">
         <v>1</v>
@@ -1636,7 +1630,7 @@
         <v>1</v>
       </c>
       <c r="I29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1659,10 +1653,10 @@
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -1908,7 +1902,7 @@
         <v>1</v>
       </c>
       <c r="D36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
@@ -1920,13 +1914,13 @@
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K36" t="n">
         <v>1</v>
@@ -1935,7 +1929,7 @@
         <v>1</v>
       </c>
       <c r="M36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -1949,10 +1943,10 @@
         <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
@@ -1967,16 +1961,16 @@
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -1990,7 +1984,7 @@
         <v>1</v>
       </c>
       <c r="D38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
@@ -2008,16 +2002,16 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2078,19 +2072,19 @@
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -2154,7 +2148,7 @@
         <v>1</v>
       </c>
       <c r="D42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
@@ -2169,10 +2163,10 @@
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -2187,7 +2181,7 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>玻璃陶瓷平</t>
+          <t>玻璃陶瓷右下</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -2213,7 +2207,7 @@
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -2228,15 +2222,15 @@
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>生技醫療業右上</t>
+          <t>玻璃陶瓷平</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
@@ -2248,19 +2242,19 @@
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
@@ -2269,39 +2263,39 @@
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>生技醫療業右下</t>
+          <t>生技醫療業右上</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
         <v>1</v>
       </c>
       <c r="G45" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
         <v>1</v>
@@ -2310,39 +2304,39 @@
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>生技醫療業平</t>
+          <t>生技醫療業右下</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D46" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E46" t="n">
         <v>1</v>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G46" t="n">
         <v>2</v>
       </c>
       <c r="H46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I46" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
         <v>1</v>
@@ -2351,12 +2345,12 @@
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>紡織纖維右上</t>
+          <t>生技醫療業平</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D47" t="n">
         <v>0</v>
@@ -2365,16 +2359,16 @@
         <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -2383,16 +2377,16 @@
         <v>1</v>
       </c>
       <c r="L47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>紡織纖維右下</t>
+          <t>紡織纖維右上</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -2418,10 +2412,10 @@
         <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
@@ -2433,15 +2427,15 @@
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>紡織纖維平</t>
+          <t>紡織纖維右下</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E49" t="n">
         <v>0</v>
@@ -2453,7 +2447,7 @@
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I49" t="n">
         <v>0</v>
@@ -2474,7 +2468,7 @@
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>綠能環保右上</t>
+          <t>紡織纖維平</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -2485,7 +2479,7 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -2497,7 +2491,7 @@
         <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -2506,7 +2500,7 @@
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
         <v>0</v>
@@ -2515,26 +2509,24 @@
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>綠能環保右下</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>0</v>
-      </c>
+          <t>綠能環保右上</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr"/>
       <c r="C51" t="n">
         <v>0</v>
       </c>
       <c r="D51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E51" t="n">
         <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H51" t="n">
         <v>1</v>
@@ -2546,7 +2538,7 @@
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L51" t="n">
         <v>1</v>
@@ -2558,7 +2550,7 @@
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>綠能環保平</t>
+          <t>綠能環保右下</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -2575,39 +2567,39 @@
         <v>0</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>航運業右上</t>
+          <t>綠能環保平</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E53" t="n">
         <v>0</v>
@@ -2616,42 +2608,42 @@
         <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L53" t="n">
         <v>1</v>
       </c>
       <c r="M53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>航運業右下</t>
+          <t>航運業右上</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D54" t="n">
         <v>0</v>
       </c>
       <c r="E54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F54" t="n">
         <v>0</v>
@@ -2660,19 +2652,19 @@
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M54" t="n">
         <v>0</v>
@@ -2681,7 +2673,7 @@
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>航運業平</t>
+          <t>航運業右下</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
@@ -2689,7 +2681,7 @@
         <v>0</v>
       </c>
       <c r="D55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E55" t="n">
         <v>0</v>
@@ -2713,7 +2705,7 @@
         <v>0</v>
       </c>
       <c r="L55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
         <v>0</v>
@@ -2722,12 +2714,12 @@
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>觀光事業右上</t>
+          <t>航運業平</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D56" t="n">
         <v>0</v>
@@ -2751,7 +2743,7 @@
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
@@ -2763,17 +2755,15 @@
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>觀光事業右下</t>
-        </is>
-      </c>
-      <c r="B57" t="n">
-        <v>0</v>
-      </c>
+          <t>觀光事業右上</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr"/>
       <c r="C57" t="n">
         <v>0</v>
       </c>
       <c r="D57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E57" t="n">
         <v>0</v>
@@ -2791,7 +2781,7 @@
         <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K57" t="n">
         <v>0</v>
@@ -2806,12 +2796,12 @@
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>觀光事業平</t>
+          <t>觀光事業右下</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D58" t="n">
         <v>0</v>
@@ -2829,7 +2819,7 @@
         <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -2847,7 +2837,7 @@
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>貿易百貨右下</t>
+          <t>觀光事業平</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -2888,7 +2878,7 @@
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>貿易百貨平</t>
+          <t>貿易百貨右下</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -2929,33 +2919,33 @@
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>資訊服務業右上</t>
+          <t>貿易百貨平</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E61" t="n">
         <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K61" t="n">
         <v>0</v>
@@ -2970,20 +2960,18 @@
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>資訊服務業右下</t>
-        </is>
-      </c>
-      <c r="B62" t="n">
-        <v>0</v>
-      </c>
+          <t>資訊服務業右上</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr"/>
       <c r="C62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D62" t="n">
         <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F62" t="n">
         <v>1</v>
@@ -2992,10 +2980,10 @@
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -3013,7 +3001,7 @@
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>資訊服務業平</t>
+          <t>資訊服務業右下</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
@@ -3024,7 +3012,7 @@
         <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
@@ -3054,7 +3042,7 @@
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>農業科技業右上</t>
+          <t>資訊服務業平</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
@@ -3095,7 +3083,7 @@
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>農業科技業右下</t>
+          <t>農業科技業右上</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
@@ -3136,53 +3124,53 @@
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>通信網路業右上</t>
+          <t>農業科技業右下</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D66" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E66" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F66" t="n">
         <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I66" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>通信網路業右下</t>
+          <t>通信網路業右上</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D67" t="n">
         <v>2</v>
@@ -3191,75 +3179,75 @@
         <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G67" t="n">
         <v>1</v>
       </c>
       <c r="H67" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I67" t="n">
         <v>1</v>
       </c>
       <c r="J67" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K67" t="n">
         <v>0</v>
       </c>
       <c r="L67" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>通信網路業平</t>
+          <t>通信網路業右下</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D68" t="n">
         <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>造紙工業右下</t>
+          <t>通信網路業平</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
@@ -3285,13 +3273,13 @@
         <v>0</v>
       </c>
       <c r="J69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M69" t="n">
         <v>0</v>
@@ -3300,7 +3288,7 @@
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>造紙工業平</t>
+          <t>造紙工業右下</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
@@ -3341,7 +3329,7 @@
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>運動休閒右上</t>
+          <t>造紙工業平</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
@@ -3382,7 +3370,7 @@
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>運動休閒右下</t>
+          <t>運動休閒右上</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
@@ -3423,10 +3411,12 @@
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>運動休閒平</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr"/>
+          <t>運動休閒右下</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>0</v>
+      </c>
       <c r="C73" t="n">
         <v>0</v>
       </c>
@@ -3440,7 +3430,7 @@
         <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
@@ -3464,7 +3454,7 @@
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>金融保險右上</t>
+          <t>運動休閒平</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
@@ -3478,7 +3468,7 @@
         <v>0</v>
       </c>
       <c r="F74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -3505,7 +3495,7 @@
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>金融保險右下</t>
+          <t>金融保險右上</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
@@ -3546,7 +3536,7 @@
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>金融保險平</t>
+          <t>金融保險右下</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
@@ -3587,7 +3577,7 @@
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>金融業右上</t>
+          <t>金融保險平</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
@@ -3622,13 +3612,13 @@
         <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>金融業右下</t>
+          <t>金融業右上</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
@@ -3669,7 +3659,7 @@
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>金融業平</t>
+          <t>金融業右下</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
@@ -3710,7 +3700,7 @@
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業右上</t>
+          <t>金融業平</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
@@ -3742,7 +3732,7 @@
         <v>0</v>
       </c>
       <c r="L80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
         <v>0</v>
@@ -3751,20 +3741,18 @@
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業右下</t>
-        </is>
-      </c>
-      <c r="B81" t="n">
-        <v>0</v>
-      </c>
+          <t>鋼鐵工業右上</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr"/>
       <c r="C81" t="n">
         <v>0</v>
       </c>
       <c r="D81" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E81" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F81" t="n">
         <v>0</v>
@@ -3782,7 +3770,7 @@
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L81" t="n">
         <v>0</v>
@@ -3794,15 +3782,15 @@
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業平</t>
+          <t>鋼鐵工業右下</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
       <c r="C82" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D82" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E82" t="n">
         <v>0</v>
@@ -3829,13 +3817,13 @@
         <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>電器電纜右上</t>
+          <t>鋼鐵工業平</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
@@ -3864,7 +3852,7 @@
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L83" t="n">
         <v>0</v>
@@ -3876,7 +3864,7 @@
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>電器電纜右下</t>
+          <t>電器電纜右上</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
@@ -3902,7 +3890,7 @@
         <v>0</v>
       </c>
       <c r="J84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K84" t="n">
         <v>0</v>
@@ -3917,7 +3905,7 @@
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>電器電纜平</t>
+          <t>電器電纜右下</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
@@ -3958,7 +3946,7 @@
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>電子通路業右上</t>
+          <t>電器電纜平</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
@@ -3975,7 +3963,7 @@
         <v>0</v>
       </c>
       <c r="G86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H86" t="n">
         <v>0</v>
@@ -3984,29 +3972,27 @@
         <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>電子通路業右下</t>
-        </is>
-      </c>
-      <c r="B87" t="n">
-        <v>0</v>
-      </c>
+          <t>電子通路業右上</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr"/>
       <c r="C87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D87" t="n">
         <v>0</v>
@@ -4024,42 +4010,42 @@
         <v>0</v>
       </c>
       <c r="I87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M87" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>電子通路業平</t>
+          <t>電子通路業右下</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F88" t="n">
         <v>0</v>
       </c>
       <c r="G88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H88" t="n">
         <v>0</v>
@@ -4068,7 +4054,7 @@
         <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K88" t="n">
         <v>1</v>
@@ -4077,86 +4063,86 @@
         <v>1</v>
       </c>
       <c r="M88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業右上</t>
+          <t>電子通路業平</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D89" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="E89" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F89" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G89" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I89" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="J89" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K89" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="L89" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M89" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業右下</t>
+          <t>電子零組件業右上</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="D90" t="n">
+        <v>2</v>
+      </c>
+      <c r="E90" t="n">
+        <v>3</v>
+      </c>
+      <c r="F90" t="n">
+        <v>12</v>
+      </c>
+      <c r="G90" t="n">
+        <v>1</v>
+      </c>
+      <c r="H90" t="n">
+        <v>14</v>
+      </c>
+      <c r="I90" t="n">
+        <v>6</v>
+      </c>
+      <c r="J90" t="n">
+        <v>14</v>
+      </c>
+      <c r="K90" t="n">
         <v>4</v>
       </c>
-      <c r="E90" t="n">
-        <v>4</v>
-      </c>
-      <c r="F90" t="n">
-        <v>0</v>
-      </c>
-      <c r="G90" t="n">
-        <v>1</v>
-      </c>
-      <c r="H90" t="n">
-        <v>1</v>
-      </c>
-      <c r="I90" t="n">
-        <v>0</v>
-      </c>
-      <c r="J90" t="n">
-        <v>2</v>
-      </c>
-      <c r="K90" t="n">
-        <v>1</v>
-      </c>
       <c r="L90" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="M90" t="n">
         <v>1</v>
@@ -4165,48 +4151,48 @@
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業平</t>
+          <t>電子零組件業右下</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D91" t="n">
         <v>4</v>
       </c>
       <c r="E91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F91" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G91" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
       </c>
       <c r="I91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J91" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K91" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L91" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>電機機械右上</t>
+          <t>電子零組件業平</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
@@ -4214,60 +4200,60 @@
         <v>2</v>
       </c>
       <c r="D92" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E92" t="n">
         <v>1</v>
       </c>
       <c r="F92" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G92" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H92" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I92" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" t="n">
+        <v>1</v>
+      </c>
+      <c r="K92" t="n">
+        <v>3</v>
+      </c>
+      <c r="L92" t="n">
         <v>4</v>
       </c>
-      <c r="J92" t="n">
-        <v>2</v>
-      </c>
-      <c r="K92" t="n">
-        <v>1</v>
-      </c>
-      <c r="L92" t="n">
-        <v>3</v>
-      </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>電機機械右下</t>
+          <t>電機機械右上</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F93" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H93" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I93" t="n">
         <v>2</v>
@@ -4276,7 +4262,7 @@
         <v>1</v>
       </c>
       <c r="K93" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L93" t="n">
         <v>0</v>
@@ -4288,12 +4274,14 @@
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>電機機械平</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr"/>
+          <t>電機機械右下</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>0</v>
+      </c>
       <c r="C94" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D94" t="n">
         <v>0</v>
@@ -4302,19 +4290,19 @@
         <v>1</v>
       </c>
       <c r="F94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I94" t="n">
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K94" t="n">
         <v>0</v>
@@ -4329,53 +4317,53 @@
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右上</t>
+          <t>電機機械平</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D95" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G95" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I95" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L95" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右下</t>
+          <t>電腦及週邊設備業右上</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D96" t="n">
         <v>1</v>
@@ -4384,19 +4372,19 @@
         <v>0</v>
       </c>
       <c r="F96" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G96" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H96" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I96" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J96" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K96" t="n">
         <v>2</v>
@@ -4405,42 +4393,42 @@
         <v>1</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業平</t>
+          <t>電腦及週邊設備業右下</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D97" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G97" t="n">
         <v>1</v>
       </c>
       <c r="H97" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I97" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K97" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L97" t="n">
         <v>0</v>
@@ -4452,33 +4440,33 @@
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>食品工業右上</t>
+          <t>電腦及週邊設備業平</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F98" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
       </c>
       <c r="H98" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J98" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K98" t="n">
         <v>0</v>
@@ -4493,7 +4481,7 @@
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>食品工業右下</t>
+          <t>食品工業右上</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
@@ -4534,41 +4522,84 @@
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
+          <t>食品工業右下</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>0</v>
+      </c>
+      <c r="C100" t="n">
+        <v>0</v>
+      </c>
+      <c r="D100" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" t="n">
+        <v>0</v>
+      </c>
+      <c r="G100" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" t="n">
+        <v>0</v>
+      </c>
+      <c r="K100" t="n">
+        <v>0</v>
+      </c>
+      <c r="L100" t="n">
+        <v>0</v>
+      </c>
+      <c r="M100" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="inlineStr">
+        <is>
           <t>食品工業平</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr"/>
-      <c r="C100" t="n">
-        <v>0</v>
-      </c>
-      <c r="D100" t="n">
-        <v>0</v>
-      </c>
-      <c r="E100" t="n">
-        <v>0</v>
-      </c>
-      <c r="F100" t="n">
-        <v>0</v>
-      </c>
-      <c r="G100" t="n">
-        <v>0</v>
-      </c>
-      <c r="H100" t="n">
-        <v>0</v>
-      </c>
-      <c r="I100" t="n">
-        <v>0</v>
-      </c>
-      <c r="J100" t="n">
-        <v>0</v>
-      </c>
-      <c r="K100" t="n">
-        <v>1</v>
-      </c>
-      <c r="L100" t="n">
-        <v>1</v>
-      </c>
-      <c r="M100" t="n">
+      <c r="B101" t="inlineStr"/>
+      <c r="C101" t="n">
+        <v>0</v>
+      </c>
+      <c r="D101" t="n">
+        <v>0</v>
+      </c>
+      <c r="E101" t="n">
+        <v>0</v>
+      </c>
+      <c r="F101" t="n">
+        <v>0</v>
+      </c>
+      <c r="G101" t="n">
+        <v>0</v>
+      </c>
+      <c r="H101" t="n">
+        <v>0</v>
+      </c>
+      <c r="I101" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" t="n">
+        <v>1</v>
+      </c>
+      <c r="K101" t="n">
+        <v>1</v>
+      </c>
+      <c r="L101" t="n">
+        <v>0</v>
+      </c>
+      <c r="M101" t="n">
         <v>0</v>
       </c>
     </row>

--- a/Result/analyze_1.xlsx
+++ b/Result/analyze_1.xlsx
@@ -441,57 +441,57 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-02</t>
         </is>
       </c>
     </row>
@@ -503,37 +503,37 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H2" t="n">
+        <v>8</v>
+      </c>
+      <c r="I2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J2" t="n">
         <v>5</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J2" t="n">
-        <v>4</v>
       </c>
       <c r="K2" t="n">
         <v>5</v>
       </c>
       <c r="L2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -542,24 +542,26 @@
           <t>光電業右下</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -568,13 +570,13 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
         <v>1</v>
       </c>
       <c r="M3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -585,22 +587,22 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I4" t="n">
         <v>2</v>
@@ -609,13 +611,13 @@
         <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -626,34 +628,34 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
         <v>3</v>
       </c>
-      <c r="D5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
       <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
         <v>3</v>
       </c>
-      <c r="G5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2</v>
-      </c>
-      <c r="I5" t="n">
-        <v>2</v>
-      </c>
-      <c r="J5" t="n">
-        <v>3</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1</v>
-      </c>
       <c r="L5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M5" t="n">
         <v>1</v>
@@ -667,13 +669,13 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -688,13 +690,13 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -714,31 +716,31 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -749,37 +751,37 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J8" t="n">
         <v>6</v>
       </c>
       <c r="K8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L8" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -790,13 +792,13 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -808,16 +810,16 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
         <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -837,31 +839,31 @@
         <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F10" t="n">
         <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H10" t="n">
         <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -872,37 +874,37 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
         <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -911,9 +913,11 @@
           <t>化學工業右下</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
+      <c r="B12" t="n">
+        <v>0</v>
+      </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -937,10 +941,10 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -981,7 +985,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -995,37 +999,37 @@
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H14" t="n">
+        <v>2</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
         <v>5</v>
       </c>
-      <c r="I14" t="n">
-        <v>3</v>
-      </c>
-      <c r="J14" t="n">
-        <v>2</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
       <c r="L14" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1038,34 +1042,34 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E15" t="n">
+        <v>9</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>5</v>
+      </c>
+      <c r="J15" t="n">
         <v>4</v>
       </c>
-      <c r="E15" t="n">
+      <c r="K15" t="n">
         <v>3</v>
       </c>
-      <c r="F15" t="n">
-        <v>9</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>1</v>
-      </c>
-      <c r="J15" t="n">
-        <v>5</v>
-      </c>
-      <c r="K15" t="n">
-        <v>4</v>
-      </c>
       <c r="L15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M15" t="n">
         <v>1</v>
@@ -1079,37 +1083,37 @@
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" t="n">
         <v>2</v>
       </c>
       <c r="G16" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H16" t="n">
         <v>5</v>
       </c>
       <c r="I16" t="n">
+        <v>5</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2</v>
+      </c>
+      <c r="K16" t="n">
         <v>4</v>
       </c>
-      <c r="J16" t="n">
-        <v>5</v>
-      </c>
-      <c r="K16" t="n">
-        <v>2</v>
-      </c>
       <c r="L16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17">
@@ -1161,16 +1165,16 @@
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -1232,7 +1236,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1243,7 +1247,7 @@
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -1284,16 +1288,16 @@
       </c>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -1311,7 +1315,7 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" t="n">
         <v>1</v>
@@ -1349,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -1405,7 +1409,9 @@
           <t>建材營造右下</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="n">
+        <v>0</v>
+      </c>
       <c r="C24" t="n">
         <v>0</v>
       </c>
@@ -1413,10 +1419,10 @@
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1495,13 +1501,13 @@
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F26" t="n">
         <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1516,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -1554,7 +1560,7 @@
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" t="n">
         <v>1</v>
@@ -1571,10 +1577,10 @@
       </c>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -1601,7 +1607,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -1618,7 +1624,7 @@
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F29" t="n">
         <v>1</v>
@@ -1627,7 +1633,7 @@
         <v>1</v>
       </c>
       <c r="H29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -1653,7 +1659,7 @@
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -1899,7 +1905,7 @@
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
@@ -1911,13 +1917,13 @@
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
         <v>1</v>
@@ -1926,7 +1932,7 @@
         <v>1</v>
       </c>
       <c r="L36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
@@ -1938,12 +1944,14 @@
           <t>汽車工業右下</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr"/>
+      <c r="B37" t="n">
+        <v>0</v>
+      </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
@@ -1961,13 +1969,13 @@
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
         <v>1</v>
@@ -1981,7 +1989,7 @@
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
@@ -1999,19 +2007,19 @@
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L38" t="n">
         <v>1</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2069,19 +2077,19 @@
         <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2145,7 +2153,7 @@
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D42" t="n">
         <v>0</v>
@@ -2160,10 +2168,10 @@
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -2242,10 +2250,10 @@
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -2268,34 +2276,34 @@
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D45" t="n">
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M45" t="n">
         <v>1</v>
@@ -2307,39 +2315,41 @@
           <t>生技醫療業右下</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr"/>
+      <c r="B46" t="n">
+        <v>0</v>
+      </c>
       <c r="C46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E46" t="n">
         <v>3</v>
       </c>
-      <c r="E46" t="n">
-        <v>1</v>
-      </c>
       <c r="F46" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H46" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I46" t="n">
+        <v>2</v>
+      </c>
+      <c r="J46" t="n">
+        <v>2</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>1</v>
+      </c>
+      <c r="M46" t="n">
         <v>3</v>
-      </c>
-      <c r="J46" t="n">
-        <v>2</v>
-      </c>
-      <c r="K46" t="n">
-        <v>2</v>
-      </c>
-      <c r="L46" t="n">
-        <v>0</v>
-      </c>
-      <c r="M46" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -2350,37 +2360,37 @@
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D47" t="n">
         <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H47" t="n">
         <v>1</v>
       </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L47" t="n">
         <v>2</v>
       </c>
       <c r="M47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -2409,13 +2419,13 @@
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J48" t="n">
         <v>1</v>
       </c>
       <c r="K48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
@@ -2432,7 +2442,7 @@
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D49" t="n">
         <v>0</v>
@@ -2482,10 +2492,10 @@
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
@@ -2514,37 +2524,37 @@
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G51" t="n">
         <v>1</v>
       </c>
       <c r="H51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K51" t="n">
         <v>1</v>
       </c>
       <c r="L51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -2564,10 +2574,10 @@
         <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
@@ -2576,10 +2586,10 @@
         <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
@@ -2605,13 +2615,13 @@
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G53" t="n">
         <v>1</v>
       </c>
       <c r="H53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I53" t="n">
         <v>0</v>
@@ -2620,10 +2630,10 @@
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
         <v>0</v>
@@ -2637,7 +2647,7 @@
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D54" t="n">
         <v>0</v>
@@ -2649,10 +2659,10 @@
         <v>0</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I54" t="n">
         <v>1</v>
@@ -2664,7 +2674,7 @@
         <v>1</v>
       </c>
       <c r="L54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
         <v>0</v>
@@ -2678,10 +2688,10 @@
       </c>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E55" t="n">
         <v>0</v>
@@ -2740,10 +2750,10 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
@@ -2801,7 +2811,7 @@
       </c>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D58" t="n">
         <v>0</v>
@@ -2816,10 +2826,10 @@
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I58" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -2965,25 +2975,25 @@
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D62" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H62" t="n">
         <v>1</v>
       </c>
       <c r="I62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -3004,15 +3014,17 @@
           <t>資訊服務業右下</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr"/>
+      <c r="B63" t="n">
+        <v>0</v>
+      </c>
       <c r="C63" t="n">
         <v>0</v>
       </c>
       <c r="D63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
@@ -3170,37 +3182,37 @@
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E67" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F67" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" t="n">
+        <v>5</v>
+      </c>
+      <c r="H67" t="n">
+        <v>1</v>
+      </c>
+      <c r="I67" t="n">
+        <v>4</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" t="n">
         <v>3</v>
       </c>
-      <c r="G67" t="n">
-        <v>1</v>
-      </c>
-      <c r="H67" t="n">
-        <v>5</v>
-      </c>
-      <c r="I67" t="n">
-        <v>1</v>
-      </c>
-      <c r="J67" t="n">
-        <v>4</v>
-      </c>
-      <c r="K67" t="n">
-        <v>0</v>
-      </c>
       <c r="L67" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -3211,10 +3223,10 @@
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E68" t="n">
         <v>1</v>
@@ -3226,19 +3238,19 @@
         <v>1</v>
       </c>
       <c r="H68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I68" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M68" t="n">
         <v>1</v>
@@ -3270,19 +3282,19 @@
         <v>0</v>
       </c>
       <c r="I69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -3414,9 +3426,7 @@
           <t>運動休閒右下</t>
         </is>
       </c>
-      <c r="B73" t="n">
-        <v>0</v>
-      </c>
+      <c r="B73" t="inlineStr"/>
       <c r="C73" t="n">
         <v>0</v>
       </c>
@@ -3465,10 +3475,10 @@
         <v>0</v>
       </c>
       <c r="E74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -3609,10 +3619,10 @@
         <v>0</v>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -3767,16 +3777,16 @@
         <v>0</v>
       </c>
       <c r="J81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L81" t="n">
         <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82">
@@ -3790,7 +3800,7 @@
         <v>2</v>
       </c>
       <c r="D82" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E82" t="n">
         <v>0</v>
@@ -3814,10 +3824,10 @@
         <v>0</v>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -3890,7 +3900,7 @@
         <v>0</v>
       </c>
       <c r="J84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K84" t="n">
         <v>0</v>
@@ -3969,7 +3979,7 @@
         <v>0</v>
       </c>
       <c r="I86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -4007,7 +4017,7 @@
         <v>0</v>
       </c>
       <c r="H87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I87" t="n">
         <v>1</v>
@@ -4019,10 +4029,10 @@
         <v>1</v>
       </c>
       <c r="L87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M87" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
@@ -4031,7 +4041,9 @@
           <t>電子通路業右下</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr"/>
+      <c r="B88" t="n">
+        <v>0</v>
+      </c>
       <c r="C88" t="n">
         <v>0</v>
       </c>
@@ -4054,13 +4066,13 @@
         <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K88" t="n">
         <v>1</v>
       </c>
       <c r="L88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
         <v>0</v>
@@ -4077,28 +4089,28 @@
         <v>1</v>
       </c>
       <c r="D89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E89" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F89" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I89" t="n">
         <v>1</v>
       </c>
       <c r="J89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L89" t="n">
         <v>1</v>
@@ -4115,37 +4127,37 @@
       </c>
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="D90" t="n">
         <v>2</v>
       </c>
       <c r="E90" t="n">
+        <v>11</v>
+      </c>
+      <c r="F90" t="n">
+        <v>1</v>
+      </c>
+      <c r="G90" t="n">
+        <v>14</v>
+      </c>
+      <c r="H90" t="n">
+        <v>6</v>
+      </c>
+      <c r="I90" t="n">
+        <v>13</v>
+      </c>
+      <c r="J90" t="n">
+        <v>4</v>
+      </c>
+      <c r="K90" t="n">
+        <v>16</v>
+      </c>
+      <c r="L90" t="n">
+        <v>1</v>
+      </c>
+      <c r="M90" t="n">
         <v>3</v>
-      </c>
-      <c r="F90" t="n">
-        <v>12</v>
-      </c>
-      <c r="G90" t="n">
-        <v>1</v>
-      </c>
-      <c r="H90" t="n">
-        <v>14</v>
-      </c>
-      <c r="I90" t="n">
-        <v>6</v>
-      </c>
-      <c r="J90" t="n">
-        <v>14</v>
-      </c>
-      <c r="K90" t="n">
-        <v>4</v>
-      </c>
-      <c r="L90" t="n">
-        <v>17</v>
-      </c>
-      <c r="M90" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="91">
@@ -4156,37 +4168,37 @@
       </c>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D91" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" t="n">
+        <v>1</v>
+      </c>
+      <c r="F91" t="n">
+        <v>1</v>
+      </c>
+      <c r="G91" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" t="n">
+        <v>2</v>
+      </c>
+      <c r="I91" t="n">
+        <v>2</v>
+      </c>
+      <c r="J91" t="n">
         <v>4</v>
       </c>
-      <c r="E91" t="n">
-        <v>0</v>
-      </c>
-      <c r="F91" t="n">
-        <v>0</v>
-      </c>
-      <c r="G91" t="n">
-        <v>1</v>
-      </c>
-      <c r="H91" t="n">
-        <v>0</v>
-      </c>
-      <c r="I91" t="n">
-        <v>2</v>
-      </c>
-      <c r="J91" t="n">
-        <v>2</v>
-      </c>
       <c r="K91" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L91" t="n">
         <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
@@ -4197,37 +4209,37 @@
       </c>
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D92" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E92" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F92" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" t="n">
+        <v>1</v>
+      </c>
+      <c r="H92" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" t="n">
+        <v>2</v>
+      </c>
+      <c r="J92" t="n">
+        <v>2</v>
+      </c>
+      <c r="K92" t="n">
         <v>4</v>
       </c>
-      <c r="G92" t="n">
-        <v>0</v>
-      </c>
-      <c r="H92" t="n">
-        <v>1</v>
-      </c>
-      <c r="I92" t="n">
-        <v>0</v>
-      </c>
-      <c r="J92" t="n">
-        <v>1</v>
-      </c>
-      <c r="K92" t="n">
-        <v>3</v>
-      </c>
       <c r="L92" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M92" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
@@ -4238,31 +4250,31 @@
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="n">
+        <v>1</v>
+      </c>
+      <c r="D93" t="n">
+        <v>1</v>
+      </c>
+      <c r="E93" t="n">
         <v>5</v>
       </c>
-      <c r="D93" t="n">
-        <v>1</v>
-      </c>
-      <c r="E93" t="n">
-        <v>1</v>
-      </c>
       <c r="F93" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G93" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H93" t="n">
+        <v>2</v>
+      </c>
+      <c r="I93" t="n">
+        <v>1</v>
+      </c>
+      <c r="J93" t="n">
         <v>3</v>
       </c>
-      <c r="I93" t="n">
-        <v>2</v>
-      </c>
-      <c r="J93" t="n">
-        <v>1</v>
-      </c>
       <c r="K93" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L93" t="n">
         <v>0</v>
@@ -4277,26 +4289,24 @@
           <t>電機機械右下</t>
         </is>
       </c>
-      <c r="B94" t="n">
-        <v>0</v>
-      </c>
+      <c r="B94" t="inlineStr"/>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E94" t="n">
         <v>1</v>
       </c>
       <c r="F94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G94" t="n">
         <v>2</v>
       </c>
       <c r="H94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I94" t="n">
         <v>0</v>
@@ -4308,7 +4318,7 @@
         <v>0</v>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M94" t="n">
         <v>1</v>
@@ -4322,34 +4332,34 @@
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H95" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I95" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
         <v>0</v>
@@ -4363,31 +4373,31 @@
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E96" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F96" t="n">
+        <v>1</v>
+      </c>
+      <c r="G96" t="n">
         <v>4</v>
       </c>
-      <c r="G96" t="n">
-        <v>1</v>
-      </c>
       <c r="H96" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I96" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J96" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K96" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L96" t="n">
         <v>1</v>
@@ -4402,33 +4412,35 @@
           <t>電腦及週邊設備業右下</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr"/>
+      <c r="B97" t="n">
+        <v>0</v>
+      </c>
       <c r="C97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D97" t="n">
         <v>0</v>
       </c>
       <c r="E97" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F97" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G97" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H97" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J97" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L97" t="n">
         <v>0</v>
@@ -4445,7 +4457,7 @@
       </c>
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D98" t="n">
         <v>1</v>
@@ -4454,19 +4466,19 @@
         <v>1</v>
       </c>
       <c r="F98" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G98" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H98" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J98" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K98" t="n">
         <v>0</v>
@@ -4475,7 +4487,7 @@
         <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99">
@@ -4516,7 +4528,7 @@
         <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100">
@@ -4525,9 +4537,7 @@
           <t>食品工業右下</t>
         </is>
       </c>
-      <c r="B100" t="n">
-        <v>0</v>
-      </c>
+      <c r="B100" t="inlineStr"/>
       <c r="C100" t="n">
         <v>0</v>
       </c>
@@ -4556,7 +4566,7 @@
         <v>0</v>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M100" t="n">
         <v>1</v>
@@ -4588,13 +4598,13 @@
         <v>0</v>
       </c>
       <c r="I101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J101" t="n">
         <v>1</v>
       </c>
       <c r="K101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L101" t="n">
         <v>0</v>

--- a/Result/analyze_1.xlsx
+++ b/Result/analyze_1.xlsx
@@ -441,57 +441,57 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-03</t>
         </is>
       </c>
     </row>
@@ -503,37 +503,37 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G2" t="n">
+        <v>8</v>
+      </c>
+      <c r="H2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I2" t="n">
         <v>5</v>
       </c>
-      <c r="D2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E2" t="n">
+      <c r="J2" t="n">
         <v>4</v>
       </c>
-      <c r="F2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" t="n">
-        <v>10</v>
-      </c>
-      <c r="H2" t="n">
-        <v>8</v>
-      </c>
-      <c r="I2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J2" t="n">
-        <v>5</v>
-      </c>
       <c r="K2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M2" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3">
@@ -542,23 +542,21 @@
           <t>光電業右下</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>0</v>
-      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -567,16 +565,16 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="n">
         <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -593,13 +591,13 @@
         <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
         <v>2</v>
@@ -608,16 +606,16 @@
         <v>2</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -631,34 +629,34 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="n">
         <v>3</v>
       </c>
-      <c r="F5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" t="n">
-        <v>2</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
       <c r="K5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
         <v>1</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -672,7 +670,7 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -687,13 +685,13 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -713,16 +711,16 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
         <v>1</v>
@@ -737,10 +735,10 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -751,34 +749,34 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I8" t="n">
         <v>6</v>
       </c>
       <c r="J8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K8" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
         <v>1</v>
@@ -790,12 +788,14 @@
           <t>其他電子業右下</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -833,34 +833,34 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
         <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -874,31 +874,31 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" t="n">
         <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -938,10 +938,10 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -982,10 +982,10 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1002,31 +1002,31 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G14" t="n">
+        <v>2</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
         <v>5</v>
       </c>
-      <c r="H14" t="n">
-        <v>2</v>
-      </c>
-      <c r="I14" t="n">
-        <v>2</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
       <c r="K14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M14" t="n">
         <v>2</v>
@@ -1042,37 +1042,37 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
+        <v>3</v>
+      </c>
+      <c r="D15" t="n">
+        <v>9</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" t="n">
+        <v>5</v>
+      </c>
+      <c r="I15" t="n">
         <v>4</v>
       </c>
-      <c r="D15" t="n">
+      <c r="J15" t="n">
         <v>3</v>
       </c>
-      <c r="E15" t="n">
-        <v>9</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>1</v>
-      </c>
-      <c r="I15" t="n">
-        <v>5</v>
-      </c>
-      <c r="J15" t="n">
-        <v>4</v>
-      </c>
       <c r="K15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
         <v>1</v>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16">
@@ -1083,16 +1083,16 @@
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F16" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G16" t="n">
         <v>5</v>
@@ -1101,19 +1101,19 @@
         <v>5</v>
       </c>
       <c r="I16" t="n">
+        <v>2</v>
+      </c>
+      <c r="J16" t="n">
+        <v>4</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2</v>
+      </c>
+      <c r="L16" t="n">
+        <v>4</v>
+      </c>
+      <c r="M16" t="n">
         <v>5</v>
-      </c>
-      <c r="J16" t="n">
-        <v>2</v>
-      </c>
-      <c r="K16" t="n">
-        <v>4</v>
-      </c>
-      <c r="L16" t="n">
-        <v>2</v>
-      </c>
-      <c r="M16" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="17">
@@ -1163,15 +1163,17 @@
           <t>塑膠工業右下</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
+      <c r="B18" t="n">
+        <v>0</v>
+      </c>
       <c r="C18" t="n">
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -1233,10 +1235,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1288,13 +1290,13 @@
       </c>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -1312,13 +1314,13 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" t="n">
         <v>1</v>
       </c>
       <c r="M21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1350,10 +1352,10 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -1409,17 +1411,15 @@
           <t>建材營造右下</t>
         </is>
       </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
+      <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -1498,13 +1498,13 @@
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E26" t="n">
         <v>1</v>
       </c>
       <c r="F26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1519,10 +1519,10 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -1557,7 +1557,7 @@
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
         <v>1</v>
@@ -1566,7 +1566,7 @@
         <v>1</v>
       </c>
       <c r="M27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -1577,7 +1577,7 @@
       </c>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -1607,7 +1607,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -1621,7 +1621,7 @@
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E29" t="n">
         <v>1</v>
@@ -1630,7 +1630,7 @@
         <v>1</v>
       </c>
       <c r="G29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -1914,13 +1914,13 @@
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I36" t="n">
         <v>1</v>
@@ -1929,7 +1929,7 @@
         <v>1</v>
       </c>
       <c r="K36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -1944,11 +1944,9 @@
           <t>汽車工業右下</t>
         </is>
       </c>
-      <c r="B37" t="n">
-        <v>0</v>
-      </c>
+      <c r="B37" t="inlineStr"/>
       <c r="C37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
@@ -1963,22 +1961,22 @@
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K37" t="n">
         <v>1</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2004,19 +2002,19 @@
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
         <v>1</v>
@@ -2074,19 +2072,19 @@
         <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
@@ -2165,10 +2163,10 @@
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -2183,13 +2181,13 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>玻璃陶瓷右下</t>
+          <t>玻璃陶瓷平</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -2206,7 +2204,7 @@
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -2230,7 +2228,7 @@
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>玻璃陶瓷平</t>
+          <t>生技醫療業右上</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -2238,10 +2236,10 @@
         <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
@@ -2250,91 +2248,91 @@
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>生技醫療業右上</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr"/>
+          <t>生技醫療業右下</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>0</v>
+      </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M45" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>生技醫療業右下</t>
-        </is>
-      </c>
-      <c r="B46" t="n">
-        <v>0</v>
-      </c>
+          <t>生技醫療業平</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
       <c r="C46" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G46" t="n">
         <v>1</v>
       </c>
       <c r="H46" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
         <v>2</v>
@@ -2343,19 +2341,19 @@
         <v>2</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L46" t="n">
         <v>1</v>
       </c>
       <c r="M46" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>生技醫療業平</t>
+          <t>紡織纖維右上</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -2366,28 +2364,28 @@
         <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
         <v>1</v>
       </c>
       <c r="I47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
         <v>1</v>
@@ -2396,7 +2394,7 @@
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>紡織纖維右上</t>
+          <t>紡織纖維右下</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -2419,10 +2417,10 @@
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
@@ -2431,13 +2429,13 @@
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>紡織纖維右下</t>
+          <t>紡織纖維平</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -2448,7 +2446,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -2478,7 +2476,7 @@
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>紡織纖維平</t>
+          <t>綠能環保右上</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -2486,10 +2484,10 @@
         <v>0</v>
       </c>
       <c r="D50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F50" t="n">
         <v>1</v>
@@ -2501,16 +2499,16 @@
         <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M50" t="n">
         <v>0</v>
@@ -2519,48 +2517,48 @@
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>綠能環保右上</t>
+          <t>綠能環保右下</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>綠能環保右下</t>
+          <t>綠能環保平</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -2571,7 +2569,7 @@
         <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F52" t="n">
         <v>1</v>
@@ -2601,7 +2599,7 @@
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>綠能環保平</t>
+          <t>航運業右上</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
@@ -2615,34 +2613,34 @@
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G53" t="n">
         <v>1</v>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>航運業右上</t>
+          <t>航運業右下</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
@@ -2659,19 +2657,19 @@
         <v>0</v>
       </c>
       <c r="G54" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
@@ -2683,12 +2681,12 @@
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>航運業右下</t>
+          <t>航運業平</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D55" t="n">
         <v>0</v>
@@ -2706,7 +2704,7 @@
         <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -2718,13 +2716,13 @@
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>航運業平</t>
+          <t>觀光事業右上</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
@@ -2750,7 +2748,7 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -2765,7 +2763,7 @@
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>觀光事業右上</t>
+          <t>觀光事業右下</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
@@ -2782,7 +2780,7 @@
         <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -2800,13 +2798,13 @@
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>觀光事業右下</t>
+          <t>觀光事業平</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
@@ -2826,7 +2824,7 @@
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I58" t="n">
         <v>0</v>
@@ -2847,7 +2845,7 @@
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>觀光事業平</t>
+          <t>貿易百貨右上</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -2975,22 +2973,22 @@
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G62" t="n">
         <v>1</v>
       </c>
       <c r="H62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I62" t="n">
         <v>0</v>
@@ -3014,14 +3012,12 @@
           <t>資訊服務業右下</t>
         </is>
       </c>
-      <c r="B63" t="n">
-        <v>0</v>
-      </c>
+      <c r="B63" t="inlineStr"/>
       <c r="C63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E63" t="n">
         <v>0</v>
@@ -3182,37 +3178,37 @@
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D67" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E67" t="n">
+        <v>1</v>
+      </c>
+      <c r="F67" t="n">
+        <v>5</v>
+      </c>
+      <c r="G67" t="n">
+        <v>1</v>
+      </c>
+      <c r="H67" t="n">
+        <v>4</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" t="n">
         <v>3</v>
       </c>
-      <c r="F67" t="n">
-        <v>1</v>
-      </c>
-      <c r="G67" t="n">
-        <v>5</v>
-      </c>
-      <c r="H67" t="n">
-        <v>1</v>
-      </c>
-      <c r="I67" t="n">
-        <v>4</v>
-      </c>
-      <c r="J67" t="n">
-        <v>0</v>
-      </c>
       <c r="K67" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" t="n">
+        <v>1</v>
+      </c>
+      <c r="M67" t="n">
         <v>3</v>
-      </c>
-      <c r="L67" t="n">
-        <v>0</v>
-      </c>
-      <c r="M67" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -3223,7 +3219,7 @@
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D68" t="n">
         <v>1</v>
@@ -3235,25 +3231,25 @@
         <v>1</v>
       </c>
       <c r="G68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H68" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L68" t="n">
         <v>1</v>
       </c>
       <c r="M68" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="69">
@@ -3279,19 +3275,19 @@
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M69" t="n">
         <v>1</v>
@@ -3472,10 +3468,10 @@
         <v>0</v>
       </c>
       <c r="D74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F74" t="n">
         <v>0</v>
@@ -3616,10 +3612,10 @@
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
         <v>0</v>
@@ -3774,19 +3770,19 @@
         <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K81" t="n">
         <v>0</v>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -3797,7 +3793,7 @@
       </c>
       <c r="B82" t="inlineStr"/>
       <c r="C82" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D82" t="n">
         <v>0</v>
@@ -3821,10 +3817,10 @@
         <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
         <v>0</v>
@@ -3894,7 +3890,7 @@
         <v>0</v>
       </c>
       <c r="H84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I84" t="n">
         <v>0</v>
@@ -3979,7 +3975,7 @@
         <v>0</v>
       </c>
       <c r="I86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -4014,7 +4010,7 @@
         <v>0</v>
       </c>
       <c r="G87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H87" t="n">
         <v>1</v>
@@ -4026,13 +4022,13 @@
         <v>1</v>
       </c>
       <c r="K87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L87" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -4041,9 +4037,7 @@
           <t>電子通路業右下</t>
         </is>
       </c>
-      <c r="B88" t="n">
-        <v>0</v>
-      </c>
+      <c r="B88" t="inlineStr"/>
       <c r="C88" t="n">
         <v>0</v>
       </c>
@@ -4063,13 +4057,13 @@
         <v>0</v>
       </c>
       <c r="I88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J88" t="n">
         <v>1</v>
       </c>
       <c r="K88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L88" t="n">
         <v>0</v>
@@ -4086,34 +4080,34 @@
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D89" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E89" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F89" t="n">
         <v>0</v>
       </c>
       <c r="G89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H89" t="n">
         <v>1</v>
       </c>
       <c r="I89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K89" t="n">
         <v>1</v>
       </c>
       <c r="L89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
         <v>0</v>
@@ -4127,37 +4121,37 @@
       </c>
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D90" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E90" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F90" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="G90" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="H90" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I90" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="J90" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="K90" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="L90" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M90" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="91">
@@ -4166,9 +4160,11 @@
           <t>電子零組件業右下</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr"/>
+      <c r="B91" t="n">
+        <v>0</v>
+      </c>
       <c r="C91" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D91" t="n">
         <v>0</v>
@@ -4177,25 +4173,25 @@
         <v>1</v>
       </c>
       <c r="F91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G91" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H91" t="n">
         <v>2</v>
       </c>
       <c r="I91" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J91" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M91" t="n">
         <v>1</v>
@@ -4209,37 +4205,37 @@
       </c>
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D92" t="n">
+        <v>4</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" t="n">
+        <v>1</v>
+      </c>
+      <c r="G92" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" t="n">
+        <v>2</v>
+      </c>
+      <c r="I92" t="n">
         <v>3</v>
       </c>
-      <c r="E92" t="n">
-        <v>4</v>
-      </c>
-      <c r="F92" t="n">
-        <v>0</v>
-      </c>
-      <c r="G92" t="n">
-        <v>1</v>
-      </c>
-      <c r="H92" t="n">
-        <v>0</v>
-      </c>
-      <c r="I92" t="n">
-        <v>2</v>
-      </c>
       <c r="J92" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K92" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L92" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93">
@@ -4253,25 +4249,25 @@
         <v>1</v>
       </c>
       <c r="D93" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E93" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F93" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G93" t="n">
+        <v>2</v>
+      </c>
+      <c r="H93" t="n">
+        <v>1</v>
+      </c>
+      <c r="I93" t="n">
         <v>3</v>
       </c>
-      <c r="H93" t="n">
-        <v>2</v>
-      </c>
-      <c r="I93" t="n">
-        <v>1</v>
-      </c>
       <c r="J93" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K93" t="n">
         <v>0</v>
@@ -4280,7 +4276,7 @@
         <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="94">
@@ -4291,13 +4287,13 @@
       </c>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D94" t="n">
         <v>1</v>
       </c>
       <c r="E94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F94" t="n">
         <v>2</v>
@@ -4306,7 +4302,7 @@
         <v>2</v>
       </c>
       <c r="H94" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I94" t="n">
         <v>0</v>
@@ -4315,13 +4311,13 @@
         <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L94" t="n">
         <v>1</v>
       </c>
       <c r="M94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="95">
@@ -4332,19 +4328,19 @@
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H95" t="n">
         <v>0</v>
@@ -4353,10 +4349,10 @@
         <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L95" t="n">
         <v>0</v>
@@ -4373,28 +4369,28 @@
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D96" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E96" t="n">
+        <v>1</v>
+      </c>
+      <c r="F96" t="n">
         <v>3</v>
       </c>
-      <c r="F96" t="n">
-        <v>1</v>
-      </c>
       <c r="G96" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H96" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I96" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J96" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K96" t="n">
         <v>1</v>
@@ -4403,7 +4399,7 @@
         <v>1</v>
       </c>
       <c r="M96" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="97">
@@ -4419,25 +4415,25 @@
         <v>0</v>
       </c>
       <c r="D97" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E97" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F97" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G97" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I97" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K97" t="n">
         <v>0</v>
@@ -4460,22 +4456,22 @@
         <v>1</v>
       </c>
       <c r="D98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F98" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G98" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I98" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -4484,10 +4480,10 @@
         <v>0</v>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -4525,10 +4521,10 @@
         <v>0</v>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -4563,7 +4559,7 @@
         <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L100" t="n">
         <v>1</v>
@@ -4595,13 +4591,13 @@
         <v>0</v>
       </c>
       <c r="H101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I101" t="n">
         <v>1</v>
       </c>
       <c r="J101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K101" t="n">
         <v>0</v>

--- a/Result/analyze_1.xlsx
+++ b/Result/analyze_1.xlsx
@@ -441,57 +441,57 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-04</t>
         </is>
       </c>
     </row>
@@ -506,34 +506,34 @@
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I2" t="n">
         <v>4</v>
       </c>
-      <c r="I2" t="n">
-        <v>5</v>
-      </c>
       <c r="J2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="M2" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -547,13 +547,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -562,16 +562,16 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M3" t="n">
         <v>1</v>
@@ -585,16 +585,16 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G4" t="n">
         <v>2</v>
@@ -603,19 +603,19 @@
         <v>2</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -626,37 +626,37 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
         <v>3</v>
       </c>
-      <c r="E5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" t="n">
-        <v>2</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1</v>
-      </c>
       <c r="J5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
         <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -667,7 +667,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -682,13 +682,13 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -697,7 +697,7 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -708,16 +708,16 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
@@ -726,16 +726,16 @@
         <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M7" t="n">
         <v>4</v>
@@ -749,37 +749,37 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
         <v>3</v>
       </c>
       <c r="E8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" t="n">
+        <v>7</v>
+      </c>
+      <c r="H8" t="n">
+        <v>5</v>
+      </c>
+      <c r="I8" t="n">
+        <v>8</v>
+      </c>
+      <c r="J8" t="n">
         <v>3</v>
       </c>
-      <c r="F8" t="n">
-        <v>5</v>
-      </c>
-      <c r="G8" t="n">
-        <v>2</v>
-      </c>
-      <c r="H8" t="n">
-        <v>6</v>
-      </c>
-      <c r="I8" t="n">
-        <v>6</v>
-      </c>
-      <c r="J8" t="n">
-        <v>7</v>
-      </c>
       <c r="K8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
         <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -788,11 +788,9 @@
           <t>其他電子業右下</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0</v>
-      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -804,25 +802,25 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
         <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -833,31 +831,31 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
         <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -874,28 +872,28 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
         <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
         <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -904,7 +902,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -913,9 +911,7 @@
           <t>化學工業右下</t>
         </is>
       </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
         <v>0</v>
       </c>
@@ -935,10 +931,10 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -979,10 +975,10 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -999,34 +995,34 @@
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F14" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M14" t="n">
         <v>2</v>
@@ -1038,41 +1034,39 @@
           <t>半導體業右下</t>
         </is>
       </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
+      <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
+        <v>8</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>5</v>
+      </c>
+      <c r="H15" t="n">
+        <v>4</v>
+      </c>
+      <c r="I15" t="n">
         <v>3</v>
       </c>
-      <c r="D15" t="n">
-        <v>9</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H15" t="n">
-        <v>5</v>
-      </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>12</v>
+      </c>
+      <c r="M15" t="n">
         <v>4</v>
-      </c>
-      <c r="J15" t="n">
-        <v>3</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1</v>
-      </c>
-      <c r="M15" t="n">
-        <v>11</v>
       </c>
     </row>
     <row r="16">
@@ -1083,37 +1077,37 @@
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F16" t="n">
         <v>5</v>
       </c>
       <c r="G16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H16" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M16" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1154,7 +1148,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1163,14 +1157,12 @@
           <t>塑膠工業右下</t>
         </is>
       </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
+      <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -1232,10 +1224,10 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -1290,10 +1282,10 @@
       </c>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -1311,16 +1303,16 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
         <v>1</v>
       </c>
       <c r="L21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1349,10 +1341,10 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -1402,7 +1394,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">
@@ -1413,10 +1405,10 @@
       </c>
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -1443,7 +1435,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25">
@@ -1484,7 +1476,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26">
@@ -1495,13 +1487,13 @@
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D26" t="n">
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -1516,16 +1508,16 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1554,7 +1546,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J27" t="n">
         <v>1</v>
@@ -1563,7 +1555,7 @@
         <v>1</v>
       </c>
       <c r="L27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -1607,7 +1599,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -1618,7 +1610,7 @@
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D29" t="n">
         <v>1</v>
@@ -1627,7 +1619,7 @@
         <v>1</v>
       </c>
       <c r="F29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1911,13 +1903,13 @@
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H36" t="n">
         <v>1</v>
@@ -1926,7 +1918,7 @@
         <v>1</v>
       </c>
       <c r="J36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -1944,7 +1936,9 @@
           <t>汽車工業右下</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr"/>
+      <c r="B37" t="n">
+        <v>0</v>
+      </c>
       <c r="C37" t="n">
         <v>0</v>
       </c>
@@ -1958,22 +1952,22 @@
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
@@ -1999,22 +1993,22 @@
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M38" t="n">
         <v>1</v>
@@ -2069,19 +2063,19 @@
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -2160,10 +2154,10 @@
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -2178,10 +2172,10 @@
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2201,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -2233,37 +2227,37 @@
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K44" t="n">
         <v>1</v>
       </c>
       <c r="L44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2272,41 +2266,39 @@
           <t>生技醫療業右下</t>
         </is>
       </c>
-      <c r="B45" t="n">
-        <v>0</v>
-      </c>
+      <c r="B45" t="inlineStr"/>
       <c r="C45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D45" t="n">
+        <v>2</v>
+      </c>
+      <c r="E45" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" t="n">
         <v>3</v>
       </c>
-      <c r="E45" t="n">
-        <v>2</v>
-      </c>
-      <c r="F45" t="n">
-        <v>1</v>
-      </c>
       <c r="G45" t="n">
+        <v>2</v>
+      </c>
+      <c r="H45" t="n">
+        <v>1</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>1</v>
+      </c>
+      <c r="K45" t="n">
         <v>3</v>
       </c>
-      <c r="H45" t="n">
-        <v>2</v>
-      </c>
-      <c r="I45" t="n">
-        <v>1</v>
-      </c>
-      <c r="J45" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" t="n">
-        <v>1</v>
-      </c>
       <c r="L45" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M45" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -2317,22 +2309,22 @@
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D46" t="n">
         <v>2</v>
       </c>
       <c r="E46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F46" t="n">
         <v>1</v>
       </c>
       <c r="G46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I46" t="n">
         <v>2</v>
@@ -2341,13 +2333,13 @@
         <v>2</v>
       </c>
       <c r="K46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -2370,13 +2362,13 @@
         <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H47" t="n">
         <v>1</v>
       </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -2385,7 +2377,7 @@
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M47" t="n">
         <v>1</v>
@@ -2426,10 +2418,10 @@
         <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -2443,10 +2435,10 @@
         <v>0</v>
       </c>
       <c r="D49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -2470,7 +2462,7 @@
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -2481,34 +2473,34 @@
       </c>
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E50" t="n">
         <v>1</v>
       </c>
       <c r="F50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I50" t="n">
         <v>1</v>
       </c>
       <c r="J50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
         <v>0</v>
@@ -2525,10 +2517,10 @@
         <v>0</v>
       </c>
       <c r="D51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F51" t="n">
         <v>0</v>
@@ -2537,10 +2529,10 @@
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -2566,13 +2558,13 @@
         <v>0</v>
       </c>
       <c r="D52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E52" t="n">
         <v>1</v>
       </c>
       <c r="F52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -2581,10 +2573,10 @@
         <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K52" t="n">
         <v>0</v>
@@ -2610,28 +2602,28 @@
         <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G53" t="n">
         <v>1</v>
       </c>
       <c r="H53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I53" t="n">
         <v>1</v>
       </c>
       <c r="J53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K53" t="n">
         <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M53" t="n">
         <v>2</v>
@@ -2643,7 +2635,9 @@
           <t>航運業右下</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr"/>
+      <c r="B54" t="n">
+        <v>0</v>
+      </c>
       <c r="C54" t="n">
         <v>0</v>
       </c>
@@ -2704,7 +2698,7 @@
         <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -2716,7 +2710,7 @@
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -2777,10 +2771,10 @@
         <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G57" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -2795,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M57" t="n">
         <v>1</v>
@@ -2973,19 +2967,19 @@
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F62" t="n">
         <v>1</v>
       </c>
       <c r="G62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H62" t="n">
         <v>0</v>
@@ -3014,7 +3008,7 @@
       </c>
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D63" t="n">
         <v>0</v>
@@ -3178,37 +3172,37 @@
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D67" t="n">
+        <v>1</v>
+      </c>
+      <c r="E67" t="n">
+        <v>5</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" t="n">
+        <v>4</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" t="n">
         <v>3</v>
       </c>
-      <c r="E67" t="n">
-        <v>1</v>
-      </c>
-      <c r="F67" t="n">
-        <v>5</v>
-      </c>
-      <c r="G67" t="n">
-        <v>1</v>
-      </c>
-      <c r="H67" t="n">
-        <v>4</v>
-      </c>
-      <c r="I67" t="n">
-        <v>0</v>
-      </c>
       <c r="J67" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" t="n">
+        <v>1</v>
+      </c>
+      <c r="L67" t="n">
         <v>3</v>
       </c>
-      <c r="K67" t="n">
-        <v>0</v>
-      </c>
-      <c r="L67" t="n">
-        <v>1</v>
-      </c>
       <c r="M67" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -3217,7 +3211,9 @@
           <t>通信網路業右下</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr"/>
+      <c r="B68" t="n">
+        <v>0</v>
+      </c>
       <c r="C68" t="n">
         <v>1</v>
       </c>
@@ -3228,10 +3224,10 @@
         <v>1</v>
       </c>
       <c r="F68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G68" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
@@ -3240,16 +3236,16 @@
         <v>1</v>
       </c>
       <c r="J68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M68" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69">
@@ -3269,28 +3265,28 @@
         <v>0</v>
       </c>
       <c r="F69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L69" t="n">
         <v>1</v>
       </c>
       <c r="M69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -3465,10 +3461,10 @@
       </c>
       <c r="B74" t="inlineStr"/>
       <c r="C74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E74" t="n">
         <v>0</v>
@@ -3609,10 +3605,10 @@
         <v>0</v>
       </c>
       <c r="J77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L77" t="n">
         <v>0</v>
@@ -3767,19 +3763,19 @@
         <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
         <v>0</v>
@@ -3814,10 +3810,10 @@
         <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L82" t="n">
         <v>0</v>
@@ -3864,7 +3860,7 @@
         <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
@@ -3887,10 +3883,10 @@
         <v>0</v>
       </c>
       <c r="G84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I84" t="n">
         <v>0</v>
@@ -3905,7 +3901,7 @@
         <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85">
@@ -3946,7 +3942,7 @@
         <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
@@ -3987,7 +3983,7 @@
         <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
@@ -4007,7 +4003,7 @@
         <v>0</v>
       </c>
       <c r="F87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G87" t="n">
         <v>1</v>
@@ -4019,13 +4015,13 @@
         <v>1</v>
       </c>
       <c r="J87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K87" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
         <v>0</v>
@@ -4054,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I88" t="n">
         <v>1</v>
       </c>
       <c r="J88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
@@ -4080,31 +4076,31 @@
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D89" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E89" t="n">
         <v>0</v>
       </c>
       <c r="F89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G89" t="n">
         <v>1</v>
       </c>
       <c r="H89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J89" t="n">
         <v>1</v>
       </c>
       <c r="K89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L89" t="n">
         <v>0</v>
@@ -4121,37 +4117,37 @@
       </c>
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="n">
+        <v>11</v>
+      </c>
+      <c r="D90" t="n">
+        <v>1</v>
+      </c>
+      <c r="E90" t="n">
+        <v>13</v>
+      </c>
+      <c r="F90" t="n">
+        <v>6</v>
+      </c>
+      <c r="G90" t="n">
+        <v>13</v>
+      </c>
+      <c r="H90" t="n">
+        <v>4</v>
+      </c>
+      <c r="I90" t="n">
+        <v>16</v>
+      </c>
+      <c r="J90" t="n">
+        <v>1</v>
+      </c>
+      <c r="K90" t="n">
         <v>3</v>
       </c>
-      <c r="D90" t="n">
-        <v>12</v>
-      </c>
-      <c r="E90" t="n">
-        <v>1</v>
-      </c>
-      <c r="F90" t="n">
-        <v>14</v>
-      </c>
-      <c r="G90" t="n">
-        <v>6</v>
-      </c>
-      <c r="H90" t="n">
-        <v>13</v>
-      </c>
-      <c r="I90" t="n">
+      <c r="L90" t="n">
+        <v>10</v>
+      </c>
+      <c r="M90" t="n">
         <v>4</v>
-      </c>
-      <c r="J90" t="n">
-        <v>16</v>
-      </c>
-      <c r="K90" t="n">
-        <v>1</v>
-      </c>
-      <c r="L90" t="n">
-        <v>3</v>
-      </c>
-      <c r="M90" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="91">
@@ -4167,34 +4163,34 @@
         <v>0</v>
       </c>
       <c r="D91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F91" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G91" t="n">
         <v>2</v>
       </c>
       <c r="H91" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I91" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L91" t="n">
         <v>1</v>
       </c>
       <c r="M91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -4205,37 +4201,37 @@
       </c>
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D92" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E92" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G92" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H92" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I92" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J92" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K92" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M92" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
@@ -4246,25 +4242,25 @@
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D93" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E93" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F93" t="n">
+        <v>2</v>
+      </c>
+      <c r="G93" t="n">
+        <v>1</v>
+      </c>
+      <c r="H93" t="n">
         <v>3</v>
       </c>
-      <c r="G93" t="n">
-        <v>2</v>
-      </c>
-      <c r="H93" t="n">
-        <v>1</v>
-      </c>
       <c r="I93" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -4273,10 +4269,10 @@
         <v>0</v>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M93" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -4290,7 +4286,7 @@
         <v>1</v>
       </c>
       <c r="D94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E94" t="n">
         <v>2</v>
@@ -4299,7 +4295,7 @@
         <v>2</v>
       </c>
       <c r="G94" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H94" t="n">
         <v>0</v>
@@ -4308,16 +4304,16 @@
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K94" t="n">
         <v>1</v>
       </c>
       <c r="L94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
@@ -4328,16 +4324,16 @@
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -4346,10 +4342,10 @@
         <v>0</v>
       </c>
       <c r="I95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K95" t="n">
         <v>0</v>
@@ -4358,7 +4354,7 @@
         <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
@@ -4369,25 +4365,25 @@
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D96" t="n">
+        <v>1</v>
+      </c>
+      <c r="E96" t="n">
         <v>4</v>
       </c>
-      <c r="E96" t="n">
-        <v>1</v>
-      </c>
       <c r="F96" t="n">
+        <v>1</v>
+      </c>
+      <c r="G96" t="n">
         <v>3</v>
       </c>
-      <c r="G96" t="n">
-        <v>1</v>
-      </c>
       <c r="H96" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I96" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J96" t="n">
         <v>1</v>
@@ -4396,10 +4392,10 @@
         <v>1</v>
       </c>
       <c r="L96" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M96" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97">
@@ -4412,25 +4408,25 @@
         <v>0</v>
       </c>
       <c r="C97" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D97" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F97" t="n">
+        <v>1</v>
+      </c>
+      <c r="G97" t="n">
         <v>3</v>
       </c>
-      <c r="G97" t="n">
-        <v>1</v>
-      </c>
       <c r="H97" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -4442,7 +4438,7 @@
         <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98">
@@ -4453,22 +4449,22 @@
       </c>
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D98" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E98" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F98" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G98" t="n">
         <v>1</v>
       </c>
       <c r="H98" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I98" t="n">
         <v>0</v>
@@ -4477,13 +4473,13 @@
         <v>0</v>
       </c>
       <c r="K98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99">
@@ -4518,10 +4514,10 @@
         <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M99" t="n">
         <v>0</v>
@@ -4556,7 +4552,7 @@
         <v>0</v>
       </c>
       <c r="J100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K100" t="n">
         <v>1</v>
@@ -4565,7 +4561,7 @@
         <v>1</v>
       </c>
       <c r="M100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -4588,13 +4584,13 @@
         <v>0</v>
       </c>
       <c r="G101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H101" t="n">
         <v>1</v>
       </c>
       <c r="I101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>

--- a/Result/analyze_1.xlsx
+++ b/Result/analyze_1.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M101"/>
+  <dimension ref="A1:M102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -565,7 +565,7 @@
         <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -574,7 +574,7 @@
         <v>2</v>
       </c>
       <c r="M3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -606,7 +606,7 @@
         <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K4" t="n">
         <v>1</v>
@@ -615,7 +615,7 @@
         <v>3</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -653,10 +653,10 @@
         <v>1</v>
       </c>
       <c r="L5" t="n">
+        <v>6</v>
+      </c>
+      <c r="M5" t="n">
         <v>4</v>
-      </c>
-      <c r="M5" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -735,10 +735,10 @@
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -749,13 +749,13 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F8" t="n">
         <v>2</v>
@@ -764,10 +764,10 @@
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J8" t="n">
         <v>3</v>
@@ -776,7 +776,7 @@
         <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
         <v>2</v>
@@ -831,13 +831,13 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F10" t="n">
         <v>1</v>
@@ -846,10 +846,10 @@
         <v>3</v>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -858,7 +858,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1013,7 +1013,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -1034,7 +1034,9 @@
           <t>半導體業右下</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
+      <c r="B15" t="n">
+        <v>0</v>
+      </c>
       <c r="C15" t="n">
         <v>8</v>
       </c>
@@ -1063,10 +1065,10 @@
         <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
@@ -1104,10 +1106,10 @@
         <v>3</v>
       </c>
       <c r="L16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1394,7 +1396,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -1435,7 +1437,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="25">
@@ -1476,7 +1478,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="26">
@@ -1649,7 +1651,9 @@
           <t>文化創意業右下</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr"/>
+      <c r="B30" t="n">
+        <v>0</v>
+      </c>
       <c r="C30" t="n">
         <v>0</v>
       </c>
@@ -1728,7 +1732,7 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>橡膠工業右下</t>
+          <t>橡膠工業右上</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -1769,7 +1773,7 @@
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>橡膠工業平</t>
+          <t>橡膠工業右下</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -1810,7 +1814,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>水泥工業右下</t>
+          <t>橡膠工業平</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -1851,7 +1855,7 @@
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>水泥工業平</t>
+          <t>水泥工業右下</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -1892,7 +1896,7 @@
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>汽車工業右上</t>
+          <t>水泥工業平</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -1903,19 +1907,19 @@
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -1933,12 +1937,10 @@
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>汽車工業右下</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>0</v>
-      </c>
+          <t>汽車工業右上</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
       <c r="C37" t="n">
         <v>0</v>
       </c>
@@ -1946,7 +1948,7 @@
         <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
@@ -1955,16 +1957,16 @@
         <v>1</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
@@ -1976,7 +1978,7 @@
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>汽車工業平</t>
+          <t>汽車工業右下</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -1999,25 +2001,25 @@
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>油電燃氣業右上</t>
+          <t>汽車工業平</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -2034,13 +2036,13 @@
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2049,21 +2051,21 @@
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>油電燃氣業右下</t>
+          <t>油電燃氣業右上</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D40" t="n">
         <v>0</v>
@@ -2072,7 +2074,7 @@
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -2099,12 +2101,12 @@
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>油電燃氣業平</t>
+          <t>油電燃氣業右下</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D41" t="n">
         <v>0</v>
@@ -2113,7 +2115,7 @@
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -2140,7 +2142,7 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>玻璃陶瓷右上</t>
+          <t>油電燃氣業平</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -2154,7 +2156,7 @@
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -2172,7 +2174,7 @@
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
@@ -2181,7 +2183,7 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>玻璃陶瓷平</t>
+          <t>玻璃陶瓷右上</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -2213,7 +2215,7 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
@@ -2222,62 +2224,62 @@
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>生技醫療業右上</t>
+          <t>玻璃陶瓷平</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>生技醫療業右下</t>
+          <t>生技醫療業右上</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D45" t="n">
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
         <v>2</v>
@@ -2292,10 +2294,10 @@
         <v>1</v>
       </c>
       <c r="K45" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L45" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M45" t="n">
         <v>1</v>
@@ -2304,12 +2306,12 @@
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>生技醫療業平</t>
+          <t>生技醫療業右下</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D46" t="n">
         <v>2</v>
@@ -2318,75 +2320,75 @@
         <v>1</v>
       </c>
       <c r="F46" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J46" t="n">
         <v>2</v>
       </c>
       <c r="K46" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>紡織纖維右上</t>
+          <t>生技醫療業平</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>紡織纖維右下</t>
+          <t>紡織纖維右上</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -2403,10 +2405,10 @@
         <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I48" t="n">
         <v>0</v>
@@ -2421,13 +2423,13 @@
         <v>1</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>紡織纖維平</t>
+          <t>紡織纖維右下</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -2435,7 +2437,7 @@
         <v>0</v>
       </c>
       <c r="D49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E49" t="n">
         <v>0</v>
@@ -2459,27 +2461,27 @@
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>綠能環保右上</t>
+          <t>紡織纖維平</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D50" t="n">
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -2488,39 +2490,39 @@
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>綠能環保右下</t>
+          <t>綠能環保右上</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D51" t="n">
         <v>1</v>
       </c>
       <c r="E51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F51" t="n">
         <v>0</v>
@@ -2532,13 +2534,13 @@
         <v>1</v>
       </c>
       <c r="I51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
@@ -2550,7 +2552,7 @@
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>綠能環保平</t>
+          <t>綠能環保右下</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -2561,7 +2563,7 @@
         <v>1</v>
       </c>
       <c r="E52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F52" t="n">
         <v>0</v>
@@ -2570,10 +2572,10 @@
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -2591,7 +2593,7 @@
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>航運業右上</t>
+          <t>綠能環保平</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
@@ -2599,19 +2601,19 @@
         <v>0</v>
       </c>
       <c r="D53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E53" t="n">
         <v>1</v>
       </c>
       <c r="F53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I53" t="n">
         <v>1</v>
@@ -2623,21 +2625,19 @@
         <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>航運業右下</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
-        <v>0</v>
-      </c>
+          <t>航運業右上</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr"/>
       <c r="C54" t="n">
         <v>0</v>
       </c>
@@ -2645,19 +2645,19 @@
         <v>0</v>
       </c>
       <c r="E54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -2666,16 +2666,16 @@
         <v>0</v>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>航運業平</t>
+          <t>航運業右下</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
@@ -2716,7 +2716,7 @@
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>觀光事業右上</t>
+          <t>航運業平</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
@@ -2757,7 +2757,7 @@
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>觀光事業右下</t>
+          <t>觀光事業右上</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
@@ -2771,7 +2771,7 @@
         <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -2789,19 +2789,21 @@
         <v>0</v>
       </c>
       <c r="L57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>觀光事業平</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr"/>
+          <t>觀光事業右下</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>0</v>
+      </c>
       <c r="C58" t="n">
         <v>0</v>
       </c>
@@ -2812,7 +2814,7 @@
         <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -2830,16 +2832,16 @@
         <v>0</v>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>貿易百貨右上</t>
+          <t>觀光事業平</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -2880,7 +2882,7 @@
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>貿易百貨右下</t>
+          <t>貿易百貨右上</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -2921,10 +2923,12 @@
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>貿易百貨平</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr"/>
+          <t>貿易百貨右下</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>0</v>
+      </c>
       <c r="C61" t="n">
         <v>0</v>
       </c>
@@ -2962,21 +2966,21 @@
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>資訊服務業右上</t>
+          <t>貿易百貨平</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D62" t="n">
         <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -3003,21 +3007,21 @@
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>資訊服務業右下</t>
+          <t>資訊服務業右上</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D63" t="n">
         <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -3044,7 +3048,7 @@
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>資訊服務業平</t>
+          <t>資訊服務業右下</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
@@ -3085,7 +3089,7 @@
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>農業科技業右上</t>
+          <t>資訊服務業平</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
@@ -3126,7 +3130,7 @@
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>農業科技業右下</t>
+          <t>農業科技業右上</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
@@ -3167,39 +3171,39 @@
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>通信網路業右上</t>
+          <t>農業科技業右下</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E67" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F67" t="n">
         <v>0</v>
       </c>
       <c r="G67" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L67" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
         <v>0</v>
@@ -3208,91 +3212,89 @@
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>通信網路業右下</t>
-        </is>
-      </c>
-      <c r="B68" t="n">
-        <v>0</v>
-      </c>
+          <t>通信網路業右上</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr"/>
       <c r="C68" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D68" t="n">
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G68" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L68" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M68" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>通信網路業平</t>
+          <t>通信網路業右下</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>造紙工業右下</t>
+          <t>通信網路業平</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
@@ -3309,31 +3311,31 @@
         <v>0</v>
       </c>
       <c r="G70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I70" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>造紙工業平</t>
+          <t>造紙工業右下</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
@@ -3374,7 +3376,7 @@
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>運動休閒右上</t>
+          <t>造紙工業平</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
@@ -3415,7 +3417,7 @@
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>運動休閒右下</t>
+          <t>運動休閒右上</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
@@ -3456,12 +3458,12 @@
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>運動休閒平</t>
+          <t>運動休閒右下</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
       <c r="C74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D74" t="n">
         <v>0</v>
@@ -3497,12 +3499,12 @@
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>金融保險右上</t>
+          <t>運動休閒平</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D75" t="n">
         <v>0</v>
@@ -3538,7 +3540,7 @@
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>金融保險右下</t>
+          <t>金融保險右上</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
@@ -3579,7 +3581,7 @@
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>金融保險平</t>
+          <t>金融保險右下</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
@@ -3605,7 +3607,7 @@
         <v>0</v>
       </c>
       <c r="J77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K77" t="n">
         <v>0</v>
@@ -3620,7 +3622,7 @@
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>金融業右上</t>
+          <t>金融保險平</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
@@ -3646,7 +3648,7 @@
         <v>0</v>
       </c>
       <c r="J78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K78" t="n">
         <v>0</v>
@@ -3661,7 +3663,7 @@
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>金融業右下</t>
+          <t>金融業右上</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
@@ -3702,7 +3704,7 @@
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>金融業平</t>
+          <t>金融業右下</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
@@ -3743,7 +3745,7 @@
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業右上</t>
+          <t>金融業平</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
@@ -3763,7 +3765,7 @@
         <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I81" t="n">
         <v>0</v>
@@ -3772,7 +3774,7 @@
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L81" t="n">
         <v>0</v>
@@ -3784,7 +3786,7 @@
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業右下</t>
+          <t>鋼鐵工業右上</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
@@ -3804,16 +3806,16 @@
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I82" t="n">
         <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L82" t="n">
         <v>0</v>
@@ -3825,7 +3827,7 @@
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業平</t>
+          <t>鋼鐵工業右下</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
@@ -3851,7 +3853,7 @@
         <v>0</v>
       </c>
       <c r="J83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K83" t="n">
         <v>0</v>
@@ -3860,13 +3862,13 @@
         <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>電器電纜右上</t>
+          <t>鋼鐵工業平</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
@@ -3883,7 +3885,7 @@
         <v>0</v>
       </c>
       <c r="G84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H84" t="n">
         <v>0</v>
@@ -3901,13 +3903,13 @@
         <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>電器電纜右下</t>
+          <t>電器電纜右上</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
@@ -3924,7 +3926,7 @@
         <v>0</v>
       </c>
       <c r="G85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H85" t="n">
         <v>0</v>
@@ -3942,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>電器電纜平</t>
+          <t>電器電纜右下</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
@@ -3989,7 +3991,7 @@
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>電子通路業右上</t>
+          <t>電器電纜平</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
@@ -4003,34 +4005,34 @@
         <v>0</v>
       </c>
       <c r="F87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L87" t="n">
         <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>電子通路業右下</t>
+          <t>電子通路業右上</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
@@ -4044,10 +4046,10 @@
         <v>0</v>
       </c>
       <c r="F88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H88" t="n">
         <v>1</v>
@@ -4056,10 +4058,10 @@
         <v>1</v>
       </c>
       <c r="J88" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L88" t="n">
         <v>0</v>
@@ -4071,12 +4073,12 @@
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>電子通路業平</t>
+          <t>電子通路業右下</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D89" t="n">
         <v>0</v>
@@ -4085,19 +4087,19 @@
         <v>0</v>
       </c>
       <c r="F89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I89" t="n">
         <v>1</v>
       </c>
       <c r="J89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K89" t="n">
         <v>0</v>
@@ -4112,105 +4114,105 @@
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業右上</t>
+          <t>電子通路業平</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E90" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="F90" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G90" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="H90" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I90" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="J90" t="n">
         <v>1</v>
       </c>
       <c r="K90" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L90" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業右下</t>
-        </is>
-      </c>
-      <c r="B91" t="n">
-        <v>0</v>
-      </c>
+          <t>電子零組件業右上</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr"/>
       <c r="C91" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D91" t="n">
         <v>1</v>
       </c>
       <c r="E91" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F91" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G91" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="H91" t="n">
+        <v>4</v>
+      </c>
+      <c r="I91" t="n">
+        <v>16</v>
+      </c>
+      <c r="J91" t="n">
+        <v>1</v>
+      </c>
+      <c r="K91" t="n">
         <v>3</v>
       </c>
-      <c r="I91" t="n">
-        <v>0</v>
-      </c>
-      <c r="J91" t="n">
-        <v>1</v>
-      </c>
-      <c r="K91" t="n">
-        <v>1</v>
-      </c>
       <c r="L91" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業平</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr"/>
+          <t>電子零組件業右下</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>0</v>
+      </c>
       <c r="C92" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E92" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F92" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G92" t="n">
         <v>2</v>
@@ -4219,7 +4221,7 @@
         <v>3</v>
       </c>
       <c r="I92" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J92" t="n">
         <v>1</v>
@@ -4228,98 +4230,98 @@
         <v>1</v>
       </c>
       <c r="L92" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>電機機械右上</t>
+          <t>電子零組件業平</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D93" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F93" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H93" t="n">
         <v>3</v>
       </c>
       <c r="I93" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L93" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>電機機械右下</t>
+          <t>電機機械右上</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D94" t="n">
         <v>2</v>
       </c>
       <c r="E94" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F94" t="n">
         <v>2</v>
       </c>
       <c r="G94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H94" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I94" t="n">
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L94" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>電機機械平</t>
+          <t>電機機械右下</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
@@ -4327,13 +4329,13 @@
         <v>1</v>
       </c>
       <c r="D95" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F95" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -4342,16 +4344,16 @@
         <v>0</v>
       </c>
       <c r="I95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M95" t="n">
         <v>1</v>
@@ -4360,39 +4362,39 @@
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右上</t>
+          <t>電機機械平</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E96" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G96" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H96" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I96" t="n">
         <v>1</v>
       </c>
       <c r="J96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L96" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
         <v>1</v>
@@ -4401,41 +4403,39 @@
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右下</t>
-        </is>
-      </c>
-      <c r="B97" t="n">
-        <v>0</v>
-      </c>
+          <t>電腦及週邊設備業右上</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr"/>
       <c r="C97" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D97" t="n">
         <v>1</v>
       </c>
       <c r="E97" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G97" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M97" t="n">
         <v>1</v>
@@ -4444,7 +4444,7 @@
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業平</t>
+          <t>電腦及週邊設備業右下</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
@@ -4452,19 +4452,19 @@
         <v>2</v>
       </c>
       <c r="D98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E98" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F98" t="n">
         <v>1</v>
       </c>
       <c r="G98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I98" t="n">
         <v>0</v>
@@ -4473,7 +4473,7 @@
         <v>0</v>
       </c>
       <c r="K98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L98" t="n">
         <v>0</v>
@@ -4485,24 +4485,24 @@
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>食品工業右上</t>
+          <t>電腦及週邊設備業平</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D99" t="n">
         <v>0</v>
       </c>
       <c r="E99" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F99" t="n">
         <v>0</v>
       </c>
       <c r="G99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H99" t="n">
         <v>0</v>
@@ -4520,13 +4520,13 @@
         <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>食品工業右下</t>
+          <t>食品工業右上</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
@@ -4552,13 +4552,13 @@
         <v>0</v>
       </c>
       <c r="J100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K100" t="n">
         <v>1</v>
       </c>
       <c r="L100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M100" t="n">
         <v>0</v>
@@ -4567,7 +4567,7 @@
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>食品工業平</t>
+          <t>食品工業右下</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
@@ -4584,24 +4584,65 @@
         <v>0</v>
       </c>
       <c r="G101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I101" t="n">
         <v>0</v>
       </c>
       <c r="J101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M101" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="inlineStr">
+        <is>
+          <t>食品工業平</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr"/>
+      <c r="C102" t="n">
+        <v>0</v>
+      </c>
+      <c r="D102" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" t="n">
+        <v>0</v>
+      </c>
+      <c r="F102" t="n">
+        <v>0</v>
+      </c>
+      <c r="G102" t="n">
+        <v>1</v>
+      </c>
+      <c r="H102" t="n">
+        <v>1</v>
+      </c>
+      <c r="I102" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" t="n">
+        <v>0</v>
+      </c>
+      <c r="K102" t="n">
+        <v>0</v>
+      </c>
+      <c r="L102" t="n">
+        <v>0</v>
+      </c>
+      <c r="M102" t="n">
         <v>0</v>
       </c>
     </row>

--- a/Result/analyze_1.xlsx
+++ b/Result/analyze_1.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M102"/>
+  <dimension ref="A1:M101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,57 +441,57 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-08</t>
         </is>
       </c>
     </row>
@@ -503,37 +503,37 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E2" t="n">
         <v>4</v>
       </c>
-      <c r="D2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E2" t="n">
-        <v>10</v>
-      </c>
       <c r="F2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G2" t="n">
         <v>4</v>
       </c>
       <c r="H2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J2" t="n">
+        <v>9</v>
+      </c>
+      <c r="K2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L2" t="n">
+        <v>7</v>
+      </c>
+      <c r="M2" t="n">
         <v>4</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>2</v>
-      </c>
-      <c r="L2" t="n">
-        <v>9</v>
-      </c>
-      <c r="M2" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -542,7 +542,9 @@
           <t>光電業右下</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
@@ -550,31 +552,31 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -585,22 +587,22 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
@@ -609,13 +611,13 @@
         <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -626,31 +628,31 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="n">
         <v>3</v>
       </c>
-      <c r="D5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" t="n">
-        <v>2</v>
-      </c>
       <c r="F5" t="n">
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H5" t="n">
         <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L5" t="n">
         <v>6</v>
@@ -665,7 +667,9 @@
           <t>其他右下</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
@@ -676,28 +680,28 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -708,7 +712,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -720,25 +724,25 @@
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K7" t="n">
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -749,37 +753,37 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
         <v>2</v>
       </c>
       <c r="E8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F8" t="n">
+        <v>6</v>
+      </c>
+      <c r="G8" t="n">
+        <v>9</v>
+      </c>
+      <c r="H8" t="n">
+        <v>3</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2</v>
+      </c>
+      <c r="L8" t="n">
+        <v>3</v>
+      </c>
+      <c r="M8" t="n">
         <v>4</v>
-      </c>
-      <c r="F8" t="n">
-        <v>2</v>
-      </c>
-      <c r="G8" t="n">
-        <v>7</v>
-      </c>
-      <c r="H8" t="n">
-        <v>6</v>
-      </c>
-      <c r="I8" t="n">
-        <v>9</v>
-      </c>
-      <c r="J8" t="n">
-        <v>3</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -788,7 +792,9 @@
           <t>其他電子業右下</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
@@ -796,28 +802,28 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -831,25 +837,25 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
         <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F10" t="n">
         <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -858,10 +864,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -872,34 +878,34 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M11" t="n">
         <v>1</v>
@@ -925,13 +931,13 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -969,22 +975,22 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -995,37 +1001,37 @@
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
+        <v>5</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
         <v>3</v>
       </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
+        <v>3</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2</v>
+      </c>
+      <c r="L14" t="n">
+        <v>8</v>
+      </c>
+      <c r="M14" t="n">
         <v>5</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1</v>
-      </c>
-      <c r="K14" t="n">
-        <v>3</v>
-      </c>
-      <c r="L14" t="n">
-        <v>3</v>
-      </c>
-      <c r="M14" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1038,37 +1044,37 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H15" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" t="n">
+        <v>9</v>
+      </c>
+      <c r="K15" t="n">
         <v>3</v>
       </c>
-      <c r="J15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1</v>
-      </c>
       <c r="L15" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="M15" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1079,16 +1085,16 @@
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E16" t="n">
         <v>4</v>
       </c>
       <c r="F16" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G16" t="n">
         <v>4</v>
@@ -1097,19 +1103,19 @@
         <v>2</v>
       </c>
       <c r="I16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J16" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -1144,13 +1150,13 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1161,7 +1167,7 @@
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -1220,13 +1226,13 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -1273,7 +1279,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1284,7 +1290,7 @@
       </c>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -1299,13 +1305,13 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
         <v>1</v>
@@ -1314,7 +1320,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1337,13 +1343,13 @@
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1390,13 +1396,13 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1405,9 +1411,11 @@
           <t>建材營造右下</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="n">
+        <v>0</v>
+      </c>
       <c r="C24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
@@ -1431,13 +1439,13 @@
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1472,13 +1480,13 @@
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M25" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1489,10 +1497,10 @@
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -1504,7 +1512,7 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -1513,7 +1521,7 @@
         <v>1</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" t="n">
         <v>1</v>
@@ -1542,19 +1550,19 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27" t="n">
         <v>1</v>
       </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -1615,10 +1623,10 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -1651,9 +1659,7 @@
           <t>文化創意業右下</t>
         </is>
       </c>
-      <c r="B30" t="n">
-        <v>0</v>
-      </c>
+      <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
         <v>0</v>
       </c>
@@ -1726,7 +1732,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -1942,37 +1948,37 @@
       </c>
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -1989,28 +1995,28 @@
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I38" t="n">
         <v>2</v>
       </c>
       <c r="J38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
@@ -2036,13 +2042,13 @@
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2051,7 +2057,7 @@
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
         <v>1</v>
@@ -2106,16 +2112,16 @@
       </c>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -2191,13 +2197,13 @@
         <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E43" t="n">
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -2209,13 +2215,13 @@
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
@@ -2232,13 +2238,13 @@
         <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -2270,37 +2276,37 @@
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
         <v>1</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K45" t="n">
         <v>1</v>
       </c>
       <c r="L45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M45" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="46">
@@ -2311,37 +2317,37 @@
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="n">
+        <v>1</v>
+      </c>
+      <c r="D46" t="n">
         <v>3</v>
       </c>
-      <c r="D46" t="n">
-        <v>2</v>
-      </c>
       <c r="E46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46" t="n">
+        <v>2</v>
+      </c>
+      <c r="I46" t="n">
         <v>3</v>
       </c>
-      <c r="G46" t="n">
-        <v>2</v>
-      </c>
-      <c r="H46" t="n">
-        <v>1</v>
-      </c>
-      <c r="I46" t="n">
-        <v>1</v>
-      </c>
       <c r="J46" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L46" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -2352,37 +2358,37 @@
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I47" t="n">
         <v>1</v>
       </c>
       <c r="J47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -2399,31 +2405,31 @@
         <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I48" t="n">
         <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L48" t="n">
         <v>1</v>
       </c>
       <c r="M48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -2455,13 +2461,13 @@
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
         <v>0</v>
@@ -2478,7 +2484,7 @@
         <v>0</v>
       </c>
       <c r="D50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E50" t="n">
         <v>0</v>
@@ -2499,13 +2505,13 @@
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -2516,31 +2522,31 @@
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
@@ -2560,19 +2566,19 @@
         <v>0</v>
       </c>
       <c r="D52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E52" t="n">
         <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I52" t="n">
         <v>0</v>
@@ -2598,19 +2604,19 @@
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F53" t="n">
         <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
@@ -2639,37 +2645,37 @@
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G54" t="n">
         <v>1</v>
       </c>
       <c r="H54" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L54" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -2707,10 +2713,10 @@
         <v>0</v>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -2801,20 +2807,18 @@
           <t>觀光事業右下</t>
         </is>
       </c>
-      <c r="B58" t="n">
-        <v>0</v>
-      </c>
+      <c r="B58" t="inlineStr"/>
       <c r="C58" t="n">
         <v>0</v>
       </c>
       <c r="D58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E58" t="n">
         <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -2826,16 +2830,16 @@
         <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L58" t="n">
         <v>1</v>
       </c>
       <c r="M58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -2926,9 +2930,7 @@
           <t>貿易百貨右下</t>
         </is>
       </c>
-      <c r="B61" t="n">
-        <v>0</v>
-      </c>
+      <c r="B61" t="inlineStr"/>
       <c r="C61" t="n">
         <v>0</v>
       </c>
@@ -2966,15 +2968,15 @@
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>貿易百貨平</t>
+          <t>資訊服務業右上</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E62" t="n">
         <v>0</v>
@@ -3001,27 +3003,29 @@
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>資訊服務業右上</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr"/>
+          <t>資訊服務業右下</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>0</v>
+      </c>
       <c r="C63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D63" t="n">
         <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -3048,7 +3052,7 @@
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>資訊服務業右下</t>
+          <t>資訊服務業平</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
@@ -3089,7 +3093,7 @@
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>資訊服務業平</t>
+          <t>農業科技業右上</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
@@ -3130,10 +3134,12 @@
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>農業科技業右上</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr"/>
+          <t>農業科技業右下</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>0</v>
+      </c>
       <c r="C66" t="n">
         <v>0</v>
       </c>
@@ -3171,80 +3177,82 @@
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>農業科技業右下</t>
+          <t>通信網路業右上</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E67" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F67" t="n">
         <v>0</v>
       </c>
       <c r="G67" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J67" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K67" t="n">
         <v>0</v>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>通信網路業右上</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr"/>
+          <t>通信網路業右下</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>0</v>
+      </c>
       <c r="C68" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E68" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I68" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K68" t="n">
         <v>1</v>
       </c>
       <c r="L68" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
         <v>0</v>
@@ -3253,24 +3261,24 @@
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>通信網路業右下</t>
+          <t>通信網路業平</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F69" t="n">
         <v>2</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -3279,22 +3287,22 @@
         <v>1</v>
       </c>
       <c r="J69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>通信網路業平</t>
+          <t>造紙工業右下</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
@@ -3311,31 +3319,31 @@
         <v>0</v>
       </c>
       <c r="G70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I70" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>造紙工業右下</t>
+          <t>造紙工業平</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
@@ -3376,7 +3384,7 @@
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>造紙工業平</t>
+          <t>運動休閒右上</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
@@ -3417,7 +3425,7 @@
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>運動休閒右上</t>
+          <t>運動休閒右下</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
@@ -3458,7 +3466,7 @@
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>運動休閒右下</t>
+          <t>運動休閒平</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
@@ -3499,12 +3507,12 @@
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>運動休閒平</t>
+          <t>金融保險右上</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D75" t="n">
         <v>0</v>
@@ -3540,7 +3548,7 @@
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>金融保險右上</t>
+          <t>金融保險右下</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
@@ -3581,7 +3589,7 @@
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>金融保險右下</t>
+          <t>金融保險平</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
@@ -3601,7 +3609,7 @@
         <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I77" t="n">
         <v>0</v>
@@ -3622,7 +3630,7 @@
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>金融保險平</t>
+          <t>金融業右上</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
@@ -3648,7 +3656,7 @@
         <v>0</v>
       </c>
       <c r="J78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K78" t="n">
         <v>0</v>
@@ -3663,7 +3671,7 @@
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>金融業右上</t>
+          <t>金融業右下</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
@@ -3704,7 +3712,7 @@
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>金融業右下</t>
+          <t>金融業平</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
@@ -3745,7 +3753,7 @@
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>金融業平</t>
+          <t>鋼鐵工業右上</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
@@ -3759,7 +3767,7 @@
         <v>0</v>
       </c>
       <c r="F81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -3768,7 +3776,7 @@
         <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -3786,7 +3794,7 @@
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業右上</t>
+          <t>鋼鐵工業右下</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
@@ -3815,7 +3823,7 @@
         <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L82" t="n">
         <v>0</v>
@@ -3827,7 +3835,7 @@
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業右下</t>
+          <t>鋼鐵工業平</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
@@ -3853,10 +3861,10 @@
         <v>0</v>
       </c>
       <c r="J83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L83" t="n">
         <v>0</v>
@@ -3868,7 +3876,7 @@
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業平</t>
+          <t>電器電纜右上</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
@@ -3879,7 +3887,7 @@
         <v>0</v>
       </c>
       <c r="E84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F84" t="n">
         <v>0</v>
@@ -3897,19 +3905,19 @@
         <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L84" t="n">
         <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>電器電纜右上</t>
+          <t>電器電纜右下</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
@@ -3926,7 +3934,7 @@
         <v>0</v>
       </c>
       <c r="G85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H85" t="n">
         <v>0</v>
@@ -3938,19 +3946,19 @@
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L85" t="n">
         <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>電器電纜右下</t>
+          <t>電器電纜平</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
@@ -3979,19 +3987,19 @@
         <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L86" t="n">
         <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>電器電纜平</t>
+          <t>電子通路業右上</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
@@ -3999,22 +4007,22 @@
         <v>0</v>
       </c>
       <c r="D87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H87" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -4023,16 +4031,16 @@
         <v>0</v>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>電子通路業右上</t>
+          <t>電子通路業右下</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
@@ -4052,16 +4060,16 @@
         <v>1</v>
       </c>
       <c r="H88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L88" t="n">
         <v>0</v>
@@ -4073,7 +4081,7 @@
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>電子通路業右下</t>
+          <t>電子通路業平</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
@@ -4081,22 +4089,22 @@
         <v>0</v>
       </c>
       <c r="D89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F89" t="n">
         <v>0</v>
       </c>
       <c r="G89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H89" t="n">
         <v>1</v>
       </c>
       <c r="I89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -4114,114 +4122,114 @@
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>電子通路業平</t>
+          <t>電子零組件業右上</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D90" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E90" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F90" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G90" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="H90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I90" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J90" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="K90" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業右上</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr"/>
+          <t>電子零組件業右下</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>0</v>
+      </c>
       <c r="C91" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E91" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="F91" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G91" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H91" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I91" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="J91" t="n">
         <v>1</v>
       </c>
       <c r="K91" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L91" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M91" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業右下</t>
-        </is>
-      </c>
-      <c r="B92" t="n">
-        <v>0</v>
-      </c>
+          <t>電子零組件業平</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr"/>
       <c r="C92" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E92" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F92" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G92" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H92" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J92" t="n">
         <v>1</v>
@@ -4230,7 +4238,7 @@
         <v>1</v>
       </c>
       <c r="L92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
         <v>0</v>
@@ -4239,7 +4247,7 @@
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業平</t>
+          <t>電機機械右上</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
@@ -4247,31 +4255,31 @@
         <v>3</v>
       </c>
       <c r="D93" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E93" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F93" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G93" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H93" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I93" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L93" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
         <v>1</v>
@@ -4280,65 +4288,65 @@
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>電機機械右上</t>
+          <t>電機機械右下</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E94" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F94" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H94" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J94" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K94" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L94" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>電機機械右下</t>
+          <t>電機機械平</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D95" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E95" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F95" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H95" t="n">
         <v>0</v>
@@ -4347,95 +4355,95 @@
         <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L95" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>電機機械平</t>
+          <t>電腦及週邊設備業右上</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D96" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E96" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F96" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I96" t="n">
         <v>1</v>
       </c>
       <c r="J96" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M96" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右上</t>
+          <t>電腦及週邊設備業右下</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D97" t="n">
         <v>1</v>
       </c>
       <c r="E97" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F97" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G97" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H97" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K97" t="n">
         <v>1</v>
       </c>
       <c r="L97" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
         <v>1</v>
@@ -4444,7 +4452,7 @@
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右下</t>
+          <t>電腦及週邊設備業平</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
@@ -4452,31 +4460,31 @@
         <v>2</v>
       </c>
       <c r="D98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E98" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G98" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
       </c>
       <c r="K98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M98" t="n">
         <v>1</v>
@@ -4485,48 +4493,48 @@
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業平</t>
+          <t>食品工業右上</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D99" t="n">
         <v>0</v>
       </c>
       <c r="E99" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F99" t="n">
         <v>0</v>
       </c>
       <c r="G99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H99" t="n">
         <v>0</v>
       </c>
       <c r="I99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L99" t="n">
         <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>食品工業右上</t>
+          <t>食品工業右下</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
@@ -4546,16 +4554,16 @@
         <v>0</v>
       </c>
       <c r="H100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L100" t="n">
         <v>0</v>
@@ -4567,7 +4575,7 @@
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>食品工業右下</t>
+          <t>食品工業平</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
@@ -4578,10 +4586,10 @@
         <v>0</v>
       </c>
       <c r="E101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -4593,56 +4601,15 @@
         <v>0</v>
       </c>
       <c r="J101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="1" t="inlineStr">
-        <is>
-          <t>食品工業平</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr"/>
-      <c r="C102" t="n">
-        <v>0</v>
-      </c>
-      <c r="D102" t="n">
-        <v>0</v>
-      </c>
-      <c r="E102" t="n">
-        <v>0</v>
-      </c>
-      <c r="F102" t="n">
-        <v>0</v>
-      </c>
-      <c r="G102" t="n">
-        <v>1</v>
-      </c>
-      <c r="H102" t="n">
-        <v>1</v>
-      </c>
-      <c r="I102" t="n">
-        <v>0</v>
-      </c>
-      <c r="J102" t="n">
-        <v>0</v>
-      </c>
-      <c r="K102" t="n">
-        <v>0</v>
-      </c>
-      <c r="L102" t="n">
-        <v>0</v>
-      </c>
-      <c r="M102" t="n">
         <v>0</v>
       </c>
     </row>

--- a/Result/analyze_1.xlsx
+++ b/Result/analyze_1.xlsx
@@ -441,57 +441,57 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-09</t>
         </is>
       </c>
     </row>
@@ -503,37 +503,37 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I2" t="n">
+        <v>9</v>
+      </c>
+      <c r="J2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2" t="n">
         <v>7</v>
       </c>
-      <c r="E2" t="n">
+      <c r="L2" t="n">
         <v>4</v>
       </c>
-      <c r="F2" t="n">
-        <v>5</v>
-      </c>
-      <c r="G2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J2" t="n">
-        <v>9</v>
-      </c>
-      <c r="K2" t="n">
+      <c r="M2" t="n">
         <v>3</v>
-      </c>
-      <c r="L2" t="n">
-        <v>7</v>
-      </c>
-      <c r="M2" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -542,11 +542,9 @@
           <t>光電業右下</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>0</v>
-      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -555,19 +553,19 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K3" t="n">
         <v>1</v>
@@ -576,7 +574,7 @@
         <v>1</v>
       </c>
       <c r="M3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -587,28 +585,28 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
         <v>3</v>
       </c>
-      <c r="E4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1</v>
-      </c>
       <c r="J4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -631,34 +629,34 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
         <v>3</v>
       </c>
-      <c r="F5" t="n">
-        <v>1</v>
-      </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
         <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J5" t="n">
+        <v>4</v>
+      </c>
+      <c r="K5" t="n">
         <v>6</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>4</v>
       </c>
-      <c r="L5" t="n">
-        <v>6</v>
-      </c>
       <c r="M5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -667,9 +665,7 @@
           <t>其他右下</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>0</v>
-      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
         <v>0</v>
       </c>
@@ -677,13 +673,13 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -692,10 +688,10 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -718,19 +714,19 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J7" t="n">
         <v>2</v>
@@ -753,37 +749,37 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G8" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" t="n">
         <v>3</v>
       </c>
-      <c r="I8" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>2</v>
-      </c>
       <c r="L8" t="n">
+        <v>4</v>
+      </c>
+      <c r="M8" t="n">
         <v>3</v>
-      </c>
-      <c r="M8" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -792,32 +788,30 @@
           <t>其他電子業右下</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0</v>
-      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
         <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -826,7 +820,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -840,16 +834,16 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -864,10 +858,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -881,16 +875,16 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
         <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -899,16 +893,16 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -928,10 +922,10 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -972,10 +966,10 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -984,7 +978,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
         <v>1</v>
@@ -1001,37 +995,37 @@
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>5</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" t="n">
         <v>3</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>5</v>
-      </c>
-      <c r="H14" t="n">
-        <v>1</v>
       </c>
       <c r="I14" t="n">
         <v>3</v>
       </c>
       <c r="J14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K14" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="L14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M14" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1040,41 +1034,39 @@
           <t>半導體業右下</t>
         </is>
       </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
+      <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F15" t="n">
+        <v>3</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2</v>
+      </c>
+      <c r="I15" t="n">
+        <v>11</v>
+      </c>
+      <c r="J15" t="n">
         <v>4</v>
       </c>
-      <c r="G15" t="n">
+      <c r="K15" t="n">
+        <v>2</v>
+      </c>
+      <c r="L15" t="n">
         <v>3</v>
       </c>
-      <c r="H15" t="n">
-        <v>1</v>
-      </c>
-      <c r="I15" t="n">
-        <v>1</v>
-      </c>
-      <c r="J15" t="n">
-        <v>9</v>
-      </c>
-      <c r="K15" t="n">
-        <v>3</v>
-      </c>
-      <c r="L15" t="n">
-        <v>2</v>
-      </c>
       <c r="M15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1085,37 +1077,37 @@
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
+        <v>5</v>
+      </c>
+      <c r="D16" t="n">
         <v>4</v>
       </c>
-      <c r="D16" t="n">
-        <v>5</v>
-      </c>
       <c r="E16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" t="n">
         <v>4</v>
       </c>
-      <c r="F16" t="n">
-        <v>2</v>
-      </c>
       <c r="G16" t="n">
+        <v>2</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2</v>
+      </c>
+      <c r="I16" t="n">
         <v>4</v>
       </c>
-      <c r="H16" t="n">
-        <v>2</v>
-      </c>
-      <c r="I16" t="n">
-        <v>3</v>
-      </c>
       <c r="J16" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M16" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1147,13 +1139,13 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
         <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -1182,7 +1174,7 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -1226,7 +1218,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1276,7 +1268,7 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" t="n">
         <v>1</v>
@@ -1302,19 +1294,19 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21" t="n">
         <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -1340,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1393,10 +1385,10 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -1411,9 +1403,7 @@
           <t>建材營造右下</t>
         </is>
       </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
+      <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
         <v>0</v>
       </c>
@@ -1436,16 +1426,16 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K24" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="L24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1477,13 +1467,13 @@
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K25" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="L25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -1509,13 +1499,13 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -1547,7 +1537,7 @@
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G27" t="n">
         <v>1</v>
@@ -1556,7 +1546,7 @@
         <v>1</v>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1620,7 +1610,7 @@
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
@@ -1729,16 +1719,16 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>橡膠工業右上</t>
+          <t>橡膠工業右下</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -1779,7 +1769,7 @@
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>橡膠工業右下</t>
+          <t>橡膠工業平</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -1820,7 +1810,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>橡膠工業平</t>
+          <t>水泥工業右下</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -1861,7 +1851,7 @@
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>水泥工業右下</t>
+          <t>水泥工業平</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -1902,7 +1892,7 @@
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>水泥工業平</t>
+          <t>汽車工業右上</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -1910,13 +1900,13 @@
         <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1943,33 +1933,33 @@
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>汽車工業右上</t>
+          <t>汽車工業右下</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
         <v>1</v>
@@ -1978,13 +1968,13 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>汽車工業右下</t>
+          <t>汽車工業平</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -1992,31 +1982,31 @@
         <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
@@ -2025,7 +2015,7 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>汽車工業平</t>
+          <t>油電燃氣業右上</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -2060,18 +2050,18 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>油電燃氣業右上</t>
+          <t>油電燃氣業右下</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D40" t="n">
         <v>0</v>
@@ -2107,7 +2097,7 @@
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>油電燃氣業右下</t>
+          <t>油電燃氣業平</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -2115,7 +2105,7 @@
         <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
@@ -2148,12 +2138,12 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>油電燃氣業平</t>
+          <t>玻璃陶瓷右上</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D42" t="n">
         <v>0</v>
@@ -2171,7 +2161,7 @@
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -2183,13 +2173,13 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>玻璃陶瓷右上</t>
+          <t>玻璃陶瓷右下</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -2197,7 +2187,7 @@
         <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E43" t="n">
         <v>0</v>
@@ -2215,7 +2205,7 @@
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -2235,10 +2225,10 @@
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
@@ -2279,34 +2269,34 @@
         <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H45" t="n">
         <v>1</v>
       </c>
       <c r="I45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K45" t="n">
         <v>1</v>
       </c>
       <c r="L45" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M45" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -2317,34 +2307,34 @@
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D46" t="n">
+        <v>2</v>
+      </c>
+      <c r="E46" t="n">
+        <v>2</v>
+      </c>
+      <c r="F46" t="n">
+        <v>2</v>
+      </c>
+      <c r="G46" t="n">
         <v>3</v>
       </c>
-      <c r="E46" t="n">
-        <v>2</v>
-      </c>
-      <c r="F46" t="n">
-        <v>1</v>
-      </c>
-      <c r="G46" t="n">
-        <v>1</v>
-      </c>
       <c r="H46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I46" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J46" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M46" t="n">
         <v>1</v>
@@ -2358,19 +2348,19 @@
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
         <v>1</v>
@@ -2379,13 +2369,13 @@
         <v>1</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M47" t="n">
         <v>1</v>
@@ -2402,13 +2392,13 @@
         <v>0</v>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E48" t="n">
         <v>1</v>
       </c>
       <c r="F48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -2417,7 +2407,7 @@
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J48" t="n">
         <v>1</v>
@@ -2426,7 +2416,7 @@
         <v>1</v>
       </c>
       <c r="L48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
         <v>0</v>
@@ -2458,10 +2448,10 @@
         <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
@@ -2502,13 +2492,13 @@
         <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K50" t="n">
         <v>1</v>
       </c>
       <c r="L50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
         <v>0</v>
@@ -2522,19 +2512,19 @@
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
@@ -2569,10 +2559,10 @@
         <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -2604,7 +2594,7 @@
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D53" t="n">
         <v>0</v>
@@ -2613,16 +2603,16 @@
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -2645,37 +2635,37 @@
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D54" t="n">
         <v>1</v>
       </c>
       <c r="E54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J54" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L54" t="n">
         <v>1</v>
       </c>
       <c r="M54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -2710,13 +2700,13 @@
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L55" t="n">
         <v>1</v>
       </c>
       <c r="M55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -2798,7 +2788,7 @@
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -2809,10 +2799,10 @@
       </c>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D58" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E58" t="n">
         <v>0</v>
@@ -2827,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J58" t="n">
         <v>1</v>
@@ -2836,7 +2826,7 @@
         <v>1</v>
       </c>
       <c r="L58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
         <v>0</v>
@@ -2976,7 +2966,7 @@
         <v>1</v>
       </c>
       <c r="D62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E62" t="n">
         <v>0</v>
@@ -3000,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M62" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -3137,9 +3127,7 @@
           <t>農業科技業右下</t>
         </is>
       </c>
-      <c r="B66" t="n">
-        <v>0</v>
-      </c>
+      <c r="B66" t="inlineStr"/>
       <c r="C66" t="n">
         <v>0</v>
       </c>
@@ -3182,37 +3170,37 @@
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D67" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E67" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G67" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" t="n">
+        <v>1</v>
+      </c>
+      <c r="I67" t="n">
         <v>3</v>
       </c>
-      <c r="H67" t="n">
-        <v>0</v>
-      </c>
-      <c r="I67" t="n">
-        <v>1</v>
-      </c>
       <c r="J67" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L67" t="n">
         <v>2</v>
       </c>
       <c r="M67" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -3221,20 +3209,18 @@
           <t>通信網路業右下</t>
         </is>
       </c>
-      <c r="B68" t="n">
-        <v>0</v>
-      </c>
+      <c r="B68" t="inlineStr"/>
       <c r="C68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D68" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E68" t="n">
         <v>0</v>
       </c>
       <c r="F68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G68" t="n">
         <v>1</v>
@@ -3243,13 +3229,13 @@
         <v>1</v>
       </c>
       <c r="I68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
@@ -3269,28 +3255,28 @@
         <v>0</v>
       </c>
       <c r="D69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E69" t="n">
         <v>2</v>
       </c>
       <c r="F69" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G69" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J69" t="n">
         <v>2</v>
       </c>
       <c r="K69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L69" t="n">
         <v>1</v>
@@ -3419,7 +3405,7 @@
         <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -3606,10 +3592,10 @@
         <v>0</v>
       </c>
       <c r="G77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I77" t="n">
         <v>0</v>
@@ -3764,19 +3750,19 @@
         <v>0</v>
       </c>
       <c r="E81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -3811,10 +3797,10 @@
         <v>0</v>
       </c>
       <c r="G82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I82" t="n">
         <v>0</v>
@@ -3861,10 +3847,10 @@
         <v>0</v>
       </c>
       <c r="J83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L83" t="n">
         <v>0</v>
@@ -3884,10 +3870,10 @@
         <v>0</v>
       </c>
       <c r="D84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F84" t="n">
         <v>0</v>
@@ -3902,10 +3888,10 @@
         <v>0</v>
       </c>
       <c r="J84" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K84" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L84" t="n">
         <v>0</v>
@@ -3943,10 +3929,10 @@
         <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L85" t="n">
         <v>0</v>
@@ -3984,10 +3970,10 @@
         <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L86" t="n">
         <v>0</v>
@@ -4004,7 +3990,7 @@
       </c>
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D87" t="n">
         <v>1</v>
@@ -4016,22 +4002,22 @@
         <v>1</v>
       </c>
       <c r="G87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H87" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
         <v>0</v>
@@ -4051,13 +4037,13 @@
         <v>0</v>
       </c>
       <c r="E88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F88" t="n">
         <v>1</v>
       </c>
       <c r="G88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H88" t="n">
         <v>0</v>
@@ -4086,22 +4072,22 @@
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D89" t="n">
         <v>1</v>
       </c>
       <c r="E89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G89" t="n">
         <v>1</v>
       </c>
       <c r="H89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I89" t="n">
         <v>0</v>
@@ -4127,37 +4113,37 @@
       </c>
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="n">
+        <v>6</v>
+      </c>
+      <c r="D90" t="n">
         <v>13</v>
       </c>
-      <c r="D90" t="n">
+      <c r="E90" t="n">
+        <v>4</v>
+      </c>
+      <c r="F90" t="n">
+        <v>16</v>
+      </c>
+      <c r="G90" t="n">
+        <v>1</v>
+      </c>
+      <c r="H90" t="n">
+        <v>2</v>
+      </c>
+      <c r="I90" t="n">
+        <v>9</v>
+      </c>
+      <c r="J90" t="n">
+        <v>3</v>
+      </c>
+      <c r="K90" t="n">
+        <v>9</v>
+      </c>
+      <c r="L90" t="n">
+        <v>3</v>
+      </c>
+      <c r="M90" t="n">
         <v>6</v>
-      </c>
-      <c r="E90" t="n">
-        <v>13</v>
-      </c>
-      <c r="F90" t="n">
-        <v>4</v>
-      </c>
-      <c r="G90" t="n">
-        <v>16</v>
-      </c>
-      <c r="H90" t="n">
-        <v>1</v>
-      </c>
-      <c r="I90" t="n">
-        <v>3</v>
-      </c>
-      <c r="J90" t="n">
-        <v>10</v>
-      </c>
-      <c r="K90" t="n">
-        <v>4</v>
-      </c>
-      <c r="L90" t="n">
-        <v>10</v>
-      </c>
-      <c r="M90" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="91">
@@ -4170,19 +4156,19 @@
         <v>0</v>
       </c>
       <c r="C91" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D91" t="n">
         <v>2</v>
       </c>
       <c r="E91" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F91" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H91" t="n">
         <v>1</v>
@@ -4191,16 +4177,16 @@
         <v>1</v>
       </c>
       <c r="J91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L91" t="n">
         <v>1</v>
       </c>
       <c r="M91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -4211,31 +4197,31 @@
       </c>
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D92" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E92" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F92" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G92" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H92" t="n">
         <v>1</v>
       </c>
       <c r="I92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J92" t="n">
         <v>1</v>
       </c>
       <c r="K92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L92" t="n">
         <v>0</v>
@@ -4252,34 +4238,34 @@
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="n">
+        <v>2</v>
+      </c>
+      <c r="D93" t="n">
+        <v>1</v>
+      </c>
+      <c r="E93" t="n">
         <v>3</v>
       </c>
-      <c r="D93" t="n">
-        <v>2</v>
-      </c>
-      <c r="E93" t="n">
-        <v>1</v>
-      </c>
       <c r="F93" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" t="n">
+        <v>0</v>
+      </c>
+      <c r="I93" t="n">
         <v>3</v>
       </c>
-      <c r="G93" t="n">
-        <v>0</v>
-      </c>
-      <c r="H93" t="n">
-        <v>0</v>
-      </c>
-      <c r="I93" t="n">
-        <v>0</v>
-      </c>
       <c r="J93" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K93" t="n">
         <v>0</v>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M93" t="n">
         <v>1</v>
@@ -4293,10 +4279,10 @@
       </c>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E94" t="n">
         <v>0</v>
@@ -4305,25 +4291,25 @@
         <v>0</v>
       </c>
       <c r="G94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H94" t="n">
         <v>1</v>
       </c>
       <c r="I94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J94" t="n">
         <v>2</v>
       </c>
       <c r="K94" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M94" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -4334,25 +4320,25 @@
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E95" t="n">
         <v>0</v>
       </c>
       <c r="F95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H95" t="n">
         <v>0</v>
       </c>
       <c r="I95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -4364,7 +4350,7 @@
         <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
@@ -4375,16 +4361,16 @@
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="n">
+        <v>2</v>
+      </c>
+      <c r="D96" t="n">
         <v>4</v>
       </c>
-      <c r="D96" t="n">
-        <v>2</v>
-      </c>
       <c r="E96" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F96" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G96" t="n">
         <v>1</v>
@@ -4393,19 +4379,19 @@
         <v>1</v>
       </c>
       <c r="I96" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J96" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K96" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L96" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M96" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="97">
@@ -4414,18 +4400,20 @@
           <t>電腦及週邊設備業右下</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr"/>
+      <c r="B97" t="n">
+        <v>0</v>
+      </c>
       <c r="C97" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E97" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -4437,13 +4425,13 @@
         <v>0</v>
       </c>
       <c r="J97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M97" t="n">
         <v>1</v>
@@ -4457,13 +4445,13 @@
       </c>
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F98" t="n">
         <v>0</v>
@@ -4472,22 +4460,22 @@
         <v>0</v>
       </c>
       <c r="H98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K98" t="n">
         <v>1</v>
       </c>
       <c r="L98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -4513,10 +4501,10 @@
         <v>0</v>
       </c>
       <c r="H99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -4551,7 +4539,7 @@
         <v>0</v>
       </c>
       <c r="G100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H100" t="n">
         <v>1</v>
@@ -4560,7 +4548,7 @@
         <v>1</v>
       </c>
       <c r="J100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K100" t="n">
         <v>0</v>
@@ -4583,13 +4571,13 @@
         <v>0</v>
       </c>
       <c r="D101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E101" t="n">
         <v>1</v>
       </c>
       <c r="F101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>

--- a/Result/analyze_1.xlsx
+++ b/Result/analyze_1.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M101"/>
+  <dimension ref="A1:M102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,57 +441,57 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-10</t>
         </is>
       </c>
     </row>
@@ -503,37 +503,37 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D2" t="n">
         <v>4</v>
       </c>
       <c r="E2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>8</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J2" t="n">
+        <v>7</v>
+      </c>
+      <c r="K2" t="n">
+        <v>4</v>
+      </c>
+      <c r="L2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M2" t="n">
         <v>5</v>
-      </c>
-      <c r="F2" t="n">
-        <v>4</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>2</v>
-      </c>
-      <c r="I2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J2" t="n">
-        <v>3</v>
-      </c>
-      <c r="K2" t="n">
-        <v>7</v>
-      </c>
-      <c r="L2" t="n">
-        <v>4</v>
-      </c>
-      <c r="M2" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -542,7 +542,9 @@
           <t>光電業右下</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
@@ -550,19 +552,19 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
@@ -571,7 +573,7 @@
         <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -585,25 +587,25 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
         <v>3</v>
       </c>
-      <c r="D4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -615,7 +617,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -626,37 +628,37 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
         <v>3</v>
       </c>
-      <c r="E5" t="n">
-        <v>1</v>
-      </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
         <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I5" t="n">
+        <v>4</v>
+      </c>
+      <c r="J5" t="n">
         <v>6</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>4</v>
       </c>
-      <c r="K5" t="n">
-        <v>6</v>
-      </c>
       <c r="L5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -670,13 +672,13 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -685,10 +687,10 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -711,25 +713,25 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I7" t="n">
         <v>2</v>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
         <v>1</v>
@@ -738,7 +740,7 @@
         <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -749,37 +751,37 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F8" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2</v>
+      </c>
+      <c r="J8" t="n">
         <v>3</v>
       </c>
-      <c r="H8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" t="n">
-        <v>2</v>
-      </c>
       <c r="K8" t="n">
+        <v>4</v>
+      </c>
+      <c r="L8" t="n">
         <v>3</v>
       </c>
-      <c r="L8" t="n">
-        <v>4</v>
-      </c>
       <c r="M8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -790,25 +792,25 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
         <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -817,10 +819,10 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -834,13 +836,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
         <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -855,10 +857,10 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -872,16 +874,16 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -890,19 +892,19 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
         <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -911,7 +913,9 @@
           <t>化學工業右下</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
+      <c r="B12" t="n">
+        <v>0</v>
+      </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
@@ -919,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -963,10 +967,10 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -975,13 +979,13 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>1</v>
@@ -995,37 +999,37 @@
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>5</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
         <v>3</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>5</v>
-      </c>
-      <c r="G14" t="n">
-        <v>1</v>
       </c>
       <c r="H14" t="n">
         <v>3</v>
       </c>
       <c r="I14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J14" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K14" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L14" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1036,37 +1040,37 @@
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D15" t="n">
+        <v>4</v>
+      </c>
+      <c r="E15" t="n">
+        <v>3</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2</v>
+      </c>
+      <c r="H15" t="n">
+        <v>13</v>
+      </c>
+      <c r="I15" t="n">
         <v>5</v>
       </c>
-      <c r="E15" t="n">
+      <c r="J15" t="n">
+        <v>2</v>
+      </c>
+      <c r="K15" t="n">
         <v>4</v>
       </c>
-      <c r="F15" t="n">
-        <v>3</v>
-      </c>
-      <c r="G15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H15" t="n">
-        <v>2</v>
-      </c>
-      <c r="I15" t="n">
-        <v>11</v>
-      </c>
-      <c r="J15" t="n">
-        <v>4</v>
-      </c>
-      <c r="K15" t="n">
-        <v>2</v>
-      </c>
       <c r="L15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1077,34 +1081,34 @@
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
+        <v>4</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" t="n">
+        <v>4</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
         <v>5</v>
       </c>
-      <c r="D16" t="n">
-        <v>4</v>
-      </c>
-      <c r="E16" t="n">
-        <v>2</v>
-      </c>
-      <c r="F16" t="n">
-        <v>4</v>
-      </c>
-      <c r="G16" t="n">
-        <v>2</v>
-      </c>
-      <c r="H16" t="n">
-        <v>2</v>
-      </c>
-      <c r="I16" t="n">
-        <v>4</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1</v>
-      </c>
       <c r="K16" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L16" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M16" t="n">
         <v>1</v>
@@ -1136,13 +1140,13 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
         <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -1171,10 +1175,10 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -1265,13 +1269,13 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" t="n">
         <v>1</v>
       </c>
       <c r="M20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1291,19 +1295,19 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -1312,7 +1316,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1329,10 +1333,10 @@
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1382,10 +1386,10 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -1423,19 +1427,19 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1464,13 +1468,13 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="J25" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -1496,10 +1500,10 @@
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1517,7 +1521,7 @@
         <v>1</v>
       </c>
       <c r="M26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1534,7 +1538,7 @@
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F27" t="n">
         <v>1</v>
@@ -1543,7 +1547,7 @@
         <v>1</v>
       </c>
       <c r="H27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -1558,7 +1562,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -1584,7 +1588,7 @@
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -1599,7 +1603,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -1716,13 +1720,13 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -1810,7 +1814,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>水泥工業右下</t>
+          <t>水泥工業右上</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -1845,13 +1849,13 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>水泥工業平</t>
+          <t>水泥工業右下</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -1892,7 +1896,7 @@
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>汽車工業右上</t>
+          <t>水泥工業平</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -1900,13 +1904,13 @@
         <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1933,30 +1937,30 @@
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>汽車工業右下</t>
+          <t>汽車工業右上</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D37" t="n">
         <v>1</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -1968,36 +1972,36 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>汽車工業平</t>
+          <t>汽車工業右下</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F38" t="n">
         <v>1</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
         <v>1</v>
@@ -2006,7 +2010,7 @@
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
@@ -2015,7 +2019,7 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>油電燃氣業右上</t>
+          <t>汽車工業平</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -2044,7 +2048,7 @@
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
@@ -2056,12 +2060,12 @@
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>油電燃氣業右下</t>
+          <t>油電燃氣業右上</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D40" t="n">
         <v>0</v>
@@ -2097,7 +2101,7 @@
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>油電燃氣業平</t>
+          <t>油電燃氣業右下</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -2138,12 +2142,12 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>玻璃陶瓷右上</t>
+          <t>油電燃氣業平</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D42" t="n">
         <v>0</v>
@@ -2161,7 +2165,7 @@
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -2173,13 +2177,13 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>玻璃陶瓷右下</t>
+          <t>玻璃陶瓷右上</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -2199,7 +2203,7 @@
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
@@ -2211,7 +2215,7 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
@@ -2220,12 +2224,12 @@
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>玻璃陶瓷平</t>
+          <t>玻璃陶瓷右下</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
@@ -2261,7 +2265,7 @@
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>生技醫療業右上</t>
+          <t>玻璃陶瓷平</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -2269,40 +2273,40 @@
         <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>生技醫療業右下</t>
+          <t>生技醫療業右上</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -2310,31 +2314,31 @@
         <v>2</v>
       </c>
       <c r="D46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G46" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I46" t="n">
+        <v>1</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
         <v>5</v>
       </c>
-      <c r="J46" t="n">
-        <v>0</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0</v>
-      </c>
       <c r="L46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M46" t="n">
         <v>1</v>
@@ -2343,7 +2347,7 @@
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>生技醫療業平</t>
+          <t>生技醫療業右下</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -2351,28 +2355,28 @@
         <v>2</v>
       </c>
       <c r="D47" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H47" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I47" t="n">
         <v>1</v>
       </c>
       <c r="J47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L47" t="n">
         <v>1</v>
@@ -2384,7 +2388,7 @@
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>紡織纖維右上</t>
+          <t>生技醫療業平</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -2392,16 +2396,16 @@
         <v>0</v>
       </c>
       <c r="D48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F48" t="n">
         <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
@@ -2413,10 +2417,10 @@
         <v>1</v>
       </c>
       <c r="K48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M48" t="n">
         <v>0</v>
@@ -2425,15 +2429,15 @@
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>紡織纖維右下</t>
+          <t>紡織纖維右上</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E49" t="n">
         <v>0</v>
@@ -2445,13 +2449,13 @@
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I49" t="n">
         <v>1</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
@@ -2466,7 +2470,7 @@
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>紡織纖維平</t>
+          <t>紡織纖維右下</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -2486,16 +2490,16 @@
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I50" t="n">
         <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
@@ -2507,7 +2511,7 @@
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>綠能環保右上</t>
+          <t>紡織纖維平</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -2518,7 +2522,7 @@
         <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F51" t="n">
         <v>0</v>
@@ -2530,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
@@ -2548,7 +2552,7 @@
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>綠能環保右下</t>
+          <t>綠能環保右上</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -2556,7 +2560,7 @@
         <v>0</v>
       </c>
       <c r="D52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E52" t="n">
         <v>1</v>
@@ -2583,13 +2587,13 @@
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>綠能環保平</t>
+          <t>綠能環保右下</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
@@ -2597,19 +2601,19 @@
         <v>0</v>
       </c>
       <c r="D53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E53" t="n">
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I53" t="n">
         <v>0</v>
@@ -2630,59 +2634,59 @@
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>航運業右上</t>
+          <t>綠能環保平</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>航運業右下</t>
+          <t>航運業右上</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -2691,28 +2695,28 @@
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K55" t="n">
         <v>1</v>
       </c>
       <c r="L55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>航運業平</t>
+          <t>航運業右下</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
@@ -2738,10 +2742,10 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
@@ -2753,7 +2757,7 @@
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>觀光事業右上</t>
+          <t>航運業平</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
@@ -2788,18 +2792,18 @@
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>觀光事業右下</t>
+          <t>觀光事業右上</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D58" t="n">
         <v>0</v>
@@ -2817,16 +2821,16 @@
         <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M58" t="n">
         <v>0</v>
@@ -2835,7 +2839,7 @@
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>觀光事業平</t>
+          <t>觀光事業右下</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -2855,13 +2859,13 @@
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K59" t="n">
         <v>0</v>
@@ -2876,7 +2880,7 @@
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>貿易百貨右上</t>
+          <t>觀光事業平</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -2917,7 +2921,7 @@
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>貿易百貨右下</t>
+          <t>貿易百貨右上</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
@@ -2958,12 +2962,12 @@
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>資訊服務業右上</t>
+          <t>貿易百貨右下</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D62" t="n">
         <v>0</v>
@@ -2990,7 +2994,7 @@
         <v>0</v>
       </c>
       <c r="L62" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
         <v>0</v>
@@ -2999,12 +3003,10 @@
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>資訊服務業右下</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>0</v>
-      </c>
+          <t>資訊服務業右上</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr"/>
       <c r="C63" t="n">
         <v>0</v>
       </c>
@@ -3030,19 +3032,19 @@
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>資訊服務業平</t>
+          <t>資訊服務業右下</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
@@ -3083,7 +3085,7 @@
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>農業科技業右上</t>
+          <t>資訊服務業平</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
@@ -3118,13 +3120,13 @@
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>農業科技業右下</t>
+          <t>農業科技業右上</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
@@ -3165,171 +3167,173 @@
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>通信網路業右上</t>
+          <t>農業科技業右下</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D67" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E67" t="n">
         <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>通信網路業右下</t>
+          <t>通信網路業右上</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D68" t="n">
         <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G68" t="n">
         <v>1</v>
       </c>
       <c r="H68" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I68" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>通信網路業平</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr"/>
+          <t>通信網路業右下</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>0</v>
+      </c>
       <c r="C69" t="n">
         <v>0</v>
       </c>
       <c r="D69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F69" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I69" t="n">
         <v>2</v>
       </c>
       <c r="J69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>造紙工業右下</t>
+          <t>通信網路業平</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E70" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F70" t="n">
         <v>0</v>
       </c>
       <c r="G70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>造紙工業平</t>
+          <t>造紙工業右下</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
@@ -3370,7 +3374,7 @@
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>運動休閒右上</t>
+          <t>造紙工業平</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
@@ -3405,13 +3409,13 @@
         <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>運動休閒右下</t>
+          <t>運動休閒右上</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
@@ -3452,7 +3456,7 @@
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>運動休閒平</t>
+          <t>運動休閒右下</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
@@ -3493,7 +3497,7 @@
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>金融保險右上</t>
+          <t>運動休閒平</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
@@ -3525,7 +3529,7 @@
         <v>0</v>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M75" t="n">
         <v>0</v>
@@ -3534,7 +3538,7 @@
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>金融保險右下</t>
+          <t>金融保險右上</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
@@ -3575,7 +3579,7 @@
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>金融保險平</t>
+          <t>金融保險右下</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
@@ -3592,7 +3596,7 @@
         <v>0</v>
       </c>
       <c r="G77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
@@ -3616,7 +3620,7 @@
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>金融業右上</t>
+          <t>金融保險平</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
@@ -3630,7 +3634,7 @@
         <v>0</v>
       </c>
       <c r="F78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -3657,7 +3661,7 @@
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>金融業右下</t>
+          <t>金融業右上</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
@@ -3698,7 +3702,7 @@
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>金融業平</t>
+          <t>金融業右下</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
@@ -3739,7 +3743,7 @@
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業右上</t>
+          <t>金融業平</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
@@ -3750,7 +3754,7 @@
         <v>0</v>
       </c>
       <c r="E81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F81" t="n">
         <v>0</v>
@@ -3759,7 +3763,7 @@
         <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I81" t="n">
         <v>0</v>
@@ -3780,7 +3784,7 @@
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業右下</t>
+          <t>鋼鐵工業右上</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
@@ -3788,7 +3792,7 @@
         <v>0</v>
       </c>
       <c r="D82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E82" t="n">
         <v>0</v>
@@ -3821,7 +3825,7 @@
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業平</t>
+          <t>鋼鐵工業右下</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
@@ -3835,7 +3839,7 @@
         <v>0</v>
       </c>
       <c r="F83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -3847,7 +3851,7 @@
         <v>0</v>
       </c>
       <c r="J83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K83" t="n">
         <v>0</v>
@@ -3862,7 +3866,7 @@
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>電器電纜右上</t>
+          <t>鋼鐵工業平</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
@@ -3870,7 +3874,7 @@
         <v>0</v>
       </c>
       <c r="D84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E84" t="n">
         <v>0</v>
@@ -3885,10 +3889,10 @@
         <v>0</v>
       </c>
       <c r="I84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J84" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K84" t="n">
         <v>0</v>
@@ -3903,12 +3907,12 @@
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>電器電纜右下</t>
+          <t>電器電纜右上</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D85" t="n">
         <v>0</v>
@@ -3926,10 +3930,10 @@
         <v>0</v>
       </c>
       <c r="I85" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K85" t="n">
         <v>0</v>
@@ -3944,7 +3948,7 @@
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>電器電纜平</t>
+          <t>電器電纜右下</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
@@ -3967,10 +3971,10 @@
         <v>0</v>
       </c>
       <c r="I86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K86" t="n">
         <v>0</v>
@@ -3985,36 +3989,36 @@
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>電子通路業右上</t>
+          <t>電器電纜平</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G87" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L87" t="n">
         <v>0</v>
@@ -4026,24 +4030,24 @@
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>電子通路業右下</t>
+          <t>電子通路業右上</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E88" t="n">
         <v>1</v>
       </c>
       <c r="F88" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H88" t="n">
         <v>0</v>
@@ -4052,7 +4056,7 @@
         <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
@@ -4061,30 +4065,30 @@
         <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>電子通路業平</t>
+          <t>電子通路業右下</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D89" t="n">
         <v>1</v>
       </c>
       <c r="E89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H89" t="n">
         <v>0</v>
@@ -4102,111 +4106,111 @@
         <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業右上</t>
+          <t>電子通路業平</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D90" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E90" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F90" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H90" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I90" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J90" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L90" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業右下</t>
-        </is>
-      </c>
-      <c r="B91" t="n">
-        <v>0</v>
-      </c>
+          <t>電子零組件業右上</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr"/>
       <c r="C91" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D91" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E91" t="n">
+        <v>16</v>
+      </c>
+      <c r="F91" t="n">
+        <v>1</v>
+      </c>
+      <c r="G91" t="n">
         <v>3</v>
       </c>
-      <c r="F91" t="n">
-        <v>0</v>
-      </c>
-      <c r="G91" t="n">
-        <v>1</v>
-      </c>
       <c r="H91" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I91" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J91" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K91" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L91" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業平</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr"/>
+          <t>電子零組件業右下</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>0</v>
+      </c>
       <c r="C92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D92" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E92" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F92" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G92" t="n">
         <v>1</v>
@@ -4215,13 +4219,13 @@
         <v>1</v>
       </c>
       <c r="I92" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J92" t="n">
         <v>1</v>
       </c>
       <c r="K92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L92" t="n">
         <v>0</v>
@@ -4233,56 +4237,56 @@
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>電機機械右上</t>
+          <t>電子零組件業平</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D93" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E93" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H93" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I93" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>電機機械右下</t>
+          <t>電機機械右上</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D94" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E94" t="n">
         <v>0</v>
@@ -4291,31 +4295,31 @@
         <v>0</v>
       </c>
       <c r="G94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H94" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I94" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>電機機械平</t>
+          <t>電機機械右下</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
@@ -4332,19 +4336,19 @@
         <v>1</v>
       </c>
       <c r="G95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H95" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L95" t="n">
         <v>0</v>
@@ -4356,55 +4360,53 @@
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右上</t>
+          <t>電機機械平</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D96" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E96" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H96" t="n">
         <v>1</v>
       </c>
       <c r="I96" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L96" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M96" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右下</t>
-        </is>
-      </c>
-      <c r="B97" t="n">
-        <v>0</v>
-      </c>
+          <t>電腦及週邊設備業右上</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr"/>
       <c r="C97" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D97" t="n">
         <v>2</v>
@@ -4413,39 +4415,41 @@
         <v>1</v>
       </c>
       <c r="F97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H97" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J97" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K97" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L97" t="n">
         <v>2</v>
       </c>
       <c r="M97" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業平</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr"/>
+          <t>電腦及週邊設備業右下</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>0</v>
+      </c>
       <c r="C98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D98" t="n">
         <v>1</v>
@@ -4460,19 +4464,19 @@
         <v>0</v>
       </c>
       <c r="H98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I98" t="n">
         <v>0</v>
       </c>
       <c r="J98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M98" t="n">
         <v>0</v>
@@ -4481,12 +4485,12 @@
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>食品工業右上</t>
+          <t>電腦及週邊設備業平</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D99" t="n">
         <v>0</v>
@@ -4498,16 +4502,16 @@
         <v>0</v>
       </c>
       <c r="G99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K99" t="n">
         <v>0</v>
@@ -4516,13 +4520,13 @@
         <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>食品工業右下</t>
+          <t>食品工業右上</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
@@ -4542,10 +4546,10 @@
         <v>1</v>
       </c>
       <c r="H100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -4563,7 +4567,7 @@
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>食品工業平</t>
+          <t>食品工業右下</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
@@ -4571,19 +4575,19 @@
         <v>0</v>
       </c>
       <c r="D101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I101" t="n">
         <v>0</v>
@@ -4598,6 +4602,47 @@
         <v>0</v>
       </c>
       <c r="M101" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="inlineStr">
+        <is>
+          <t>食品工業平</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr"/>
+      <c r="C102" t="n">
+        <v>1</v>
+      </c>
+      <c r="D102" t="n">
+        <v>1</v>
+      </c>
+      <c r="E102" t="n">
+        <v>0</v>
+      </c>
+      <c r="F102" t="n">
+        <v>0</v>
+      </c>
+      <c r="G102" t="n">
+        <v>0</v>
+      </c>
+      <c r="H102" t="n">
+        <v>0</v>
+      </c>
+      <c r="I102" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" t="n">
+        <v>0</v>
+      </c>
+      <c r="K102" t="n">
+        <v>0</v>
+      </c>
+      <c r="L102" t="n">
+        <v>0</v>
+      </c>
+      <c r="M102" t="n">
         <v>0</v>
       </c>
     </row>

--- a/Result/analyze_1.xlsx
+++ b/Result/analyze_1.xlsx
@@ -441,57 +441,57 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-11</t>
         </is>
       </c>
     </row>
@@ -506,34 +506,34 @@
         <v>4</v>
       </c>
       <c r="D2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G2" t="n">
+        <v>8</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J2" t="n">
         <v>4</v>
       </c>
-      <c r="E2" t="n">
-        <v>4</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H2" t="n">
-        <v>8</v>
-      </c>
-      <c r="I2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J2" t="n">
-        <v>7</v>
-      </c>
       <c r="K2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -549,19 +549,19 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
         <v>1</v>
@@ -570,13 +570,13 @@
         <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -590,19 +590,19 @@
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -628,37 +628,37 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
         <v>3</v>
       </c>
-      <c r="D5" t="n">
-        <v>1</v>
-      </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H5" t="n">
+        <v>4</v>
+      </c>
+      <c r="I5" t="n">
         <v>6</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>4</v>
       </c>
-      <c r="J5" t="n">
-        <v>6</v>
-      </c>
       <c r="K5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -669,13 +669,13 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -684,16 +684,16 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -719,25 +719,25 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
         <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -751,37 +751,37 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
+        <v>6</v>
+      </c>
+      <c r="D8" t="n">
         <v>8</v>
       </c>
-      <c r="D8" t="n">
-        <v>6</v>
-      </c>
       <c r="E8" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" t="n">
         <v>3</v>
-      </c>
-      <c r="G8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" t="n">
-        <v>2</v>
       </c>
       <c r="J8" t="n">
         <v>3</v>
       </c>
       <c r="K8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -792,22 +792,22 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -816,13 +816,13 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -836,16 +836,16 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -854,16 +854,16 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -874,13 +874,13 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
         <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -889,22 +889,22 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -920,10 +920,10 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -967,7 +967,7 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -976,7 +976,7 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -985,7 +985,7 @@
         <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M13" t="n">
         <v>1</v>
@@ -999,37 +999,37 @@
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>5</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
         <v>3</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>5</v>
-      </c>
-      <c r="F14" t="n">
-        <v>1</v>
       </c>
       <c r="G14" t="n">
         <v>3</v>
       </c>
       <c r="H14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J14" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K14" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
         <v>1</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1040,37 +1040,37 @@
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
+        <v>4</v>
+      </c>
+      <c r="D15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" t="n">
+        <v>13</v>
+      </c>
+      <c r="H15" t="n">
         <v>5</v>
       </c>
-      <c r="D15" t="n">
+      <c r="I15" t="n">
+        <v>3</v>
+      </c>
+      <c r="J15" t="n">
         <v>4</v>
       </c>
-      <c r="E15" t="n">
-        <v>3</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" t="n">
-        <v>2</v>
-      </c>
-      <c r="H15" t="n">
-        <v>13</v>
-      </c>
-      <c r="I15" t="n">
-        <v>5</v>
-      </c>
-      <c r="J15" t="n">
-        <v>2</v>
-      </c>
       <c r="K15" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1081,37 +1081,37 @@
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" t="n">
         <v>4</v>
       </c>
-      <c r="D16" t="n">
-        <v>2</v>
-      </c>
       <c r="E16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
         <v>4</v>
       </c>
-      <c r="F16" t="n">
-        <v>2</v>
-      </c>
-      <c r="G16" t="n">
-        <v>2</v>
-      </c>
-      <c r="H16" t="n">
-        <v>2</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
       <c r="J16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K16" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1137,13 +1137,13 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17" t="n">
         <v>1</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1175,7 +1175,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -1213,7 +1213,7 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -1234,7 +1234,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1266,13 +1266,13 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
         <v>1</v>
       </c>
       <c r="L20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -1292,19 +1292,19 @@
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F21" t="n">
         <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1313,10 +1313,10 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1330,10 +1330,10 @@
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -1383,10 +1383,10 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1398,7 +1398,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1424,19 +1424,19 @@
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I24" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -1465,13 +1465,13 @@
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="I25" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -1500,13 +1500,13 @@
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26" t="n">
         <v>1</v>
@@ -1518,10 +1518,10 @@
         <v>1</v>
       </c>
       <c r="L26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1535,7 +1535,7 @@
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E27" t="n">
         <v>1</v>
@@ -1544,7 +1544,7 @@
         <v>1</v>
       </c>
       <c r="G27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -1579,16 +1579,16 @@
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -1603,7 +1603,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -1644,7 +1644,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -1685,7 +1685,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -1717,13 +1717,13 @@
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -1846,10 +1846,10 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -1942,37 +1942,37 @@
       </c>
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H37" t="n">
         <v>1</v>
       </c>
       <c r="I37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -1983,28 +1983,28 @@
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -2045,16 +2045,16 @@
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2200,10 +2200,10 @@
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
@@ -2212,10 +2212,10 @@
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
@@ -2311,34 +2311,34 @@
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F46" t="n">
         <v>1</v>
       </c>
       <c r="G46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K46" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M46" t="n">
         <v>1</v>
@@ -2352,37 +2352,37 @@
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D47" t="n">
+        <v>2</v>
+      </c>
+      <c r="E47" t="n">
         <v>3</v>
-      </c>
-      <c r="E47" t="n">
-        <v>2</v>
       </c>
       <c r="F47" t="n">
         <v>3</v>
       </c>
       <c r="G47" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H47" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K47" t="n">
         <v>1</v>
       </c>
       <c r="L47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -2402,22 +2402,22 @@
         <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I48" t="n">
         <v>1</v>
       </c>
       <c r="J48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L48" t="n">
         <v>1</v>
@@ -2437,7 +2437,7 @@
         <v>1</v>
       </c>
       <c r="D49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E49" t="n">
         <v>0</v>
@@ -2446,16 +2446,16 @@
         <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H49" t="n">
         <v>1</v>
       </c>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
@@ -2473,7 +2473,9 @@
           <t>紡織纖維右下</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr"/>
+      <c r="B50" t="n">
+        <v>0</v>
+      </c>
       <c r="C50" t="n">
         <v>0</v>
       </c>
@@ -2487,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I50" t="n">
         <v>0</v>
@@ -2531,13 +2533,13 @@
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
@@ -2557,13 +2559,13 @@
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F52" t="n">
         <v>0</v>
@@ -2584,10 +2586,10 @@
         <v>0</v>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -2598,10 +2600,10 @@
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E53" t="n">
         <v>0</v>
@@ -2642,16 +2644,16 @@
         <v>0</v>
       </c>
       <c r="D54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
@@ -2666,10 +2668,10 @@
         <v>0</v>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M54" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -2680,37 +2682,37 @@
       </c>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J55" t="n">
         <v>1</v>
       </c>
       <c r="K55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -2739,13 +2741,13 @@
         <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J56" t="n">
         <v>1</v>
       </c>
       <c r="K56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
@@ -2827,10 +2829,10 @@
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
         <v>0</v>
@@ -2856,7 +2858,7 @@
         <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H59" t="n">
         <v>1</v>
@@ -2865,7 +2867,7 @@
         <v>1</v>
       </c>
       <c r="J59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K59" t="n">
         <v>0</v>
@@ -2965,7 +2967,9 @@
           <t>貿易百貨右下</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr"/>
+      <c r="B62" t="n">
+        <v>0</v>
+      </c>
       <c r="C62" t="n">
         <v>0</v>
       </c>
@@ -3029,16 +3033,16 @@
         <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K63" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M63" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -3117,10 +3121,10 @@
         <v>0</v>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -3213,37 +3217,37 @@
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D68" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E68" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" t="n">
+        <v>1</v>
+      </c>
+      <c r="G68" t="n">
         <v>3</v>
       </c>
-      <c r="F68" t="n">
-        <v>0</v>
-      </c>
-      <c r="G68" t="n">
-        <v>1</v>
-      </c>
       <c r="H68" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J68" t="n">
         <v>2</v>
       </c>
       <c r="K68" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -3252,38 +3256,36 @@
           <t>通信網路業右下</t>
         </is>
       </c>
-      <c r="B69" t="n">
-        <v>0</v>
-      </c>
+      <c r="B69" t="inlineStr"/>
       <c r="C69" t="n">
         <v>0</v>
       </c>
       <c r="D69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E69" t="n">
         <v>1</v>
       </c>
       <c r="F69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K69" t="n">
         <v>0</v>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M69" t="n">
         <v>1</v>
@@ -3303,22 +3305,22 @@
         <v>2</v>
       </c>
       <c r="E70" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F70" t="n">
         <v>0</v>
       </c>
       <c r="G70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K70" t="n">
         <v>1</v>
@@ -3491,7 +3493,7 @@
         <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -3526,10 +3528,10 @@
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
         <v>0</v>
@@ -3582,7 +3584,9 @@
           <t>金融保險右下</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr"/>
+      <c r="B77" t="n">
+        <v>0</v>
+      </c>
       <c r="C77" t="n">
         <v>0</v>
       </c>
@@ -3631,10 +3635,10 @@
         <v>0</v>
       </c>
       <c r="E78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -3789,19 +3793,19 @@
       </c>
       <c r="B82" t="inlineStr"/>
       <c r="C82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E82" t="n">
         <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H82" t="n">
         <v>0</v>
@@ -3836,10 +3840,10 @@
         <v>0</v>
       </c>
       <c r="E83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -3886,10 +3890,10 @@
         <v>0</v>
       </c>
       <c r="H84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -3912,7 +3916,7 @@
       </c>
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D85" t="n">
         <v>0</v>
@@ -3927,10 +3931,10 @@
         <v>0</v>
       </c>
       <c r="H85" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I85" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -3968,10 +3972,10 @@
         <v>0</v>
       </c>
       <c r="H86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -4009,10 +4013,10 @@
         <v>0</v>
       </c>
       <c r="H87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -4041,31 +4045,31 @@
         <v>1</v>
       </c>
       <c r="E88" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F88" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H88" t="n">
         <v>0</v>
       </c>
       <c r="I88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -4076,13 +4080,13 @@
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D89" t="n">
         <v>1</v>
       </c>
       <c r="E89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F89" t="n">
         <v>0</v>
@@ -4103,10 +4107,10 @@
         <v>0</v>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -4117,13 +4121,13 @@
       </c>
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F90" t="n">
         <v>0</v>
@@ -4147,7 +4151,7 @@
         <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
@@ -4158,37 +4162,37 @@
       </c>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D91" t="n">
+        <v>16</v>
+      </c>
+      <c r="E91" t="n">
+        <v>1</v>
+      </c>
+      <c r="F91" t="n">
+        <v>3</v>
+      </c>
+      <c r="G91" t="n">
+        <v>10</v>
+      </c>
+      <c r="H91" t="n">
         <v>4</v>
       </c>
-      <c r="E91" t="n">
-        <v>16</v>
-      </c>
-      <c r="F91" t="n">
-        <v>1</v>
-      </c>
-      <c r="G91" t="n">
+      <c r="I91" t="n">
+        <v>9</v>
+      </c>
+      <c r="J91" t="n">
         <v>3</v>
       </c>
-      <c r="H91" t="n">
-        <v>10</v>
-      </c>
-      <c r="I91" t="n">
-        <v>4</v>
-      </c>
-      <c r="J91" t="n">
-        <v>10</v>
-      </c>
       <c r="K91" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L91" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="M91" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="92">
@@ -4197,41 +4201,39 @@
           <t>電子零組件業右下</t>
         </is>
       </c>
-      <c r="B92" t="n">
-        <v>0</v>
-      </c>
+      <c r="B92" t="inlineStr"/>
       <c r="C92" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D92" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F92" t="n">
         <v>1</v>
       </c>
       <c r="G92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H92" t="n">
         <v>1</v>
       </c>
       <c r="I92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J92" t="n">
         <v>1</v>
       </c>
       <c r="K92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L92" t="n">
         <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
@@ -4242,13 +4244,13 @@
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D93" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E93" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F93" t="n">
         <v>1</v>
@@ -4257,16 +4259,16 @@
         <v>1</v>
       </c>
       <c r="H93" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I93" t="n">
         <v>1</v>
       </c>
       <c r="J93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L93" t="n">
         <v>0</v>
@@ -4283,28 +4285,28 @@
       </c>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D94" t="n">
+        <v>0</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" t="n">
+        <v>0</v>
+      </c>
+      <c r="G94" t="n">
         <v>3</v>
       </c>
-      <c r="E94" t="n">
-        <v>0</v>
-      </c>
-      <c r="F94" t="n">
-        <v>0</v>
-      </c>
-      <c r="G94" t="n">
-        <v>0</v>
-      </c>
       <c r="H94" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I94" t="n">
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K94" t="n">
         <v>1</v>
@@ -4322,7 +4324,9 @@
           <t>電機機械右下</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr"/>
+      <c r="B95" t="n">
+        <v>0</v>
+      </c>
       <c r="C95" t="n">
         <v>0</v>
       </c>
@@ -4330,31 +4334,31 @@
         <v>0</v>
       </c>
       <c r="E95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F95" t="n">
         <v>1</v>
       </c>
       <c r="G95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H95" t="n">
         <v>2</v>
       </c>
       <c r="I95" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K95" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -4368,19 +4372,19 @@
         <v>0</v>
       </c>
       <c r="D96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F96" t="n">
         <v>0</v>
       </c>
       <c r="G96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I96" t="n">
         <v>0</v>
@@ -4392,10 +4396,10 @@
         <v>0</v>
       </c>
       <c r="L96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97">
@@ -4406,10 +4410,10 @@
       </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D97" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E97" t="n">
         <v>1</v>
@@ -4418,25 +4422,25 @@
         <v>1</v>
       </c>
       <c r="G97" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H97" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I97" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J97" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K97" t="n">
+        <v>2</v>
+      </c>
+      <c r="L97" t="n">
+        <v>8</v>
+      </c>
+      <c r="M97" t="n">
         <v>3</v>
-      </c>
-      <c r="L97" t="n">
-        <v>2</v>
-      </c>
-      <c r="M97" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="98">
@@ -4445,14 +4449,12 @@
           <t>電腦及週邊設備業右下</t>
         </is>
       </c>
-      <c r="B98" t="n">
-        <v>0</v>
-      </c>
+      <c r="B98" t="inlineStr"/>
       <c r="C98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E98" t="n">
         <v>0</v>
@@ -4464,22 +4466,22 @@
         <v>0</v>
       </c>
       <c r="H98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I98" t="n">
         <v>0</v>
       </c>
       <c r="J98" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K98" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="99">
@@ -4490,7 +4492,7 @@
       </c>
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D99" t="n">
         <v>0</v>
@@ -4499,28 +4501,28 @@
         <v>0</v>
       </c>
       <c r="F99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G99" t="n">
         <v>1</v>
       </c>
       <c r="H99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I99" t="n">
         <v>1</v>
       </c>
       <c r="J99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K99" t="n">
         <v>0</v>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="100">
@@ -4540,10 +4542,10 @@
         <v>0</v>
       </c>
       <c r="F100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H100" t="n">
         <v>0</v>
@@ -4581,13 +4583,13 @@
         <v>0</v>
       </c>
       <c r="F101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I101" t="n">
         <v>0</v>
@@ -4616,16 +4618,16 @@
         <v>1</v>
       </c>
       <c r="D102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H102" t="n">
         <v>0</v>
@@ -4643,7 +4645,7 @@
         <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/Result/analyze_1.xlsx
+++ b/Result/analyze_1.xlsx
@@ -441,57 +441,57 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
     </row>
@@ -506,34 +506,34 @@
         <v>4</v>
       </c>
       <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" t="n">
+        <v>9</v>
+      </c>
+      <c r="G2" t="n">
         <v>3</v>
       </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G2" t="n">
-        <v>8</v>
-      </c>
       <c r="H2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2" t="n">
         <v>6</v>
       </c>
-      <c r="J2" t="n">
-        <v>4</v>
-      </c>
-      <c r="K2" t="n">
-        <v>2</v>
-      </c>
       <c r="L2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -542,23 +542,21 @@
           <t>光電業右下</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>0</v>
-      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
         <v>1</v>
@@ -567,7 +565,7 @@
         <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -587,19 +585,19 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -611,13 +609,13 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -628,34 +626,34 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G5" t="n">
         <v>3</v>
       </c>
-      <c r="E5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>6</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>4</v>
       </c>
-      <c r="I5" t="n">
-        <v>6</v>
-      </c>
       <c r="J5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -667,9 +665,11 @@
           <t>其他右下</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -681,10 +681,10 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -693,7 +693,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -713,16 +713,16 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H7" t="n">
         <v>1</v>
@@ -740,7 +740,7 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -751,22 +751,22 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D8" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" t="n">
         <v>3</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>2</v>
       </c>
       <c r="I8" t="n">
         <v>3</v>
@@ -775,10 +775,10 @@
         <v>3</v>
       </c>
       <c r="K8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
         <v>1</v>
@@ -790,21 +790,23 @@
           <t>其他電子業右下</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -813,13 +815,13 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M9" t="n">
         <v>1</v>
@@ -833,37 +835,37 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -877,7 +879,7 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -886,22 +888,22 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -913,14 +915,12 @@
           <t>化學工業右下</t>
         </is>
       </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -961,7 +961,7 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -973,7 +973,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
@@ -982,10 +982,10 @@
         <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M13" t="n">
         <v>1</v>
@@ -999,37 +999,37 @@
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F14" t="n">
         <v>3</v>
       </c>
       <c r="G14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H14" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I14" t="n">
         <v>8</v>
       </c>
       <c r="J14" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -1038,39 +1038,41 @@
           <t>半導體業右下</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
+      <c r="B15" t="n">
+        <v>0</v>
+      </c>
       <c r="C15" t="n">
+        <v>3</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" t="n">
+        <v>12</v>
+      </c>
+      <c r="G15" t="n">
         <v>4</v>
       </c>
-      <c r="D15" t="n">
-        <v>3</v>
-      </c>
-      <c r="E15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" t="n">
-        <v>2</v>
-      </c>
-      <c r="G15" t="n">
-        <v>13</v>
-      </c>
       <c r="H15" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I15" t="n">
         <v>3</v>
       </c>
       <c r="J15" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16">
@@ -1081,37 +1083,37 @@
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" t="n">
+        <v>3</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" t="n">
+        <v>3</v>
+      </c>
+      <c r="I16" t="n">
+        <v>5</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
         <v>4</v>
-      </c>
-      <c r="E16" t="n">
-        <v>2</v>
-      </c>
-      <c r="F16" t="n">
-        <v>2</v>
-      </c>
-      <c r="G16" t="n">
-        <v>2</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>4</v>
-      </c>
-      <c r="J16" t="n">
-        <v>6</v>
-      </c>
-      <c r="K16" t="n">
-        <v>2</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1134,13 +1136,13 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" t="n">
         <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1210,10 +1212,10 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -1231,7 +1233,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" t="n">
         <v>1</v>
@@ -1263,19 +1265,19 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1289,19 +1291,19 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E21" t="n">
         <v>1</v>
       </c>
       <c r="F21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -1310,10 +1312,10 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -1327,10 +1329,10 @@
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -1380,10 +1382,10 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -1395,10 +1397,10 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1421,19 +1423,19 @@
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H24" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -1462,16 +1464,16 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="H25" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -1480,7 +1482,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -1503,7 +1505,7 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H26" t="n">
         <v>1</v>
@@ -1515,13 +1517,13 @@
         <v>1</v>
       </c>
       <c r="K26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1532,7 +1534,7 @@
       </c>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D27" t="n">
         <v>1</v>
@@ -1541,7 +1543,7 @@
         <v>1</v>
       </c>
       <c r="F27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1556,10 +1558,10 @@
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -1576,16 +1578,16 @@
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -1641,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -1682,10 +1684,10 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -1714,19 +1716,19 @@
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -1843,10 +1845,10 @@
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
@@ -1942,37 +1944,37 @@
       </c>
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G37" t="n">
         <v>1</v>
       </c>
       <c r="H37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -1983,25 +1985,25 @@
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2013,7 +2015,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2042,19 +2044,19 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2197,10 +2199,10 @@
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -2209,10 +2211,10 @@
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -2311,37 +2313,37 @@
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E46" t="n">
         <v>1</v>
       </c>
       <c r="F46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H46" t="n">
         <v>1</v>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J46" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L46" t="n">
         <v>1</v>
       </c>
       <c r="M46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -2350,33 +2352,35 @@
           <t>生技醫療業右下</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr"/>
+      <c r="B47" t="n">
+        <v>0</v>
+      </c>
       <c r="C47" t="n">
+        <v>2</v>
+      </c>
+      <c r="D47" t="n">
         <v>3</v>
-      </c>
-      <c r="D47" t="n">
-        <v>2</v>
       </c>
       <c r="E47" t="n">
         <v>3</v>
       </c>
       <c r="F47" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G47" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J47" t="n">
         <v>1</v>
       </c>
       <c r="K47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
@@ -2399,28 +2403,28 @@
         <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K48" t="n">
         <v>1</v>
       </c>
       <c r="L48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
         <v>0</v>
@@ -2434,7 +2438,7 @@
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D49" t="n">
         <v>0</v>
@@ -2443,16 +2447,16 @@
         <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G49" t="n">
         <v>1</v>
       </c>
       <c r="H49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -2473,9 +2477,7 @@
           <t>紡織纖維右下</t>
         </is>
       </c>
-      <c r="B50" t="n">
-        <v>0</v>
-      </c>
+      <c r="B50" t="inlineStr"/>
       <c r="C50" t="n">
         <v>0</v>
       </c>
@@ -2486,10 +2488,10 @@
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
@@ -2530,10 +2532,10 @@
         <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I51" t="n">
         <v>0</v>
@@ -2583,10 +2585,10 @@
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
         <v>0</v>
@@ -2600,7 +2602,7 @@
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D53" t="n">
         <v>0</v>
@@ -2641,16 +2643,16 @@
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D54" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -2665,10 +2667,10 @@
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L54" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
         <v>0</v>
@@ -2682,37 +2684,37 @@
       </c>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E55" t="n">
         <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I55" t="n">
         <v>1</v>
       </c>
       <c r="J55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -2738,13 +2740,13 @@
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I56" t="n">
         <v>1</v>
       </c>
       <c r="J56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -2826,10 +2828,10 @@
         <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
@@ -2855,7 +2857,7 @@
         <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G59" t="n">
         <v>1</v>
@@ -2864,7 +2866,7 @@
         <v>1</v>
       </c>
       <c r="I59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -2967,9 +2969,7 @@
           <t>貿易百貨右下</t>
         </is>
       </c>
-      <c r="B62" t="n">
-        <v>0</v>
-      </c>
+      <c r="B62" t="inlineStr"/>
       <c r="C62" t="n">
         <v>0</v>
       </c>
@@ -3001,7 +3001,7 @@
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -3030,19 +3030,19 @@
         <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J63" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L63" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -3051,7 +3051,9 @@
           <t>資訊服務業右下</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr"/>
+      <c r="B64" t="n">
+        <v>0</v>
+      </c>
       <c r="C64" t="n">
         <v>0</v>
       </c>
@@ -3118,7 +3120,7 @@
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L65" t="n">
         <v>1</v>
@@ -3217,37 +3219,37 @@
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D68" t="n">
+        <v>0</v>
+      </c>
+      <c r="E68" t="n">
+        <v>1</v>
+      </c>
+      <c r="F68" t="n">
         <v>3</v>
       </c>
-      <c r="E68" t="n">
-        <v>0</v>
-      </c>
-      <c r="F68" t="n">
-        <v>1</v>
-      </c>
       <c r="G68" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I68" t="n">
         <v>2</v>
       </c>
       <c r="J68" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -3258,19 +3260,19 @@
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F69" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G69" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H69" t="n">
         <v>1</v>
@@ -3282,13 +3284,13 @@
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L69" t="n">
         <v>1</v>
       </c>
       <c r="M69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -3299,25 +3301,25 @@
       </c>
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E70" t="n">
         <v>0</v>
       </c>
       <c r="F70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J70" t="n">
         <v>1</v>
@@ -3329,7 +3331,7 @@
         <v>1</v>
       </c>
       <c r="M70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -3490,10 +3492,10 @@
         <v>0</v>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -3525,10 +3527,10 @@
         <v>0</v>
       </c>
       <c r="J75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L75" t="n">
         <v>0</v>
@@ -3584,9 +3586,7 @@
           <t>金融保險右下</t>
         </is>
       </c>
-      <c r="B77" t="n">
-        <v>0</v>
-      </c>
+      <c r="B77" t="inlineStr"/>
       <c r="C77" t="n">
         <v>0</v>
       </c>
@@ -3632,10 +3632,10 @@
         <v>0</v>
       </c>
       <c r="D78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F78" t="n">
         <v>0</v>
@@ -3793,16 +3793,16 @@
       </c>
       <c r="B82" t="inlineStr"/>
       <c r="C82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D82" t="n">
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -3832,7 +3832,9 @@
           <t>鋼鐵工業右下</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr"/>
+      <c r="B83" t="n">
+        <v>0</v>
+      </c>
       <c r="C83" t="n">
         <v>0</v>
       </c>
@@ -3840,7 +3842,7 @@
         <v>0</v>
       </c>
       <c r="E83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F83" t="n">
         <v>0</v>
@@ -3864,7 +3866,7 @@
         <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
@@ -3887,10 +3889,10 @@
         <v>0</v>
       </c>
       <c r="G84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I84" t="n">
         <v>0</v>
@@ -3928,10 +3930,10 @@
         <v>0</v>
       </c>
       <c r="G85" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H85" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I85" t="n">
         <v>0</v>
@@ -3969,10 +3971,10 @@
         <v>0</v>
       </c>
       <c r="G86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I86" t="n">
         <v>0</v>
@@ -4010,10 +4012,10 @@
         <v>0</v>
       </c>
       <c r="G87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I87" t="n">
         <v>0</v>
@@ -4042,22 +4044,22 @@
         <v>1</v>
       </c>
       <c r="D88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E88" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
       </c>
       <c r="H88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -4066,7 +4068,7 @@
         <v>0</v>
       </c>
       <c r="L88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
         <v>0</v>
@@ -4083,7 +4085,7 @@
         <v>1</v>
       </c>
       <c r="D89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E89" t="n">
         <v>0</v>
@@ -4104,10 +4106,10 @@
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
         <v>0</v>
@@ -4121,7 +4123,7 @@
       </c>
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D90" t="n">
         <v>1</v>
@@ -4145,13 +4147,13 @@
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
@@ -4162,37 +4164,37 @@
       </c>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="n">
+        <v>16</v>
+      </c>
+      <c r="D91" t="n">
+        <v>1</v>
+      </c>
+      <c r="E91" t="n">
         <v>3</v>
       </c>
-      <c r="D91" t="n">
-        <v>16</v>
-      </c>
-      <c r="E91" t="n">
-        <v>1</v>
-      </c>
       <c r="F91" t="n">
+        <v>10</v>
+      </c>
+      <c r="G91" t="n">
+        <v>4</v>
+      </c>
+      <c r="H91" t="n">
+        <v>9</v>
+      </c>
+      <c r="I91" t="n">
         <v>3</v>
       </c>
-      <c r="G91" t="n">
-        <v>10</v>
-      </c>
-      <c r="H91" t="n">
-        <v>4</v>
-      </c>
-      <c r="I91" t="n">
-        <v>9</v>
-      </c>
       <c r="J91" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K91" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="L91" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="M91" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
@@ -4201,9 +4203,11 @@
           <t>電子零組件業右下</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr"/>
+      <c r="B92" t="n">
+        <v>0</v>
+      </c>
       <c r="C92" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D92" t="n">
         <v>1</v>
@@ -4215,7 +4219,7 @@
         <v>1</v>
       </c>
       <c r="G92" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H92" t="n">
         <v>1</v>
@@ -4224,16 +4228,16 @@
         <v>1</v>
       </c>
       <c r="J92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K92" t="n">
         <v>0</v>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M92" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="93">
@@ -4244,10 +4248,10 @@
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D93" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E93" t="n">
         <v>1</v>
@@ -4256,16 +4260,16 @@
         <v>1</v>
       </c>
       <c r="G93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I93" t="n">
         <v>1</v>
       </c>
       <c r="J93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K93" t="n">
         <v>0</v>
@@ -4274,7 +4278,7 @@
         <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">
@@ -4285,25 +4289,25 @@
       </c>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="n">
+        <v>0</v>
+      </c>
+      <c r="D94" t="n">
+        <v>0</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" t="n">
         <v>3</v>
       </c>
-      <c r="D94" t="n">
-        <v>0</v>
-      </c>
-      <c r="E94" t="n">
-        <v>0</v>
-      </c>
-      <c r="F94" t="n">
-        <v>0</v>
-      </c>
       <c r="G94" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H94" t="n">
         <v>0</v>
       </c>
       <c r="I94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J94" t="n">
         <v>1</v>
@@ -4315,7 +4319,7 @@
         <v>1</v>
       </c>
       <c r="M94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -4324,38 +4328,36 @@
           <t>電機機械右下</t>
         </is>
       </c>
-      <c r="B95" t="n">
-        <v>0</v>
-      </c>
+      <c r="B95" t="inlineStr"/>
       <c r="C95" t="n">
         <v>0</v>
       </c>
       <c r="D95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E95" t="n">
         <v>1</v>
       </c>
       <c r="F95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G95" t="n">
         <v>2</v>
       </c>
       <c r="H95" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I95" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J95" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K95" t="n">
         <v>1</v>
       </c>
       <c r="L95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
         <v>0</v>
@@ -4369,19 +4371,19 @@
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E96" t="n">
         <v>0</v>
       </c>
       <c r="F96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -4390,13 +4392,13 @@
         <v>0</v>
       </c>
       <c r="J96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K96" t="n">
         <v>0</v>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M96" t="n">
         <v>1</v>
@@ -4410,7 +4412,7 @@
       </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D97" t="n">
         <v>1</v>
@@ -4419,28 +4421,28 @@
         <v>1</v>
       </c>
       <c r="F97" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G97" t="n">
+        <v>1</v>
+      </c>
+      <c r="H97" t="n">
         <v>5</v>
       </c>
-      <c r="H97" t="n">
-        <v>1</v>
-      </c>
       <c r="I97" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J97" t="n">
+        <v>2</v>
+      </c>
+      <c r="K97" t="n">
+        <v>8</v>
+      </c>
+      <c r="L97" t="n">
         <v>3</v>
       </c>
-      <c r="K97" t="n">
-        <v>2</v>
-      </c>
-      <c r="L97" t="n">
-        <v>8</v>
-      </c>
       <c r="M97" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -4463,25 +4465,25 @@
         <v>0</v>
       </c>
       <c r="G98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I98" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J98" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M98" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -4492,37 +4494,37 @@
       </c>
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D99" t="n">
         <v>0</v>
       </c>
       <c r="E99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F99" t="n">
         <v>1</v>
       </c>
       <c r="G99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H99" t="n">
         <v>1</v>
       </c>
       <c r="I99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M99" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100">
@@ -4539,10 +4541,10 @@
         <v>0</v>
       </c>
       <c r="E100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -4572,7 +4574,9 @@
           <t>食品工業右下</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr"/>
+      <c r="B101" t="n">
+        <v>0</v>
+      </c>
       <c r="C101" t="n">
         <v>0</v>
       </c>
@@ -4615,10 +4619,10 @@
       </c>
       <c r="B102" t="inlineStr"/>
       <c r="C102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E102" t="n">
         <v>1</v>
@@ -4627,7 +4631,7 @@
         <v>1</v>
       </c>
       <c r="G102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H102" t="n">
         <v>0</v>
@@ -4642,10 +4646,10 @@
         <v>0</v>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M102" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Result/analyze_1.xlsx
+++ b/Result/analyze_1.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M102"/>
+  <dimension ref="A1:M101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,57 +441,57 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-19</t>
         </is>
       </c>
     </row>
@@ -503,34 +503,34 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
+        <v>7</v>
+      </c>
+      <c r="D2" t="n">
         <v>4</v>
       </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J2" t="n">
         <v>3</v>
       </c>
       <c r="K2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M2" t="n">
         <v>1</v>
@@ -544,19 +544,19 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>1</v>
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M3" t="n">
         <v>1</v>
@@ -588,34 +588,34 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -626,31 +626,31 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -665,32 +665,30 @@
           <t>其他右下</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>0</v>
-      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -699,7 +697,7 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -710,28 +708,28 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -740,7 +738,7 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -751,37 +749,37 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
+        <v>4</v>
+      </c>
+      <c r="E8" t="n">
         <v>3</v>
       </c>
-      <c r="E8" t="n">
-        <v>1</v>
-      </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -790,41 +788,39 @@
           <t>其他電子業右下</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0</v>
-      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -835,16 +831,16 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -853,13 +849,13 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L10" t="n">
         <v>1</v>
@@ -876,37 +872,37 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" t="n">
         <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -915,9 +911,11 @@
           <t>化學工業右下</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
+      <c r="B12" t="n">
+        <v>0</v>
+      </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -958,37 +956,37 @@
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
         <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>1</v>
       </c>
       <c r="M13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -999,34 +997,34 @@
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I14" t="n">
         <v>8</v>
       </c>
       <c r="J14" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M14" t="n">
         <v>3</v>
@@ -1038,41 +1036,39 @@
           <t>半導體業右下</t>
         </is>
       </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
+      <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
         <v>3</v>
       </c>
-      <c r="D15" t="n">
-        <v>1</v>
-      </c>
-      <c r="E15" t="n">
-        <v>2</v>
-      </c>
-      <c r="F15" t="n">
-        <v>12</v>
-      </c>
-      <c r="G15" t="n">
+      <c r="I15" t="n">
+        <v>7</v>
+      </c>
+      <c r="J15" t="n">
         <v>4</v>
       </c>
-      <c r="H15" t="n">
-        <v>2</v>
-      </c>
-      <c r="I15" t="n">
-        <v>3</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1</v>
-      </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="M15" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1086,34 +1082,34 @@
         <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I16" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M16" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1124,7 +1120,7 @@
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -1136,10 +1132,10 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -1183,7 +1179,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1192,10 +1188,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1212,16 +1208,16 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -1233,10 +1229,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1250,10 +1246,10 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -1262,13 +1258,13 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -1277,7 +1273,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1291,16 +1287,16 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -1309,10 +1305,10 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -1329,7 +1325,7 @@
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
@@ -1338,7 +1334,7 @@
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1356,7 +1352,7 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -1382,7 +1378,7 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -1397,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -1409,30 +1405,32 @@
           <t>建材營造右下</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="n">
+        <v>0</v>
+      </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -1452,7 +1450,7 @@
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
@@ -1464,7 +1462,7 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
         <v>2</v>
@@ -1473,7 +1471,7 @@
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -1482,7 +1480,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1493,13 +1491,13 @@
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -1508,10 +1506,10 @@
         <v>1</v>
       </c>
       <c r="H26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -1520,10 +1518,10 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1534,16 +1532,16 @@
       </c>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1555,10 +1553,10 @@
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -1578,7 +1576,7 @@
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -1593,7 +1591,7 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1628,7 +1626,7 @@
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -1643,7 +1641,7 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
@@ -1669,7 +1667,7 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -1678,13 +1676,13 @@
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -1701,10 +1699,10 @@
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -1713,22 +1711,22 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31" t="n">
         <v>1</v>
       </c>
       <c r="J31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -1816,7 +1814,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>水泥工業右上</t>
+          <t>水泥工業右下</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -1845,7 +1843,7 @@
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -1857,7 +1855,7 @@
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>水泥工業右下</t>
+          <t>水泥工業平</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -1871,7 +1869,7 @@
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1898,7 +1896,7 @@
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>水泥工業平</t>
+          <t>汽車工業右上</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -1906,7 +1904,7 @@
         <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
@@ -1918,7 +1916,7 @@
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
@@ -1927,10 +1925,10 @@
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
@@ -1939,12 +1937,12 @@
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>汽車工業右上</t>
+          <t>汽車工業右下</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
@@ -1953,54 +1951,54 @@
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>汽車工業右下</t>
+          <t>汽車工業平</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D38" t="n">
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -2015,13 +2013,13 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>汽車工業平</t>
+          <t>油電燃氣業右下</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -2044,7 +2042,7 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2053,16 +2051,16 @@
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>油電燃氣業右上</t>
+          <t>油電燃氣業平</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -2103,7 +2101,7 @@
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>油電燃氣業右下</t>
+          <t>玻璃陶瓷右上</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -2114,7 +2112,7 @@
         <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
@@ -2144,7 +2142,7 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>油電燃氣業平</t>
+          <t>玻璃陶瓷右下</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -2185,7 +2183,7 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>玻璃陶瓷右上</t>
+          <t>玻璃陶瓷平</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -2199,7 +2197,7 @@
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -2211,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -2226,7 +2224,7 @@
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>玻璃陶瓷右下</t>
+          <t>生技醫療業右上</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -2234,25 +2232,25 @@
         <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
@@ -2261,13 +2259,13 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>玻璃陶瓷平</t>
+          <t>生技醫療業右下</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -2275,10 +2273,10 @@
         <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
@@ -2290,13 +2288,13 @@
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
@@ -2308,39 +2306,39 @@
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>生技醫療業右上</t>
+          <t>生技醫療業平</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D46" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E46" t="n">
         <v>1</v>
       </c>
       <c r="F46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K46" t="n">
         <v>1</v>
       </c>
       <c r="L46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -2349,26 +2347,24 @@
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>生技醫療業右下</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
-        <v>0</v>
-      </c>
+          <t>紡織纖維右上</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr"/>
       <c r="C47" t="n">
         <v>2</v>
       </c>
       <c r="D47" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
@@ -2377,7 +2373,7 @@
         <v>1</v>
       </c>
       <c r="J47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
@@ -2392,7 +2388,7 @@
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>生技醫療業平</t>
+          <t>紡織纖維右下</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -2403,25 +2399,25 @@
         <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F48" t="n">
         <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
@@ -2433,7 +2429,7 @@
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>紡織纖維右上</t>
+          <t>紡織纖維平</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -2447,13 +2443,13 @@
         <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I49" t="n">
         <v>0</v>
@@ -2474,7 +2470,7 @@
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>紡織纖維右下</t>
+          <t>綠能環保右上</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -2497,13 +2493,13 @@
         <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
@@ -2515,7 +2511,7 @@
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>紡織纖維平</t>
+          <t>綠能環保右下</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -2532,7 +2528,7 @@
         <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
@@ -2556,12 +2552,12 @@
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>綠能環保右上</t>
+          <t>綠能環保平</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D52" t="n">
         <v>0</v>
@@ -2570,7 +2566,7 @@
         <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -2585,7 +2581,7 @@
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
@@ -2597,24 +2593,24 @@
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>綠能環保右下</t>
+          <t>航運業右上</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E53" t="n">
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
@@ -2638,7 +2634,7 @@
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>綠能環保平</t>
+          <t>航運業右下</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
@@ -2646,10 +2642,10 @@
         <v>1</v>
       </c>
       <c r="D54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F54" t="n">
         <v>0</v>
@@ -2667,7 +2663,7 @@
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
@@ -2679,12 +2675,12 @@
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>航運業右上</t>
+          <t>航運業平</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D55" t="n">
         <v>0</v>
@@ -2693,25 +2689,25 @@
         <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G55" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
         <v>0</v>
@@ -2720,7 +2716,7 @@
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>航運業右下</t>
+          <t>觀光事業右上</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
@@ -2731,7 +2727,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -2740,10 +2736,10 @@
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -2761,12 +2757,14 @@
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>航運業平</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr"/>
+          <t>觀光事業右下</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>0</v>
+      </c>
       <c r="C57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D57" t="n">
         <v>0</v>
@@ -2802,7 +2800,7 @@
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>觀光事業右上</t>
+          <t>觀光事業平</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
@@ -2828,7 +2826,7 @@
         <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K58" t="n">
         <v>0</v>
@@ -2843,7 +2841,7 @@
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>觀光事業右下</t>
+          <t>貿易百貨右上</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -2857,13 +2855,13 @@
         <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I59" t="n">
         <v>0</v>
@@ -2884,7 +2882,7 @@
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>觀光事業平</t>
+          <t>貿易百貨右下</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -2904,13 +2902,13 @@
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I60" t="n">
         <v>0</v>
       </c>
       <c r="J60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K60" t="n">
         <v>0</v>
@@ -2925,7 +2923,7 @@
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>貿易百貨右上</t>
+          <t>貿易百貨平</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
@@ -2945,13 +2943,13 @@
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I61" t="n">
         <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K61" t="n">
         <v>0</v>
@@ -2966,7 +2964,7 @@
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>貿易百貨右下</t>
+          <t>資訊服務業右上</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
@@ -2974,13 +2972,13 @@
         <v>0</v>
       </c>
       <c r="D62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E62" t="n">
         <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -3007,7 +3005,7 @@
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>資訊服務業右上</t>
+          <t>資訊服務業右下</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
@@ -3021,7 +3019,7 @@
         <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -3030,13 +3028,13 @@
         <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
@@ -3048,17 +3046,15 @@
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>資訊服務業右下</t>
-        </is>
-      </c>
-      <c r="B64" t="n">
-        <v>0</v>
-      </c>
+          <t>資訊服務業平</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr"/>
       <c r="C64" t="n">
         <v>0</v>
       </c>
       <c r="D64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E64" t="n">
         <v>0</v>
@@ -3067,7 +3063,7 @@
         <v>0</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H64" t="n">
         <v>0</v>
@@ -3079,7 +3075,7 @@
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
@@ -3091,7 +3087,7 @@
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>資訊服務業平</t>
+          <t>農業科技業右上</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
@@ -3120,10 +3116,10 @@
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
         <v>0</v>
@@ -3132,10 +3128,12 @@
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>農業科技業右上</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr"/>
+          <t>農業科技業右下</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>0</v>
+      </c>
       <c r="C66" t="n">
         <v>0</v>
       </c>
@@ -3173,30 +3171,30 @@
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>農業科技業右下</t>
+          <t>通信網路業右上</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E67" t="n">
         <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -3208,18 +3206,20 @@
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>通信網路業右上</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr"/>
+          <t>通信網路業右下</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>0</v>
+      </c>
       <c r="C68" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D68" t="n">
         <v>0</v>
@@ -3228,66 +3228,66 @@
         <v>1</v>
       </c>
       <c r="F68" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H68" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L68" t="n">
         <v>1</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>通信網路業右下</t>
+          <t>通信網路業平</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D69" t="n">
         <v>1</v>
       </c>
       <c r="E69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F69" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G69" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
         <v>0</v>
@@ -3296,12 +3296,12 @@
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>通信網路業平</t>
+          <t>造紙工業右下</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D70" t="n">
         <v>0</v>
@@ -3310,7 +3310,7 @@
         <v>0</v>
       </c>
       <c r="F70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -3319,16 +3319,16 @@
         <v>0</v>
       </c>
       <c r="I70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
         <v>0</v>
@@ -3337,7 +3337,7 @@
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>造紙工業右下</t>
+          <t>造紙工業平</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
@@ -3378,7 +3378,7 @@
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>造紙工業平</t>
+          <t>運動休閒右上</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
@@ -3407,7 +3407,7 @@
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L72" t="n">
         <v>0</v>
@@ -3419,7 +3419,7 @@
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>運動休閒右上</t>
+          <t>運動休閒右下</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
@@ -3436,7 +3436,7 @@
         <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
@@ -3454,13 +3454,13 @@
         <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>運動休閒右下</t>
+          <t>運動休閒平</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
@@ -3471,7 +3471,7 @@
         <v>0</v>
       </c>
       <c r="E74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F74" t="n">
         <v>0</v>
@@ -3492,7 +3492,7 @@
         <v>0</v>
       </c>
       <c r="L74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
         <v>0</v>
@@ -3501,7 +3501,7 @@
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>運動休閒平</t>
+          <t>金融保險右上</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
@@ -3527,7 +3527,7 @@
         <v>0</v>
       </c>
       <c r="J75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K75" t="n">
         <v>0</v>
@@ -3542,7 +3542,7 @@
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>金融保險右上</t>
+          <t>金融保險右下</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
@@ -3583,7 +3583,7 @@
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>金融保險右下</t>
+          <t>金融保險平</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
@@ -3624,7 +3624,7 @@
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>金融保險平</t>
+          <t>金融業右上</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
@@ -3632,7 +3632,7 @@
         <v>0</v>
       </c>
       <c r="D78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E78" t="n">
         <v>0</v>
@@ -3665,7 +3665,7 @@
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>金融業右上</t>
+          <t>金融業右下</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
@@ -3706,7 +3706,7 @@
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>金融業右下</t>
+          <t>金融業平</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
@@ -3747,7 +3747,7 @@
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>金融業平</t>
+          <t>鋼鐵工業右上</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
@@ -3788,7 +3788,7 @@
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業右上</t>
+          <t>鋼鐵工業右下</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
@@ -3799,7 +3799,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -3808,7 +3808,7 @@
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I82" t="n">
         <v>0</v>
@@ -3829,12 +3829,10 @@
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業右下</t>
-        </is>
-      </c>
-      <c r="B83" t="n">
-        <v>0</v>
-      </c>
+          <t>鋼鐵工業平</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr"/>
       <c r="C83" t="n">
         <v>0</v>
       </c>
@@ -3866,13 +3864,13 @@
         <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業平</t>
+          <t>電器電纜右上</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
@@ -3889,7 +3887,7 @@
         <v>0</v>
       </c>
       <c r="G84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H84" t="n">
         <v>0</v>
@@ -3913,7 +3911,7 @@
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>電器電纜右上</t>
+          <t>電器電纜右下</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
@@ -3930,7 +3928,7 @@
         <v>0</v>
       </c>
       <c r="G85" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H85" t="n">
         <v>0</v>
@@ -3954,7 +3952,7 @@
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>電器電纜右下</t>
+          <t>電器電纜平</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
@@ -3971,7 +3969,7 @@
         <v>0</v>
       </c>
       <c r="G86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H86" t="n">
         <v>0</v>
@@ -3995,12 +3993,12 @@
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>電器電纜平</t>
+          <t>電子通路業右上</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D87" t="n">
         <v>0</v>
@@ -4009,7 +4007,7 @@
         <v>0</v>
       </c>
       <c r="F87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G87" t="n">
         <v>1</v>
@@ -4021,13 +4019,13 @@
         <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K87" t="n">
         <v>0</v>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M87" t="n">
         <v>0</v>
@@ -4036,27 +4034,29 @@
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>電子通路業右上</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr"/>
+          <t>電子通路業右下</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>0</v>
+      </c>
       <c r="C88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D88" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
       </c>
       <c r="H88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I88" t="n">
         <v>0</v>
@@ -4068,7 +4068,7 @@
         <v>0</v>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M88" t="n">
         <v>0</v>
@@ -4077,12 +4077,12 @@
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>電子通路業右下</t>
+          <t>電子通路業平</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D89" t="n">
         <v>0</v>
@@ -4100,16 +4100,16 @@
         <v>0</v>
       </c>
       <c r="I89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M89" t="n">
         <v>0</v>
@@ -4118,117 +4118,115 @@
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>電子通路業平</t>
+          <t>電子零組件業右上</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D90" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E90" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F90" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H90" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I90" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J90" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K90" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L90" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業右上</t>
+          <t>電子零組件業右下</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="D91" t="n">
         <v>1</v>
       </c>
       <c r="E91" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" t="n">
+        <v>1</v>
+      </c>
+      <c r="H91" t="n">
+        <v>4</v>
+      </c>
+      <c r="I91" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" t="n">
+        <v>4</v>
+      </c>
+      <c r="K91" t="n">
         <v>3</v>
       </c>
-      <c r="F91" t="n">
-        <v>10</v>
-      </c>
-      <c r="G91" t="n">
-        <v>4</v>
-      </c>
-      <c r="H91" t="n">
-        <v>9</v>
-      </c>
-      <c r="I91" t="n">
-        <v>3</v>
-      </c>
-      <c r="J91" t="n">
-        <v>6</v>
-      </c>
-      <c r="K91" t="n">
-        <v>11</v>
-      </c>
       <c r="L91" t="n">
         <v>2</v>
       </c>
       <c r="M91" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業右下</t>
-        </is>
-      </c>
-      <c r="B92" t="n">
-        <v>0</v>
-      </c>
+          <t>電子零組件業平</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr"/>
       <c r="C92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D92" t="n">
         <v>1</v>
       </c>
       <c r="E92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F92" t="n">
         <v>1</v>
       </c>
       <c r="G92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K92" t="n">
         <v>0</v>
@@ -4237,18 +4235,18 @@
         <v>1</v>
       </c>
       <c r="M92" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業平</t>
+          <t>電機機械右上</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D93" t="n">
         <v>1</v>
@@ -4260,19 +4258,19 @@
         <v>1</v>
       </c>
       <c r="G93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L93" t="n">
         <v>0</v>
@@ -4284,21 +4282,23 @@
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>電機機械右上</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr"/>
+          <t>電機機械右下</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>0</v>
+      </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E94" t="n">
         <v>0</v>
       </c>
       <c r="F94" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -4307,16 +4307,16 @@
         <v>0</v>
       </c>
       <c r="I94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
         <v>0</v>
@@ -4325,7 +4325,7 @@
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>電機機械右下</t>
+          <t>電機機械平</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
@@ -4333,66 +4333,66 @@
         <v>0</v>
       </c>
       <c r="D95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E95" t="n">
         <v>1</v>
       </c>
       <c r="F95" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G95" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I95" t="n">
         <v>2</v>
       </c>
       <c r="J95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>電機機械平</t>
+          <t>電腦及週邊設備業右上</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D96" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E96" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F96" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G96" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
       </c>
       <c r="I96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K96" t="n">
         <v>0</v>
@@ -4407,39 +4407,39 @@
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右上</t>
+          <t>電腦及週邊設備業右下</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E97" t="n">
         <v>1</v>
       </c>
       <c r="F97" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H97" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I97" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" t="n">
         <v>3</v>
       </c>
-      <c r="J97" t="n">
-        <v>2</v>
-      </c>
       <c r="K97" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="L97" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
         <v>0</v>
@@ -4448,12 +4448,12 @@
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右下</t>
+          <t>電腦及週邊設備業平</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D98" t="n">
         <v>0</v>
@@ -4462,25 +4462,25 @@
         <v>0</v>
       </c>
       <c r="F98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G98" t="n">
         <v>1</v>
       </c>
       <c r="H98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I98" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J98" t="n">
         <v>1</v>
       </c>
       <c r="K98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L98" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
         <v>0</v>
@@ -4489,7 +4489,7 @@
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業平</t>
+          <t>食品工業右上</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
@@ -4500,10 +4500,10 @@
         <v>0</v>
       </c>
       <c r="E99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -4521,19 +4521,21 @@
         <v>1</v>
       </c>
       <c r="L99" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>食品工業右上</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr"/>
+          <t>食品工業右下</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>0</v>
+      </c>
       <c r="C100" t="n">
         <v>0</v>
       </c>
@@ -4541,13 +4543,13 @@
         <v>0</v>
       </c>
       <c r="E100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F100" t="n">
         <v>0</v>
       </c>
       <c r="G100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H100" t="n">
         <v>0</v>
@@ -4571,12 +4573,10 @@
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>食品工業右下</t>
-        </is>
-      </c>
-      <c r="B101" t="n">
-        <v>0</v>
-      </c>
+          <t>食品工業平</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr"/>
       <c r="C101" t="n">
         <v>0</v>
       </c>
@@ -4590,7 +4590,7 @@
         <v>0</v>
       </c>
       <c r="G101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H101" t="n">
         <v>0</v>
@@ -4609,47 +4609,6 @@
       </c>
       <c r="M101" t="n">
         <v>0</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="1" t="inlineStr">
-        <is>
-          <t>食品工業平</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr"/>
-      <c r="C102" t="n">
-        <v>0</v>
-      </c>
-      <c r="D102" t="n">
-        <v>1</v>
-      </c>
-      <c r="E102" t="n">
-        <v>1</v>
-      </c>
-      <c r="F102" t="n">
-        <v>1</v>
-      </c>
-      <c r="G102" t="n">
-        <v>0</v>
-      </c>
-      <c r="H102" t="n">
-        <v>0</v>
-      </c>
-      <c r="I102" t="n">
-        <v>0</v>
-      </c>
-      <c r="J102" t="n">
-        <v>0</v>
-      </c>
-      <c r="K102" t="n">
-        <v>0</v>
-      </c>
-      <c r="L102" t="n">
-        <v>2</v>
-      </c>
-      <c r="M102" t="n">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Result/analyze_1.xlsx
+++ b/Result/analyze_1.xlsx
@@ -441,57 +441,57 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-09-22</t>
         </is>
       </c>
     </row>
@@ -503,37 +503,37 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" t="n">
         <v>4</v>
-      </c>
-      <c r="E2" t="n">
-        <v>3</v>
-      </c>
-      <c r="F2" t="n">
-        <v>5</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J2" t="n">
-        <v>3</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L2" t="n">
-        <v>3</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -542,12 +542,14 @@
           <t>光電業右下</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -556,25 +558,25 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
         <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K3" t="n">
         <v>2</v>
       </c>
       <c r="L3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -591,7 +593,7 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
         <v>2</v>
@@ -600,22 +602,22 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
         <v>1</v>
       </c>
       <c r="M4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -626,16 +628,16 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -644,10 +646,10 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -656,7 +658,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -670,34 +672,34 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -711,7 +713,7 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -720,10 +722,10 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -738,7 +740,7 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -749,37 +751,37 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="n">
         <v>3</v>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" t="n">
         <v>4</v>
       </c>
-      <c r="E8" t="n">
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>4</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2</v>
+      </c>
+      <c r="M8" t="n">
         <v>3</v>
-      </c>
-      <c r="F8" t="n">
-        <v>2</v>
-      </c>
-      <c r="G8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" t="n">
-        <v>2</v>
-      </c>
-      <c r="J8" t="n">
-        <v>4</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" t="n">
-        <v>4</v>
-      </c>
-      <c r="M8" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -793,19 +795,19 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F9" t="n">
         <v>2</v>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -831,10 +833,10 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -849,16 +851,16 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -872,13 +874,13 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F11" t="n">
         <v>1</v>
@@ -887,22 +889,22 @@
         <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -911,9 +913,7 @@
           <t>化學工業右下</t>
         </is>
       </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
         <v>0</v>
       </c>
@@ -962,10 +962,10 @@
         <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -980,10 +980,10 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -997,37 +997,37 @@
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>4</v>
+      </c>
+      <c r="H14" t="n">
+        <v>8</v>
+      </c>
+      <c r="I14" t="n">
         <v>6</v>
       </c>
-      <c r="E14" t="n">
-        <v>2</v>
-      </c>
-      <c r="F14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>4</v>
-      </c>
-      <c r="I14" t="n">
-        <v>8</v>
-      </c>
       <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>10</v>
+      </c>
+      <c r="L14" t="n">
+        <v>3</v>
+      </c>
+      <c r="M14" t="n">
         <v>5</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" t="n">
-        <v>9</v>
-      </c>
-      <c r="M14" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -1036,39 +1036,41 @@
           <t>半導體業右下</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
+      <c r="B15" t="n">
+        <v>0</v>
+      </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H15" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I15" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K15" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="L15" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="M15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1079,37 +1081,37 @@
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="n">
         <v>8</v>
       </c>
-      <c r="E16" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" t="n">
-        <v>1</v>
-      </c>
-      <c r="G16" t="n">
-        <v>1</v>
-      </c>
       <c r="H16" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I16" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K16" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L16" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -1120,7 +1122,7 @@
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -1176,22 +1178,22 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1211,13 +1213,13 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19" t="n">
         <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -1243,22 +1245,22 @@
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D20" t="n">
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -1302,10 +1304,10 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -1331,10 +1333,10 @@
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1349,10 +1351,10 @@
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -1375,10 +1377,10 @@
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -1405,23 +1407,21 @@
           <t>建材營造右下</t>
         </is>
       </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
+      <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24" t="n">
         <v>1</v>
@@ -1430,7 +1430,7 @@
         <v>1</v>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -1450,7 +1450,7 @@
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
@@ -1462,16 +1462,16 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -1497,31 +1497,31 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1538,10 +1538,10 @@
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1550,10 +1550,10 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -1582,16 +1582,16 @@
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1623,10 +1623,10 @@
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -1655,37 +1655,37 @@
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -1702,25 +1702,25 @@
         <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H31" t="n">
         <v>1</v>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -1866,10 +1866,10 @@
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1901,10 +1901,10 @@
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
@@ -1913,22 +1913,22 @@
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
@@ -1969,10 +1969,10 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -1983,22 +1983,22 @@
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F38" t="n">
         <v>1</v>
       </c>
       <c r="G38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -2013,7 +2013,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2109,10 +2109,10 @@
         <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
@@ -2229,34 +2229,34 @@
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F44" t="n">
         <v>1</v>
       </c>
       <c r="G44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I44" t="n">
         <v>1</v>
       </c>
       <c r="J44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M44" t="n">
         <v>1</v>
@@ -2270,13 +2270,13 @@
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D45" t="n">
         <v>1</v>
       </c>
       <c r="E45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
@@ -2285,22 +2285,22 @@
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J45" t="n">
         <v>1</v>
       </c>
       <c r="K45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -2311,16 +2311,16 @@
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D46" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E46" t="n">
         <v>1</v>
       </c>
       <c r="F46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -2329,13 +2329,13 @@
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J46" t="n">
         <v>1</v>
       </c>
       <c r="K46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
@@ -2352,7 +2352,7 @@
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D47" t="n">
         <v>0</v>
@@ -2367,10 +2367,10 @@
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -2391,7 +2391,9 @@
           <t>紡織纖維右下</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr"/>
+      <c r="B48" t="n">
+        <v>0</v>
+      </c>
       <c r="C48" t="n">
         <v>0</v>
       </c>
@@ -2481,25 +2483,25 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J50" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
@@ -2563,22 +2565,22 @@
         <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F52" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K52" t="n">
         <v>0</v>
@@ -2587,7 +2589,7 @@
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -2601,16 +2603,16 @@
         <v>1</v>
       </c>
       <c r="D53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
@@ -2628,7 +2630,7 @@
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -2642,7 +2644,7 @@
         <v>1</v>
       </c>
       <c r="D54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E54" t="n">
         <v>0</v>
@@ -2724,10 +2726,10 @@
         <v>0</v>
       </c>
       <c r="D56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -2764,7 +2766,7 @@
         <v>0</v>
       </c>
       <c r="C57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D57" t="n">
         <v>0</v>
@@ -2899,16 +2901,16 @@
         <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K60" t="n">
         <v>0</v>
@@ -2940,16 +2942,16 @@
         <v>0</v>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K61" t="n">
         <v>0</v>
@@ -2969,16 +2971,16 @@
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F62" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2996,10 +2998,10 @@
         <v>0</v>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -3019,7 +3021,7 @@
         <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -3051,19 +3053,19 @@
       </c>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H64" t="n">
         <v>0</v>
@@ -3072,10 +3074,10 @@
         <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
@@ -3131,9 +3133,7 @@
           <t>農業科技業右下</t>
         </is>
       </c>
-      <c r="B66" t="n">
-        <v>0</v>
-      </c>
+      <c r="B66" t="inlineStr"/>
       <c r="C66" t="n">
         <v>0</v>
       </c>
@@ -3179,22 +3179,22 @@
         <v>2</v>
       </c>
       <c r="D67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -3219,10 +3219,10 @@
         <v>0</v>
       </c>
       <c r="C68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E68" t="n">
         <v>1</v>
@@ -3231,13 +3231,13 @@
         <v>1</v>
       </c>
       <c r="G68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J68" t="n">
         <v>1</v>
@@ -3260,25 +3260,25 @@
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F69" t="n">
         <v>1</v>
       </c>
       <c r="G69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -3290,7 +3290,7 @@
         <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -3404,16 +3404,16 @@
         <v>0</v>
       </c>
       <c r="J72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L72" t="n">
         <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -3433,10 +3433,10 @@
         <v>0</v>
       </c>
       <c r="F73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
@@ -3451,10 +3451,10 @@
         <v>0</v>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -3468,10 +3468,10 @@
         <v>0</v>
       </c>
       <c r="D74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F74" t="n">
         <v>0</v>
@@ -3545,7 +3545,9 @@
           <t>金融保險右下</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr"/>
+      <c r="B76" t="n">
+        <v>0</v>
+      </c>
       <c r="C76" t="n">
         <v>0</v>
       </c>
@@ -3805,10 +3807,10 @@
         <v>0</v>
       </c>
       <c r="G82" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H82" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I82" t="n">
         <v>0</v>
@@ -3998,37 +4000,37 @@
       </c>
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D87" t="n">
         <v>0</v>
       </c>
       <c r="E87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F87" t="n">
         <v>1</v>
       </c>
       <c r="G87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H87" t="n">
         <v>0</v>
       </c>
       <c r="I87" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J87" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
@@ -4037,9 +4039,7 @@
           <t>電子通路業右下</t>
         </is>
       </c>
-      <c r="B88" t="n">
-        <v>0</v>
-      </c>
+      <c r="B88" t="inlineStr"/>
       <c r="C88" t="n">
         <v>0</v>
       </c>
@@ -4047,10 +4047,10 @@
         <v>0</v>
       </c>
       <c r="E88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -4065,10 +4065,10 @@
         <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
         <v>0</v>
@@ -4097,19 +4097,19 @@
         <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
         <v>0</v>
@@ -4123,37 +4123,37 @@
       </c>
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D90" t="n">
+        <v>5</v>
+      </c>
+      <c r="E90" t="n">
+        <v>10</v>
+      </c>
+      <c r="F90" t="n">
+        <v>1</v>
+      </c>
+      <c r="G90" t="n">
         <v>3</v>
       </c>
-      <c r="E90" t="n">
+      <c r="H90" t="n">
+        <v>2</v>
+      </c>
+      <c r="I90" t="n">
         <v>6</v>
       </c>
-      <c r="F90" t="n">
+      <c r="J90" t="n">
+        <v>4</v>
+      </c>
+      <c r="K90" t="n">
+        <v>7</v>
+      </c>
+      <c r="L90" t="n">
         <v>10</v>
       </c>
-      <c r="G90" t="n">
-        <v>1</v>
-      </c>
-      <c r="H90" t="n">
-        <v>3</v>
-      </c>
-      <c r="I90" t="n">
-        <v>2</v>
-      </c>
-      <c r="J90" t="n">
-        <v>5</v>
-      </c>
-      <c r="K90" t="n">
-        <v>4</v>
-      </c>
-      <c r="L90" t="n">
-        <v>8</v>
-      </c>
       <c r="M90" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="91">
@@ -4167,34 +4167,34 @@
         <v>1</v>
       </c>
       <c r="D91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E91" t="n">
         <v>0</v>
       </c>
       <c r="F91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G91" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H91" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I91" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J91" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K91" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L91" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M91" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
@@ -4208,10 +4208,10 @@
         <v>1</v>
       </c>
       <c r="D92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F92" t="n">
         <v>1</v>
@@ -4223,19 +4223,19 @@
         <v>0</v>
       </c>
       <c r="I92" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J92" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L92" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M92" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="93">
@@ -4246,7 +4246,7 @@
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D93" t="n">
         <v>1</v>
@@ -4258,7 +4258,7 @@
         <v>1</v>
       </c>
       <c r="G93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H93" t="n">
         <v>0</v>
@@ -4267,16 +4267,16 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K93" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M93" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="94">
@@ -4289,16 +4289,16 @@
         <v>0</v>
       </c>
       <c r="C94" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D94" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -4319,7 +4319,7 @@
         <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
@@ -4333,25 +4333,25 @@
         <v>0</v>
       </c>
       <c r="D95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G95" t="n">
         <v>1</v>
       </c>
       <c r="H95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I95" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K95" t="n">
         <v>0</v>
@@ -4360,7 +4360,7 @@
         <v>1</v>
       </c>
       <c r="M95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -4371,37 +4371,37 @@
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D96" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E96" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F96" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>1</v>
+      </c>
+      <c r="I96" t="n">
+        <v>1</v>
+      </c>
+      <c r="J96" t="n">
+        <v>1</v>
+      </c>
+      <c r="K96" t="n">
+        <v>1</v>
+      </c>
+      <c r="L96" t="n">
+        <v>1</v>
+      </c>
+      <c r="M96" t="n">
         <v>4</v>
-      </c>
-      <c r="H96" t="n">
-        <v>0</v>
-      </c>
-      <c r="I96" t="n">
-        <v>1</v>
-      </c>
-      <c r="J96" t="n">
-        <v>0</v>
-      </c>
-      <c r="K96" t="n">
-        <v>0</v>
-      </c>
-      <c r="L96" t="n">
-        <v>1</v>
-      </c>
-      <c r="M96" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="97">
@@ -4410,33 +4410,35 @@
           <t>電腦及週邊設備業右下</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr"/>
+      <c r="B97" t="n">
+        <v>0</v>
+      </c>
       <c r="C97" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D97" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F97" t="n">
         <v>0</v>
       </c>
       <c r="G97" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H97" t="n">
         <v>0</v>
       </c>
       <c r="I97" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J97" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K97" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L97" t="n">
         <v>0</v>
@@ -4453,37 +4455,37 @@
       </c>
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D98" t="n">
         <v>0</v>
       </c>
       <c r="E98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G98" t="n">
         <v>1</v>
       </c>
       <c r="H98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I98" t="n">
         <v>0</v>
       </c>
       <c r="J98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L98" t="n">
         <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="99">
@@ -4509,7 +4511,7 @@
         <v>0</v>
       </c>
       <c r="H99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I99" t="n">
         <v>0</v>
@@ -4518,7 +4520,7 @@
         <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L99" t="n">
         <v>0</v>
@@ -4549,7 +4551,7 @@
         <v>0</v>
       </c>
       <c r="G100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H100" t="n">
         <v>0</v>
@@ -4587,7 +4589,7 @@
         <v>0</v>
       </c>
       <c r="F101" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G101" t="n">
         <v>1</v>
@@ -4599,7 +4601,7 @@
         <v>0</v>
       </c>
       <c r="J101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K101" t="n">
         <v>0</v>

--- a/Result/analyze_1.xlsx
+++ b/Result/analyze_1.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M101"/>
+  <dimension ref="A1:M102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,57 +441,57 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-23</t>
         </is>
       </c>
     </row>
@@ -503,37 +503,37 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L2" t="n">
         <v>4</v>
       </c>
-      <c r="D2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E2" t="n">
-        <v>5</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H2" t="n">
-        <v>2</v>
-      </c>
-      <c r="I2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K2" t="n">
-        <v>3</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1</v>
-      </c>
       <c r="M2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -546,7 +546,7 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -555,25 +555,25 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J3" t="n">
         <v>2</v>
       </c>
       <c r="K3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -590,7 +590,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
         <v>2</v>
@@ -599,16 +599,16 @@
         <v>2</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
         <v>1</v>
@@ -617,7 +617,7 @@
         <v>1</v>
       </c>
       <c r="M4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -628,13 +628,13 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -643,10 +643,10 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -655,10 +655,10 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -669,37 +669,37 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -710,19 +710,19 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -737,7 +737,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M7" t="n">
         <v>1</v>
@@ -751,37 +751,37 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" t="n">
         <v>4</v>
       </c>
-      <c r="D8" t="n">
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>4</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2</v>
+      </c>
+      <c r="L8" t="n">
         <v>3</v>
       </c>
-      <c r="E8" t="n">
-        <v>2</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" t="n">
-        <v>2</v>
-      </c>
-      <c r="I8" t="n">
-        <v>4</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>4</v>
-      </c>
-      <c r="L8" t="n">
-        <v>2</v>
-      </c>
       <c r="M8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -792,19 +792,19 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
         <v>2</v>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -833,7 +833,7 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -848,16 +848,16 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -874,37 +874,37 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -913,7 +913,9 @@
           <t>化學工業右下</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
+      <c r="B12" t="n">
+        <v>0</v>
+      </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
@@ -959,13 +961,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -977,7 +979,7 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
@@ -986,7 +988,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -997,34 +999,34 @@
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G14" t="n">
+        <v>9</v>
+      </c>
+      <c r="H14" t="n">
+        <v>5</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>10</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3</v>
+      </c>
+      <c r="L14" t="n">
         <v>4</v>
-      </c>
-      <c r="H14" t="n">
-        <v>8</v>
-      </c>
-      <c r="I14" t="n">
-        <v>6</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>10</v>
-      </c>
-      <c r="L14" t="n">
-        <v>3</v>
       </c>
       <c r="M14" t="n">
         <v>5</v>
@@ -1040,37 +1042,37 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G15" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I15" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J15" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="K15" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="L15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1081,37 +1083,37 @@
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" t="n">
         <v>7</v>
       </c>
-      <c r="D16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" t="n">
-        <v>1</v>
-      </c>
       <c r="G16" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H16" t="n">
+        <v>6</v>
+      </c>
+      <c r="I16" t="n">
         <v>7</v>
       </c>
-      <c r="I16" t="n">
-        <v>6</v>
-      </c>
       <c r="J16" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K16" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1175,25 +1177,25 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1210,13 +1212,13 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19" t="n">
         <v>1</v>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -1248,16 +1250,16 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -1301,10 +1303,10 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1330,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -1348,10 +1350,10 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -1374,10 +1376,10 @@
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1407,18 +1409,20 @@
           <t>建材營造右下</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="n">
+        <v>0</v>
+      </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
@@ -1427,7 +1431,7 @@
         <v>1</v>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1459,16 +1463,16 @@
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1494,31 +1498,31 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -1535,10 +1539,10 @@
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -1547,10 +1551,10 @@
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1576,7 +1580,7 @@
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -1585,10 +1589,10 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -1620,10 +1624,10 @@
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1644,7 +1648,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -1658,34 +1662,34 @@
         <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -1696,28 +1700,28 @@
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G31" t="n">
         <v>1</v>
       </c>
       <c r="H31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -1863,10 +1867,10 @@
         <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
@@ -1901,7 +1905,7 @@
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
@@ -1910,22 +1914,22 @@
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -1954,7 +1958,7 @@
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -1966,10 +1970,10 @@
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
@@ -1983,19 +1987,19 @@
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E38" t="n">
         <v>1</v>
       </c>
       <c r="F38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -2010,16 +2014,16 @@
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>油電燃氣業右下</t>
+          <t>油電燃氣業右上</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -2060,7 +2064,7 @@
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>油電燃氣業平</t>
+          <t>油電燃氣業右下</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -2101,7 +2105,7 @@
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>玻璃陶瓷右上</t>
+          <t>油電燃氣業平</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -2109,7 +2113,7 @@
         <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
@@ -2142,12 +2146,12 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>玻璃陶瓷右下</t>
+          <t>玻璃陶瓷右上</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D42" t="n">
         <v>0</v>
@@ -2183,7 +2187,7 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>玻璃陶瓷平</t>
+          <t>玻璃陶瓷右下</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -2224,30 +2228,30 @@
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>生技醫療業右上</t>
+          <t>玻璃陶瓷平</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -2256,48 +2260,48 @@
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>生技醫療業右下</t>
+          <t>生技醫療業右上</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D45" t="n">
         <v>1</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M45" t="n">
         <v>1</v>
@@ -2306,56 +2310,58 @@
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>生技醫療業平</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr"/>
+          <t>生技醫療業右下</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>0</v>
+      </c>
       <c r="C46" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I46" t="n">
         <v>1</v>
       </c>
       <c r="J46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>紡織纖維右上</t>
+          <t>生技醫療業平</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E47" t="n">
         <v>0</v>
@@ -2370,7 +2376,7 @@
         <v>1</v>
       </c>
       <c r="I47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -2388,12 +2394,10 @@
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>紡織纖維右下</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>0</v>
-      </c>
+          <t>紡織纖維右上</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
       <c r="C48" t="n">
         <v>0</v>
       </c>
@@ -2407,7 +2411,7 @@
         <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
@@ -2431,7 +2435,7 @@
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>紡織纖維平</t>
+          <t>紡織纖維右下</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -2472,7 +2476,7 @@
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>綠能環保右上</t>
+          <t>紡織纖維平</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -2483,7 +2487,7 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -2492,10 +2496,10 @@
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -2513,7 +2517,7 @@
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>綠能環保右下</t>
+          <t>綠能環保右上</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -2521,7 +2525,7 @@
         <v>0</v>
       </c>
       <c r="D51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E51" t="n">
         <v>0</v>
@@ -2530,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I51" t="n">
         <v>0</v>
@@ -2554,7 +2558,7 @@
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>綠能環保平</t>
+          <t>綠能環保右下</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -2565,7 +2569,7 @@
         <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F52" t="n">
         <v>0</v>
@@ -2574,13 +2578,13 @@
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K52" t="n">
         <v>0</v>
@@ -2589,13 +2593,13 @@
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>航運業右上</t>
+          <t>綠能環保平</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
@@ -2603,22 +2607,22 @@
         <v>1</v>
       </c>
       <c r="D53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -2627,27 +2631,27 @@
         <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>航運業右下</t>
+          <t>航運業右上</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F54" t="n">
         <v>0</v>
@@ -2668,7 +2672,7 @@
         <v>0</v>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M54" t="n">
         <v>0</v>
@@ -2677,7 +2681,7 @@
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>航運業平</t>
+          <t>航運業右下</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
@@ -2718,7 +2722,7 @@
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>觀光事業右上</t>
+          <t>航運業平</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
@@ -2726,7 +2730,7 @@
         <v>0</v>
       </c>
       <c r="D56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E56" t="n">
         <v>0</v>
@@ -2759,14 +2763,12 @@
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>觀光事業右下</t>
-        </is>
-      </c>
-      <c r="B57" t="n">
-        <v>0</v>
-      </c>
+          <t>觀光事業右上</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr"/>
       <c r="C57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D57" t="n">
         <v>0</v>
@@ -2802,7 +2804,7 @@
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>觀光事業平</t>
+          <t>觀光事業右下</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
@@ -2843,7 +2845,7 @@
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>貿易百貨右上</t>
+          <t>觀光事業平</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -2884,7 +2886,7 @@
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>貿易百貨右下</t>
+          <t>貿易百貨右上</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -2901,13 +2903,13 @@
         <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -2925,7 +2927,7 @@
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>貿易百貨平</t>
+          <t>貿易百貨右下</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
@@ -2939,16 +2941,16 @@
         <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -2960,33 +2962,33 @@
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>資訊服務業右上</t>
+          <t>貿易百貨平</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D62" t="n">
         <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I62" t="n">
         <v>0</v>
@@ -2998,7 +3000,7 @@
         <v>0</v>
       </c>
       <c r="L62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
         <v>0</v>
@@ -3007,7 +3009,7 @@
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>資訊服務業右下</t>
+          <t>資訊服務業右上</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
@@ -3015,7 +3017,7 @@
         <v>0</v>
       </c>
       <c r="D63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E63" t="n">
         <v>0</v>
@@ -3036,7 +3038,7 @@
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
@@ -3048,21 +3050,23 @@
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>資訊服務業平</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr"/>
+          <t>資訊服務業右下</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>0</v>
+      </c>
       <c r="C64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E64" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -3074,7 +3078,7 @@
         <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>
@@ -3089,7 +3093,7 @@
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>農業科技業右上</t>
+          <t>資訊服務業平</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
@@ -3097,10 +3101,10 @@
         <v>0</v>
       </c>
       <c r="D65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -3112,7 +3116,7 @@
         <v>0</v>
       </c>
       <c r="I65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -3130,7 +3134,7 @@
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>農業科技業右下</t>
+          <t>農業科技業右上</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
@@ -3171,27 +3175,27 @@
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>通信網路業右上</t>
+          <t>農業科技業右下</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D67" t="n">
         <v>0</v>
       </c>
       <c r="E67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I67" t="n">
         <v>0</v>
@@ -3203,59 +3207,57 @@
         <v>0</v>
       </c>
       <c r="L67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>通信網路業右下</t>
-        </is>
-      </c>
-      <c r="B68" t="n">
-        <v>0</v>
-      </c>
+          <t>通信網路業右上</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr"/>
       <c r="C68" t="n">
         <v>0</v>
       </c>
       <c r="D68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E68" t="n">
         <v>1</v>
       </c>
       <c r="F68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L68" t="n">
         <v>1</v>
       </c>
       <c r="M68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>通信網路業平</t>
+          <t>通信網路業右下</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
@@ -3263,13 +3265,13 @@
         <v>1</v>
       </c>
       <c r="D69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E69" t="n">
         <v>1</v>
       </c>
       <c r="F69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -3278,25 +3280,25 @@
         <v>1</v>
       </c>
       <c r="I69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>造紙工業右下</t>
+          <t>通信網路業平</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
@@ -3304,16 +3306,16 @@
         <v>0</v>
       </c>
       <c r="D70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F70" t="n">
         <v>0</v>
       </c>
       <c r="G70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
@@ -3328,16 +3330,16 @@
         <v>0</v>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>造紙工業平</t>
+          <t>造紙工業右下</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
@@ -3378,7 +3380,7 @@
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>運動休閒右上</t>
+          <t>造紙工業平</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
@@ -3404,7 +3406,7 @@
         <v>0</v>
       </c>
       <c r="J72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K72" t="n">
         <v>0</v>
@@ -3413,13 +3415,13 @@
         <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>運動休閒右下</t>
+          <t>運動休閒右上</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
@@ -3433,7 +3435,7 @@
         <v>0</v>
       </c>
       <c r="F73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -3442,7 +3444,7 @@
         <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -3460,7 +3462,7 @@
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>運動休閒平</t>
+          <t>運動休閒右下</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
@@ -3468,10 +3470,10 @@
         <v>0</v>
       </c>
       <c r="D74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F74" t="n">
         <v>0</v>
@@ -3489,7 +3491,7 @@
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L74" t="n">
         <v>0</v>
@@ -3501,12 +3503,12 @@
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>金融保險右上</t>
+          <t>運動休閒平</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D75" t="n">
         <v>0</v>
@@ -3542,12 +3544,10 @@
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>金融保險右下</t>
-        </is>
-      </c>
-      <c r="B76" t="n">
-        <v>0</v>
-      </c>
+          <t>金融保險右上</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr"/>
       <c r="C76" t="n">
         <v>0</v>
       </c>
@@ -3585,7 +3585,7 @@
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>金融保險平</t>
+          <t>金融保險右下</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
@@ -3626,7 +3626,7 @@
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>金融業右上</t>
+          <t>金融保險平</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
@@ -3667,7 +3667,7 @@
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>金融業右下</t>
+          <t>金融業右上</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
@@ -3708,7 +3708,7 @@
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>金融業平</t>
+          <t>金融業右下</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
@@ -3749,7 +3749,7 @@
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業右上</t>
+          <t>金融業平</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
@@ -3790,7 +3790,7 @@
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業右下</t>
+          <t>鋼鐵工業右上</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
@@ -3807,7 +3807,7 @@
         <v>0</v>
       </c>
       <c r="G82" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H82" t="n">
         <v>0</v>
@@ -3825,13 +3825,13 @@
         <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業平</t>
+          <t>鋼鐵工業右下</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
@@ -3845,7 +3845,7 @@
         <v>0</v>
       </c>
       <c r="F83" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -3872,7 +3872,7 @@
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>電器電纜右上</t>
+          <t>鋼鐵工業平</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
@@ -3913,7 +3913,7 @@
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>電器電纜右下</t>
+          <t>電器電纜右上</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
@@ -3954,10 +3954,12 @@
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>電器電纜平</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr"/>
+          <t>電器電纜右下</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>0</v>
+      </c>
       <c r="C86" t="n">
         <v>0</v>
       </c>
@@ -3995,7 +3997,7 @@
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>電子通路業右上</t>
+          <t>電器電纜平</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
@@ -4006,10 +4008,10 @@
         <v>0</v>
       </c>
       <c r="E87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -4018,25 +4020,25 @@
         <v>0</v>
       </c>
       <c r="I87" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L87" t="n">
         <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>電子通路業右下</t>
+          <t>電子通路業右上</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
@@ -4044,7 +4046,7 @@
         <v>0</v>
       </c>
       <c r="D88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E88" t="n">
         <v>1</v>
@@ -4056,28 +4058,28 @@
         <v>0</v>
       </c>
       <c r="H88" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I88" t="n">
         <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>電子通路業平</t>
+          <t>電子通路業右下</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
@@ -4085,7 +4087,7 @@
         <v>0</v>
       </c>
       <c r="D89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E89" t="n">
         <v>0</v>
@@ -4097,16 +4099,16 @@
         <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I89" t="n">
         <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L89" t="n">
         <v>0</v>
@@ -4118,94 +4120,96 @@
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業右上</t>
+          <t>電子通路業平</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D90" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E90" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G90" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H90" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I90" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J90" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K90" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L90" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業右下</t>
+          <t>電子零組件業右上</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D91" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E91" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G91" t="n">
+        <v>2</v>
+      </c>
+      <c r="H91" t="n">
+        <v>5</v>
+      </c>
+      <c r="I91" t="n">
         <v>3</v>
       </c>
-      <c r="H91" t="n">
-        <v>0</v>
-      </c>
-      <c r="I91" t="n">
-        <v>2</v>
-      </c>
       <c r="J91" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K91" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="L91" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="M91" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業平</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr"/>
+          <t>電子零組件業右下</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>0</v>
+      </c>
       <c r="C92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D92" t="n">
         <v>0</v>
@@ -4214,85 +4218,83 @@
         <v>1</v>
       </c>
       <c r="F92" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H92" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I92" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J92" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K92" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L92" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M92" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>電機機械右上</t>
+          <t>電子零組件業平</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
       </c>
       <c r="H93" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J93" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K93" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L93" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M93" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>電機機械右下</t>
-        </is>
-      </c>
-      <c r="B94" t="n">
-        <v>0</v>
-      </c>
+          <t>電機機械右上</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr"/>
       <c r="C94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E94" t="n">
         <v>1</v>
@@ -4307,16 +4309,16 @@
         <v>0</v>
       </c>
       <c r="I94" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K94" t="n">
         <v>0</v>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M94" t="n">
         <v>1</v>
@@ -4325,7 +4327,7 @@
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>電機機械平</t>
+          <t>電機機械右下</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
@@ -4339,16 +4341,16 @@
         <v>0</v>
       </c>
       <c r="F95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H95" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -4366,82 +4368,80 @@
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右上</t>
+          <t>電機機械平</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D96" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E96" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F96" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G96" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H96" t="n">
         <v>1</v>
       </c>
       <c r="I96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L96" t="n">
         <v>1</v>
       </c>
       <c r="M96" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右下</t>
-        </is>
-      </c>
-      <c r="B97" t="n">
-        <v>0</v>
-      </c>
+          <t>電腦及週邊設備業右上</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr"/>
       <c r="C97" t="n">
         <v>2</v>
       </c>
       <c r="D97" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E97" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F97" t="n">
         <v>0</v>
       </c>
       <c r="G97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I97" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J97" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M97" t="n">
         <v>0</v>
@@ -4450,30 +4450,32 @@
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業平</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr"/>
+          <t>電腦及週邊設備業右下</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>0</v>
+      </c>
       <c r="C98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D98" t="n">
         <v>0</v>
       </c>
       <c r="E98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F98" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H98" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I98" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -4485,13 +4487,13 @@
         <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>食品工業右上</t>
+          <t>電腦及週邊設備業平</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
@@ -4499,19 +4501,19 @@
         <v>0</v>
       </c>
       <c r="D99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
       </c>
       <c r="H99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I99" t="n">
         <v>0</v>
@@ -4523,21 +4525,19 @@
         <v>0</v>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>食品工業右下</t>
-        </is>
-      </c>
-      <c r="B100" t="n">
-        <v>0</v>
-      </c>
+          <t>食品工業右上</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr"/>
       <c r="C100" t="n">
         <v>0</v>
       </c>
@@ -4575,7 +4575,7 @@
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>食品工業平</t>
+          <t>食品工業右下</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
@@ -4586,13 +4586,13 @@
         <v>0</v>
       </c>
       <c r="E101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F101" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H101" t="n">
         <v>0</v>
@@ -4601,7 +4601,7 @@
         <v>0</v>
       </c>
       <c r="J101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K101" t="n">
         <v>0</v>
@@ -4610,6 +4610,47 @@
         <v>0</v>
       </c>
       <c r="M101" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="inlineStr">
+        <is>
+          <t>食品工業平</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr"/>
+      <c r="C102" t="n">
+        <v>0</v>
+      </c>
+      <c r="D102" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" t="n">
+        <v>1</v>
+      </c>
+      <c r="F102" t="n">
+        <v>1</v>
+      </c>
+      <c r="G102" t="n">
+        <v>0</v>
+      </c>
+      <c r="H102" t="n">
+        <v>0</v>
+      </c>
+      <c r="I102" t="n">
+        <v>1</v>
+      </c>
+      <c r="J102" t="n">
+        <v>0</v>
+      </c>
+      <c r="K102" t="n">
+        <v>0</v>
+      </c>
+      <c r="L102" t="n">
+        <v>0</v>
+      </c>
+      <c r="M102" t="n">
         <v>0</v>
       </c>
     </row>

--- a/Result/analyze_1.xlsx
+++ b/Result/analyze_1.xlsx
@@ -441,57 +441,57 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-24</t>
         </is>
       </c>
     </row>
@@ -503,34 +503,34 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G2" t="n">
         <v>3</v>
       </c>
-      <c r="D2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" t="n">
-        <v>2</v>
-      </c>
       <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
         <v>3</v>
       </c>
-      <c r="I2" t="n">
-        <v>1</v>
-      </c>
       <c r="J2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
         <v>1</v>
@@ -552,25 +552,25 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
         <v>2</v>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -587,7 +587,7 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
         <v>2</v>
@@ -596,25 +596,25 @@
         <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -628,10 +628,10 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -640,10 +640,10 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -652,10 +652,10 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -669,37 +669,37 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -713,13 +713,13 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -734,13 +734,13 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -751,37 +751,37 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" t="n">
+        <v>4</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>4</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" t="n">
         <v>3</v>
       </c>
-      <c r="D8" t="n">
-        <v>2</v>
-      </c>
-      <c r="E8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" t="n">
-        <v>2</v>
-      </c>
-      <c r="H8" t="n">
-        <v>4</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" t="n">
-        <v>4</v>
-      </c>
-      <c r="K8" t="n">
-        <v>2</v>
-      </c>
       <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
         <v>3</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -792,16 +792,16 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
         <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -845,16 +845,16 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -874,34 +874,34 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K11" t="n">
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -958,16 +958,16 @@
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -976,19 +976,19 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -999,37 +999,37 @@
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F14" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G14" t="n">
+        <v>5</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
         <v>9</v>
       </c>
-      <c r="H14" t="n">
+      <c r="J14" t="n">
+        <v>3</v>
+      </c>
+      <c r="K14" t="n">
         <v>5</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>10</v>
-      </c>
-      <c r="K14" t="n">
-        <v>3</v>
       </c>
       <c r="L14" t="n">
         <v>4</v>
       </c>
       <c r="M14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1038,35 +1038,33 @@
           <t>半導體業右下</t>
         </is>
       </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
+      <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F15" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G15" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H15" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="J15" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="K15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
         <v>1</v>
@@ -1089,7 +1087,7 @@
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F16" t="n">
         <v>7</v>
@@ -1098,16 +1096,16 @@
         <v>6</v>
       </c>
       <c r="H16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I16" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="J16" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
         <v>2</v>
@@ -1174,25 +1172,25 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -1209,13 +1207,13 @@
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19" t="n">
         <v>1</v>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -1247,16 +1245,16 @@
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -1300,10 +1298,10 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -1329,10 +1327,10 @@
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -1347,10 +1345,10 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -1373,10 +1371,10 @@
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -1409,17 +1407,15 @@
           <t>建材營造右下</t>
         </is>
       </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
+      <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24" t="n">
         <v>1</v>
@@ -1428,7 +1424,7 @@
         <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -1443,7 +1439,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1460,16 +1456,16 @@
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
@@ -1495,31 +1491,31 @@
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -1536,10 +1532,10 @@
       </c>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -1548,10 +1544,10 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -1580,16 +1576,16 @@
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -1621,10 +1617,10 @@
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -1645,10 +1641,10 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -1659,34 +1655,34 @@
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -1700,25 +1696,25 @@
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F31" t="n">
         <v>1</v>
       </c>
       <c r="G31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1730,7 +1726,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -1864,10 +1860,10 @@
       </c>
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
@@ -1911,22 +1907,22 @@
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -1944,7 +1940,9 @@
           <t>汽車工業右下</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr"/>
+      <c r="B37" t="n">
+        <v>0</v>
+      </c>
       <c r="C37" t="n">
         <v>0</v>
       </c>
@@ -1952,7 +1950,7 @@
         <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
@@ -1967,10 +1965,10 @@
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
@@ -1987,16 +1985,16 @@
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D38" t="n">
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -2011,10 +2009,10 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
@@ -2151,7 +2149,7 @@
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D42" t="n">
         <v>0</v>
@@ -2274,28 +2272,28 @@
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D45" t="n">
         <v>1</v>
       </c>
       <c r="E45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G45" t="n">
         <v>1</v>
       </c>
       <c r="H45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K45" t="n">
         <v>1</v>
@@ -2317,7 +2315,7 @@
         <v>0</v>
       </c>
       <c r="C46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D46" t="n">
         <v>0</v>
@@ -2326,28 +2324,28 @@
         <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H46" t="n">
         <v>1</v>
       </c>
       <c r="I46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46" t="n">
         <v>1</v>
       </c>
       <c r="M46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -2361,7 +2359,7 @@
         <v>1</v>
       </c>
       <c r="D47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E47" t="n">
         <v>0</v>
@@ -2370,13 +2368,13 @@
         <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H47" t="n">
         <v>1</v>
       </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -2388,7 +2386,7 @@
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -2408,10 +2406,10 @@
         <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
@@ -2429,7 +2427,7 @@
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -2438,7 +2436,9 @@
           <t>紡織纖維右下</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr"/>
+      <c r="B49" t="n">
+        <v>0</v>
+      </c>
       <c r="C49" t="n">
         <v>0</v>
       </c>
@@ -2522,22 +2522,22 @@
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E51" t="n">
         <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G51" t="n">
         <v>1</v>
       </c>
       <c r="H51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I51" t="n">
         <v>0</v>
@@ -2552,7 +2552,7 @@
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -2587,7 +2587,7 @@
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
@@ -2604,16 +2604,16 @@
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E53" t="n">
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G53" t="n">
         <v>1</v>
@@ -2622,7 +2622,7 @@
         <v>1</v>
       </c>
       <c r="I53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -2631,7 +2631,7 @@
         <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
         <v>0</v>
@@ -2645,13 +2645,13 @@
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F54" t="n">
         <v>0</v>
@@ -2669,10 +2669,10 @@
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
         <v>0</v>
@@ -2768,7 +2768,7 @@
       </c>
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D57" t="n">
         <v>0</v>
@@ -2938,16 +2938,16 @@
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I61" t="n">
         <v>0</v>
@@ -2959,10 +2959,10 @@
         <v>0</v>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -2979,16 +2979,16 @@
         <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I62" t="n">
         <v>0</v>
@@ -3014,10 +3014,10 @@
       </c>
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D63" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E63" t="n">
         <v>0</v>
@@ -3035,16 +3035,16 @@
         <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -3053,14 +3053,12 @@
           <t>資訊服務業右下</t>
         </is>
       </c>
-      <c r="B64" t="n">
-        <v>0</v>
-      </c>
+      <c r="B64" t="inlineStr"/>
       <c r="C64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E64" t="n">
         <v>0</v>
@@ -3104,7 +3102,7 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -3113,10 +3111,10 @@
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -3221,19 +3219,19 @@
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
@@ -3242,13 +3240,13 @@
         <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
         <v>0</v>
@@ -3268,13 +3266,13 @@
         <v>1</v>
       </c>
       <c r="E69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F69" t="n">
         <v>0</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H69" t="n">
         <v>1</v>
@@ -3289,10 +3287,10 @@
         <v>1</v>
       </c>
       <c r="L69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -3303,19 +3301,19 @@
       </c>
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D70" t="n">
         <v>1</v>
       </c>
       <c r="E70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
@@ -3327,13 +3325,13 @@
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -3441,19 +3439,19 @@
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
         <v>0</v>
@@ -3470,10 +3468,10 @@
         <v>0</v>
       </c>
       <c r="D74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F74" t="n">
         <v>0</v>
@@ -3488,16 +3486,16 @@
         <v>0</v>
       </c>
       <c r="J74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L74" t="n">
         <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -3508,7 +3506,7 @@
       </c>
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D75" t="n">
         <v>0</v>
@@ -3822,10 +3820,10 @@
         <v>0</v>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -3842,10 +3840,10 @@
         <v>0</v>
       </c>
       <c r="E83" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F83" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -3957,9 +3955,7 @@
           <t>電器電纜右下</t>
         </is>
       </c>
-      <c r="B86" t="n">
-        <v>0</v>
-      </c>
+      <c r="B86" t="inlineStr"/>
       <c r="C86" t="n">
         <v>0</v>
       </c>
@@ -4043,37 +4039,37 @@
       </c>
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D88" t="n">
         <v>1</v>
       </c>
       <c r="E88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F88" t="n">
         <v>0</v>
       </c>
       <c r="G88" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H88" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L88" t="n">
         <v>1</v>
       </c>
       <c r="M88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -4084,10 +4080,10 @@
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E89" t="n">
         <v>0</v>
@@ -4102,10 +4098,10 @@
         <v>0</v>
       </c>
       <c r="I89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K89" t="n">
         <v>0</v>
@@ -4134,19 +4130,19 @@
         <v>0</v>
       </c>
       <c r="F90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
       </c>
       <c r="I90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K90" t="n">
         <v>0</v>
@@ -4155,7 +4151,7 @@
         <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
@@ -4166,37 +4162,37 @@
       </c>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D91" t="n">
+        <v>2</v>
+      </c>
+      <c r="E91" t="n">
+        <v>4</v>
+      </c>
+      <c r="F91" t="n">
+        <v>2</v>
+      </c>
+      <c r="G91" t="n">
+        <v>5</v>
+      </c>
+      <c r="H91" t="n">
+        <v>4</v>
+      </c>
+      <c r="I91" t="n">
+        <v>7</v>
+      </c>
+      <c r="J91" t="n">
         <v>11</v>
-      </c>
-      <c r="E91" t="n">
-        <v>2</v>
-      </c>
-      <c r="F91" t="n">
-        <v>2</v>
-      </c>
-      <c r="G91" t="n">
-        <v>2</v>
-      </c>
-      <c r="H91" t="n">
-        <v>5</v>
-      </c>
-      <c r="I91" t="n">
-        <v>3</v>
-      </c>
-      <c r="J91" t="n">
-        <v>6</v>
       </c>
       <c r="K91" t="n">
         <v>9</v>
       </c>
       <c r="L91" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M91" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="92">
@@ -4212,34 +4208,34 @@
         <v>0</v>
       </c>
       <c r="D92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E92" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F92" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" t="n">
         <v>3</v>
-      </c>
-      <c r="G92" t="n">
-        <v>0</v>
       </c>
       <c r="H92" t="n">
         <v>3</v>
       </c>
       <c r="I92" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J92" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K92" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L92" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M92" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -4250,7 +4246,7 @@
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D93" t="n">
         <v>0</v>
@@ -4259,28 +4255,28 @@
         <v>0</v>
       </c>
       <c r="F93" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G93" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H93" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I93" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J93" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K93" t="n">
         <v>5</v>
       </c>
       <c r="L93" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="94">
@@ -4297,7 +4293,7 @@
         <v>1</v>
       </c>
       <c r="E94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F94" t="n">
         <v>0</v>
@@ -4306,19 +4302,19 @@
         <v>0</v>
       </c>
       <c r="H94" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M94" t="n">
         <v>1</v>
@@ -4332,10 +4328,10 @@
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E95" t="n">
         <v>0</v>
@@ -4356,13 +4352,13 @@
         <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
@@ -4373,37 +4369,37 @@
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E96" t="n">
         <v>1</v>
       </c>
       <c r="F96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G96" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I96" t="n">
         <v>0</v>
       </c>
       <c r="J96" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K96" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L96" t="n">
         <v>1</v>
       </c>
       <c r="M96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -4414,37 +4410,37 @@
       </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D97" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E97" t="n">
+        <v>1</v>
+      </c>
+      <c r="F97" t="n">
+        <v>1</v>
+      </c>
+      <c r="G97" t="n">
+        <v>1</v>
+      </c>
+      <c r="H97" t="n">
+        <v>1</v>
+      </c>
+      <c r="I97" t="n">
+        <v>1</v>
+      </c>
+      <c r="J97" t="n">
+        <v>1</v>
+      </c>
+      <c r="K97" t="n">
         <v>4</v>
       </c>
-      <c r="F97" t="n">
-        <v>0</v>
-      </c>
-      <c r="G97" t="n">
-        <v>1</v>
-      </c>
-      <c r="H97" t="n">
-        <v>1</v>
-      </c>
-      <c r="I97" t="n">
-        <v>1</v>
-      </c>
-      <c r="J97" t="n">
-        <v>1</v>
-      </c>
-      <c r="K97" t="n">
-        <v>1</v>
-      </c>
       <c r="L97" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="98">
@@ -4453,29 +4449,27 @@
           <t>電腦及週邊設備業右下</t>
         </is>
       </c>
-      <c r="B98" t="n">
-        <v>0</v>
-      </c>
+      <c r="B98" t="inlineStr"/>
       <c r="C98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D98" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E98" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F98" t="n">
         <v>0</v>
       </c>
       <c r="G98" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H98" t="n">
         <v>2</v>
       </c>
       <c r="I98" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -4484,10 +4478,10 @@
         <v>0</v>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -4498,22 +4492,22 @@
       </c>
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D99" t="n">
         <v>1</v>
       </c>
       <c r="E99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I99" t="n">
         <v>0</v>
@@ -4522,13 +4516,13 @@
         <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L99" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -4583,10 +4577,10 @@
         <v>0</v>
       </c>
       <c r="D101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F101" t="n">
         <v>0</v>
@@ -4624,22 +4618,22 @@
         <v>0</v>
       </c>
       <c r="D102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E102" t="n">
         <v>1</v>
       </c>
       <c r="F102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
       </c>
       <c r="H102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>

--- a/Result/analyze_1.xlsx
+++ b/Result/analyze_1.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M102"/>
+  <dimension ref="A1:M103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,57 +441,57 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-25</t>
         </is>
       </c>
     </row>
@@ -503,31 +503,31 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="n">
         <v>3</v>
       </c>
-      <c r="H2" t="n">
-        <v>1</v>
-      </c>
       <c r="I2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
         <v>1</v>
@@ -542,32 +542,30 @@
           <t>光電業右下</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>0</v>
-      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
         <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -576,7 +574,7 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -593,25 +591,25 @@
         <v>2</v>
       </c>
       <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
         <v>2</v>
       </c>
-      <c r="F4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1</v>
-      </c>
       <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="n">
         <v>2</v>
       </c>
-      <c r="I4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1</v>
-      </c>
       <c r="K4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -628,31 +626,31 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
         <v>2</v>
       </c>
-      <c r="D5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
       <c r="K5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -672,31 +670,31 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -713,10 +711,10 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -731,16 +729,16 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -751,34 +749,34 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
         <v>2</v>
       </c>
-      <c r="D8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" t="n">
-        <v>1</v>
-      </c>
       <c r="F8" t="n">
+        <v>4</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>4</v>
+      </c>
+      <c r="I8" t="n">
         <v>2</v>
       </c>
-      <c r="G8" t="n">
-        <v>4</v>
-      </c>
-      <c r="H8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" t="n">
-        <v>4</v>
-      </c>
       <c r="J8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
         <v>3</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1</v>
       </c>
       <c r="M8" t="n">
         <v>3</v>
@@ -795,10 +793,10 @@
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -842,16 +840,16 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -863,7 +861,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -874,37 +872,37 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
         <v>2</v>
       </c>
-      <c r="D11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>1</v>
-      </c>
       <c r="J11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -958,7 +956,7 @@
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -973,19 +971,19 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -999,34 +997,34 @@
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E14" t="n">
+        <v>7</v>
+      </c>
+      <c r="F14" t="n">
+        <v>5</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>9</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3</v>
+      </c>
+      <c r="J14" t="n">
+        <v>5</v>
+      </c>
+      <c r="K14" t="n">
         <v>4</v>
       </c>
-      <c r="F14" t="n">
-        <v>8</v>
-      </c>
-      <c r="G14" t="n">
-        <v>5</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>9</v>
-      </c>
-      <c r="J14" t="n">
-        <v>3</v>
-      </c>
-      <c r="K14" t="n">
-        <v>5</v>
-      </c>
       <c r="L14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M14" t="n">
         <v>1</v>
@@ -1038,30 +1036,32 @@
           <t>半導體業右下</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
+      <c r="B15" t="n">
+        <v>0</v>
+      </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E15" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F15" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G15" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H15" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="I15" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="J15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
@@ -1070,7 +1070,7 @@
         <v>1</v>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1084,34 +1084,34 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E16" t="n">
         <v>7</v>
       </c>
       <c r="F16" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G16" t="n">
         <v>6</v>
       </c>
       <c r="H16" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I16" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1169,25 +1169,25 @@
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -1204,13 +1204,13 @@
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D19" t="n">
         <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -1248,10 +1248,10 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -1295,10 +1295,10 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
@@ -1342,10 +1342,10 @@
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1368,10 +1368,10 @@
       </c>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -1412,7 +1412,7 @@
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24" t="n">
         <v>1</v>
@@ -1421,7 +1421,7 @@
         <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1436,10 +1436,10 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1453,16 +1453,16 @@
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
         <v>2</v>
       </c>
-      <c r="F25" t="n">
-        <v>0</v>
-      </c>
       <c r="G25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1491,28 +1491,28 @@
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
@@ -1541,10 +1541,10 @@
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1579,10 +1579,10 @@
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1614,10 +1614,10 @@
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -1638,13 +1638,13 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -1655,31 +1655,31 @@
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -1699,19 +1699,19 @@
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E31" t="n">
         <v>1</v>
       </c>
       <c r="F31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M31" t="n">
         <v>1</v>
@@ -1814,7 +1814,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>水泥工業右下</t>
+          <t>水泥工業右上</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -1855,12 +1855,12 @@
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>水泥工業平</t>
+          <t>水泥工業右下</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
@@ -1896,7 +1896,7 @@
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>汽車工業右上</t>
+          <t>水泥工業平</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -1907,7 +1907,7 @@
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
@@ -1916,10 +1916,10 @@
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -1937,35 +1937,33 @@
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>汽車工業右下</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>0</v>
-      </c>
+          <t>汽車工業右上</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
       <c r="C37" t="n">
         <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -1980,18 +1978,18 @@
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>汽車工業平</t>
+          <t>汽車工業右下</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D38" t="n">
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -2003,13 +2001,13 @@
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
@@ -2021,15 +2019,15 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>油電燃氣業右上</t>
+          <t>汽車工業平</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
@@ -2047,7 +2045,7 @@
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -2062,7 +2060,7 @@
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>油電燃氣業右下</t>
+          <t>油電燃氣業右上</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -2103,7 +2101,7 @@
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>油電燃氣業平</t>
+          <t>油電燃氣業右下</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -2144,7 +2142,7 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>玻璃陶瓷右上</t>
+          <t>油電燃氣業平</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -2185,7 +2183,7 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>玻璃陶瓷右下</t>
+          <t>玻璃陶瓷右上</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -2220,13 +2218,13 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>玻璃陶瓷平</t>
+          <t>玻璃陶瓷右下</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -2267,24 +2265,24 @@
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>生技醫療業右上</t>
+          <t>玻璃陶瓷平</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E45" t="n">
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -2293,76 +2291,74 @@
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>生技醫療業右下</t>
-        </is>
-      </c>
-      <c r="B46" t="n">
-        <v>0</v>
-      </c>
+          <t>生技醫療業右上</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D46" t="n">
         <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K46" t="n">
         <v>1</v>
       </c>
       <c r="L46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>生技醫療業平</t>
+          <t>生技醫療業右下</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D47" t="n">
         <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F47" t="n">
         <v>0</v>
@@ -2371,28 +2367,28 @@
         <v>1</v>
       </c>
       <c r="H47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I47" t="n">
         <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>紡織纖維右上</t>
+          <t>生技醫療業平</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -2403,13 +2399,13 @@
         <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F48" t="n">
         <v>1</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
@@ -2424,21 +2420,19 @@
         <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>紡織纖維右下</t>
-        </is>
-      </c>
-      <c r="B49" t="n">
-        <v>0</v>
-      </c>
+          <t>紡織纖維右上</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr"/>
       <c r="C49" t="n">
         <v>0</v>
       </c>
@@ -2467,7 +2461,7 @@
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M49" t="n">
         <v>0</v>
@@ -2476,10 +2470,12 @@
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>紡織纖維平</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr"/>
+          <t>紡織纖維右下</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>0</v>
+      </c>
       <c r="C50" t="n">
         <v>0</v>
       </c>
@@ -2517,12 +2513,12 @@
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>綠能環保右上</t>
+          <t>紡織纖維平</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>
@@ -2531,10 +2527,10 @@
         <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
@@ -2552,13 +2548,13 @@
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>綠能環保右下</t>
+          <t>綠能環保右上</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -2569,10 +2565,10 @@
         <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -2587,10 +2583,10 @@
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M52" t="n">
         <v>0</v>
@@ -2599,12 +2595,14 @@
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>綠能環保平</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr"/>
+          <t>綠能環保右下</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>0</v>
+      </c>
       <c r="C53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D53" t="n">
         <v>0</v>
@@ -2613,13 +2611,13 @@
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I53" t="n">
         <v>0</v>
@@ -2640,24 +2638,24 @@
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>航運業右上</t>
+          <t>綠能環保平</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
@@ -2666,10 +2664,10 @@
         <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
@@ -2681,12 +2679,12 @@
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>航運業右下</t>
+          <t>航運業右上</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D55" t="n">
         <v>0</v>
@@ -2707,7 +2705,7 @@
         <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K55" t="n">
         <v>0</v>
@@ -2722,7 +2720,7 @@
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>航運業平</t>
+          <t>航運業右下</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
@@ -2763,7 +2761,7 @@
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>觀光事業右上</t>
+          <t>航運業平</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
@@ -2804,7 +2802,7 @@
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>觀光事業右下</t>
+          <t>觀光事業右上</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
@@ -2845,10 +2843,12 @@
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>觀光事業平</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr"/>
+          <t>觀光事業右下</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>0</v>
+      </c>
       <c r="C59" t="n">
         <v>0</v>
       </c>
@@ -2886,7 +2886,7 @@
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>貿易百貨右上</t>
+          <t>觀光事業平</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -2927,7 +2927,7 @@
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>貿易百貨右下</t>
+          <t>貿易百貨右上</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
@@ -2938,13 +2938,13 @@
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
       </c>
       <c r="G61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
@@ -2959,7 +2959,7 @@
         <v>0</v>
       </c>
       <c r="L61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
         <v>0</v>
@@ -2968,7 +2968,7 @@
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>貿易百貨平</t>
+          <t>貿易百貨右下</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
@@ -2976,16 +2976,16 @@
         <v>0</v>
       </c>
       <c r="D62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H62" t="n">
         <v>0</v>
@@ -2997,7 +2997,7 @@
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
@@ -3009,21 +3009,21 @@
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>資訊服務業右上</t>
+          <t>貿易百貨平</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E63" t="n">
         <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -3035,7 +3035,7 @@
         <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K63" t="n">
         <v>0</v>
@@ -3044,18 +3044,18 @@
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>資訊服務業右下</t>
+          <t>資訊服務業右上</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D64" t="n">
         <v>0</v>
@@ -3073,7 +3073,7 @@
         <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -3082,7 +3082,7 @@
         <v>0</v>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M64" t="n">
         <v>0</v>
@@ -3091,7 +3091,7 @@
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>資訊服務業平</t>
+          <t>資訊服務業右下</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
@@ -3099,7 +3099,7 @@
         <v>0</v>
       </c>
       <c r="D65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E65" t="n">
         <v>0</v>
@@ -3111,7 +3111,7 @@
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I65" t="n">
         <v>0</v>
@@ -3126,18 +3126,18 @@
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>農業科技業右上</t>
+          <t>資訊服務業平</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D66" t="n">
         <v>0</v>
@@ -3149,7 +3149,7 @@
         <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -3164,7 +3164,7 @@
         <v>0</v>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M66" t="n">
         <v>0</v>
@@ -3173,7 +3173,7 @@
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>農業科技業右下</t>
+          <t>農業科技業右上</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
@@ -3214,21 +3214,21 @@
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>通信網路業右上</t>
+          <t>農業科技業右下</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E68" t="n">
         <v>0</v>
       </c>
       <c r="F68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -3240,10 +3240,10 @@
         <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
@@ -3255,7 +3255,7 @@
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>通信網路業右下</t>
+          <t>通信網路業右上</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
@@ -3263,48 +3263,50 @@
         <v>1</v>
       </c>
       <c r="D69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F69" t="n">
         <v>0</v>
       </c>
       <c r="G69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J69" t="n">
         <v>1</v>
       </c>
       <c r="K69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>通信網路業平</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr"/>
+          <t>通信網路業右下</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>0</v>
+      </c>
       <c r="C70" t="n">
         <v>1</v>
       </c>
       <c r="D70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E70" t="n">
         <v>0</v>
@@ -3313,42 +3315,42 @@
         <v>1</v>
       </c>
       <c r="G70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K70" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>造紙工業右下</t>
+          <t>通信網路業平</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D71" t="n">
         <v>0</v>
       </c>
       <c r="E71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F71" t="n">
         <v>0</v>
@@ -3363,13 +3365,13 @@
         <v>0</v>
       </c>
       <c r="J71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M71" t="n">
         <v>0</v>
@@ -3378,7 +3380,7 @@
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>造紙工業平</t>
+          <t>造紙工業右下</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
@@ -3419,7 +3421,7 @@
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>運動休閒右上</t>
+          <t>造紙工業平</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
@@ -3439,7 +3441,7 @@
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I73" t="n">
         <v>0</v>
@@ -3448,7 +3450,7 @@
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L73" t="n">
         <v>0</v>
@@ -3460,7 +3462,7 @@
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>運動休閒右下</t>
+          <t>運動休閒右上</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
@@ -3468,7 +3470,7 @@
         <v>0</v>
       </c>
       <c r="D74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E74" t="n">
         <v>0</v>
@@ -3477,7 +3479,7 @@
         <v>0</v>
       </c>
       <c r="G74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
@@ -3495,18 +3497,18 @@
         <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>運動休閒平</t>
+          <t>運動休閒右下</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D75" t="n">
         <v>0</v>
@@ -3524,7 +3526,7 @@
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -3533,7 +3535,7 @@
         <v>0</v>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M75" t="n">
         <v>0</v>
@@ -3542,7 +3544,7 @@
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>金融保險右上</t>
+          <t>運動休閒平</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
@@ -3583,7 +3585,7 @@
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>金融保險右下</t>
+          <t>金融保險右上</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
@@ -3624,7 +3626,7 @@
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>金融保險平</t>
+          <t>金融保險右下</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
@@ -3665,7 +3667,7 @@
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>金融業右上</t>
+          <t>金融保險平</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
@@ -3706,7 +3708,7 @@
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>金融業右下</t>
+          <t>金融業右上</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
@@ -3747,7 +3749,7 @@
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>金融業平</t>
+          <t>金融業右下</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
@@ -3788,7 +3790,7 @@
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業右上</t>
+          <t>金融業平</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
@@ -3820,7 +3822,7 @@
         <v>0</v>
       </c>
       <c r="L82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
         <v>0</v>
@@ -3829,7 +3831,7 @@
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業右下</t>
+          <t>鋼鐵工業右上</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
@@ -3840,7 +3842,7 @@
         <v>0</v>
       </c>
       <c r="E83" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F83" t="n">
         <v>0</v>
@@ -3858,19 +3860,19 @@
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L83" t="n">
         <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業平</t>
+          <t>鋼鐵工業右下</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
@@ -3878,7 +3880,7 @@
         <v>0</v>
       </c>
       <c r="D84" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E84" t="n">
         <v>0</v>
@@ -3911,7 +3913,7 @@
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>電器電纜右上</t>
+          <t>鋼鐵工業平</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
@@ -3946,13 +3948,13 @@
         <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>電器電纜右下</t>
+          <t>電器電纜右上</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
@@ -3987,13 +3989,13 @@
         <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>電器電纜平</t>
+          <t>電器電纜右下</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
@@ -4028,21 +4030,21 @@
         <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>電子通路業右上</t>
+          <t>電器電纜平</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E88" t="n">
         <v>0</v>
@@ -4051,31 +4053,31 @@
         <v>0</v>
       </c>
       <c r="G88" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H88" t="n">
         <v>0</v>
       </c>
       <c r="I88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>電子通路業右下</t>
+          <t>電子通路業右上</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
@@ -4089,22 +4091,22 @@
         <v>0</v>
       </c>
       <c r="F89" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L89" t="n">
         <v>0</v>
@@ -4116,7 +4118,7 @@
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>電子通路業平</t>
+          <t>電子通路業右下</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
@@ -4130,16 +4132,16 @@
         <v>0</v>
       </c>
       <c r="F90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
       </c>
       <c r="H90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -4151,88 +4153,86 @@
         <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業右上</t>
+          <t>電子通路業平</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D91" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E91" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F91" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G91" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H91" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I91" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L91" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M91" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業右下</t>
-        </is>
-      </c>
-      <c r="B92" t="n">
-        <v>0</v>
-      </c>
+          <t>電子零組件業右上</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr"/>
       <c r="C92" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D92" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E92" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F92" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G92" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H92" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I92" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J92" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="K92" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L92" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="M92" t="n">
         <v>0</v>
@@ -4241,62 +4241,64 @@
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業平</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr"/>
+          <t>電子零組件業右下</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>0</v>
+      </c>
       <c r="C93" t="n">
         <v>1</v>
       </c>
       <c r="D93" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E93" t="n">
         <v>0</v>
       </c>
       <c r="F93" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G93" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H93" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I93" t="n">
+        <v>1</v>
+      </c>
+      <c r="J93" t="n">
+        <v>2</v>
+      </c>
+      <c r="K93" t="n">
         <v>3</v>
       </c>
-      <c r="J93" t="n">
-        <v>5</v>
-      </c>
-      <c r="K93" t="n">
-        <v>5</v>
-      </c>
       <c r="L93" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M93" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>電機機械右上</t>
+          <t>電子零組件業平</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E94" t="n">
         <v>0</v>
       </c>
       <c r="F94" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -4305,25 +4307,25 @@
         <v>2</v>
       </c>
       <c r="I94" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J94" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K94" t="n">
+        <v>0</v>
+      </c>
+      <c r="L94" t="n">
         <v>2</v>
       </c>
-      <c r="L94" t="n">
-        <v>1</v>
-      </c>
       <c r="M94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>電機機械右下</t>
+          <t>電機機械右上</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
@@ -4334,28 +4336,28 @@
         <v>0</v>
       </c>
       <c r="E95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G95" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I95" t="n">
         <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K95" t="n">
         <v>1</v>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M95" t="n">
         <v>1</v>
@@ -4364,7 +4366,7 @@
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>電機機械平</t>
+          <t>電機機械右下</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
@@ -4372,16 +4374,16 @@
         <v>0</v>
       </c>
       <c r="D96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F96" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -4393,118 +4395,120 @@
         <v>2</v>
       </c>
       <c r="K96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L96" t="n">
         <v>1</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右上</t>
+          <t>電機機械平</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D97" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E97" t="n">
         <v>1</v>
       </c>
       <c r="F97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K97" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L97" t="n">
         <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右下</t>
+          <t>電腦及週邊設備業右上</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D98" t="n">
+        <v>1</v>
+      </c>
+      <c r="E98" t="n">
+        <v>1</v>
+      </c>
+      <c r="F98" t="n">
+        <v>1</v>
+      </c>
+      <c r="G98" t="n">
+        <v>1</v>
+      </c>
+      <c r="H98" t="n">
+        <v>1</v>
+      </c>
+      <c r="I98" t="n">
+        <v>1</v>
+      </c>
+      <c r="J98" t="n">
+        <v>4</v>
+      </c>
+      <c r="K98" t="n">
+        <v>0</v>
+      </c>
+      <c r="L98" t="n">
         <v>2</v>
       </c>
-      <c r="E98" t="n">
-        <v>0</v>
-      </c>
-      <c r="F98" t="n">
-        <v>0</v>
-      </c>
-      <c r="G98" t="n">
+      <c r="M98" t="n">
         <v>2</v>
-      </c>
-      <c r="H98" t="n">
-        <v>2</v>
-      </c>
-      <c r="I98" t="n">
-        <v>0</v>
-      </c>
-      <c r="J98" t="n">
-        <v>0</v>
-      </c>
-      <c r="K98" t="n">
-        <v>0</v>
-      </c>
-      <c r="L98" t="n">
-        <v>1</v>
-      </c>
-      <c r="M98" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業平</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr"/>
+          <t>電腦及週邊設備業右下</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>0</v>
+      </c>
       <c r="C99" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E99" t="n">
         <v>0</v>
       </c>
       <c r="F99" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H99" t="n">
         <v>0</v>
@@ -4516,10 +4520,10 @@
         <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M99" t="n">
         <v>0</v>
@@ -4528,7 +4532,7 @@
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>食品工業右上</t>
+          <t>電腦及週邊設備業平</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
@@ -4542,7 +4546,7 @@
         <v>0</v>
       </c>
       <c r="F100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -4554,10 +4558,10 @@
         <v>0</v>
       </c>
       <c r="J100" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L100" t="n">
         <v>0</v>
@@ -4569,7 +4573,7 @@
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>食品工業右下</t>
+          <t>食品工業右上</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
@@ -4577,7 +4581,7 @@
         <v>0</v>
       </c>
       <c r="D101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E101" t="n">
         <v>0</v>
@@ -4610,7 +4614,7 @@
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>食品工業平</t>
+          <t>食品工業右下</t>
         </is>
       </c>
       <c r="B102" t="inlineStr"/>
@@ -4621,16 +4625,16 @@
         <v>1</v>
       </c>
       <c r="E102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F102" t="n">
         <v>0</v>
       </c>
       <c r="G102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I102" t="n">
         <v>0</v>
@@ -4645,6 +4649,47 @@
         <v>0</v>
       </c>
       <c r="M102" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="inlineStr">
+        <is>
+          <t>食品工業平</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr"/>
+      <c r="C103" t="n">
+        <v>2</v>
+      </c>
+      <c r="D103" t="n">
+        <v>0</v>
+      </c>
+      <c r="E103" t="n">
+        <v>0</v>
+      </c>
+      <c r="F103" t="n">
+        <v>0</v>
+      </c>
+      <c r="G103" t="n">
+        <v>0</v>
+      </c>
+      <c r="H103" t="n">
+        <v>0</v>
+      </c>
+      <c r="I103" t="n">
+        <v>0</v>
+      </c>
+      <c r="J103" t="n">
+        <v>0</v>
+      </c>
+      <c r="K103" t="n">
+        <v>0</v>
+      </c>
+      <c r="L103" t="n">
+        <v>0</v>
+      </c>
+      <c r="M103" t="n">
         <v>0</v>
       </c>
     </row>

--- a/Result/analyze_1.xlsx
+++ b/Result/analyze_1.xlsx
@@ -441,57 +441,57 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-26</t>
         </is>
       </c>
     </row>
@@ -503,28 +503,28 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
         <v>3</v>
       </c>
-      <c r="G2" t="n">
-        <v>1</v>
-      </c>
       <c r="H2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
         <v>1</v>
@@ -533,7 +533,7 @@
         <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -542,27 +542,29 @@
           <t>光電業右下</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -571,7 +573,7 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" t="n">
         <v>1</v>
@@ -585,28 +587,28 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
         <v>2</v>
       </c>
-      <c r="D4" t="n">
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
         <v>2</v>
       </c>
-      <c r="E4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1</v>
-      </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -632,10 +634,10 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -644,10 +646,10 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -656,7 +658,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -667,31 +669,31 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -708,10 +710,10 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -726,19 +728,19 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
         <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -755,31 +757,31 @@
         <v>1</v>
       </c>
       <c r="E8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>4</v>
+      </c>
+      <c r="H8" t="n">
         <v>2</v>
       </c>
-      <c r="F8" t="n">
-        <v>4</v>
-      </c>
-      <c r="G8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" t="n">
-        <v>4</v>
-      </c>
       <c r="I8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
         <v>3</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1</v>
       </c>
       <c r="L8" t="n">
         <v>3</v>
       </c>
       <c r="M8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -790,10 +792,10 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -834,19 +836,19 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -858,7 +860,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
         <v>1</v>
@@ -875,31 +877,31 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" t="n">
         <v>1</v>
@@ -968,19 +970,19 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -997,37 +999,37 @@
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D14" t="n">
+        <v>5</v>
+      </c>
+      <c r="E14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>8</v>
+      </c>
+      <c r="H14" t="n">
+        <v>3</v>
+      </c>
+      <c r="I14" t="n">
         <v>4</v>
       </c>
-      <c r="E14" t="n">
-        <v>7</v>
-      </c>
-      <c r="F14" t="n">
-        <v>5</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>9</v>
-      </c>
-      <c r="I14" t="n">
-        <v>3</v>
-      </c>
       <c r="J14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K14" t="n">
         <v>4</v>
       </c>
       <c r="L14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1040,25 +1042,25 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E15" t="n">
         <v>8</v>
       </c>
       <c r="F15" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G15" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="H15" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="I15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -1067,7 +1069,7 @@
         <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -1081,34 +1083,34 @@
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D16" t="n">
+        <v>9</v>
+      </c>
+      <c r="E16" t="n">
         <v>6</v>
       </c>
-      <c r="E16" t="n">
-        <v>7</v>
-      </c>
       <c r="F16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G16" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H16" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -1166,25 +1168,25 @@
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -1207,7 +1209,7 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -1245,10 +1247,10 @@
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -1295,7 +1297,7 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -1333,16 +1335,16 @@
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
@@ -1368,7 +1370,7 @@
       </c>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
@@ -1409,16 +1411,16 @@
       </c>
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D24" t="n">
         <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1433,10 +1435,10 @@
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -1450,16 +1452,16 @@
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1491,7 +1493,7 @@
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
@@ -1500,16 +1502,16 @@
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1535,13 +1537,13 @@
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1588,7 +1590,7 @@
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -1614,7 +1616,7 @@
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
@@ -1635,16 +1637,16 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -1655,28 +1657,28 @@
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -1685,7 +1687,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -1696,19 +1698,19 @@
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D31" t="n">
         <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -1720,13 +1722,13 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31" t="n">
         <v>1</v>
       </c>
       <c r="M31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -1814,7 +1816,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>水泥工業右上</t>
+          <t>水泥工業右下</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -1855,7 +1857,7 @@
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>水泥工業右下</t>
+          <t>水泥工業平</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -1896,12 +1898,12 @@
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>水泥工業平</t>
+          <t>汽車工業右上</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
@@ -1910,10 +1912,10 @@
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -1937,15 +1939,15 @@
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>汽車工業右上</t>
+          <t>汽車工業右下</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
@@ -1954,10 +1956,10 @@
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
@@ -1978,15 +1980,15 @@
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>汽車工業右下</t>
+          <t>汽車工業平</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
@@ -1995,7 +1997,7 @@
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -2019,15 +2021,15 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>汽車工業平</t>
+          <t>油電燃氣業右上</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
@@ -2045,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -2060,7 +2062,7 @@
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>油電燃氣業右上</t>
+          <t>油電燃氣業右下</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -2101,7 +2103,7 @@
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>油電燃氣業右下</t>
+          <t>油電燃氣業平</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -2142,7 +2144,7 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>油電燃氣業平</t>
+          <t>玻璃陶瓷右上</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -2174,7 +2176,7 @@
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
@@ -2183,7 +2185,7 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>玻璃陶瓷右上</t>
+          <t>玻璃陶瓷右下</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -2218,13 +2220,13 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>玻璃陶瓷右下</t>
+          <t>玻璃陶瓷平</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -2265,7 +2267,7 @@
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>玻璃陶瓷平</t>
+          <t>生技醫療業右上</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -2273,10 +2275,10 @@
         <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
@@ -2285,13 +2287,13 @@
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
@@ -2306,15 +2308,17 @@
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>生技醫療業右上</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr"/>
+          <t>生技醫療業右下</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>0</v>
+      </c>
       <c r="C46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E46" t="n">
         <v>1</v>
@@ -2338,7 +2342,7 @@
         <v>1</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -2347,7 +2351,7 @@
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>生技醫療業右下</t>
+          <t>生技醫療業平</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -2361,10 +2365,10 @@
         <v>1</v>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
@@ -2373,22 +2377,22 @@
         <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>生技醫療業平</t>
+          <t>紡織纖維右上</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -2396,16 +2400,16 @@
         <v>0</v>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
@@ -2417,10 +2421,10 @@
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
         <v>0</v>
@@ -2429,7 +2433,7 @@
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>紡織纖維右上</t>
+          <t>紡織纖維右下</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -2461,7 +2465,7 @@
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
         <v>0</v>
@@ -2470,12 +2474,10 @@
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>紡織纖維右下</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
-        <v>0</v>
-      </c>
+          <t>紡織纖維平</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr"/>
       <c r="C50" t="n">
         <v>0</v>
       </c>
@@ -2513,7 +2515,7 @@
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>紡織纖維平</t>
+          <t>綠能環保右上</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -2521,10 +2523,10 @@
         <v>0</v>
       </c>
       <c r="D51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F51" t="n">
         <v>0</v>
@@ -2542,7 +2544,7 @@
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
@@ -2554,7 +2556,7 @@
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>綠能環保右上</t>
+          <t>綠能環保右下</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -2565,10 +2567,10 @@
         <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -2577,7 +2579,7 @@
         <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -2586,7 +2588,7 @@
         <v>0</v>
       </c>
       <c r="L52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
         <v>0</v>
@@ -2595,23 +2597,21 @@
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>綠能環保右下</t>
-        </is>
-      </c>
-      <c r="B53" t="n">
-        <v>0</v>
-      </c>
+          <t>綠能環保平</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr"/>
       <c r="C53" t="n">
         <v>0</v>
       </c>
       <c r="D53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -2638,7 +2638,7 @@
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>綠能環保平</t>
+          <t>航運業右上</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
@@ -2649,22 +2649,22 @@
         <v>0</v>
       </c>
       <c r="E54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K54" t="n">
         <v>0</v>
@@ -2679,12 +2679,14 @@
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>航運業右上</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr"/>
+          <t>航運業右下</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>0</v>
+      </c>
       <c r="C55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D55" t="n">
         <v>0</v>
@@ -2705,7 +2707,7 @@
         <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K55" t="n">
         <v>0</v>
@@ -2720,7 +2722,7 @@
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>航運業右下</t>
+          <t>航運業平</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
@@ -2761,7 +2763,7 @@
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>航運業平</t>
+          <t>觀光事業右上</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
@@ -2802,7 +2804,7 @@
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>觀光事業右上</t>
+          <t>觀光事業右下</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
@@ -2843,12 +2845,10 @@
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>觀光事業右下</t>
-        </is>
-      </c>
-      <c r="B59" t="n">
-        <v>0</v>
-      </c>
+          <t>觀光事業平</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr"/>
       <c r="C59" t="n">
         <v>0</v>
       </c>
@@ -2886,7 +2886,7 @@
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>觀光事業平</t>
+          <t>貿易百貨右上</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -2927,18 +2927,18 @@
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>貿易百貨右上</t>
+          <t>貿易百貨右下</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D61" t="n">
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
@@ -2953,7 +2953,7 @@
         <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K61" t="n">
         <v>0</v>
@@ -2968,21 +2968,21 @@
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>貿易百貨右下</t>
+          <t>貿易百貨平</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2997,7 +2997,7 @@
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
@@ -3009,7 +3009,7 @@
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>貿易百貨平</t>
+          <t>資訊服務業右上</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
@@ -3017,19 +3017,19 @@
         <v>0</v>
       </c>
       <c r="D63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E63" t="n">
         <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I63" t="n">
         <v>0</v>
@@ -3038,7 +3038,7 @@
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
@@ -3050,10 +3050,12 @@
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>資訊服務業右上</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr"/>
+          <t>資訊服務業右下</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>0</v>
+      </c>
       <c r="C64" t="n">
         <v>0</v>
       </c>
@@ -3073,7 +3075,7 @@
         <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -3091,7 +3093,7 @@
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>資訊服務業右下</t>
+          <t>資訊服務業平</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
@@ -3105,7 +3107,7 @@
         <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -3120,24 +3122,24 @@
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>資訊服務業平</t>
+          <t>農業科技業右上</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D66" t="n">
         <v>0</v>
@@ -3149,7 +3151,7 @@
         <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -3164,7 +3166,7 @@
         <v>0</v>
       </c>
       <c r="L66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
         <v>0</v>
@@ -3173,7 +3175,7 @@
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>農業科技業右上</t>
+          <t>農業科技業右下</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
@@ -3214,7 +3216,7 @@
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>農業科技業右下</t>
+          <t>農業科技業平</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
@@ -3260,13 +3262,13 @@
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F69" t="n">
         <v>0</v>
@@ -3275,13 +3277,13 @@
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K69" t="n">
         <v>0</v>
@@ -3299,17 +3301,15 @@
           <t>通信網路業右下</t>
         </is>
       </c>
-      <c r="B70" t="n">
-        <v>0</v>
-      </c>
+      <c r="B70" t="inlineStr"/>
       <c r="C70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D70" t="n">
         <v>0</v>
       </c>
       <c r="E70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F70" t="n">
         <v>1</v>
@@ -3324,13 +3324,13 @@
         <v>1</v>
       </c>
       <c r="J70" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K70" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
         <v>0</v>
@@ -3344,13 +3344,13 @@
       </c>
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F71" t="n">
         <v>0</v>
@@ -3362,7 +3362,7 @@
         <v>0</v>
       </c>
       <c r="I71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J71" t="n">
         <v>1</v>
@@ -3371,7 +3371,7 @@
         <v>1</v>
       </c>
       <c r="L71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
         <v>0</v>
@@ -3476,19 +3476,19 @@
         <v>0</v>
       </c>
       <c r="F74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K74" t="n">
         <v>0</v>
@@ -3508,7 +3508,7 @@
       </c>
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D75" t="n">
         <v>0</v>
@@ -3523,19 +3523,19 @@
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
         <v>0</v>
@@ -3857,13 +3857,13 @@
         <v>0</v>
       </c>
       <c r="J83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M83" t="n">
         <v>1</v>
@@ -3877,10 +3877,10 @@
       </c>
       <c r="B84" t="inlineStr"/>
       <c r="C84" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D84" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E84" t="n">
         <v>0</v>
@@ -3948,7 +3948,7 @@
         <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -3986,10 +3986,10 @@
         <v>0</v>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -4027,10 +4027,10 @@
         <v>0</v>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M87" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -4068,10 +4068,10 @@
         <v>0</v>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -4082,37 +4082,37 @@
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D89" t="n">
         <v>0</v>
       </c>
       <c r="E89" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F89" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J89" t="n">
         <v>1</v>
       </c>
       <c r="K89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L89" t="n">
         <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
@@ -4135,10 +4135,10 @@
         <v>0</v>
       </c>
       <c r="G90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I90" t="n">
         <v>0</v>
@@ -4167,19 +4167,19 @@
         <v>0</v>
       </c>
       <c r="D91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F91" t="n">
         <v>0</v>
       </c>
       <c r="G91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I91" t="n">
         <v>0</v>
@@ -4188,10 +4188,10 @@
         <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
         <v>0</v>
@@ -4205,37 +4205,37 @@
       </c>
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="n">
+        <v>4</v>
+      </c>
+      <c r="D92" t="n">
         <v>2</v>
       </c>
-      <c r="D92" t="n">
+      <c r="E92" t="n">
+        <v>5</v>
+      </c>
+      <c r="F92" t="n">
         <v>4</v>
       </c>
-      <c r="E92" t="n">
-        <v>2</v>
-      </c>
-      <c r="F92" t="n">
-        <v>6</v>
-      </c>
       <c r="G92" t="n">
+        <v>7</v>
+      </c>
+      <c r="H92" t="n">
+        <v>9</v>
+      </c>
+      <c r="I92" t="n">
+        <v>8</v>
+      </c>
+      <c r="J92" t="n">
         <v>4</v>
       </c>
-      <c r="H92" t="n">
-        <v>7</v>
-      </c>
-      <c r="I92" t="n">
-        <v>10</v>
-      </c>
-      <c r="J92" t="n">
-        <v>9</v>
-      </c>
       <c r="K92" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L92" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="93">
@@ -4248,34 +4248,34 @@
         <v>0</v>
       </c>
       <c r="C93" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D93" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" t="n">
         <v>3</v>
-      </c>
-      <c r="E93" t="n">
-        <v>0</v>
       </c>
       <c r="F93" t="n">
         <v>3</v>
       </c>
       <c r="G93" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H93" t="n">
         <v>2</v>
       </c>
       <c r="I93" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J93" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K93" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
         <v>0</v>
@@ -4295,28 +4295,28 @@
         <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F94" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G94" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H94" t="n">
+        <v>6</v>
+      </c>
+      <c r="I94" t="n">
+        <v>4</v>
+      </c>
+      <c r="J94" t="n">
+        <v>0</v>
+      </c>
+      <c r="K94" t="n">
         <v>2</v>
       </c>
-      <c r="I94" t="n">
-        <v>6</v>
-      </c>
-      <c r="J94" t="n">
-        <v>4</v>
-      </c>
-      <c r="K94" t="n">
-        <v>0</v>
-      </c>
       <c r="L94" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
         <v>0</v>
@@ -4330,28 +4330,28 @@
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E95" t="n">
         <v>1</v>
       </c>
       <c r="F95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G95" t="n">
+        <v>1</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" t="n">
         <v>2</v>
       </c>
-      <c r="H95" t="n">
-        <v>1</v>
-      </c>
-      <c r="I95" t="n">
-        <v>0</v>
-      </c>
       <c r="J95" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K95" t="n">
         <v>1</v>
@@ -4360,7 +4360,7 @@
         <v>1</v>
       </c>
       <c r="M95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -4389,13 +4389,13 @@
         <v>0</v>
       </c>
       <c r="I96" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J96" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L96" t="n">
         <v>1</v>
@@ -4418,7 +4418,7 @@
         <v>1</v>
       </c>
       <c r="E97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F97" t="n">
         <v>0</v>
@@ -4427,16 +4427,16 @@
         <v>0</v>
       </c>
       <c r="H97" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I97" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L97" t="n">
         <v>0</v>
@@ -4453,16 +4453,16 @@
       </c>
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D98" t="n">
         <v>1</v>
       </c>
       <c r="E98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G98" t="n">
         <v>1</v>
@@ -4471,19 +4471,19 @@
         <v>1</v>
       </c>
       <c r="I98" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J98" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L98" t="n">
         <v>2</v>
       </c>
       <c r="M98" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -4492,35 +4492,33 @@
           <t>電腦及週邊設備業右下</t>
         </is>
       </c>
-      <c r="B99" t="n">
-        <v>0</v>
-      </c>
+      <c r="B99" t="inlineStr"/>
       <c r="C99" t="n">
+        <v>0</v>
+      </c>
+      <c r="D99" t="n">
+        <v>0</v>
+      </c>
+      <c r="E99" t="n">
         <v>3</v>
-      </c>
-      <c r="D99" t="n">
-        <v>0</v>
-      </c>
-      <c r="E99" t="n">
-        <v>0</v>
       </c>
       <c r="F99" t="n">
         <v>2</v>
       </c>
       <c r="G99" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" t="n">
+        <v>0</v>
+      </c>
+      <c r="I99" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" t="n">
         <v>2</v>
       </c>
-      <c r="H99" t="n">
-        <v>0</v>
-      </c>
-      <c r="I99" t="n">
-        <v>0</v>
-      </c>
-      <c r="J99" t="n">
-        <v>0</v>
-      </c>
       <c r="K99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L99" t="n">
         <v>0</v>
@@ -4537,13 +4535,13 @@
       </c>
       <c r="B100" t="inlineStr"/>
       <c r="C100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D100" t="n">
         <v>0</v>
       </c>
       <c r="E100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F100" t="n">
         <v>1</v>
@@ -4555,10 +4553,10 @@
         <v>0</v>
       </c>
       <c r="I100" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J100" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K100" t="n">
         <v>1</v>
@@ -4617,21 +4615,23 @@
           <t>食品工業右下</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr"/>
+      <c r="B102" t="n">
+        <v>0</v>
+      </c>
       <c r="C102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E102" t="n">
         <v>0</v>
       </c>
       <c r="F102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H102" t="n">
         <v>0</v>
@@ -4660,7 +4660,7 @@
       </c>
       <c r="B103" t="inlineStr"/>
       <c r="C103" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D103" t="n">
         <v>0</v>

--- a/Result/analyze_1.xlsx
+++ b/Result/analyze_1.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M103"/>
+  <dimension ref="A1:L104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,57 +441,52 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>2025-09-26</t>
+          <t>2025-09-30</t>
         </is>
       </c>
     </row>
@@ -503,7 +498,7 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
@@ -515,24 +510,21 @@
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -546,36 +538,33 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
-      </c>
-      <c r="M3" t="n">
         <v>1</v>
       </c>
     </row>
@@ -590,34 +579,31 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
         <v>2</v>
       </c>
-      <c r="G4" t="n">
-        <v>1</v>
-      </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
         <v>2</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -628,36 +614,33 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -675,10 +658,10 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -690,15 +673,12 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -710,7 +690,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -722,13 +702,13 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>1</v>
@@ -737,9 +717,6 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -751,7 +728,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
         <v>1</v>
@@ -760,28 +737,25 @@
         <v>4</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
         <v>3</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>3</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -792,7 +766,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -819,9 +793,6 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -833,19 +804,19 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
         <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -854,15 +825,12 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -883,28 +851,25 @@
         <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G11" t="n">
         <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -913,9 +878,7 @@
           <t>化學工業右下</t>
         </is>
       </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
         <v>0</v>
       </c>
@@ -944,9 +907,6 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -964,30 +924,27 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -999,37 +956,34 @@
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
+        <v>10</v>
+      </c>
+      <c r="F14" t="n">
         <v>3</v>
       </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
       <c r="G14" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I14" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -1038,41 +992,36 @@
           <t>半導體業右下</t>
         </is>
       </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
+      <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D15" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F15" t="n">
         <v>3</v>
       </c>
       <c r="G15" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1083,37 +1032,34 @@
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
+        <v>5</v>
+      </c>
+      <c r="D16" t="n">
+        <v>7</v>
+      </c>
+      <c r="E16" t="n">
         <v>8</v>
       </c>
-      <c r="D16" t="n">
-        <v>9</v>
-      </c>
-      <c r="E16" t="n">
-        <v>6</v>
-      </c>
       <c r="F16" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17">
@@ -1153,9 +1099,6 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -1168,22 +1111,22 @@
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G18" t="n">
         <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1192,9 +1135,6 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1206,7 +1146,7 @@
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -1233,9 +1173,6 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1247,7 +1184,7 @@
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -1274,9 +1211,6 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1286,7 +1220,9 @@
           <t>居家生活右下</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr"/>
+      <c r="B21" t="n">
+        <v>0</v>
+      </c>
       <c r="C21" t="n">
         <v>0</v>
       </c>
@@ -1315,10 +1251,7 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1329,7 +1262,7 @@
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
@@ -1341,7 +1274,7 @@
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1356,9 +1289,6 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1399,9 +1329,6 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
@@ -1409,39 +1336,38 @@
           <t>建材營造右下</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="n">
+        <v>0</v>
+      </c>
       <c r="C24" t="n">
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
         <v>2</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>1</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1452,13 +1378,13 @@
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -1479,9 +1405,6 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1493,7 +1416,7 @@
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
@@ -1502,13 +1425,13 @@
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -1520,9 +1443,6 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1534,13 +1454,13 @@
       </c>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -1561,9 +1481,6 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1581,7 +1498,7 @@
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
@@ -1590,7 +1507,7 @@
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -1602,9 +1519,6 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1619,7 +1533,7 @@
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -1631,7 +1545,7 @@
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -1644,9 +1558,6 @@
       </c>
       <c r="L29" t="n">
         <v>1</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -1655,27 +1566,29 @@
           <t>文化創意業右下</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr"/>
+      <c r="B30" t="n">
+        <v>0</v>
+      </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1685,9 +1598,6 @@
       </c>
       <c r="L30" t="n">
         <v>0</v>
-      </c>
-      <c r="M30" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -1698,16 +1608,16 @@
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1716,18 +1626,15 @@
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31" t="n">
         <v>1</v>
       </c>
       <c r="L31" t="n">
-        <v>1</v>
-      </c>
-      <c r="M31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1768,9 +1675,6 @@
       <c r="L32" t="n">
         <v>0</v>
       </c>
-      <c r="M32" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
@@ -1809,14 +1713,11 @@
       <c r="L33" t="n">
         <v>0</v>
       </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>水泥工業右下</t>
+          <t>水泥工業右上</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -1850,14 +1751,11 @@
       <c r="L34" t="n">
         <v>0</v>
       </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>水泥工業平</t>
+          <t>水泥工業右下</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -1891,19 +1789,16 @@
       <c r="L35" t="n">
         <v>0</v>
       </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>汽車工業右上</t>
+          <t>水泥工業平</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
@@ -1912,10 +1807,10 @@
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -1930,27 +1825,24 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>汽車工業右下</t>
+          <t>汽車工業右上</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
@@ -1959,7 +1851,7 @@
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
@@ -1971,21 +1863,18 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M37" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>汽車工業平</t>
+          <t>汽車工業右下</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
@@ -1994,16 +1883,16 @@
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2012,16 +1901,13 @@
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
-      </c>
-      <c r="M38" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>油電燃氣業右上</t>
+          <t>汽車工業平</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -2032,13 +1918,13 @@
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -2053,16 +1939,13 @@
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>油電燃氣業右下</t>
+          <t>油電燃氣業右上</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -2096,14 +1979,11 @@
       <c r="L40" t="n">
         <v>0</v>
       </c>
-      <c r="M40" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>油電燃氣業平</t>
+          <t>油電燃氣業右下</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -2137,14 +2017,11 @@
       <c r="L41" t="n">
         <v>0</v>
       </c>
-      <c r="M41" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>玻璃陶瓷右上</t>
+          <t>油電燃氣業平</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -2176,16 +2053,13 @@
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>1</v>
-      </c>
-      <c r="M42" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>玻璃陶瓷右下</t>
+          <t>玻璃陶瓷右上</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -2211,22 +2085,19 @@
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
-      </c>
-      <c r="M43" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>玻璃陶瓷平</t>
+          <t>玻璃陶瓷右下</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -2260,14 +2131,11 @@
       <c r="L44" t="n">
         <v>0</v>
       </c>
-      <c r="M44" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>生技醫療業右上</t>
+          <t>玻璃陶瓷平</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -2275,10 +2143,10 @@
         <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
@@ -2287,117 +2155,108 @@
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
-      </c>
-      <c r="M45" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>生技醫療業右下</t>
-        </is>
-      </c>
-      <c r="B46" t="n">
-        <v>0</v>
-      </c>
+          <t>生技醫療業右上</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F46" t="n">
         <v>1</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>1</v>
-      </c>
-      <c r="M46" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>生技醫療業平</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr"/>
+          <t>生技醫療業右下</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>0</v>
+      </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K47" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>1</v>
-      </c>
-      <c r="M47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>紡織纖維右上</t>
+          <t>生技醫療業平</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D48" t="n">
         <v>1</v>
@@ -2415,25 +2274,22 @@
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K48" t="n">
         <v>1</v>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
-      </c>
-      <c r="M48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>紡織纖維右下</t>
+          <t>紡織纖維右上</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -2456,7 +2312,7 @@
         <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -2465,16 +2321,13 @@
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
-      </c>
-      <c r="M49" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>紡織纖維平</t>
+          <t>紡織纖維右下</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -2506,16 +2359,13 @@
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
-      </c>
-      <c r="M50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>綠能環保右上</t>
+          <t>紡織纖維平</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -2523,10 +2373,10 @@
         <v>0</v>
       </c>
       <c r="D51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F51" t="n">
         <v>0</v>
@@ -2544,24 +2394,21 @@
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
-      </c>
-      <c r="M51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>綠能環保右下</t>
+          <t>綠能環保右上</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D52" t="n">
         <v>0</v>
@@ -2588,16 +2435,13 @@
         <v>0</v>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
-      </c>
-      <c r="M52" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>綠能環保平</t>
+          <t>綠能環保右下</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
@@ -2605,16 +2449,16 @@
         <v>0</v>
       </c>
       <c r="D53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
@@ -2629,24 +2473,21 @@
         <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
-      </c>
-      <c r="M53" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>航運業右上</t>
+          <t>綠能環保平</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E54" t="n">
         <v>0</v>
@@ -2661,7 +2502,7 @@
         <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -2670,21 +2511,16 @@
         <v>0</v>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
-      </c>
-      <c r="M54" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>航運業右下</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
-        <v>0</v>
-      </c>
+          <t>航運業右上</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr"/>
       <c r="C55" t="n">
         <v>0</v>
       </c>
@@ -2698,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
@@ -2713,19 +2549,18 @@
         <v>0</v>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
-      </c>
-      <c r="M55" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>航運業平</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr"/>
+          <t>航運業右下</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>0</v>
+      </c>
       <c r="C56" t="n">
         <v>0</v>
       </c>
@@ -2754,16 +2589,13 @@
         <v>0</v>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
-      </c>
-      <c r="M56" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>觀光事業右上</t>
+          <t>航運業平</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
@@ -2797,14 +2629,11 @@
       <c r="L57" t="n">
         <v>0</v>
       </c>
-      <c r="M57" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>觀光事業右下</t>
+          <t>觀光事業右上</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
@@ -2838,14 +2667,11 @@
       <c r="L58" t="n">
         <v>0</v>
       </c>
-      <c r="M58" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>觀光事業平</t>
+          <t>觀光事業右下</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -2879,14 +2705,11 @@
       <c r="L59" t="n">
         <v>0</v>
       </c>
-      <c r="M59" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>貿易百貨右上</t>
+          <t>觀光事業平</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -2920,25 +2743,22 @@
       <c r="L60" t="n">
         <v>0</v>
       </c>
-      <c r="M60" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>貿易百貨右下</t>
+          <t>貿易百貨右上</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D61" t="n">
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
@@ -2953,22 +2773,19 @@
         <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K61" t="n">
         <v>0</v>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
-      </c>
-      <c r="M61" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>貿易百貨平</t>
+          <t>貿易百貨右下</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
@@ -2979,7 +2796,7 @@
         <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F62" t="n">
         <v>0</v>
@@ -2988,7 +2805,7 @@
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I62" t="n">
         <v>0</v>
@@ -3000,21 +2817,18 @@
         <v>0</v>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
-      </c>
-      <c r="M62" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>資訊服務業右上</t>
+          <t>貿易百貨平</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D63" t="n">
         <v>0</v>
@@ -3029,7 +2843,7 @@
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I63" t="n">
         <v>0</v>
@@ -3038,24 +2852,19 @@
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
-      </c>
-      <c r="M63" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>資訊服務業右下</t>
-        </is>
-      </c>
-      <c r="B64" t="n">
-        <v>0</v>
-      </c>
+          <t>資訊服務業右上</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr"/>
       <c r="C64" t="n">
         <v>0</v>
       </c>
@@ -3066,7 +2875,7 @@
         <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -3075,7 +2884,7 @@
         <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -3084,16 +2893,13 @@
         <v>0</v>
       </c>
       <c r="L64" t="n">
-        <v>1</v>
-      </c>
-      <c r="M64" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>資訊服務業平</t>
+          <t>資訊服務業右下</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
@@ -3107,7 +2913,7 @@
         <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -3119,22 +2925,19 @@
         <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
-      </c>
-      <c r="M65" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>農業科技業右上</t>
+          <t>資訊服務業平</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
@@ -3142,7 +2945,7 @@
         <v>0</v>
       </c>
       <c r="D66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E66" t="n">
         <v>0</v>
@@ -3166,16 +2969,13 @@
         <v>0</v>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
-      </c>
-      <c r="M66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>農業科技業右下</t>
+          <t>農業科技業右上</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
@@ -3209,14 +3009,11 @@
       <c r="L67" t="n">
         <v>0</v>
       </c>
-      <c r="M67" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>農業科技業平</t>
+          <t>農業科技業右下</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
@@ -3250,14 +3047,11 @@
       <c r="L68" t="n">
         <v>0</v>
       </c>
-      <c r="M68" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>通信網路業右上</t>
+          <t>農業科技業平</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
@@ -3265,7 +3059,7 @@
         <v>0</v>
       </c>
       <c r="D69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E69" t="n">
         <v>0</v>
@@ -3277,10 +3071,10 @@
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -3289,16 +3083,13 @@
         <v>0</v>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
-      </c>
-      <c r="M69" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>通信網路業右下</t>
+          <t>通信網路業右上</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
@@ -3309,78 +3100,72 @@
         <v>0</v>
       </c>
       <c r="E70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G70" t="n">
         <v>1</v>
       </c>
       <c r="H70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J70" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
-      </c>
-      <c r="M70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>通信網路業平</t>
+          <t>通信網路業右下</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D71" t="n">
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H71" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I71" t="n">
         <v>1</v>
       </c>
       <c r="J71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
-      </c>
-      <c r="M71" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>造紙工業右下</t>
+          <t>通信網路業平</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
@@ -3397,13 +3182,13 @@
         <v>0</v>
       </c>
       <c r="G72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -3412,16 +3197,13 @@
         <v>0</v>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
-      </c>
-      <c r="M72" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>造紙工業平</t>
+          <t>造紙工業右下</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
@@ -3455,14 +3237,11 @@
       <c r="L73" t="n">
         <v>0</v>
       </c>
-      <c r="M73" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>運動休閒右上</t>
+          <t>造紙工業平</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
@@ -3476,7 +3255,7 @@
         <v>0</v>
       </c>
       <c r="F74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -3485,7 +3264,7 @@
         <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -3494,16 +3273,13 @@
         <v>0</v>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
-      </c>
-      <c r="M74" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>運動休閒右下</t>
+          <t>運動休閒右上</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
@@ -3511,7 +3287,7 @@
         <v>0</v>
       </c>
       <c r="D75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E75" t="n">
         <v>0</v>
@@ -3520,10 +3296,10 @@
         <v>0</v>
       </c>
       <c r="G75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I75" t="n">
         <v>0</v>
@@ -3532,19 +3308,16 @@
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
-      </c>
-      <c r="M75" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>運動休閒平</t>
+          <t>運動休閒右下</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
@@ -3558,7 +3331,7 @@
         <v>0</v>
       </c>
       <c r="F76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -3567,7 +3340,7 @@
         <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -3576,16 +3349,13 @@
         <v>0</v>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
-      </c>
-      <c r="M76" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>金融保險右上</t>
+          <t>運動休閒平</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
@@ -3619,14 +3389,11 @@
       <c r="L77" t="n">
         <v>0</v>
       </c>
-      <c r="M77" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>金融保險右下</t>
+          <t>金融保險右上</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
@@ -3660,14 +3427,11 @@
       <c r="L78" t="n">
         <v>0</v>
       </c>
-      <c r="M78" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>金融保險平</t>
+          <t>金融保險右下</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
@@ -3701,14 +3465,11 @@
       <c r="L79" t="n">
         <v>0</v>
       </c>
-      <c r="M79" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>金融業右上</t>
+          <t>金融保險平</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
@@ -3742,14 +3503,11 @@
       <c r="L80" t="n">
         <v>0</v>
       </c>
-      <c r="M80" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>金融業右下</t>
+          <t>金融業右上</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
@@ -3783,17 +3541,16 @@
       <c r="L81" t="n">
         <v>0</v>
       </c>
-      <c r="M81" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>金融業平</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr"/>
+          <t>金融業右下</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>0</v>
+      </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
@@ -3822,16 +3579,13 @@
         <v>0</v>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
-      </c>
-      <c r="M82" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業右上</t>
+          <t>金融業平</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
@@ -3857,66 +3611,62 @@
         <v>0</v>
       </c>
       <c r="J83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K83" t="n">
         <v>0</v>
       </c>
       <c r="L83" t="n">
-        <v>2</v>
-      </c>
-      <c r="M83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業右下</t>
+          <t>鋼鐵工業右上</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
       <c r="C84" t="n">
+        <v>0</v>
+      </c>
+      <c r="D84" t="n">
+        <v>0</v>
+      </c>
+      <c r="E84" t="n">
+        <v>0</v>
+      </c>
+      <c r="F84" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" t="n">
+        <v>1</v>
+      </c>
+      <c r="I84" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" t="n">
         <v>2</v>
       </c>
-      <c r="D84" t="n">
-        <v>0</v>
-      </c>
-      <c r="E84" t="n">
-        <v>0</v>
-      </c>
-      <c r="F84" t="n">
-        <v>0</v>
-      </c>
-      <c r="G84" t="n">
-        <v>0</v>
-      </c>
-      <c r="H84" t="n">
-        <v>0</v>
-      </c>
-      <c r="I84" t="n">
-        <v>0</v>
-      </c>
-      <c r="J84" t="n">
-        <v>0</v>
-      </c>
       <c r="K84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
-      </c>
-      <c r="M84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業平</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr"/>
+          <t>鋼鐵工業右下</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>0</v>
+      </c>
       <c r="C85" t="n">
         <v>0</v>
       </c>
@@ -3945,16 +3695,13 @@
         <v>0</v>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
-      </c>
-      <c r="M85" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>電器電纜右上</t>
+          <t>鋼鐵工業平</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
@@ -3986,16 +3733,13 @@
         <v>0</v>
       </c>
       <c r="L86" t="n">
-        <v>1</v>
-      </c>
-      <c r="M86" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>電器電纜右下</t>
+          <t>電器電纜右上</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
@@ -4021,22 +3765,19 @@
         <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K87" t="n">
         <v>0</v>
       </c>
       <c r="L87" t="n">
-        <v>2</v>
-      </c>
-      <c r="M87" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>電器電纜平</t>
+          <t>電器電纜右下</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
@@ -4062,22 +3803,19 @@
         <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
       </c>
       <c r="L88" t="n">
-        <v>1</v>
-      </c>
-      <c r="M88" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>電子通路業右上</t>
+          <t>電器電纜平</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
@@ -4088,19 +3826,19 @@
         <v>0</v>
       </c>
       <c r="E89" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F89" t="n">
         <v>0</v>
       </c>
       <c r="G89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H89" t="n">
         <v>0</v>
       </c>
       <c r="I89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J89" t="n">
         <v>1</v>
@@ -4109,27 +3847,24 @@
         <v>0</v>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
-      </c>
-      <c r="M89" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>電子通路業右下</t>
+          <t>電子通路業右上</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D90" t="n">
         <v>0</v>
       </c>
       <c r="E90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F90" t="n">
         <v>0</v>
@@ -4138,7 +3873,7 @@
         <v>1</v>
       </c>
       <c r="H90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I90" t="n">
         <v>0</v>
@@ -4147,19 +3882,16 @@
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
-      </c>
-      <c r="M90" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>電子通路業平</t>
+          <t>電子通路業右下</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
@@ -4167,16 +3899,16 @@
         <v>0</v>
       </c>
       <c r="D91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F91" t="n">
         <v>0</v>
       </c>
       <c r="G91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
@@ -4188,161 +3920,149 @@
         <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
-      </c>
-      <c r="M91" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業右上</t>
+          <t>電子通路業平</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D92" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E92" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F92" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G92" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H92" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I92" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J92" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L92" t="n">
         <v>0</v>
-      </c>
-      <c r="M92" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業右下</t>
-        </is>
-      </c>
-      <c r="B93" t="n">
-        <v>0</v>
-      </c>
+          <t>電子零組件業右上</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr"/>
       <c r="C93" t="n">
+        <v>6</v>
+      </c>
+      <c r="D93" t="n">
+        <v>4</v>
+      </c>
+      <c r="E93" t="n">
+        <v>7</v>
+      </c>
+      <c r="F93" t="n">
+        <v>10</v>
+      </c>
+      <c r="G93" t="n">
+        <v>8</v>
+      </c>
+      <c r="H93" t="n">
+        <v>4</v>
+      </c>
+      <c r="I93" t="n">
+        <v>8</v>
+      </c>
+      <c r="J93" t="n">
+        <v>0</v>
+      </c>
+      <c r="K93" t="n">
         <v>3</v>
       </c>
-      <c r="D93" t="n">
-        <v>0</v>
-      </c>
-      <c r="E93" t="n">
-        <v>3</v>
-      </c>
-      <c r="F93" t="n">
-        <v>3</v>
-      </c>
-      <c r="G93" t="n">
-        <v>2</v>
-      </c>
-      <c r="H93" t="n">
-        <v>2</v>
-      </c>
-      <c r="I93" t="n">
-        <v>3</v>
-      </c>
-      <c r="J93" t="n">
-        <v>3</v>
-      </c>
-      <c r="K93" t="n">
-        <v>1</v>
-      </c>
       <c r="L93" t="n">
-        <v>0</v>
-      </c>
-      <c r="M93" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業平</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr"/>
+          <t>電子零組件業右下</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>0</v>
+      </c>
       <c r="C94" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D94" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E94" t="n">
+        <v>2</v>
+      </c>
+      <c r="F94" t="n">
+        <v>2</v>
+      </c>
+      <c r="G94" t="n">
+        <v>4</v>
+      </c>
+      <c r="H94" t="n">
         <v>3</v>
       </c>
-      <c r="F94" t="n">
-        <v>0</v>
-      </c>
-      <c r="G94" t="n">
+      <c r="I94" t="n">
+        <v>1</v>
+      </c>
+      <c r="J94" t="n">
+        <v>0</v>
+      </c>
+      <c r="K94" t="n">
+        <v>0</v>
+      </c>
+      <c r="L94" t="n">
         <v>2</v>
-      </c>
-      <c r="H94" t="n">
-        <v>6</v>
-      </c>
-      <c r="I94" t="n">
-        <v>4</v>
-      </c>
-      <c r="J94" t="n">
-        <v>0</v>
-      </c>
-      <c r="K94" t="n">
-        <v>2</v>
-      </c>
-      <c r="L94" t="n">
-        <v>0</v>
-      </c>
-      <c r="M94" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>電機機械右上</t>
+          <t>電子零組件業平</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F95" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G95" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H95" t="n">
         <v>0</v>
@@ -4351,71 +4071,67 @@
         <v>2</v>
       </c>
       <c r="J95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L95" t="n">
-        <v>1</v>
-      </c>
-      <c r="M95" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>電機機械右下</t>
+          <t>電機機械右上</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D96" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F96" t="n">
         <v>0</v>
       </c>
       <c r="G96" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I96" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L96" t="n">
-        <v>1</v>
-      </c>
-      <c r="M96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>電機機械平</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr"/>
+          <t>電機機械右下</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>0</v>
+      </c>
       <c r="C97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E97" t="n">
         <v>0</v>
@@ -4424,31 +4140,28 @@
         <v>0</v>
       </c>
       <c r="G97" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H97" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J97" t="n">
         <v>1</v>
       </c>
       <c r="K97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
-      </c>
-      <c r="M97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右上</t>
+          <t>電機機械平</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
@@ -4456,63 +4169,60 @@
         <v>0</v>
       </c>
       <c r="D98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E98" t="n">
         <v>0</v>
       </c>
       <c r="F98" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H98" t="n">
         <v>1</v>
       </c>
       <c r="I98" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
       </c>
       <c r="K98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L98" t="n">
-        <v>2</v>
-      </c>
-      <c r="M98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右下</t>
+          <t>電腦及週邊設備業右上</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E99" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F99" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G99" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H99" t="n">
         <v>0</v>
       </c>
       <c r="I99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J99" t="n">
         <v>2</v>
@@ -4521,57 +4231,51 @@
         <v>0</v>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
-      </c>
-      <c r="M99" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業平</t>
+          <t>電腦及週邊設備業右下</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
       <c r="C100" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D100" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
       </c>
       <c r="H100" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I100" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
-      </c>
-      <c r="M100" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>食品工業右上</t>
+          <t>電腦及週邊設備業平</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
@@ -4588,13 +4292,13 @@
         <v>0</v>
       </c>
       <c r="G101" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H101" t="n">
         <v>0</v>
       </c>
       <c r="I101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -4603,23 +4307,18 @@
         <v>0</v>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
-      </c>
-      <c r="M101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>食品工業右下</t>
-        </is>
-      </c>
-      <c r="B102" t="n">
-        <v>0</v>
-      </c>
+          <t>食品工業右上</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr"/>
       <c r="C102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D102" t="n">
         <v>0</v>
@@ -4628,7 +4327,7 @@
         <v>0</v>
       </c>
       <c r="F102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -4646,16 +4345,13 @@
         <v>0</v>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
-      </c>
-      <c r="M102" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>食品工業平</t>
+          <t>食品工業右下</t>
         </is>
       </c>
       <c r="B103" t="inlineStr"/>
@@ -4663,7 +4359,7 @@
         <v>0</v>
       </c>
       <c r="D103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E103" t="n">
         <v>0</v>
@@ -4689,7 +4385,42 @@
       <c r="L103" t="n">
         <v>0</v>
       </c>
-      <c r="M103" t="n">
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="inlineStr">
+        <is>
+          <t>食品工業平</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr"/>
+      <c r="C104" t="n">
+        <v>0</v>
+      </c>
+      <c r="D104" t="n">
+        <v>0</v>
+      </c>
+      <c r="E104" t="n">
+        <v>0</v>
+      </c>
+      <c r="F104" t="n">
+        <v>0</v>
+      </c>
+      <c r="G104" t="n">
+        <v>0</v>
+      </c>
+      <c r="H104" t="n">
+        <v>0</v>
+      </c>
+      <c r="I104" t="n">
+        <v>0</v>
+      </c>
+      <c r="J104" t="n">
+        <v>0</v>
+      </c>
+      <c r="K104" t="n">
+        <v>0</v>
+      </c>
+      <c r="L104" t="n">
         <v>0</v>
       </c>
     </row>

--- a/Result/analyze_1.xlsx
+++ b/Result/analyze_1.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L104"/>
+  <dimension ref="A1:L103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,52 +441,52 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-10-01</t>
         </is>
       </c>
     </row>
@@ -498,19 +498,19 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
         <v>3</v>
       </c>
-      <c r="D2" t="n">
-        <v>1</v>
-      </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
@@ -519,7 +519,7 @@
         <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -534,20 +534,18 @@
           <t>光電業右下</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>0</v>
-      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -556,7 +554,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
@@ -576,34 +574,34 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
         <v>2</v>
       </c>
-      <c r="E4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1</v>
-      </c>
       <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
         <v>2</v>
       </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
       <c r="L4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -614,7 +612,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -623,10 +621,10 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -635,13 +633,13 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
         <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -652,22 +650,22 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -699,19 +697,19 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -728,34 +726,34 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
         <v>4</v>
       </c>
-      <c r="D8" t="n">
-        <v>1</v>
-      </c>
       <c r="E8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
         <v>3</v>
-      </c>
-      <c r="H8" t="n">
-        <v>1</v>
       </c>
       <c r="I8" t="n">
         <v>3</v>
       </c>
       <c r="J8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -804,13 +802,13 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -822,7 +820,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -831,7 +829,7 @@
         <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -842,34 +840,34 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -921,19 +919,19 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -945,7 +943,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -956,34 +954,34 @@
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="n">
+        <v>11</v>
+      </c>
+      <c r="E14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" t="n">
+        <v>4</v>
+      </c>
+      <c r="G14" t="n">
         <v>5</v>
       </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>10</v>
-      </c>
-      <c r="F14" t="n">
-        <v>3</v>
-      </c>
-      <c r="G14" t="n">
+      <c r="H14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>12</v>
+      </c>
+      <c r="L14" t="n">
         <v>4</v>
-      </c>
-      <c r="H14" t="n">
-        <v>4</v>
-      </c>
-      <c r="I14" t="n">
-        <v>1</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -994,16 +992,16 @@
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E15" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="F15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
@@ -1012,13 +1010,13 @@
         <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
         <v>1</v>
@@ -1038,28 +1036,28 @@
         <v>7</v>
       </c>
       <c r="E16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L16" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1111,16 +1109,16 @@
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -1173,7 +1171,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1220,14 +1218,12 @@
           <t>居家生活右下</t>
         </is>
       </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
+      <c r="B21" t="inlineStr"/>
       <c r="C21" t="n">
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -1248,10 +1244,10 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1262,13 +1258,13 @@
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -1336,11 +1332,9 @@
           <t>建材營造右下</t>
         </is>
       </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
+      <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
@@ -1355,19 +1349,19 @@
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1378,7 +1372,7 @@
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
@@ -1416,16 +1410,16 @@
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1454,7 +1448,7 @@
       </c>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
@@ -1530,10 +1524,10 @@
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -1542,22 +1536,22 @@
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -1566,23 +1560,21 @@
           <t>文化創意業右下</t>
         </is>
       </c>
-      <c r="B30" t="n">
-        <v>0</v>
-      </c>
+      <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -1591,7 +1583,7 @@
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -1623,16 +1615,16 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31" t="n">
         <v>1</v>
       </c>
       <c r="J31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -1717,7 +1709,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>水泥工業右上</t>
+          <t>水泥工業右下</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -1755,7 +1747,7 @@
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>水泥工業右下</t>
+          <t>水泥工業平</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -1793,15 +1785,15 @@
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>水泥工業平</t>
+          <t>汽車工業右上</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
@@ -1831,7 +1823,7 @@
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>汽車工業右上</t>
+          <t>汽車工業右下</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
@@ -1839,7 +1831,7 @@
         <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E37" t="n">
         <v>1</v>
@@ -1869,7 +1861,7 @@
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>汽車工業右下</t>
+          <t>汽車工業平</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -1907,7 +1899,7 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>汽車工業平</t>
+          <t>油電燃氣業右上</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -1918,13 +1910,13 @@
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -1945,7 +1937,7 @@
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>油電燃氣業右上</t>
+          <t>油電燃氣業右下</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -1983,7 +1975,7 @@
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>油電燃氣業右下</t>
+          <t>油電燃氣業平</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -2021,7 +2013,7 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>油電燃氣業平</t>
+          <t>玻璃陶瓷右上</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -2044,7 +2036,7 @@
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -2059,7 +2051,7 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>玻璃陶瓷右上</t>
+          <t>玻璃陶瓷右下</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -2085,7 +2077,7 @@
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -2097,7 +2089,7 @@
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>玻璃陶瓷右下</t>
+          <t>玻璃陶瓷平</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -2135,7 +2127,7 @@
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>玻璃陶瓷平</t>
+          <t>生技醫療業右上</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -2146,13 +2138,13 @@
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -2164,16 +2156,16 @@
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>生技醫療業右上</t>
+          <t>生技醫療業右下</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -2196,7 +2188,7 @@
         <v>1</v>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -2211,17 +2203,15 @@
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>生技醫療業右下</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
-        <v>0</v>
-      </c>
+          <t>生技醫療業平</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr"/>
       <c r="C47" t="n">
         <v>1</v>
       </c>
       <c r="D47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E47" t="n">
         <v>0</v>
@@ -2230,10 +2220,10 @@
         <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I47" t="n">
         <v>1</v>
@@ -2242,24 +2232,24 @@
         <v>1</v>
       </c>
       <c r="K47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>生技醫療業平</t>
+          <t>紡織纖維右上</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E48" t="n">
         <v>0</v>
@@ -2271,25 +2261,25 @@
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I48" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>紡織纖維右上</t>
+          <t>紡織纖維右下</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -2312,13 +2302,13 @@
         <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
@@ -2327,7 +2317,7 @@
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>紡織纖維右下</t>
+          <t>紡織纖維平</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -2356,7 +2346,7 @@
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L50" t="n">
         <v>1</v>
@@ -2365,7 +2355,7 @@
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>紡織纖維平</t>
+          <t>綠能環保右上</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -2385,7 +2375,7 @@
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I51" t="n">
         <v>0</v>
@@ -2397,18 +2387,18 @@
         <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>綠能環保右上</t>
+          <t>綠能環保右下</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D52" t="n">
         <v>0</v>
@@ -2417,7 +2407,7 @@
         <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -2426,7 +2416,7 @@
         <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -2441,12 +2431,12 @@
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>綠能環保右下</t>
+          <t>綠能環保平</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D53" t="n">
         <v>0</v>
@@ -2458,7 +2448,7 @@
         <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
@@ -2479,21 +2469,21 @@
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>綠能環保平</t>
+          <t>航運業右上</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E54" t="n">
         <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -2517,7 +2507,7 @@
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>航運業右上</t>
+          <t>航運業右下</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
@@ -2534,7 +2524,7 @@
         <v>0</v>
       </c>
       <c r="G55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
@@ -2555,12 +2545,10 @@
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>航運業右下</t>
-        </is>
-      </c>
-      <c r="B56" t="n">
-        <v>0</v>
-      </c>
+          <t>航運業平</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr"/>
       <c r="C56" t="n">
         <v>0</v>
       </c>
@@ -2595,7 +2583,7 @@
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>航運業平</t>
+          <t>觀光事業右上</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
@@ -2627,13 +2615,13 @@
         <v>0</v>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>觀光事業右上</t>
+          <t>觀光事業右下</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
@@ -2671,7 +2659,7 @@
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>觀光事業右下</t>
+          <t>觀光事業平</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -2709,7 +2697,7 @@
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>觀光事業平</t>
+          <t>貿易百貨右上</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -2747,7 +2735,7 @@
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>貿易百貨右上</t>
+          <t>貿易百貨右下</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
@@ -2764,7 +2752,7 @@
         <v>0</v>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
@@ -2785,12 +2773,12 @@
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>貿易百貨右下</t>
+          <t>貿易百貨平</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D62" t="n">
         <v>0</v>
@@ -2805,7 +2793,7 @@
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I62" t="n">
         <v>0</v>
@@ -2823,18 +2811,18 @@
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>貿易百貨平</t>
+          <t>資訊服務業右上</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D63" t="n">
         <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
@@ -2843,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I63" t="n">
         <v>0</v>
@@ -2855,13 +2843,13 @@
         <v>0</v>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>資訊服務業右上</t>
+          <t>資訊服務業右下</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
@@ -2875,7 +2863,7 @@
         <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2884,7 +2872,7 @@
         <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -2899,12 +2887,12 @@
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>資訊服務業右下</t>
+          <t>資訊服務業平</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D65" t="n">
         <v>0</v>
@@ -2925,10 +2913,10 @@
         <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
@@ -2937,7 +2925,7 @@
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>資訊服務業平</t>
+          <t>農業科技業右上</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
@@ -2945,7 +2933,7 @@
         <v>0</v>
       </c>
       <c r="D66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E66" t="n">
         <v>0</v>
@@ -2968,14 +2956,12 @@
       <c r="K66" t="n">
         <v>0</v>
       </c>
-      <c r="L66" t="n">
-        <v>2</v>
-      </c>
+      <c r="L66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>農業科技業右上</t>
+          <t>農業科技業右下</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
@@ -3013,7 +2999,7 @@
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>農業科技業右下</t>
+          <t>農業科技業平</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
@@ -3051,7 +3037,7 @@
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>農業科技業平</t>
+          <t>通信網路業右上</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
@@ -3062,13 +3048,13 @@
         <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -3080,7 +3066,7 @@
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L69" t="n">
         <v>0</v>
@@ -3089,27 +3075,27 @@
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>通信網路業右上</t>
+          <t>通信網路業右下</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G70" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I70" t="n">
         <v>0</v>
@@ -3121,36 +3107,36 @@
         <v>0</v>
       </c>
       <c r="L70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>通信網路業右下</t>
+          <t>通信網路業平</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F71" t="n">
         <v>1</v>
       </c>
       <c r="G71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -3165,7 +3151,7 @@
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>通信網路業平</t>
+          <t>造紙工業右下</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
@@ -3182,13 +3168,13 @@
         <v>0</v>
       </c>
       <c r="G72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -3203,7 +3189,7 @@
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>造紙工業右下</t>
+          <t>造紙工業平</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
@@ -3241,12 +3227,12 @@
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>造紙工業平</t>
+          <t>運動休閒右上</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
       <c r="C74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D74" t="n">
         <v>0</v>
@@ -3255,7 +3241,7 @@
         <v>0</v>
       </c>
       <c r="F74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -3279,7 +3265,7 @@
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>運動休閒右上</t>
+          <t>運動休閒右下</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
@@ -3287,19 +3273,19 @@
         <v>0</v>
       </c>
       <c r="D75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F75" t="n">
         <v>0</v>
       </c>
       <c r="G75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I75" t="n">
         <v>0</v>
@@ -3311,13 +3297,13 @@
         <v>0</v>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>運動休閒右下</t>
+          <t>運動休閒平</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
@@ -3331,7 +3317,7 @@
         <v>0</v>
       </c>
       <c r="F76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -3340,7 +3326,7 @@
         <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -3355,7 +3341,7 @@
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>運動休閒平</t>
+          <t>金融保險右上</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
@@ -3393,7 +3379,7 @@
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>金融保險右上</t>
+          <t>金融保險右下</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
@@ -3431,7 +3417,7 @@
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>金融保險右下</t>
+          <t>金融保險平</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
@@ -3469,7 +3455,7 @@
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>金融保險平</t>
+          <t>金融業右上</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
@@ -3507,7 +3493,7 @@
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>金融業右上</t>
+          <t>金融業右下</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
@@ -3545,12 +3531,10 @@
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>金融業右下</t>
-        </is>
-      </c>
-      <c r="B82" t="n">
-        <v>0</v>
-      </c>
+          <t>金融業平</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr"/>
       <c r="C82" t="n">
         <v>0</v>
       </c>
@@ -3585,7 +3569,7 @@
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>金融業平</t>
+          <t>鋼鐵工業右上</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
@@ -3602,19 +3586,19 @@
         <v>0</v>
       </c>
       <c r="G83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
       </c>
       <c r="I83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L83" t="n">
         <v>0</v>
@@ -3623,7 +3607,7 @@
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業右上</t>
+          <t>鋼鐵工業右下</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
@@ -3643,16 +3627,16 @@
         <v>0</v>
       </c>
       <c r="H84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I84" t="n">
         <v>0</v>
       </c>
       <c r="J84" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L84" t="n">
         <v>1</v>
@@ -3661,12 +3645,10 @@
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業右下</t>
-        </is>
-      </c>
-      <c r="B85" t="n">
-        <v>0</v>
-      </c>
+          <t>鋼鐵工業平</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr"/>
       <c r="C85" t="n">
         <v>0</v>
       </c>
@@ -3686,10 +3668,10 @@
         <v>0</v>
       </c>
       <c r="I85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K85" t="n">
         <v>0</v>
@@ -3701,7 +3683,7 @@
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業平</t>
+          <t>電器電纜右上</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
@@ -3724,7 +3706,7 @@
         <v>0</v>
       </c>
       <c r="I86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -3739,7 +3721,7 @@
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>電器電纜右上</t>
+          <t>電器電纜右下</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
@@ -3762,10 +3744,10 @@
         <v>0</v>
       </c>
       <c r="I87" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K87" t="n">
         <v>0</v>
@@ -3777,7 +3759,7 @@
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>電器電纜右下</t>
+          <t>電器電纜平</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
@@ -3800,13 +3782,13 @@
         <v>0</v>
       </c>
       <c r="I88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J88" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L88" t="n">
         <v>0</v>
@@ -3815,7 +3797,7 @@
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>電器電纜平</t>
+          <t>電子通路業右上</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
@@ -3823,16 +3805,16 @@
         <v>0</v>
       </c>
       <c r="D89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E89" t="n">
         <v>0</v>
       </c>
       <c r="F89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H89" t="n">
         <v>0</v>
@@ -3847,33 +3829,33 @@
         <v>0</v>
       </c>
       <c r="L89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>電子通路業右上</t>
+          <t>電子通路業右下</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F90" t="n">
         <v>0</v>
       </c>
       <c r="G90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I90" t="n">
         <v>0</v>
@@ -3882,7 +3864,7 @@
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L90" t="n">
         <v>0</v>
@@ -3891,7 +3873,7 @@
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>電子通路業右下</t>
+          <t>電子通路業平</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
@@ -3899,10 +3881,10 @@
         <v>0</v>
       </c>
       <c r="D91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F91" t="n">
         <v>0</v>
@@ -3911,7 +3893,7 @@
         <v>0</v>
       </c>
       <c r="H91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I91" t="n">
         <v>0</v>
@@ -3929,152 +3911,152 @@
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>電子通路業平</t>
+          <t>電子零組件業右上</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D92" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E92" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F92" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G92" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H92" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K92" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業右上</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr"/>
+          <t>電子零組件業右下</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>0</v>
+      </c>
       <c r="C93" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D93" t="n">
+        <v>2</v>
+      </c>
+      <c r="E93" t="n">
+        <v>3</v>
+      </c>
+      <c r="F93" t="n">
         <v>4</v>
       </c>
-      <c r="E93" t="n">
-        <v>7</v>
-      </c>
-      <c r="F93" t="n">
-        <v>10</v>
-      </c>
       <c r="G93" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H93" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I93" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L93" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業右下</t>
-        </is>
-      </c>
-      <c r="B94" t="n">
-        <v>0</v>
-      </c>
+          <t>電子零組件業平</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr"/>
       <c r="C94" t="n">
+        <v>0</v>
+      </c>
+      <c r="D94" t="n">
+        <v>2</v>
+      </c>
+      <c r="E94" t="n">
+        <v>5</v>
+      </c>
+      <c r="F94" t="n">
         <v>3</v>
       </c>
-      <c r="D94" t="n">
+      <c r="G94" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" t="n">
+        <v>2</v>
+      </c>
+      <c r="I94" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" t="n">
+        <v>0</v>
+      </c>
+      <c r="K94" t="n">
         <v>3</v>
       </c>
-      <c r="E94" t="n">
-        <v>2</v>
-      </c>
-      <c r="F94" t="n">
-        <v>2</v>
-      </c>
-      <c r="G94" t="n">
-        <v>4</v>
-      </c>
-      <c r="H94" t="n">
-        <v>3</v>
-      </c>
-      <c r="I94" t="n">
-        <v>1</v>
-      </c>
-      <c r="J94" t="n">
-        <v>0</v>
-      </c>
-      <c r="K94" t="n">
-        <v>0</v>
-      </c>
       <c r="L94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業平</t>
+          <t>電機機械右上</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E95" t="n">
+        <v>0</v>
+      </c>
+      <c r="F95" t="n">
         <v>2</v>
       </c>
-      <c r="F95" t="n">
-        <v>5</v>
-      </c>
       <c r="G95" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I95" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L95" t="n">
         <v>3</v>
@@ -4083,24 +4065,24 @@
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>電機機械右上</t>
+          <t>電機機械右下</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D96" t="n">
+        <v>0</v>
+      </c>
+      <c r="E96" t="n">
+        <v>0</v>
+      </c>
+      <c r="F96" t="n">
         <v>2</v>
       </c>
-      <c r="E96" t="n">
-        <v>1</v>
-      </c>
-      <c r="F96" t="n">
-        <v>0</v>
-      </c>
       <c r="G96" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H96" t="n">
         <v>1</v>
@@ -4109,7 +4091,7 @@
         <v>1</v>
       </c>
       <c r="J96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K96" t="n">
         <v>0</v>
@@ -4121,12 +4103,10 @@
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>電機機械右下</t>
-        </is>
-      </c>
-      <c r="B97" t="n">
-        <v>0</v>
-      </c>
+          <t>電機機械平</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr"/>
       <c r="C97" t="n">
         <v>0</v>
       </c>
@@ -4134,34 +4114,34 @@
         <v>0</v>
       </c>
       <c r="E97" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F97" t="n">
         <v>0</v>
       </c>
       <c r="G97" t="n">
+        <v>1</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" t="n">
+        <v>1</v>
+      </c>
+      <c r="K97" t="n">
+        <v>1</v>
+      </c>
+      <c r="L97" t="n">
         <v>2</v>
-      </c>
-      <c r="H97" t="n">
-        <v>0</v>
-      </c>
-      <c r="I97" t="n">
-        <v>1</v>
-      </c>
-      <c r="J97" t="n">
-        <v>1</v>
-      </c>
-      <c r="K97" t="n">
-        <v>1</v>
-      </c>
-      <c r="L97" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>電機機械平</t>
+          <t>電腦及週邊設備業右上</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
@@ -4169,95 +4149,95 @@
         <v>0</v>
       </c>
       <c r="D98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F98" t="n">
+        <v>3</v>
+      </c>
+      <c r="G98" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" t="n">
+        <v>1</v>
+      </c>
+      <c r="I98" t="n">
         <v>2</v>
       </c>
-      <c r="G98" t="n">
-        <v>0</v>
-      </c>
-      <c r="H98" t="n">
-        <v>1</v>
-      </c>
-      <c r="I98" t="n">
-        <v>0</v>
-      </c>
       <c r="J98" t="n">
         <v>0</v>
       </c>
       <c r="K98" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右上</t>
+          <t>電腦及週邊設備業右下</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G99" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H99" t="n">
         <v>0</v>
       </c>
       <c r="I99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J99" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K99" t="n">
         <v>0</v>
       </c>
       <c r="L99" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右下</t>
+          <t>電腦及週邊設備業平</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
       <c r="C100" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D100" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E100" t="n">
         <v>0</v>
       </c>
       <c r="F100" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
       </c>
       <c r="H100" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I100" t="n">
         <v>0</v>
@@ -4266,7 +4246,7 @@
         <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L100" t="n">
         <v>0</v>
@@ -4275,7 +4255,7 @@
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業平</t>
+          <t>食品工業右上</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
@@ -4292,13 +4272,13 @@
         <v>0</v>
       </c>
       <c r="G101" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H101" t="n">
         <v>0</v>
       </c>
       <c r="I101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -4307,18 +4287,18 @@
         <v>0</v>
       </c>
       <c r="L101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>食品工業右上</t>
+          <t>食品工業右下</t>
         </is>
       </c>
       <c r="B102" t="inlineStr"/>
       <c r="C102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D102" t="n">
         <v>0</v>
@@ -4351,7 +4331,7 @@
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>食品工業右下</t>
+          <t>食品工業平</t>
         </is>
       </c>
       <c r="B103" t="inlineStr"/>
@@ -4359,7 +4339,7 @@
         <v>0</v>
       </c>
       <c r="D103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E103" t="n">
         <v>0</v>
@@ -4383,44 +4363,6 @@
         <v>0</v>
       </c>
       <c r="L103" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="1" t="inlineStr">
-        <is>
-          <t>食品工業平</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr"/>
-      <c r="C104" t="n">
-        <v>0</v>
-      </c>
-      <c r="D104" t="n">
-        <v>0</v>
-      </c>
-      <c r="E104" t="n">
-        <v>0</v>
-      </c>
-      <c r="F104" t="n">
-        <v>0</v>
-      </c>
-      <c r="G104" t="n">
-        <v>0</v>
-      </c>
-      <c r="H104" t="n">
-        <v>0</v>
-      </c>
-      <c r="I104" t="n">
-        <v>0</v>
-      </c>
-      <c r="J104" t="n">
-        <v>0</v>
-      </c>
-      <c r="K104" t="n">
-        <v>0</v>
-      </c>
-      <c r="L104" t="n">
         <v>0</v>
       </c>
     </row>

--- a/Result/analyze_1.xlsx
+++ b/Result/analyze_1.xlsx
@@ -441,52 +441,52 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-03</t>
         </is>
       </c>
     </row>
@@ -501,31 +501,31 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -536,22 +536,22 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
         <v>1</v>
@@ -560,10 +560,10 @@
         <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -574,31 +574,31 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
         <v>2</v>
       </c>
-      <c r="D4" t="n">
-        <v>1</v>
-      </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
         <v>2</v>
       </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>1</v>
@@ -615,25 +615,25 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>1</v>
@@ -650,7 +650,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -662,7 +662,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -674,7 +674,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -691,13 +691,13 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
@@ -726,31 +726,31 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
         <v>3</v>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>4</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" t="n">
         <v>3</v>
-      </c>
-      <c r="I8" t="n">
-        <v>3</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>4</v>
       </c>
       <c r="L8" t="n">
         <v>2</v>
@@ -802,10 +802,10 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -814,19 +814,19 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
         <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -840,34 +840,34 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
         <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
       </c>
       <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
         <v>3</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -919,16 +919,16 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -937,13 +937,13 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -954,34 +954,34 @@
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E14" t="n">
+        <v>5</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>14</v>
+      </c>
+      <c r="J14" t="n">
+        <v>4</v>
+      </c>
+      <c r="K14" t="n">
+        <v>13</v>
+      </c>
+      <c r="L14" t="n">
         <v>3</v>
-      </c>
-      <c r="F14" t="n">
-        <v>4</v>
-      </c>
-      <c r="G14" t="n">
-        <v>5</v>
-      </c>
-      <c r="H14" t="n">
-        <v>1</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>12</v>
-      </c>
-      <c r="L14" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -995,31 +995,31 @@
         <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
         <v>1</v>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1030,34 +1030,34 @@
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>10</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
         <v>2</v>
-      </c>
-      <c r="G16" t="n">
-        <v>1</v>
-      </c>
-      <c r="H16" t="n">
-        <v>1</v>
-      </c>
-      <c r="I16" t="n">
-        <v>1</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>12</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1106,16 +1106,16 @@
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
         <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -1165,13 +1165,13 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1223,7 +1223,7 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -1238,13 +1238,13 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -1343,22 +1343,22 @@
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -1410,13 +1410,13 @@
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
@@ -1548,7 +1548,7 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -1565,25 +1565,25 @@
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -1606,19 +1606,19 @@
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1790,10 +1790,10 @@
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -1828,13 +1828,13 @@
       </c>
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
@@ -1869,13 +1869,13 @@
         <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1893,7 +1893,7 @@
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2030,13 +2030,13 @@
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -2132,34 +2132,34 @@
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E45" t="n">
         <v>1</v>
       </c>
       <c r="F45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K45" t="n">
         <v>1</v>
       </c>
       <c r="L45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -2170,13 +2170,13 @@
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F46" t="n">
         <v>1</v>
@@ -2185,7 +2185,7 @@
         <v>1</v>
       </c>
       <c r="H46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
         <v>1</v>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D47" t="n">
         <v>0</v>
@@ -2217,25 +2217,25 @@
         <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H47" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K47" t="n">
         <v>1</v>
       </c>
       <c r="L47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -2255,13 +2255,13 @@
         <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I48" t="n">
         <v>0</v>
@@ -2302,13 +2302,13 @@
         <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
@@ -2340,16 +2340,16 @@
         <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -2369,13 +2369,13 @@
         <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I51" t="n">
         <v>0</v>
@@ -2401,13 +2401,13 @@
         <v>0</v>
       </c>
       <c r="D52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E52" t="n">
         <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D53" t="n">
         <v>0</v>
@@ -2463,7 +2463,7 @@
         <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -2477,13 +2477,13 @@
         <v>0</v>
       </c>
       <c r="D54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E54" t="n">
         <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -2609,13 +2609,13 @@
         <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K57" t="n">
         <v>0</v>
       </c>
       <c r="L57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -2746,13 +2746,13 @@
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
       </c>
       <c r="G61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
@@ -2816,31 +2816,31 @@
       </c>
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D63" t="n">
         <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" t="n">
+        <v>1</v>
+      </c>
+      <c r="K63" t="n">
         <v>2</v>
-      </c>
-      <c r="I63" t="n">
-        <v>0</v>
-      </c>
-      <c r="J63" t="n">
-        <v>0</v>
-      </c>
-      <c r="K63" t="n">
-        <v>0</v>
       </c>
       <c r="L63" t="n">
         <v>1</v>
@@ -2866,13 +2866,13 @@
         <v>0</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H64" t="n">
         <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -2892,7 +2892,7 @@
       </c>
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D65" t="n">
         <v>0</v>
@@ -2910,13 +2910,13 @@
         <v>0</v>
       </c>
       <c r="I65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
@@ -2956,7 +2956,9 @@
       <c r="K66" t="n">
         <v>0</v>
       </c>
-      <c r="L66" t="inlineStr"/>
+      <c r="L66" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
@@ -3042,31 +3044,31 @@
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E69" t="n">
+        <v>1</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" t="n">
         <v>2</v>
       </c>
-      <c r="F69" t="n">
-        <v>1</v>
-      </c>
-      <c r="G69" t="n">
-        <v>1</v>
-      </c>
-      <c r="H69" t="n">
-        <v>0</v>
-      </c>
-      <c r="I69" t="n">
-        <v>0</v>
-      </c>
       <c r="J69" t="n">
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L69" t="n">
         <v>0</v>
@@ -3086,16 +3088,16 @@
         <v>1</v>
       </c>
       <c r="E70" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F70" t="n">
         <v>1</v>
       </c>
       <c r="G70" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I70" t="n">
         <v>0</v>
@@ -3107,7 +3109,7 @@
         <v>0</v>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
@@ -3121,7 +3123,7 @@
         <v>0</v>
       </c>
       <c r="D71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E71" t="n">
         <v>0</v>
@@ -3133,7 +3135,7 @@
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I71" t="n">
         <v>0</v>
@@ -3232,16 +3234,16 @@
       </c>
       <c r="B74" t="inlineStr"/>
       <c r="C74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E74" t="n">
         <v>0</v>
       </c>
       <c r="F74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -3256,7 +3258,7 @@
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L74" t="n">
         <v>0</v>
@@ -3270,34 +3272,34 @@
       </c>
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D75" t="n">
         <v>0</v>
       </c>
       <c r="E75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I75" t="n">
         <v>0</v>
       </c>
       <c r="J75" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K75" t="n">
         <v>0</v>
       </c>
       <c r="L75" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -3373,7 +3375,7 @@
         <v>0</v>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -3589,16 +3591,16 @@
         <v>1</v>
       </c>
       <c r="H83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L83" t="n">
         <v>0</v>
@@ -3636,10 +3638,10 @@
         <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -3656,13 +3658,13 @@
         <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F85" t="n">
         <v>0</v>
       </c>
       <c r="G85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H85" t="n">
         <v>0</v>
@@ -3700,13 +3702,13 @@
         <v>0</v>
       </c>
       <c r="G86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H86" t="n">
         <v>0</v>
       </c>
       <c r="I86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -3738,13 +3740,13 @@
         <v>0</v>
       </c>
       <c r="G87" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H87" t="n">
         <v>0</v>
       </c>
       <c r="I87" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -3776,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="G88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H88" t="n">
         <v>0</v>
@@ -3788,7 +3790,7 @@
         <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L88" t="n">
         <v>0</v>
@@ -3808,28 +3810,28 @@
         <v>1</v>
       </c>
       <c r="E89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I89" t="n">
         <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K89" t="n">
         <v>0</v>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
@@ -3843,7 +3845,7 @@
         <v>0</v>
       </c>
       <c r="D90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E90" t="n">
         <v>0</v>
@@ -3864,7 +3866,7 @@
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L90" t="n">
         <v>0</v>
@@ -3881,19 +3883,19 @@
         <v>0</v>
       </c>
       <c r="D91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E91" t="n">
         <v>0</v>
       </c>
       <c r="F91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
       </c>
       <c r="H91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I91" t="n">
         <v>0</v>
@@ -3905,7 +3907,7 @@
         <v>0</v>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
@@ -3916,34 +3918,34 @@
       </c>
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D92" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E92" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F92" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G92" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H92" t="n">
+        <v>3</v>
+      </c>
+      <c r="I92" t="n">
+        <v>6</v>
+      </c>
+      <c r="J92" t="n">
+        <v>6</v>
+      </c>
+      <c r="K92" t="n">
+        <v>3</v>
+      </c>
+      <c r="L92" t="n">
         <v>8</v>
-      </c>
-      <c r="I92" t="n">
-        <v>0</v>
-      </c>
-      <c r="J92" t="n">
-        <v>3</v>
-      </c>
-      <c r="K92" t="n">
-        <v>7</v>
-      </c>
-      <c r="L92" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="93">
@@ -3952,29 +3954,27 @@
           <t>電子零組件業右下</t>
         </is>
       </c>
-      <c r="B93" t="n">
-        <v>0</v>
-      </c>
+      <c r="B93" t="inlineStr"/>
       <c r="C93" t="n">
+        <v>2</v>
+      </c>
+      <c r="D93" t="n">
         <v>3</v>
-      </c>
-      <c r="D93" t="n">
-        <v>2</v>
       </c>
       <c r="E93" t="n">
         <v>3</v>
       </c>
       <c r="F93" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G93" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I93" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -3994,31 +3994,31 @@
       </c>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D94" t="n">
+        <v>4</v>
+      </c>
+      <c r="E94" t="n">
+        <v>1</v>
+      </c>
+      <c r="F94" t="n">
         <v>2</v>
       </c>
-      <c r="E94" t="n">
-        <v>5</v>
-      </c>
-      <c r="F94" t="n">
-        <v>3</v>
-      </c>
       <c r="G94" t="n">
         <v>0</v>
       </c>
       <c r="H94" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" t="n">
+        <v>4</v>
+      </c>
+      <c r="J94" t="n">
+        <v>1</v>
+      </c>
+      <c r="K94" t="n">
         <v>2</v>
-      </c>
-      <c r="I94" t="n">
-        <v>0</v>
-      </c>
-      <c r="J94" t="n">
-        <v>0</v>
-      </c>
-      <c r="K94" t="n">
-        <v>3</v>
       </c>
       <c r="L94" t="n">
         <v>1</v>
@@ -4032,34 +4032,34 @@
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" t="n">
         <v>2</v>
       </c>
-      <c r="D95" t="n">
-        <v>1</v>
-      </c>
       <c r="E95" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F95" t="n">
+        <v>1</v>
+      </c>
+      <c r="G95" t="n">
+        <v>1</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" t="n">
+        <v>1</v>
+      </c>
+      <c r="J95" t="n">
+        <v>3</v>
+      </c>
+      <c r="K95" t="n">
+        <v>4</v>
+      </c>
+      <c r="L95" t="n">
         <v>2</v>
-      </c>
-      <c r="G95" t="n">
-        <v>1</v>
-      </c>
-      <c r="H95" t="n">
-        <v>1</v>
-      </c>
-      <c r="I95" t="n">
-        <v>1</v>
-      </c>
-      <c r="J95" t="n">
-        <v>0</v>
-      </c>
-      <c r="K95" t="n">
-        <v>1</v>
-      </c>
-      <c r="L95" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="96">
@@ -4068,27 +4068,29 @@
           <t>電機機械右下</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr"/>
+      <c r="B96" t="n">
+        <v>0</v>
+      </c>
       <c r="C96" t="n">
         <v>0</v>
       </c>
       <c r="D96" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E96" t="n">
         <v>0</v>
       </c>
       <c r="F96" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -4108,34 +4110,34 @@
       </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D97" t="n">
         <v>0</v>
       </c>
       <c r="E97" t="n">
+        <v>0</v>
+      </c>
+      <c r="F97" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
+        <v>1</v>
+      </c>
+      <c r="I97" t="n">
+        <v>1</v>
+      </c>
+      <c r="J97" t="n">
         <v>2</v>
       </c>
-      <c r="F97" t="n">
-        <v>0</v>
-      </c>
-      <c r="G97" t="n">
-        <v>1</v>
-      </c>
-      <c r="H97" t="n">
-        <v>0</v>
-      </c>
-      <c r="I97" t="n">
-        <v>0</v>
-      </c>
-      <c r="J97" t="n">
-        <v>1</v>
-      </c>
       <c r="K97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L97" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98">
@@ -4146,34 +4148,34 @@
       </c>
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D98" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F98" t="n">
+        <v>1</v>
+      </c>
+      <c r="G98" t="n">
+        <v>2</v>
+      </c>
+      <c r="H98" t="n">
+        <v>0</v>
+      </c>
+      <c r="I98" t="n">
         <v>3</v>
       </c>
-      <c r="G98" t="n">
-        <v>0</v>
-      </c>
-      <c r="H98" t="n">
-        <v>1</v>
-      </c>
-      <c r="I98" t="n">
+      <c r="J98" t="n">
+        <v>0</v>
+      </c>
+      <c r="K98" t="n">
         <v>2</v>
       </c>
-      <c r="J98" t="n">
-        <v>0</v>
-      </c>
-      <c r="K98" t="n">
-        <v>3</v>
-      </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99">
@@ -4182,21 +4184,23 @@
           <t>電腦及週邊設備業右下</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr"/>
+      <c r="B99" t="n">
+        <v>0</v>
+      </c>
       <c r="C99" t="n">
+        <v>0</v>
+      </c>
+      <c r="D99" t="n">
+        <v>0</v>
+      </c>
+      <c r="E99" t="n">
         <v>2</v>
       </c>
-      <c r="D99" t="n">
-        <v>0</v>
-      </c>
-      <c r="E99" t="n">
-        <v>0</v>
-      </c>
       <c r="F99" t="n">
         <v>0</v>
       </c>
       <c r="G99" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H99" t="n">
         <v>0</v>
@@ -4222,34 +4226,34 @@
       </c>
       <c r="B100" t="inlineStr"/>
       <c r="C100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D100" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E100" t="n">
         <v>0</v>
       </c>
       <c r="F100" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
       </c>
       <c r="H100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101">
@@ -4287,7 +4291,7 @@
         <v>0</v>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102">
@@ -4298,7 +4302,7 @@
       </c>
       <c r="B102" t="inlineStr"/>
       <c r="C102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D102" t="n">
         <v>0</v>

--- a/Result/analyze_1.xlsx
+++ b/Result/analyze_1.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L103"/>
+  <dimension ref="A1:K103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,52 +441,47 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>2025-10-03</t>
+          <t>2025-10-07</t>
         </is>
       </c>
     </row>
@@ -501,31 +496,28 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K2" t="n">
         <v>1</v>
-      </c>
-      <c r="L2" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -536,16 +528,16 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
@@ -554,15 +546,12 @@
         <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -574,33 +563,30 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
         <v>2</v>
       </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -615,30 +601,27 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -656,7 +639,7 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -668,16 +651,13 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -688,10 +668,10 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
@@ -700,21 +680,18 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -726,25 +703,25 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
         <v>3</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>4</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" t="n">
         <v>3</v>
-      </c>
-      <c r="G8" t="n">
-        <v>3</v>
-      </c>
-      <c r="H8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" t="n">
-        <v>4</v>
       </c>
       <c r="J8" t="n">
         <v>2</v>
@@ -752,9 +729,6 @@
       <c r="K8" t="n">
         <v>3</v>
       </c>
-      <c r="L8" t="n">
-        <v>2</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -788,10 +762,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -808,27 +779,24 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
         <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -840,34 +808,31 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
         <v>2</v>
       </c>
-      <c r="D11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>1</v>
-      </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
         <v>3</v>
       </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
       <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -876,7 +841,9 @@
           <t>化學工業右下</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
+      <c r="B12" t="n">
+        <v>0</v>
+      </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
@@ -902,9 +869,6 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -916,33 +880,30 @@
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -954,34 +915,31 @@
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>15</v>
+      </c>
+      <c r="H14" t="n">
         <v>4</v>
       </c>
-      <c r="E14" t="n">
-        <v>5</v>
-      </c>
-      <c r="F14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
       <c r="I14" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J14" t="n">
         <v>4</v>
       </c>
       <c r="K14" t="n">
-        <v>13</v>
-      </c>
-      <c r="L14" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -992,34 +950,31 @@
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D15" t="n">
         <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -1030,34 +985,31 @@
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>9</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
         <v>2</v>
       </c>
-      <c r="E16" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" t="n">
-        <v>1</v>
-      </c>
-      <c r="G16" t="n">
-        <v>1</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>10</v>
-      </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -1094,9 +1046,6 @@
       <c r="K17" t="n">
         <v>0</v>
       </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -1106,10 +1055,10 @@
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -1130,10 +1079,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1159,18 +1105,15 @@
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1208,9 +1151,6 @@
       <c r="K20" t="n">
         <v>0</v>
       </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
@@ -1232,21 +1172,18 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1284,9 +1221,6 @@
       <c r="K22" t="n">
         <v>0</v>
       </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
@@ -1322,9 +1256,6 @@
       <c r="K23" t="n">
         <v>0</v>
       </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
@@ -1337,30 +1268,27 @@
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1398,9 +1326,6 @@
       <c r="K25" t="n">
         <v>0</v>
       </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
@@ -1410,7 +1335,7 @@
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
@@ -1434,10 +1359,7 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1472,10 +1394,7 @@
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -1512,9 +1431,6 @@
       <c r="K28" t="n">
         <v>0</v>
       </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
@@ -1524,33 +1440,30 @@
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1565,19 +1478,19 @@
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -1586,9 +1499,6 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1603,13 +1513,13 @@
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E31" t="n">
         <v>1</v>
       </c>
       <c r="F31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
         <v>1</v>
@@ -1624,10 +1534,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -1664,9 +1571,6 @@
       <c r="K32" t="n">
         <v>0</v>
       </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
@@ -1702,9 +1606,6 @@
       <c r="K33" t="n">
         <v>0</v>
       </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
@@ -1712,7 +1613,9 @@
           <t>水泥工業右下</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr"/>
+      <c r="B34" t="n">
+        <v>0</v>
+      </c>
       <c r="C34" t="n">
         <v>0</v>
       </c>
@@ -1738,9 +1641,6 @@
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1778,9 +1678,6 @@
       <c r="K35" t="n">
         <v>0</v>
       </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
@@ -1811,13 +1708,10 @@
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
-      </c>
-      <c r="L36" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -1828,7 +1722,7 @@
       </c>
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
@@ -1852,10 +1746,7 @@
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -1869,7 +1760,7 @@
         <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
@@ -1887,13 +1778,10 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
-      </c>
-      <c r="L38" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -1930,9 +1818,6 @@
       <c r="K39" t="n">
         <v>0</v>
       </c>
-      <c r="L39" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
@@ -1968,9 +1853,6 @@
       <c r="K40" t="n">
         <v>0</v>
       </c>
-      <c r="L40" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
@@ -2006,9 +1888,6 @@
       <c r="K41" t="n">
         <v>0</v>
       </c>
-      <c r="L41" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
@@ -2024,13 +1903,13 @@
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -2042,10 +1921,7 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
-      </c>
-      <c r="L42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2082,9 +1958,6 @@
       <c r="K43" t="n">
         <v>0</v>
       </c>
-      <c r="L43" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
@@ -2118,10 +1991,7 @@
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2135,30 +2005,27 @@
         <v>1</v>
       </c>
       <c r="D45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I45" t="n">
         <v>1</v>
       </c>
       <c r="J45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K45" t="n">
-        <v>1</v>
-      </c>
-      <c r="L45" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2168,9 +2035,11 @@
           <t>生技醫療業右下</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr"/>
+      <c r="B46" t="n">
+        <v>0</v>
+      </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D46" t="n">
         <v>1</v>
@@ -2179,7 +2048,7 @@
         <v>1</v>
       </c>
       <c r="F46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G46" t="n">
         <v>1</v>
@@ -2188,15 +2057,12 @@
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2211,31 +2077,28 @@
         <v>0</v>
       </c>
       <c r="D47" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F47" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>1</v>
-      </c>
-      <c r="L47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -2249,13 +2112,13 @@
         <v>0</v>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E48" t="n">
         <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -2270,10 +2133,7 @@
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -2282,7 +2142,9 @@
           <t>紡織纖維右下</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr"/>
+      <c r="B49" t="n">
+        <v>0</v>
+      </c>
       <c r="C49" t="n">
         <v>0</v>
       </c>
@@ -2296,21 +2158,18 @@
         <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2334,21 +2193,18 @@
         <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>0</v>
-      </c>
-      <c r="L50" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2363,13 +2219,13 @@
         <v>0</v>
       </c>
       <c r="D51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E51" t="n">
         <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -2381,12 +2237,9 @@
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K51" t="n">
-        <v>0</v>
-      </c>
-      <c r="L51" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2401,7 +2254,7 @@
         <v>0</v>
       </c>
       <c r="D52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E52" t="n">
         <v>0</v>
@@ -2422,9 +2275,6 @@
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>0</v>
-      </c>
-      <c r="L52" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2460,9 +2310,6 @@
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>0</v>
-      </c>
-      <c r="L53" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2477,7 +2324,7 @@
         <v>0</v>
       </c>
       <c r="D54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E54" t="n">
         <v>0</v>
@@ -2498,9 +2345,6 @@
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2538,9 +2382,6 @@
       <c r="K55" t="n">
         <v>0</v>
       </c>
-      <c r="L55" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
@@ -2576,9 +2417,6 @@
       <c r="K56" t="n">
         <v>0</v>
       </c>
-      <c r="L56" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
@@ -2603,18 +2441,15 @@
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I57" t="n">
         <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>0</v>
-      </c>
-      <c r="L57" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2650,10 +2485,7 @@
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>0</v>
-      </c>
-      <c r="L58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -2690,9 +2522,6 @@
       <c r="K59" t="n">
         <v>0</v>
       </c>
-      <c r="L59" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
@@ -2728,9 +2557,6 @@
       <c r="K60" t="n">
         <v>0</v>
       </c>
-      <c r="L60" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
@@ -2740,13 +2566,13 @@
       </c>
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D61" t="n">
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
@@ -2764,9 +2590,6 @@
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>0</v>
-      </c>
-      <c r="L61" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2804,9 +2627,6 @@
       <c r="K62" t="n">
         <v>0</v>
       </c>
-      <c r="L62" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
@@ -2816,34 +2636,31 @@
       </c>
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E63" t="n">
         <v>0</v>
       </c>
       <c r="F63" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" t="n">
+        <v>1</v>
+      </c>
+      <c r="I63" t="n">
         <v>2</v>
       </c>
-      <c r="G63" t="n">
-        <v>0</v>
-      </c>
-      <c r="H63" t="n">
-        <v>0</v>
-      </c>
-      <c r="I63" t="n">
-        <v>0</v>
-      </c>
       <c r="J63" t="n">
         <v>1</v>
       </c>
       <c r="K63" t="n">
-        <v>2</v>
-      </c>
-      <c r="L63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -2860,13 +2677,13 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
       </c>
       <c r="G64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H64" t="n">
         <v>0</v>
@@ -2878,9 +2695,6 @@
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
-      </c>
-      <c r="L64" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2904,21 +2718,18 @@
         <v>0</v>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>
       </c>
       <c r="I65" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>0</v>
-      </c>
-      <c r="L65" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2956,9 +2767,6 @@
       <c r="K66" t="n">
         <v>0</v>
       </c>
-      <c r="L66" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
@@ -2994,9 +2802,6 @@
       <c r="K67" t="n">
         <v>0</v>
       </c>
-      <c r="L67" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
@@ -3032,9 +2837,6 @@
       <c r="K68" t="n">
         <v>0</v>
       </c>
-      <c r="L68" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
@@ -3044,33 +2846,30 @@
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="n">
+        <v>1</v>
+      </c>
+      <c r="D69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" t="n">
         <v>2</v>
       </c>
-      <c r="D69" t="n">
-        <v>1</v>
-      </c>
-      <c r="E69" t="n">
-        <v>1</v>
-      </c>
-      <c r="F69" t="n">
-        <v>0</v>
-      </c>
-      <c r="G69" t="n">
-        <v>0</v>
-      </c>
       <c r="H69" t="n">
         <v>0</v>
       </c>
       <c r="I69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>0</v>
-      </c>
-      <c r="L69" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3080,18 +2879,20 @@
           <t>通信網路業右下</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr"/>
+      <c r="B70" t="n">
+        <v>0</v>
+      </c>
       <c r="C70" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D70" t="n">
         <v>1</v>
       </c>
       <c r="E70" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -3103,13 +2904,10 @@
         <v>0</v>
       </c>
       <c r="J70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K70" t="n">
         <v>0</v>
-      </c>
-      <c r="L70" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="71">
@@ -3129,7 +2927,7 @@
         <v>0</v>
       </c>
       <c r="F71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -3141,13 +2939,10 @@
         <v>0</v>
       </c>
       <c r="J71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K71" t="n">
-        <v>0</v>
-      </c>
-      <c r="L71" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="72">
@@ -3184,9 +2979,6 @@
       <c r="K72" t="n">
         <v>0</v>
       </c>
-      <c r="L72" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
@@ -3222,9 +3014,6 @@
       <c r="K73" t="n">
         <v>0</v>
       </c>
-      <c r="L73" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
@@ -3237,7 +3026,7 @@
         <v>0</v>
       </c>
       <c r="D74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E74" t="n">
         <v>0</v>
@@ -3252,15 +3041,12 @@
         <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>1</v>
-      </c>
-      <c r="L74" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3272,33 +3058,30 @@
       </c>
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E75" t="n">
         <v>0</v>
       </c>
       <c r="F75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I75" t="n">
         <v>0</v>
       </c>
       <c r="J75" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>0</v>
-      </c>
-      <c r="L75" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3336,9 +3119,6 @@
       <c r="K76" t="n">
         <v>0</v>
       </c>
-      <c r="L76" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
@@ -3374,9 +3154,6 @@
       <c r="K77" t="n">
         <v>0</v>
       </c>
-      <c r="L77" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
@@ -3412,9 +3189,6 @@
       <c r="K78" t="n">
         <v>0</v>
       </c>
-      <c r="L78" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
@@ -3445,12 +3219,9 @@
         <v>0</v>
       </c>
       <c r="J79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K79" t="n">
-        <v>0</v>
-      </c>
-      <c r="L79" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3488,9 +3259,6 @@
       <c r="K80" t="n">
         <v>0</v>
       </c>
-      <c r="L80" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
@@ -3526,9 +3294,6 @@
       <c r="K81" t="n">
         <v>0</v>
       </c>
-      <c r="L81" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
@@ -3564,9 +3329,6 @@
       <c r="K82" t="n">
         <v>0</v>
       </c>
-      <c r="L82" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
@@ -3582,16 +3344,16 @@
         <v>0</v>
       </c>
       <c r="E83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I83" t="n">
         <v>0</v>
@@ -3600,10 +3362,7 @@
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>0</v>
-      </c>
-      <c r="L83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
@@ -3632,15 +3391,12 @@
         <v>0</v>
       </c>
       <c r="I84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>1</v>
-      </c>
-      <c r="L84" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3652,7 +3408,7 @@
       </c>
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D85" t="n">
         <v>0</v>
@@ -3667,18 +3423,15 @@
         <v>1</v>
       </c>
       <c r="H85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>0</v>
-      </c>
-      <c r="L85" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3696,13 +3449,13 @@
         <v>0</v>
       </c>
       <c r="E86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F86" t="n">
         <v>0</v>
       </c>
       <c r="G86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H86" t="n">
         <v>0</v>
@@ -3714,10 +3467,7 @@
         <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>0</v>
-      </c>
-      <c r="L86" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
@@ -3734,13 +3484,13 @@
         <v>0</v>
       </c>
       <c r="E87" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F87" t="n">
         <v>0</v>
       </c>
       <c r="G87" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H87" t="n">
         <v>0</v>
@@ -3752,10 +3502,7 @@
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>0</v>
-      </c>
-      <c r="L87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
@@ -3772,7 +3519,7 @@
         <v>0</v>
       </c>
       <c r="E88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F88" t="n">
         <v>0</v>
@@ -3784,15 +3531,12 @@
         <v>0</v>
       </c>
       <c r="I88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>0</v>
-      </c>
-      <c r="L88" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3804,34 +3548,31 @@
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I89" t="n">
         <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K89" t="n">
         <v>0</v>
-      </c>
-      <c r="L89" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="90">
@@ -3860,16 +3601,13 @@
         <v>0</v>
       </c>
       <c r="I90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>1</v>
-      </c>
-      <c r="L90" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="91">
@@ -3883,13 +3621,13 @@
         <v>0</v>
       </c>
       <c r="D91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E91" t="n">
         <v>0</v>
       </c>
       <c r="F91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -3901,13 +3639,10 @@
         <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K91" t="n">
         <v>0</v>
-      </c>
-      <c r="L91" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="92">
@@ -3918,34 +3653,31 @@
       </c>
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D92" t="n">
         <v>8</v>
       </c>
       <c r="E92" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" t="n">
         <v>3</v>
       </c>
-      <c r="F92" t="n">
-        <v>8</v>
-      </c>
       <c r="G92" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H92" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I92" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J92" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K92" t="n">
-        <v>3</v>
-      </c>
-      <c r="L92" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="93">
@@ -3956,19 +3688,19 @@
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="n">
+        <v>3</v>
+      </c>
+      <c r="D93" t="n">
+        <v>1</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" t="n">
         <v>2</v>
-      </c>
-      <c r="D93" t="n">
-        <v>3</v>
-      </c>
-      <c r="E93" t="n">
-        <v>3</v>
-      </c>
-      <c r="F93" t="n">
-        <v>1</v>
-      </c>
-      <c r="G93" t="n">
-        <v>0</v>
       </c>
       <c r="H93" t="n">
         <v>0</v>
@@ -3980,10 +3712,7 @@
         <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>2</v>
-      </c>
-      <c r="L93" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="94">
@@ -3994,33 +3723,30 @@
       </c>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D94" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F94" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G94" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I94" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J94" t="n">
         <v>1</v>
       </c>
       <c r="K94" t="n">
-        <v>2</v>
-      </c>
-      <c r="L94" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4032,33 +3758,30 @@
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D95" t="n">
+        <v>1</v>
+      </c>
+      <c r="E95" t="n">
+        <v>1</v>
+      </c>
+      <c r="F95" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" t="n">
+        <v>1</v>
+      </c>
+      <c r="H95" t="n">
+        <v>3</v>
+      </c>
+      <c r="I95" t="n">
+        <v>4</v>
+      </c>
+      <c r="J95" t="n">
         <v>2</v>
       </c>
-      <c r="E95" t="n">
-        <v>2</v>
-      </c>
-      <c r="F95" t="n">
-        <v>1</v>
-      </c>
-      <c r="G95" t="n">
-        <v>1</v>
-      </c>
-      <c r="H95" t="n">
-        <v>0</v>
-      </c>
-      <c r="I95" t="n">
-        <v>1</v>
-      </c>
-      <c r="J95" t="n">
-        <v>3</v>
-      </c>
       <c r="K95" t="n">
-        <v>4</v>
-      </c>
-      <c r="L95" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4068,23 +3791,21 @@
           <t>電機機械右下</t>
         </is>
       </c>
-      <c r="B96" t="n">
-        <v>0</v>
-      </c>
+      <c r="B96" t="inlineStr"/>
       <c r="C96" t="n">
         <v>0</v>
       </c>
       <c r="D96" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -4096,9 +3817,6 @@
         <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>0</v>
-      </c>
-      <c r="L96" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4110,34 +3828,31 @@
       </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" t="n">
+        <v>0</v>
+      </c>
+      <c r="E97" t="n">
+        <v>0</v>
+      </c>
+      <c r="F97" t="n">
+        <v>1</v>
+      </c>
+      <c r="G97" t="n">
+        <v>1</v>
+      </c>
+      <c r="H97" t="n">
         <v>2</v>
       </c>
-      <c r="D97" t="n">
-        <v>0</v>
-      </c>
-      <c r="E97" t="n">
-        <v>0</v>
-      </c>
-      <c r="F97" t="n">
-        <v>0</v>
-      </c>
-      <c r="G97" t="n">
-        <v>0</v>
-      </c>
-      <c r="H97" t="n">
-        <v>1</v>
-      </c>
       <c r="I97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J97" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K97" t="n">
-        <v>2</v>
-      </c>
-      <c r="L97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -4148,34 +3863,31 @@
       </c>
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D98" t="n">
+        <v>1</v>
+      </c>
+      <c r="E98" t="n">
+        <v>2</v>
+      </c>
+      <c r="F98" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" t="n">
         <v>3</v>
       </c>
-      <c r="E98" t="n">
-        <v>0</v>
-      </c>
-      <c r="F98" t="n">
-        <v>1</v>
-      </c>
-      <c r="G98" t="n">
+      <c r="H98" t="n">
+        <v>0</v>
+      </c>
+      <c r="I98" t="n">
         <v>2</v>
       </c>
-      <c r="H98" t="n">
-        <v>0</v>
-      </c>
-      <c r="I98" t="n">
-        <v>3</v>
-      </c>
       <c r="J98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K98" t="n">
-        <v>2</v>
-      </c>
-      <c r="L98" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="99">
@@ -4184,17 +3896,15 @@
           <t>電腦及週邊設備業右下</t>
         </is>
       </c>
-      <c r="B99" t="n">
-        <v>0</v>
-      </c>
+      <c r="B99" t="inlineStr"/>
       <c r="C99" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D99" t="n">
         <v>0</v>
       </c>
       <c r="E99" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F99" t="n">
         <v>0</v>
@@ -4212,9 +3922,6 @@
         <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>0</v>
-      </c>
-      <c r="L99" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4229,31 +3936,28 @@
         <v>0</v>
       </c>
       <c r="D100" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E100" t="n">
         <v>0</v>
       </c>
       <c r="F100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H100" t="n">
         <v>0</v>
       </c>
       <c r="I100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K100" t="n">
-        <v>0</v>
-      </c>
-      <c r="L100" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="101">
@@ -4285,13 +3989,10 @@
         <v>0</v>
       </c>
       <c r="J101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K101" t="n">
         <v>0</v>
-      </c>
-      <c r="L101" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="102">
@@ -4328,9 +4029,6 @@
       <c r="K102" t="n">
         <v>0</v>
       </c>
-      <c r="L102" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
@@ -4364,9 +4062,6 @@
         <v>0</v>
       </c>
       <c r="K103" t="n">
-        <v>0</v>
-      </c>
-      <c r="L103" t="n">
         <v>0</v>
       </c>
     </row>

--- a/Result/analyze_1.xlsx
+++ b/Result/analyze_1.xlsx
@@ -441,47 +441,47 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
     </row>
@@ -499,7 +499,7 @@
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -508,16 +508,16 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -526,12 +526,14 @@
           <t>光電業右下</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -543,7 +545,7 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -572,16 +574,16 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -604,19 +606,19 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -633,7 +635,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -648,16 +650,16 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -668,16 +670,16 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -689,10 +691,10 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -703,31 +705,31 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
         <v>3</v>
       </c>
       <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>4</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" t="n">
         <v>3</v>
       </c>
-      <c r="F8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" t="n">
-        <v>4</v>
-      </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>2</v>
-      </c>
-      <c r="I8" t="n">
-        <v>3</v>
       </c>
       <c r="J8" t="n">
         <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -736,7 +738,9 @@
           <t>其他電子業右下</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
@@ -759,7 +763,7 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
         <v>1</v>
@@ -776,7 +780,7 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
         <v>1</v>
@@ -785,7 +789,7 @@
         <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -794,7 +798,7 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -811,28 +815,28 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -841,9 +845,7 @@
           <t>化學工業右下</t>
         </is>
       </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
         <v>0</v>
       </c>
@@ -880,7 +882,7 @@
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -889,13 +891,13 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -915,31 +917,31 @@
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G14" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="H14" t="n">
+        <v>12</v>
+      </c>
+      <c r="I14" t="n">
         <v>4</v>
       </c>
-      <c r="I14" t="n">
-        <v>12</v>
-      </c>
       <c r="J14" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="K14" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -959,7 +961,7 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
@@ -968,13 +970,13 @@
         <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K15" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -988,28 +990,28 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G16" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1076,10 +1078,10 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1102,10 +1104,10 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -1169,10 +1171,10 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -1263,21 +1265,23 @@
           <t>建材營造右下</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="n">
+        <v>0</v>
+      </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1356,7 +1360,7 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" t="n">
         <v>1</v>
@@ -1391,10 +1395,10 @@
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -1440,13 +1444,13 @@
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -1461,10 +1465,10 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -1481,10 +1485,10 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1510,19 +1514,19 @@
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -1534,7 +1538,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -1613,9 +1617,7 @@
           <t>水泥工業右下</t>
         </is>
       </c>
-      <c r="B34" t="n">
-        <v>0</v>
-      </c>
+      <c r="B34" t="inlineStr"/>
       <c r="C34" t="n">
         <v>0</v>
       </c>
@@ -1705,10 +1707,10 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -1720,7 +1722,9 @@
           <t>汽車工業右下</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr"/>
+      <c r="B37" t="n">
+        <v>0</v>
+      </c>
       <c r="C37" t="n">
         <v>0</v>
       </c>
@@ -1743,10 +1747,10 @@
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -1775,10 +1779,10 @@
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -1900,10 +1904,10 @@
         <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -1918,10 +1922,10 @@
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -1988,10 +1992,10 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2005,28 +2009,28 @@
         <v>1</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G45" t="n">
         <v>1</v>
       </c>
       <c r="H45" t="n">
+        <v>1</v>
+      </c>
+      <c r="I45" t="n">
+        <v>1</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
         <v>2</v>
-      </c>
-      <c r="I45" t="n">
-        <v>1</v>
-      </c>
-      <c r="J45" t="n">
-        <v>1</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -2045,13 +2049,13 @@
         <v>1</v>
       </c>
       <c r="E46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
@@ -2074,25 +2078,25 @@
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D47" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" t="n">
         <v>3</v>
       </c>
-      <c r="E47" t="n">
-        <v>1</v>
-      </c>
-      <c r="F47" t="n">
-        <v>1</v>
-      </c>
-      <c r="G47" t="n">
-        <v>0</v>
-      </c>
       <c r="H47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -2109,10 +2113,10 @@
       </c>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E48" t="n">
         <v>0</v>
@@ -2130,10 +2134,10 @@
         <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -2142,9 +2146,7 @@
           <t>紡織纖維右下</t>
         </is>
       </c>
-      <c r="B49" t="n">
-        <v>0</v>
-      </c>
+      <c r="B49" t="inlineStr"/>
       <c r="C49" t="n">
         <v>0</v>
       </c>
@@ -2155,10 +2157,10 @@
         <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
@@ -2170,7 +2172,7 @@
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -2190,13 +2192,13 @@
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G50" t="n">
         <v>1</v>
       </c>
       <c r="H50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I50" t="n">
         <v>0</v>
@@ -2216,10 +2218,10 @@
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E51" t="n">
         <v>0</v>
@@ -2237,10 +2239,10 @@
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -2304,13 +2306,13 @@
         <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -2438,10 +2440,10 @@
         <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I57" t="n">
         <v>0</v>
@@ -2459,7 +2461,9 @@
           <t>觀光事業右下</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr"/>
+      <c r="B58" t="n">
+        <v>0</v>
+      </c>
       <c r="C58" t="n">
         <v>0</v>
       </c>
@@ -2482,7 +2486,7 @@
         <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K58" t="n">
         <v>1</v>
@@ -2566,7 +2570,7 @@
       </c>
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D61" t="n">
         <v>0</v>
@@ -2636,28 +2640,28 @@
       </c>
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D63" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" t="n">
+        <v>1</v>
+      </c>
+      <c r="H63" t="n">
         <v>2</v>
       </c>
-      <c r="E63" t="n">
-        <v>0</v>
-      </c>
-      <c r="F63" t="n">
-        <v>0</v>
-      </c>
-      <c r="G63" t="n">
-        <v>0</v>
-      </c>
-      <c r="H63" t="n">
-        <v>1</v>
-      </c>
       <c r="I63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K63" t="n">
         <v>0</v>
@@ -2674,10 +2678,10 @@
         <v>0</v>
       </c>
       <c r="D64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -2715,10 +2719,10 @@
         <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G65" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>
@@ -2846,7 +2850,7 @@
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D69" t="n">
         <v>0</v>
@@ -2855,10 +2859,10 @@
         <v>0</v>
       </c>
       <c r="F69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -2879,14 +2883,12 @@
           <t>通信網路業右下</t>
         </is>
       </c>
-      <c r="B70" t="n">
-        <v>0</v>
-      </c>
+      <c r="B70" t="inlineStr"/>
       <c r="C70" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E70" t="n">
         <v>0</v>
@@ -2901,10 +2903,10 @@
         <v>0</v>
       </c>
       <c r="I70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K70" t="n">
         <v>0</v>
@@ -2918,10 +2920,10 @@
       </c>
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E71" t="n">
         <v>0</v>
@@ -2939,10 +2941,10 @@
         <v>0</v>
       </c>
       <c r="J71" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K71" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -3038,10 +3040,10 @@
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -3058,10 +3060,10 @@
       </c>
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E75" t="n">
         <v>0</v>
@@ -3070,10 +3072,10 @@
         <v>0</v>
       </c>
       <c r="G75" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H75" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I75" t="n">
         <v>0</v>
@@ -3216,10 +3218,10 @@
         <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K79" t="n">
         <v>0</v>
@@ -3341,13 +3343,13 @@
         <v>0</v>
       </c>
       <c r="D83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E83" t="n">
         <v>1</v>
       </c>
       <c r="F83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -3359,10 +3361,10 @@
         <v>0</v>
       </c>
       <c r="J83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -3371,7 +3373,9 @@
           <t>鋼鐵工業右下</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr"/>
+      <c r="B84" t="n">
+        <v>0</v>
+      </c>
       <c r="C84" t="n">
         <v>0</v>
       </c>
@@ -3388,10 +3392,10 @@
         <v>0</v>
       </c>
       <c r="H84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -3408,22 +3412,22 @@
       </c>
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G85" t="n">
         <v>1</v>
       </c>
       <c r="H85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I85" t="n">
         <v>0</v>
@@ -3446,10 +3450,10 @@
         <v>0</v>
       </c>
       <c r="D86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F86" t="n">
         <v>0</v>
@@ -3464,10 +3468,10 @@
         <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K86" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -3481,10 +3485,10 @@
         <v>0</v>
       </c>
       <c r="D87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E87" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F87" t="n">
         <v>0</v>
@@ -3502,7 +3506,7 @@
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -3516,16 +3520,16 @@
         <v>0</v>
       </c>
       <c r="D88" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H88" t="n">
         <v>0</v>
@@ -3534,10 +3538,10 @@
         <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
@@ -3548,16 +3552,16 @@
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D89" t="n">
         <v>0</v>
       </c>
       <c r="E89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -3566,13 +3570,13 @@
         <v>0</v>
       </c>
       <c r="I89" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
@@ -3581,7 +3585,9 @@
           <t>電子通路業右下</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr"/>
+      <c r="B90" t="n">
+        <v>0</v>
+      </c>
       <c r="C90" t="n">
         <v>0</v>
       </c>
@@ -3598,16 +3604,16 @@
         <v>0</v>
       </c>
       <c r="H90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J90" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K90" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
@@ -3618,10 +3624,10 @@
       </c>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E91" t="n">
         <v>0</v>
@@ -3642,7 +3648,7 @@
         <v>1</v>
       </c>
       <c r="K91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
@@ -3653,31 +3659,31 @@
       </c>
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="n">
+        <v>8</v>
+      </c>
+      <c r="D92" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" t="n">
         <v>3</v>
       </c>
-      <c r="D92" t="n">
-        <v>8</v>
-      </c>
-      <c r="E92" t="n">
-        <v>0</v>
-      </c>
       <c r="F92" t="n">
+        <v>7</v>
+      </c>
+      <c r="G92" t="n">
+        <v>6</v>
+      </c>
+      <c r="H92" t="n">
+        <v>4</v>
+      </c>
+      <c r="I92" t="n">
+        <v>9</v>
+      </c>
+      <c r="J92" t="n">
+        <v>4</v>
+      </c>
+      <c r="K92" t="n">
         <v>3</v>
-      </c>
-      <c r="G92" t="n">
-        <v>7</v>
-      </c>
-      <c r="H92" t="n">
-        <v>6</v>
-      </c>
-      <c r="I92" t="n">
-        <v>4</v>
-      </c>
-      <c r="J92" t="n">
-        <v>9</v>
-      </c>
-      <c r="K92" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="93">
@@ -3686,33 +3692,35 @@
           <t>電子零組件業右下</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr"/>
+      <c r="B93" t="n">
+        <v>0</v>
+      </c>
       <c r="C93" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E93" t="n">
         <v>0</v>
       </c>
       <c r="F93" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G93" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" t="n">
         <v>2</v>
       </c>
-      <c r="H93" t="n">
-        <v>0</v>
-      </c>
       <c r="I93" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" t="n">
         <v>2</v>
       </c>
-      <c r="J93" t="n">
-        <v>0</v>
-      </c>
       <c r="K93" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="94">
@@ -3723,31 +3731,31 @@
       </c>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D94" t="n">
+        <v>0</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" t="n">
+        <v>3</v>
+      </c>
+      <c r="G94" t="n">
+        <v>1</v>
+      </c>
+      <c r="H94" t="n">
+        <v>1</v>
+      </c>
+      <c r="I94" t="n">
+        <v>1</v>
+      </c>
+      <c r="J94" t="n">
         <v>2</v>
       </c>
-      <c r="E94" t="n">
-        <v>0</v>
-      </c>
-      <c r="F94" t="n">
-        <v>0</v>
-      </c>
-      <c r="G94" t="n">
-        <v>3</v>
-      </c>
-      <c r="H94" t="n">
-        <v>1</v>
-      </c>
-      <c r="I94" t="n">
-        <v>1</v>
-      </c>
-      <c r="J94" t="n">
-        <v>1</v>
-      </c>
       <c r="K94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -3758,31 +3766,31 @@
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="n">
+        <v>1</v>
+      </c>
+      <c r="D95" t="n">
+        <v>1</v>
+      </c>
+      <c r="E95" t="n">
+        <v>0</v>
+      </c>
+      <c r="F95" t="n">
+        <v>1</v>
+      </c>
+      <c r="G95" t="n">
+        <v>3</v>
+      </c>
+      <c r="H95" t="n">
+        <v>4</v>
+      </c>
+      <c r="I95" t="n">
         <v>2</v>
-      </c>
-      <c r="D95" t="n">
-        <v>1</v>
-      </c>
-      <c r="E95" t="n">
-        <v>1</v>
-      </c>
-      <c r="F95" t="n">
-        <v>0</v>
-      </c>
-      <c r="G95" t="n">
-        <v>1</v>
-      </c>
-      <c r="H95" t="n">
-        <v>3</v>
-      </c>
-      <c r="I95" t="n">
-        <v>4</v>
       </c>
       <c r="J95" t="n">
         <v>2</v>
       </c>
       <c r="K95" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
@@ -3793,13 +3801,13 @@
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D96" t="n">
         <v>1</v>
       </c>
       <c r="E96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F96" t="n">
         <v>0</v>
@@ -3834,22 +3842,22 @@
         <v>0</v>
       </c>
       <c r="E97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F97" t="n">
         <v>1</v>
       </c>
       <c r="G97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H97" t="n">
         <v>2</v>
       </c>
       <c r="I97" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K97" t="n">
         <v>0</v>
@@ -3863,31 +3871,31 @@
       </c>
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E98" t="n">
+        <v>0</v>
+      </c>
+      <c r="F98" t="n">
+        <v>3</v>
+      </c>
+      <c r="G98" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" t="n">
         <v>2</v>
       </c>
-      <c r="F98" t="n">
-        <v>0</v>
-      </c>
-      <c r="G98" t="n">
+      <c r="I98" t="n">
+        <v>1</v>
+      </c>
+      <c r="J98" t="n">
+        <v>4</v>
+      </c>
+      <c r="K98" t="n">
         <v>3</v>
-      </c>
-      <c r="H98" t="n">
-        <v>0</v>
-      </c>
-      <c r="I98" t="n">
-        <v>2</v>
-      </c>
-      <c r="J98" t="n">
-        <v>1</v>
-      </c>
-      <c r="K98" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="99">
@@ -3898,31 +3906,31 @@
       </c>
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="n">
+        <v>0</v>
+      </c>
+      <c r="D99" t="n">
+        <v>0</v>
+      </c>
+      <c r="E99" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" t="n">
+        <v>0</v>
+      </c>
+      <c r="G99" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" t="n">
+        <v>0</v>
+      </c>
+      <c r="I99" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" t="n">
+        <v>0</v>
+      </c>
+      <c r="K99" t="n">
         <v>2</v>
-      </c>
-      <c r="D99" t="n">
-        <v>0</v>
-      </c>
-      <c r="E99" t="n">
-        <v>0</v>
-      </c>
-      <c r="F99" t="n">
-        <v>0</v>
-      </c>
-      <c r="G99" t="n">
-        <v>0</v>
-      </c>
-      <c r="H99" t="n">
-        <v>0</v>
-      </c>
-      <c r="I99" t="n">
-        <v>0</v>
-      </c>
-      <c r="J99" t="n">
-        <v>0</v>
-      </c>
-      <c r="K99" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -3933,28 +3941,28 @@
       </c>
       <c r="B100" t="inlineStr"/>
       <c r="C100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E100" t="n">
         <v>0</v>
       </c>
       <c r="F100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H100" t="n">
         <v>0</v>
       </c>
       <c r="I100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J100" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K100" t="n">
         <v>2</v>
@@ -3986,10 +3994,10 @@
         <v>0</v>
       </c>
       <c r="I101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K101" t="n">
         <v>0</v>

--- a/Result/analyze_1.xlsx
+++ b/Result/analyze_1.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K103"/>
+  <dimension ref="A1:K102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,47 +441,47 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-09</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -505,16 +505,16 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -526,11 +526,9 @@
           <t>光電業右下</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>0</v>
-      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
         <v>1</v>
@@ -542,7 +540,7 @@
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -571,16 +569,16 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
@@ -589,7 +587,7 @@
         <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -606,16 +604,16 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -647,19 +645,19 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -670,16 +668,16 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
         <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -691,10 +689,10 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -708,28 +706,28 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" t="n">
         <v>3</v>
       </c>
-      <c r="E8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F8" t="n">
-        <v>4</v>
-      </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>2</v>
-      </c>
-      <c r="H8" t="n">
-        <v>3</v>
       </c>
       <c r="I8" t="n">
         <v>2</v>
       </c>
       <c r="J8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -738,9 +736,7 @@
           <t>其他電子業右下</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0</v>
-      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
         <v>0</v>
       </c>
@@ -760,13 +756,13 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
         <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -777,7 +773,7 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
         <v>1</v>
@@ -786,7 +782,7 @@
         <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -795,13 +791,13 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -812,28 +808,28 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
         <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -853,10 +849,10 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -894,7 +890,7 @@
         <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -917,31 +913,31 @@
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F14" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="G14" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="H14" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="I14" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="J14" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="K14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -955,10 +951,10 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
         <v>1</v>
@@ -967,16 +963,16 @@
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J15" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -987,31 +983,31 @@
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
         <v>3</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1075,13 +1071,13 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -1101,10 +1097,10 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -1168,10 +1164,10 @@
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -1265,20 +1261,18 @@
           <t>建材營造右下</t>
         </is>
       </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
+      <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1357,13 +1351,13 @@
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
       </c>
       <c r="K26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1392,13 +1386,13 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -1444,10 +1438,10 @@
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -1462,7 +1456,7 @@
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J29" t="n">
         <v>1</v>
@@ -1482,10 +1476,10 @@
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -1514,16 +1508,16 @@
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1573,7 +1567,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -1704,10 +1698,10 @@
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -1722,9 +1716,7 @@
           <t>汽車工業右下</t>
         </is>
       </c>
-      <c r="B37" t="n">
-        <v>0</v>
-      </c>
+      <c r="B37" t="inlineStr"/>
       <c r="C37" t="n">
         <v>0</v>
       </c>
@@ -1744,10 +1736,10 @@
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -1779,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -1901,10 +1893,10 @@
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
@@ -1919,10 +1911,10 @@
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -1989,10 +1981,10 @@
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
@@ -2006,10 +1998,10 @@
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E45" t="n">
         <v>1</v>
@@ -2021,16 +2013,16 @@
         <v>1</v>
       </c>
       <c r="H45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -2043,19 +2035,19 @@
         <v>0</v>
       </c>
       <c r="C46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F46" t="n">
         <v>1</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
@@ -2067,7 +2059,7 @@
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47">
@@ -2081,16 +2073,16 @@
         <v>2</v>
       </c>
       <c r="D47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E47" t="n">
         <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G47" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
         <v>1</v>
@@ -2102,7 +2094,7 @@
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -2113,7 +2105,7 @@
       </c>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
@@ -2131,10 +2123,10 @@
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
@@ -2154,10 +2146,10 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -2169,10 +2161,10 @@
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -2189,13 +2181,13 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F50" t="n">
         <v>1</v>
       </c>
       <c r="G50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
@@ -2218,7 +2210,7 @@
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>
@@ -2239,10 +2231,10 @@
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -2303,13 +2295,13 @@
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I53" t="n">
         <v>1</v>
       </c>
       <c r="J53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K53" t="n">
         <v>0</v>
@@ -2437,10 +2429,10 @@
         <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -2461,9 +2453,7 @@
           <t>觀光事業右下</t>
         </is>
       </c>
-      <c r="B58" t="n">
-        <v>0</v>
-      </c>
+      <c r="B58" t="inlineStr"/>
       <c r="C58" t="n">
         <v>0</v>
       </c>
@@ -2489,7 +2479,7 @@
         <v>1</v>
       </c>
       <c r="K58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -2518,7 +2508,7 @@
         <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -2640,31 +2630,31 @@
       </c>
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="n">
+        <v>0</v>
+      </c>
+      <c r="D63" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" t="n">
+        <v>1</v>
+      </c>
+      <c r="G63" t="n">
         <v>2</v>
       </c>
-      <c r="D63" t="n">
-        <v>0</v>
-      </c>
-      <c r="E63" t="n">
-        <v>0</v>
-      </c>
-      <c r="F63" t="n">
-        <v>0</v>
-      </c>
-      <c r="G63" t="n">
-        <v>1</v>
-      </c>
       <c r="H63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -2675,10 +2665,10 @@
       </c>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E64" t="n">
         <v>0</v>
@@ -2716,10 +2706,10 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F65" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2856,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2885,7 +2875,7 @@
       </c>
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D70" t="n">
         <v>0</v>
@@ -2900,16 +2890,16 @@
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -2920,7 +2910,7 @@
       </c>
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D71" t="n">
         <v>0</v>
@@ -2938,10 +2928,10 @@
         <v>0</v>
       </c>
       <c r="I71" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J71" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K71" t="n">
         <v>0</v>
@@ -2985,7 +2975,7 @@
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>造紙工業平</t>
+          <t>運動休閒右上</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
@@ -3002,7 +2992,7 @@
         <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
@@ -3020,7 +3010,7 @@
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>運動休閒右上</t>
+          <t>運動休閒右下</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
@@ -3034,13 +3024,13 @@
         <v>0</v>
       </c>
       <c r="F74" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I74" t="n">
         <v>0</v>
@@ -3049,18 +3039,18 @@
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>運動休閒右下</t>
+          <t>運動休閒平</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D75" t="n">
         <v>0</v>
@@ -3072,7 +3062,7 @@
         <v>0</v>
       </c>
       <c r="G75" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
@@ -3090,7 +3080,7 @@
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>運動休閒平</t>
+          <t>金融保險右上</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
@@ -3125,7 +3115,7 @@
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>金融保險右上</t>
+          <t>金融保險右下</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
@@ -3160,7 +3150,7 @@
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>金融保險右下</t>
+          <t>金融保險平</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
@@ -3180,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I78" t="n">
         <v>0</v>
@@ -3195,7 +3185,7 @@
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>金融保險平</t>
+          <t>金融業右上</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
@@ -3218,7 +3208,7 @@
         <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -3230,7 +3220,7 @@
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>金融業右上</t>
+          <t>金融業右下</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
@@ -3265,7 +3255,7 @@
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>金融業右下</t>
+          <t>金融業平</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
@@ -3300,15 +3290,15 @@
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>金融業平</t>
+          <t>鋼鐵工業右上</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
       <c r="C82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E82" t="n">
         <v>0</v>
@@ -3323,7 +3313,7 @@
         <v>0</v>
       </c>
       <c r="I82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -3335,7 +3325,7 @@
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業右上</t>
+          <t>鋼鐵工業右下</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
@@ -3343,16 +3333,16 @@
         <v>0</v>
       </c>
       <c r="D83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
@@ -3361,7 +3351,7 @@
         <v>0</v>
       </c>
       <c r="J83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K83" t="n">
         <v>0</v>
@@ -3370,20 +3360,18 @@
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業右下</t>
-        </is>
-      </c>
-      <c r="B84" t="n">
-        <v>0</v>
-      </c>
+          <t>鋼鐵工業平</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr"/>
       <c r="C84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D84" t="n">
         <v>0</v>
       </c>
       <c r="E84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F84" t="n">
         <v>0</v>
@@ -3392,7 +3380,7 @@
         <v>0</v>
       </c>
       <c r="H84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I84" t="n">
         <v>0</v>
@@ -3407,30 +3395,30 @@
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業平</t>
+          <t>電器電纜右上</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E85" t="n">
         <v>0</v>
       </c>
       <c r="F85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H85" t="n">
         <v>0</v>
       </c>
       <c r="I85" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -3442,15 +3430,15 @@
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>電器電纜右上</t>
+          <t>電器電纜右下</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
       <c r="C86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E86" t="n">
         <v>0</v>
@@ -3468,7 +3456,7 @@
         <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K86" t="n">
         <v>0</v>
@@ -3477,18 +3465,18 @@
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>電器電纜右下</t>
+          <t>電器電纜平</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F87" t="n">
         <v>0</v>
@@ -3500,19 +3488,19 @@
         <v>0</v>
       </c>
       <c r="I87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>電器電纜平</t>
+          <t>電子通路業右上</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
@@ -3520,20 +3508,20 @@
         <v>0</v>
       </c>
       <c r="D88" t="n">
+        <v>1</v>
+      </c>
+      <c r="E88" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" t="n">
         <v>2</v>
       </c>
-      <c r="E88" t="n">
-        <v>0</v>
-      </c>
-      <c r="F88" t="n">
-        <v>1</v>
-      </c>
-      <c r="G88" t="n">
-        <v>0</v>
-      </c>
-      <c r="H88" t="n">
-        <v>0</v>
-      </c>
       <c r="I88" t="n">
         <v>0</v>
       </c>
@@ -3541,13 +3529,13 @@
         <v>1</v>
       </c>
       <c r="K88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>電子通路業右上</t>
+          <t>電子通路業右下</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
@@ -3558,13 +3546,13 @@
         <v>0</v>
       </c>
       <c r="E89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F89" t="n">
         <v>0</v>
       </c>
       <c r="G89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H89" t="n">
         <v>0</v>
@@ -3576,18 +3564,16 @@
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>電子通路業右下</t>
-        </is>
-      </c>
-      <c r="B90" t="n">
-        <v>0</v>
-      </c>
+          <t>電子通路業平</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr"/>
       <c r="C90" t="n">
         <v>0</v>
       </c>
@@ -3604,190 +3590,192 @@
         <v>0</v>
       </c>
       <c r="H90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J90" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>電子通路業平</t>
+          <t>電子零組件業右上</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D91" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E91" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F91" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G91" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H91" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I91" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J91" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K91" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業右上</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr"/>
+          <t>電子零組件業右下</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>0</v>
+      </c>
       <c r="C92" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D92" t="n">
         <v>0</v>
       </c>
       <c r="E92" t="n">
+        <v>2</v>
+      </c>
+      <c r="F92" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" t="n">
+        <v>2</v>
+      </c>
+      <c r="H92" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" t="n">
         <v>3</v>
       </c>
-      <c r="F92" t="n">
-        <v>7</v>
-      </c>
-      <c r="G92" t="n">
-        <v>6</v>
-      </c>
-      <c r="H92" t="n">
-        <v>4</v>
-      </c>
-      <c r="I92" t="n">
-        <v>9</v>
-      </c>
       <c r="J92" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K92" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業右下</t>
-        </is>
-      </c>
-      <c r="B93" t="n">
-        <v>0</v>
-      </c>
+          <t>電子零組件業平</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr"/>
       <c r="C93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D93" t="n">
         <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F93" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H93" t="n">
         <v>2</v>
       </c>
       <c r="I93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J93" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業平</t>
+          <t>電機機械右上</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D94" t="n">
         <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F94" t="n">
         <v>3</v>
       </c>
       <c r="G94" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I94" t="n">
         <v>1</v>
       </c>
       <c r="J94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K94" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>電機機械右上</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr"/>
+          <t>電機機械右下</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>0</v>
+      </c>
       <c r="C95" t="n">
         <v>1</v>
       </c>
       <c r="D95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E95" t="n">
         <v>0</v>
       </c>
       <c r="F95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G95" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H95" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I95" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K95" t="n">
         <v>1</v>
@@ -3796,30 +3784,30 @@
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>電機機械右下</t>
+          <t>電機機械平</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D96" t="n">
         <v>1</v>
       </c>
       <c r="E96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F96" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G96" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -3831,77 +3819,77 @@
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>電機機械平</t>
+          <t>電腦及週邊設備業右上</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D97" t="n">
         <v>0</v>
       </c>
       <c r="E97" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G97" t="n">
         <v>2</v>
       </c>
       <c r="H97" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I97" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J97" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K97" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右上</t>
+          <t>電腦及週邊設備業右下</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D98" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E98" t="n">
         <v>0</v>
       </c>
       <c r="F98" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
       </c>
       <c r="H98" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J98" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K98" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右下</t>
+          <t>電腦及週邊設備業平</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
@@ -3912,7 +3900,7 @@
         <v>0</v>
       </c>
       <c r="E99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F99" t="n">
         <v>0</v>
@@ -3921,27 +3909,27 @@
         <v>0</v>
       </c>
       <c r="H99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I99" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J99" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K99" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業平</t>
+          <t>食品工業右上</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
       <c r="C100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D100" t="n">
         <v>0</v>
@@ -3950,28 +3938,28 @@
         <v>0</v>
       </c>
       <c r="F100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
       </c>
       <c r="H100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J100" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>食品工業右上</t>
+          <t>食品工業右下</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
@@ -3994,7 +3982,7 @@
         <v>0</v>
       </c>
       <c r="I101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -4006,7 +3994,7 @@
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>食品工業右下</t>
+          <t>食品工業平</t>
         </is>
       </c>
       <c r="B102" t="inlineStr"/>
@@ -4035,41 +4023,6 @@
         <v>0</v>
       </c>
       <c r="K102" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="1" t="inlineStr">
-        <is>
-          <t>食品工業平</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr"/>
-      <c r="C103" t="n">
-        <v>0</v>
-      </c>
-      <c r="D103" t="n">
-        <v>0</v>
-      </c>
-      <c r="E103" t="n">
-        <v>0</v>
-      </c>
-      <c r="F103" t="n">
-        <v>0</v>
-      </c>
-      <c r="G103" t="n">
-        <v>0</v>
-      </c>
-      <c r="H103" t="n">
-        <v>0</v>
-      </c>
-      <c r="I103" t="n">
-        <v>0</v>
-      </c>
-      <c r="J103" t="n">
-        <v>0</v>
-      </c>
-      <c r="K103" t="n">
         <v>0</v>
       </c>
     </row>

--- a/Result/analyze_1.xlsx
+++ b/Result/analyze_1.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K102"/>
+  <dimension ref="A1:J102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,47 +441,42 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>2025-10-09</t>
+          <t>2025-10-13</t>
         </is>
       </c>
     </row>
@@ -493,30 +488,27 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -526,7 +518,9 @@
           <t>光電業右下</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
@@ -534,10 +528,10 @@
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -549,9 +543,6 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -563,31 +554,28 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -604,13 +592,13 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -619,9 +607,6 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -639,7 +624,7 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -648,15 +633,12 @@
         <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>2</v>
-      </c>
-      <c r="K6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -671,28 +653,25 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -703,31 +682,28 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" t="n">
         <v>3</v>
-      </c>
-      <c r="D8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" t="n">
-        <v>4</v>
       </c>
       <c r="F8" t="n">
         <v>2</v>
       </c>
       <c r="G8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
         <v>3</v>
       </c>
-      <c r="H8" t="n">
-        <v>2</v>
-      </c>
-      <c r="I8" t="n">
-        <v>2</v>
-      </c>
       <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -750,18 +726,15 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -776,16 +749,16 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -795,9 +768,6 @@
       </c>
       <c r="J10" t="n">
         <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -808,30 +778,27 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -841,18 +808,20 @@
           <t>化學工業右下</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
+      <c r="B12" t="n">
+        <v>0</v>
+      </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -864,9 +833,6 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -881,13 +847,13 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -899,9 +865,6 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -913,31 +876,28 @@
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E14" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G14" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="H14" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I14" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J14" t="n">
-        <v>3</v>
-      </c>
-      <c r="K14" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -951,28 +911,25 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -983,31 +940,28 @@
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17">
@@ -1039,10 +993,7 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1065,19 +1016,16 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -1091,13 +1039,13 @@
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -1109,9 +1057,6 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1146,9 +1091,6 @@
       <c r="J20" t="n">
         <v>0</v>
       </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
@@ -1158,13 +1100,13 @@
       </c>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -1179,9 +1121,6 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1216,9 +1155,6 @@
       <c r="J22" t="n">
         <v>0</v>
       </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
@@ -1251,9 +1187,6 @@
       <c r="J23" t="n">
         <v>0</v>
       </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
@@ -1261,15 +1194,17 @@
           <t>建材營造右下</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="n">
+        <v>0</v>
+      </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -1284,9 +1219,6 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1321,9 +1253,6 @@
       <c r="J25" t="n">
         <v>0</v>
       </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
@@ -1345,18 +1274,15 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>1</v>
-      </c>
-      <c r="K26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1380,19 +1306,16 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
-      </c>
-      <c r="K27" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -1426,9 +1349,6 @@
       <c r="J28" t="n">
         <v>0</v>
       </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
@@ -1438,7 +1358,7 @@
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
@@ -1450,19 +1370,16 @@
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29" t="n">
         <v>1</v>
       </c>
       <c r="J29" t="n">
-        <v>1</v>
-      </c>
-      <c r="K29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -1476,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -1494,9 +1411,6 @@
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1508,13 +1422,13 @@
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -1529,10 +1443,7 @@
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -1561,12 +1472,9 @@
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1601,9 +1509,6 @@
       <c r="J33" t="n">
         <v>0</v>
       </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
@@ -1636,9 +1541,6 @@
       <c r="J34" t="n">
         <v>0</v>
       </c>
-      <c r="K34" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
@@ -1671,9 +1573,6 @@
       <c r="J35" t="n">
         <v>0</v>
       </c>
-      <c r="K35" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
@@ -1692,21 +1591,18 @@
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1730,19 +1626,16 @@
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -1762,7 +1655,7 @@
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1774,9 +1667,6 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1811,9 +1701,6 @@
       <c r="J39" t="n">
         <v>0</v>
       </c>
-      <c r="K39" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
@@ -1846,9 +1733,6 @@
       <c r="J40" t="n">
         <v>0</v>
       </c>
-      <c r="K40" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r=